--- a/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
+++ b/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
@@ -20956,58 +20956,58 @@
         <v>491.74</v>
       </c>
       <c r="AJ169" s="14" t="n">
-        <v>-80.81</v>
+        <v>-67.86</v>
       </c>
       <c r="AK169" s="15" t="n">
-        <v>-182</v>
+        <v>-191.22</v>
       </c>
       <c r="AL169" s="15" t="n">
-        <v>14707.42</v>
+        <v>12975.91</v>
       </c>
       <c r="AM169" s="15" t="n">
-        <v>-637</v>
+        <v>-669.27</v>
       </c>
       <c r="AN169" s="15" t="n">
-        <v>-600.6</v>
+        <v>-631.03</v>
       </c>
       <c r="AO169" s="15" t="n">
-        <v>-1748.21</v>
+        <v>-5363.8</v>
       </c>
       <c r="AP169" s="15" t="n">
-        <v>-247.5</v>
+        <v>-759.37</v>
       </c>
       <c r="AQ169" s="15" t="n">
-        <v>-2265.17</v>
+        <v>554.54</v>
       </c>
       <c r="AR169" s="15" t="n">
-        <v>-1617.98</v>
+        <v>-1609.27</v>
       </c>
       <c r="AS169" s="15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AT169" s="16" t="n">
-        <v>7590.96</v>
+        <v>4497.71</v>
       </c>
       <c r="AU169" s="15" t="n">
-        <v>438.76</v>
+        <v>397.23</v>
       </c>
       <c r="AV169" s="15" t="n">
-        <v>172.89</v>
+        <v>163.27</v>
       </c>
       <c r="AW169" s="16" t="n">
-        <v>75857.22</v>
+        <v>64854.54</v>
       </c>
       <c r="AX169" s="16" t="n">
-        <v>83448.17999999999</v>
+        <v>69352.25999999999</v>
       </c>
       <c r="AY169" s="28" t="n">
-        <v>90564.64</v>
+        <v>77830.46000000001</v>
       </c>
       <c r="AZ169" s="28" t="n">
-        <v>0.9499450549450549</v>
+        <v>0.8538280514590524</v>
       </c>
       <c r="BA169" s="15" t="n">
-        <v>519.5700000000001</v>
+        <v>465.08</v>
       </c>
       <c r="BB169" s="5" t="n"/>
       <c r="BC169" s="5" t="n"/>
@@ -22099,58 +22099,58 @@
         <v>89.22</v>
       </c>
       <c r="AJ176" s="15" t="n">
-        <v>451.91</v>
+        <v>459.25</v>
       </c>
       <c r="AK176" s="15" t="n">
-        <v>-363.49</v>
+        <v>-380.5</v>
       </c>
       <c r="AL176" s="15" t="n">
-        <v>-164265.16</v>
+        <v>-174746.59</v>
       </c>
       <c r="AM176" s="15" t="n">
-        <v>-1272.22</v>
+        <v>-1331.76</v>
       </c>
       <c r="AN176" s="15" t="n">
-        <v>-1199.52</v>
+        <v>-1255.66</v>
       </c>
       <c r="AO176" s="15" t="n">
-        <v>-4170.95</v>
+        <v>-10693.24</v>
       </c>
       <c r="AP176" s="15" t="n">
-        <v>-590.5</v>
+        <v>-1513.88</v>
       </c>
       <c r="AQ176" s="15" t="n">
-        <v>1054.12</v>
+        <v>1103.46</v>
       </c>
       <c r="AR176" s="15" t="n">
-        <v>-10974.06</v>
+        <v>-15002.71</v>
       </c>
       <c r="AS176" s="15" t="n">
-        <v>0.43</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AT176" s="15" t="n">
-        <v>-181418.27</v>
+        <v>-203440.38</v>
       </c>
       <c r="AU176" s="15" t="n">
-        <v>541.13</v>
+        <v>537.79</v>
       </c>
       <c r="AV176" s="15" t="n">
-        <v>341.75</v>
+        <v>324.78</v>
       </c>
       <c r="AW176" s="15" t="n">
-        <v>184935.32</v>
+        <v>174651.22</v>
       </c>
       <c r="AX176" s="16" t="n">
-        <v>3517.05</v>
+        <v>-28789.16</v>
       </c>
       <c r="AY176" s="16" t="n">
-        <v>20670.17</v>
+        <v>-95.37</v>
       </c>
       <c r="AZ176" s="28" t="n">
-        <v>0.9402046823846598</v>
+        <v>0.853553989203736</v>
       </c>
       <c r="BA176" s="15" t="n">
-        <v>89.22</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="BB176" s="5" t="n"/>
       <c r="BC176" s="5" t="n"/>
@@ -22264,58 +22264,58 @@
         <v>614.79</v>
       </c>
       <c r="AJ177" s="15" t="n">
-        <v>-83.91</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="AK177" s="15" t="n">
-        <v>-178.62</v>
+        <v>-192.28</v>
       </c>
       <c r="AL177" s="15" t="n">
-        <v>14987.48</v>
+        <v>12874.18</v>
       </c>
       <c r="AM177" s="15" t="n">
-        <v>-625.16</v>
+        <v>-672.97</v>
       </c>
       <c r="AN177" s="15" t="n">
-        <v>-589.4400000000001</v>
+        <v>-634.51</v>
       </c>
       <c r="AO177" s="15" t="n">
-        <v>-1027.14</v>
+        <v>-5566.64</v>
       </c>
       <c r="AP177" s="15" t="n">
-        <v>-145.42</v>
+        <v>-788.09</v>
       </c>
       <c r="AQ177" s="15" t="n">
-        <v>517.99</v>
+        <v>557.6</v>
       </c>
       <c r="AR177" s="15" t="n">
-        <v>-1556.27</v>
+        <v>-1664.28</v>
       </c>
       <c r="AS177" s="15" t="n">
         <v>0.12</v>
       </c>
       <c r="AT177" s="15" t="n">
-        <v>11562.04</v>
+        <v>4105.29</v>
       </c>
       <c r="AU177" s="15" t="n">
-        <v>530.88</v>
+        <v>529.22</v>
       </c>
       <c r="AV177" s="15" t="n">
-        <v>173.27</v>
+        <v>163.27</v>
       </c>
       <c r="AW177" s="15" t="n">
-        <v>91983.39999999999</v>
+        <v>86404</v>
       </c>
       <c r="AX177" s="16" t="n">
-        <v>103545.45</v>
+        <v>90509.3</v>
       </c>
       <c r="AY177" s="16" t="n">
-        <v>106970.89</v>
+        <v>99278.17999999999</v>
       </c>
       <c r="AZ177" s="28" t="n">
-        <v>0.9700337312973255</v>
+        <v>0.8491343218377654</v>
       </c>
       <c r="BA177" s="15" t="n">
-        <v>614.79</v>
+        <v>596.17</v>
       </c>
       <c r="BB177" s="5" t="n"/>
       <c r="BC177" s="5" t="n"/>
@@ -22429,58 +22429,58 @@
         <v>675.8200000000001</v>
       </c>
       <c r="AJ178" s="15" t="n">
-        <v>-78.45</v>
+        <v>-63.78</v>
       </c>
       <c r="AK178" s="15" t="n">
-        <v>-175.12</v>
+        <v>-188.4</v>
       </c>
       <c r="AL178" s="15" t="n">
-        <v>13738.49</v>
+        <v>12016.99</v>
       </c>
       <c r="AM178" s="15" t="n">
-        <v>-612.9</v>
+        <v>-659.4</v>
       </c>
       <c r="AN178" s="15" t="n">
-        <v>-577.88</v>
+        <v>-621.72</v>
       </c>
       <c r="AO178" s="15" t="n">
-        <v>-762.8</v>
+        <v>-5463.97</v>
       </c>
       <c r="AP178" s="15" t="n">
-        <v>-107.99</v>
+        <v>-773.55</v>
       </c>
       <c r="AQ178" s="15" t="n">
-        <v>507.83</v>
+        <v>546.36</v>
       </c>
       <c r="AR178" s="15" t="n">
-        <v>-1826.77</v>
+        <v>-1364.75</v>
       </c>
       <c r="AS178" s="15" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AT178" s="15" t="n">
-        <v>10357.97</v>
+        <v>3679.95</v>
       </c>
       <c r="AU178" s="15" t="n">
-        <v>597.37</v>
+        <v>595.39</v>
       </c>
       <c r="AV178" s="15" t="n">
-        <v>171.14</v>
+        <v>159.93</v>
       </c>
       <c r="AW178" s="15" t="n">
-        <v>102233.33</v>
+        <v>95219.31</v>
       </c>
       <c r="AX178" s="16" t="n">
-        <v>112591.31</v>
+        <v>98899.27</v>
       </c>
       <c r="AY178" s="16" t="n">
-        <v>115971.82</v>
+        <v>107236.3</v>
       </c>
       <c r="AZ178" s="28" t="n">
-        <v>0.9773006310139053</v>
+        <v>0.848870228926598</v>
       </c>
       <c r="BA178" s="15" t="n">
-        <v>675.8200000000001</v>
+        <v>659.17</v>
       </c>
       <c r="BB178" s="5" t="n"/>
       <c r="BC178" s="5" t="n"/>
@@ -22594,58 +22594,58 @@
         <v>526</v>
       </c>
       <c r="AJ179" s="15" t="n">
-        <v>-26.19</v>
+        <v>-13.53</v>
       </c>
       <c r="AK179" s="15" t="n">
-        <v>-189.89</v>
+        <v>-202.23</v>
       </c>
       <c r="AL179" s="15" t="n">
-        <v>4972.91</v>
+        <v>2736.45</v>
       </c>
       <c r="AM179" s="15" t="n">
-        <v>-664.6</v>
+        <v>-707.8</v>
       </c>
       <c r="AN179" s="15" t="n">
-        <v>-626.62</v>
+        <v>-667.36</v>
       </c>
       <c r="AO179" s="15" t="n">
-        <v>-2189.58</v>
+        <v>25744.15</v>
       </c>
       <c r="AP179" s="15" t="n">
-        <v>-309.99</v>
+        <v>3644.7</v>
       </c>
       <c r="AQ179" s="15" t="n">
-        <v>550.67</v>
+        <v>586.47</v>
       </c>
       <c r="AR179" s="15" t="n">
-        <v>-1463.73</v>
+        <v>-2228.85</v>
       </c>
       <c r="AS179" s="15" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="AT179" s="15" t="n">
-        <v>269.07</v>
+        <v>29107.75</v>
       </c>
       <c r="AU179" s="15" t="n">
-        <v>499.82</v>
+        <v>507.05</v>
       </c>
       <c r="AV179" s="15" t="n">
-        <v>178.48</v>
+        <v>336.38</v>
       </c>
       <c r="AW179" s="15" t="n">
-        <v>89204.62</v>
+        <v>170558.93</v>
       </c>
       <c r="AX179" s="16" t="n">
-        <v>89473.69</v>
+        <v>199666.68</v>
       </c>
       <c r="AY179" s="16" t="n">
-        <v>94177.53</v>
+        <v>173295.38</v>
       </c>
       <c r="AZ179" s="28" t="n">
-        <v>0.9399109987624088</v>
+        <v>1.663373386737873</v>
       </c>
       <c r="BA179" s="15" t="n">
-        <v>526</v>
+        <v>520.59</v>
       </c>
       <c r="BB179" s="5" t="n"/>
       <c r="BC179" s="5" t="n"/>
@@ -22759,58 +22759,58 @@
         <v>677.3099999999999</v>
       </c>
       <c r="AJ180" s="15" t="n">
-        <v>-95.79000000000001</v>
+        <v>-75.87</v>
       </c>
       <c r="AK180" s="15" t="n">
-        <v>-178.42</v>
+        <v>-191.48</v>
       </c>
       <c r="AL180" s="15" t="n">
-        <v>17091.46</v>
+        <v>14527.71</v>
       </c>
       <c r="AM180" s="15" t="n">
-        <v>-624.47</v>
+        <v>-670.1900000000001</v>
       </c>
       <c r="AN180" s="15" t="n">
-        <v>-588.79</v>
+        <v>-631.9</v>
       </c>
       <c r="AO180" s="15" t="n">
-        <v>-1234.88</v>
+        <v>-5363.8</v>
       </c>
       <c r="AP180" s="15" t="n">
-        <v>-174.83</v>
+        <v>-759.37</v>
       </c>
       <c r="AQ180" s="15" t="n">
-        <v>517.42</v>
+        <v>555.3</v>
       </c>
       <c r="AR180" s="15" t="n">
-        <v>-1257.86</v>
+        <v>-1679.55</v>
       </c>
       <c r="AS180" s="15" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AT180" s="15" t="n">
-        <v>13728.06</v>
+        <v>5978.21</v>
       </c>
       <c r="AU180" s="15" t="n">
-        <v>581.51</v>
+        <v>581.42</v>
       </c>
       <c r="AV180" s="15" t="n">
-        <v>171.99</v>
+        <v>163.53</v>
       </c>
       <c r="AW180" s="15" t="n">
-        <v>100011.58</v>
+        <v>95076.78999999999</v>
       </c>
       <c r="AX180" s="16" t="n">
-        <v>113739.63</v>
+        <v>101054.99</v>
       </c>
       <c r="AY180" s="16" t="n">
-        <v>117103.04</v>
+        <v>109604.49</v>
       </c>
       <c r="AZ180" s="28" t="n">
-        <v>0.9639334155363751</v>
+        <v>0.8540295794948924</v>
       </c>
       <c r="BA180" s="15" t="n">
-        <v>677.3099999999999</v>
+        <v>657.29</v>
       </c>
       <c r="BB180" s="5" t="n"/>
       <c r="BC180" s="5" t="n"/>
@@ -22924,58 +22924,58 @@
         <v>611.35</v>
       </c>
       <c r="AJ181" s="15" t="n">
-        <v>-40.35</v>
+        <v>3.02</v>
       </c>
       <c r="AK181" s="15" t="n">
-        <v>-179.02</v>
+        <v>-192.63</v>
       </c>
       <c r="AL181" s="15" t="n">
-        <v>7223.98</v>
+        <v>-582.6</v>
       </c>
       <c r="AM181" s="15" t="n">
-        <v>-626.5700000000001</v>
+        <v>-674.2</v>
       </c>
       <c r="AN181" s="15" t="n">
-        <v>-590.77</v>
+        <v>-635.6799999999999</v>
       </c>
       <c r="AO181" s="15" t="n">
-        <v>-1511.69</v>
+        <v>-5701.73</v>
       </c>
       <c r="AP181" s="15" t="n">
-        <v>-214.02</v>
+        <v>-807.22</v>
       </c>
       <c r="AQ181" s="15" t="n">
-        <v>519.16</v>
+        <v>558.62</v>
       </c>
       <c r="AR181" s="15" t="n">
-        <v>-2059.45</v>
+        <v>-1612.01</v>
       </c>
       <c r="AS181" s="15" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AT181" s="15" t="n">
-        <v>2740.65</v>
+        <v>-9454.809999999999</v>
       </c>
       <c r="AU181" s="15" t="n">
-        <v>571</v>
+        <v>570.13</v>
       </c>
       <c r="AV181" s="15" t="n">
-        <v>171.14</v>
+        <v>162.92</v>
       </c>
       <c r="AW181" s="15" t="n">
-        <v>97722.71000000001</v>
+        <v>92882.34</v>
       </c>
       <c r="AX181" s="16" t="n">
-        <v>100463.36</v>
+        <v>83427.52</v>
       </c>
       <c r="AY181" s="16" t="n">
-        <v>104946.69</v>
+        <v>92299.74000000001</v>
       </c>
       <c r="AZ181" s="28" t="n">
-        <v>0.95599653669981</v>
+        <v>0.8457553120246692</v>
       </c>
       <c r="BA181" s="15" t="n">
-        <v>611.35</v>
+        <v>567.1</v>
       </c>
       <c r="BB181" s="5" t="n"/>
       <c r="BC181" s="5" t="n"/>
@@ -23089,58 +23089,58 @@
         <v>418.19</v>
       </c>
       <c r="AJ182" s="15" t="n">
-        <v>-1.84</v>
+        <v>24.95</v>
       </c>
       <c r="AK182" s="15" t="n">
-        <v>-180.86</v>
+        <v>-193.6</v>
       </c>
       <c r="AL182" s="15" t="n">
-        <v>333.29</v>
+        <v>-4829.74</v>
       </c>
       <c r="AM182" s="15" t="n">
-        <v>-633.03</v>
+        <v>-677.59</v>
       </c>
       <c r="AN182" s="15" t="n">
-        <v>-596.85</v>
+        <v>-638.87</v>
       </c>
       <c r="AO182" s="15" t="n">
-        <v>-1788.51</v>
+        <v>-6107.03</v>
       </c>
       <c r="AP182" s="15" t="n">
-        <v>-253.21</v>
+        <v>-864.59</v>
       </c>
       <c r="AQ182" s="15" t="n">
-        <v>524.51</v>
+        <v>561.4299999999999</v>
       </c>
       <c r="AR182" s="15" t="n">
-        <v>-1275.1</v>
+        <v>-1793.08</v>
       </c>
       <c r="AS182" s="15" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AT182" s="15" t="n">
-        <v>-3688.89</v>
+        <v>-14349.48</v>
       </c>
       <c r="AU182" s="15" t="n">
-        <v>416.35</v>
+        <v>413.88</v>
       </c>
       <c r="AV182" s="15" t="n">
-        <v>171.54</v>
+        <v>161.77</v>
       </c>
       <c r="AW182" s="15" t="n">
-        <v>71422.92999999999</v>
+        <v>66936.75</v>
       </c>
       <c r="AX182" s="16" t="n">
-        <v>67734.03</v>
+        <v>52587.28</v>
       </c>
       <c r="AY182" s="16" t="n">
-        <v>71756.22</v>
+        <v>62107.01</v>
       </c>
       <c r="AZ182" s="28" t="n">
-        <v>0.9484698532054293</v>
+        <v>0.8356181365509974</v>
       </c>
       <c r="BA182" s="15" t="n">
-        <v>418.19</v>
+        <v>388.94</v>
       </c>
       <c r="BB182" s="5" t="n"/>
       <c r="BC182" s="5" t="n"/>
@@ -23254,58 +23254,58 @@
         <v>51.02</v>
       </c>
       <c r="AJ183" s="15" t="n">
-        <v>366.17</v>
+        <v>376.64</v>
       </c>
       <c r="AK183" s="15" t="n">
-        <v>-177.15</v>
+        <v>-187.26</v>
       </c>
       <c r="AL183" s="15" t="n">
-        <v>-64866.29</v>
+        <v>-70527.75999999999</v>
       </c>
       <c r="AM183" s="15" t="n">
-        <v>-620.03</v>
+        <v>-655.4</v>
       </c>
       <c r="AN183" s="15" t="n">
-        <v>-584.6</v>
+        <v>-617.9400000000001</v>
       </c>
       <c r="AO183" s="15" t="n">
-        <v>-268.66</v>
+        <v>-4147.53</v>
       </c>
       <c r="AP183" s="15" t="n">
-        <v>-38.04</v>
+        <v>-587.1799999999999</v>
       </c>
       <c r="AQ183" s="15" t="n">
-        <v>513.74</v>
+        <v>543.04</v>
       </c>
       <c r="AR183" s="15" t="n">
-        <v>-12489.08</v>
+        <v>-13201.55</v>
       </c>
       <c r="AS183" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AT183" s="15" t="n">
-        <v>-78352.95</v>
+        <v>-89194.33</v>
       </c>
       <c r="AU183" s="15" t="n">
-        <v>417.19</v>
+        <v>416.74</v>
       </c>
       <c r="AV183" s="15" t="n">
-        <v>175.75</v>
+        <v>165.64</v>
       </c>
       <c r="AW183" s="15" t="n">
-        <v>73320.75999999999</v>
+        <v>69029.28</v>
       </c>
       <c r="AX183" s="16" t="n">
-        <v>-5032.18</v>
+        <v>-20165.05</v>
       </c>
       <c r="AY183" s="16" t="n">
-        <v>8454.469999999999</v>
+        <v>-1498.49</v>
       </c>
       <c r="AZ183" s="28" t="n">
-        <v>0.9920970928591589</v>
+        <v>0.8845804673815525</v>
       </c>
       <c r="BA183" s="15" t="n">
-        <v>51.02</v>
+        <v>40.1</v>
       </c>
       <c r="BB183" s="5" t="n"/>
       <c r="BC183" s="5" t="n"/>
@@ -23389,7 +23389,7 @@
         <v>0</v>
       </c>
       <c r="Z184" s="14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA184" s="14" t="n">
         <v>0</v>
@@ -23418,24 +23418,60 @@
       <c r="AI184" s="15" t="n">
         <v>417.86</v>
       </c>
-      <c r="AJ184" s="15" t="n"/>
-      <c r="AK184" s="15" t="n"/>
-      <c r="AL184" s="15" t="n"/>
-      <c r="AM184" s="15" t="n"/>
-      <c r="AN184" s="15" t="n"/>
-      <c r="AO184" s="15" t="n"/>
-      <c r="AP184" s="15" t="n"/>
-      <c r="AQ184" s="15" t="n"/>
-      <c r="AR184" s="15" t="n"/>
-      <c r="AS184" s="15" t="n"/>
-      <c r="AT184" s="15" t="n"/>
-      <c r="AU184" s="15" t="n"/>
-      <c r="AV184" s="15" t="n"/>
-      <c r="AW184" s="15" t="n"/>
-      <c r="AX184" s="16" t="n"/>
-      <c r="AY184" s="16" t="n"/>
-      <c r="AZ184" s="28" t="n"/>
-      <c r="BA184" s="15" t="n"/>
+      <c r="AJ184" s="15" t="n">
+        <v>343.92</v>
+      </c>
+      <c r="AK184" s="15" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="AL184" s="15" t="n">
+        <v>-2695.97</v>
+      </c>
+      <c r="AM184" s="15" t="n">
+        <v>-27.44</v>
+      </c>
+      <c r="AN184" s="15" t="n">
+        <v>-25.87</v>
+      </c>
+      <c r="AO184" s="15" t="n">
+        <v>-1217.41</v>
+      </c>
+      <c r="AP184" s="15" t="n">
+        <v>-172.35</v>
+      </c>
+      <c r="AQ184" s="15" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="AR184" s="15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS184" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT184" s="15" t="n">
+        <v>-4116.31</v>
+      </c>
+      <c r="AU184" s="15" t="n">
+        <v>426.02</v>
+      </c>
+      <c r="AV184" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AW184" s="15" t="n">
+        <v>636.91</v>
+      </c>
+      <c r="AX184" s="16" t="n">
+        <v>-3479.41</v>
+      </c>
+      <c r="AY184" s="16" t="n">
+        <v>-2059.07</v>
+      </c>
+      <c r="AZ184" s="28" t="n">
+        <v>0.1907131011608623</v>
+      </c>
+      <c r="BA184" s="15" t="n">
+        <v>82.11</v>
+      </c>
       <c r="BB184" s="5" t="n"/>
       <c r="BC184" s="5" t="n"/>
       <c r="BD184" s="5" t="n"/>
@@ -23521,7 +23557,7 @@
         <v>0.04</v>
       </c>
       <c r="AA185" s="14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB185" s="31" t="n">
         <v>0</v>
@@ -23547,23 +23583,60 @@
       <c r="AI185" s="15" t="n">
         <v>148.49</v>
       </c>
-      <c r="AJ185" s="15" t="n"/>
-      <c r="AK185" s="15" t="n"/>
-      <c r="AL185" s="15" t="n"/>
-      <c r="AM185" s="15" t="n"/>
-      <c r="AN185" s="15" t="n"/>
-      <c r="AO185" s="15" t="n"/>
-      <c r="AP185" s="15" t="n"/>
-      <c r="AQ185" s="15" t="n"/>
-      <c r="AR185" s="15" t="n"/>
-      <c r="AS185" s="15" t="n"/>
-      <c r="AT185" s="15" t="n"/>
-      <c r="AU185" s="15" t="n"/>
-      <c r="AV185" s="15" t="n"/>
-      <c r="AX185" s="16" t="n"/>
-      <c r="AY185" s="16" t="n"/>
-      <c r="AZ185" s="28" t="n"/>
-      <c r="BA185" s="15" t="n"/>
+      <c r="AJ185" s="15" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="AK185" s="15" t="n">
+        <v>-8.02</v>
+      </c>
+      <c r="AL185" s="15" t="n">
+        <v>-3059.06</v>
+      </c>
+      <c r="AM185" s="15" t="n">
+        <v>-28.05</v>
+      </c>
+      <c r="AN185" s="15" t="n">
+        <v>-26.45</v>
+      </c>
+      <c r="AO185" s="15" t="n">
+        <v>-1538.08</v>
+      </c>
+      <c r="AP185" s="15" t="n">
+        <v>-217.75</v>
+      </c>
+      <c r="AQ185" s="15" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="AR185" s="15" t="n">
+        <v>-565.0599999999999</v>
+      </c>
+      <c r="AS185" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT185" s="15" t="n">
+        <v>-5411.21</v>
+      </c>
+      <c r="AU185" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV185" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW185" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX185" s="16" t="n">
+        <v>-5411.21</v>
+      </c>
+      <c r="AY185" s="16" t="n">
+        <v>-3059.06</v>
+      </c>
+      <c r="AZ185" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA185" s="15" t="n">
+        <v>-381.67</v>
+      </c>
       <c r="BB185" s="5" t="n"/>
       <c r="BC185" s="5" t="n"/>
       <c r="BD185" s="5" t="n"/>
@@ -23675,23 +23748,60 @@
       <c r="AI186" s="15" t="n">
         <v>694.62</v>
       </c>
-      <c r="AJ186" s="15" t="n"/>
-      <c r="AK186" s="15" t="n"/>
-      <c r="AL186" s="15" t="n"/>
-      <c r="AM186" s="15" t="n"/>
-      <c r="AN186" s="15" t="n"/>
-      <c r="AO186" s="15" t="n"/>
-      <c r="AP186" s="15" t="n"/>
-      <c r="AQ186" s="15" t="n"/>
-      <c r="AR186" s="15" t="n"/>
-      <c r="AS186" s="15" t="n"/>
-      <c r="AT186" s="15" t="n"/>
-      <c r="AU186" s="15" t="n"/>
-      <c r="AV186" s="15" t="n"/>
-      <c r="AX186" s="16" t="n"/>
-      <c r="AY186" s="16" t="n"/>
-      <c r="AZ186" s="28" t="n"/>
-      <c r="BA186" s="15" t="n"/>
+      <c r="AJ186" s="15" t="n">
+        <v>-70.56999999999999</v>
+      </c>
+      <c r="AK186" s="15" t="n">
+        <v>-193.51</v>
+      </c>
+      <c r="AL186" s="15" t="n">
+        <v>13655.34</v>
+      </c>
+      <c r="AM186" s="15" t="n">
+        <v>-677.28</v>
+      </c>
+      <c r="AN186" s="15" t="n">
+        <v>-638.58</v>
+      </c>
+      <c r="AO186" s="15" t="n">
+        <v>-6056.36</v>
+      </c>
+      <c r="AP186" s="15" t="n">
+        <v>-857.42</v>
+      </c>
+      <c r="AQ186" s="15" t="n">
+        <v>561.1799999999999</v>
+      </c>
+      <c r="AR186" s="15" t="n">
+        <v>-1585.91</v>
+      </c>
+      <c r="AS186" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AT186" s="15" t="n">
+        <v>4400.96</v>
+      </c>
+      <c r="AU186" s="15" t="n">
+        <v>615.34</v>
+      </c>
+      <c r="AV186" s="15" t="n">
+        <v>161.95</v>
+      </c>
+      <c r="AW186" s="0" t="n">
+        <v>99652.85000000001</v>
+      </c>
+      <c r="AX186" s="16" t="n">
+        <v>104053.81</v>
+      </c>
+      <c r="AY186" s="16" t="n">
+        <v>113308.19</v>
+      </c>
+      <c r="AZ186" s="28" t="n">
+        <v>0.8369076533512479</v>
+      </c>
+      <c r="BA186" s="15" t="n">
+        <v>685.91</v>
+      </c>
       <c r="BB186" s="5" t="n"/>
       <c r="BC186" s="5" t="n"/>
       <c r="BD186" s="5" t="n"/>
@@ -33298,7 +33408,7 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="AJ1:AZ1"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
@@ -33308,7 +33418,7 @@
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
-    <mergeCell ref="S1:AI1"/>
+    <mergeCell ref="AJ1:AZ1"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>
@@ -35390,7 +35500,7 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="AJ1:AZ1"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
@@ -35400,7 +35510,7 @@
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
-    <mergeCell ref="S1:AI1"/>
+    <mergeCell ref="AJ1:AZ1"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>

--- a/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
+++ b/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
@@ -23338,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="I184" s="10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J184" s="10" t="n">
         <v>0</v>
@@ -23506,7 +23506,7 @@
         <v>0.04</v>
       </c>
       <c r="J185" s="10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K185" s="10" t="n">
         <v>0</v>
@@ -23836,7 +23836,7 @@
         <v>55.16</v>
       </c>
       <c r="J187" s="10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K187" s="10" t="n">
         <v>0</v>
@@ -23913,23 +23913,60 @@
       <c r="AI187" s="15" t="n">
         <v>-29.17</v>
       </c>
-      <c r="AJ187" s="15" t="n"/>
-      <c r="AK187" s="15" t="n"/>
-      <c r="AL187" s="15" t="n"/>
-      <c r="AM187" s="15" t="n"/>
-      <c r="AN187" s="15" t="n"/>
-      <c r="AO187" s="15" t="n"/>
-      <c r="AP187" s="15" t="n"/>
-      <c r="AQ187" s="15" t="n"/>
-      <c r="AR187" s="15" t="n"/>
-      <c r="AS187" s="15" t="n"/>
-      <c r="AT187" s="15" t="n"/>
-      <c r="AU187" s="15" t="n"/>
-      <c r="AV187" s="15" t="n"/>
-      <c r="AX187" s="16" t="n"/>
-      <c r="AY187" s="16" t="n"/>
-      <c r="AZ187" s="28" t="n"/>
-      <c r="BA187" s="15" t="n"/>
+      <c r="AJ187" s="15" t="n">
+        <v>386.62</v>
+      </c>
+      <c r="AK187" s="15" t="n">
+        <v>-35.67</v>
+      </c>
+      <c r="AL187" s="15" t="n">
+        <v>-13791.4</v>
+      </c>
+      <c r="AM187" s="15" t="n">
+        <v>-124.85</v>
+      </c>
+      <c r="AN187" s="15" t="n">
+        <v>-117.72</v>
+      </c>
+      <c r="AO187" s="15" t="n">
+        <v>-1986.36</v>
+      </c>
+      <c r="AP187" s="15" t="n">
+        <v>-281.22</v>
+      </c>
+      <c r="AQ187" s="15" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="AR187" s="15" t="n">
+        <v>-2514.88</v>
+      </c>
+      <c r="AS187" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT187" s="15" t="n">
+        <v>-18712.97</v>
+      </c>
+      <c r="AU187" s="15" t="n">
+        <v>404.74</v>
+      </c>
+      <c r="AV187" s="15" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AW187" s="0" t="n">
+        <v>10228.61</v>
+      </c>
+      <c r="AX187" s="16" t="n">
+        <v>-8484.35</v>
+      </c>
+      <c r="AY187" s="16" t="n">
+        <v>-3562.78</v>
+      </c>
+      <c r="AZ187" s="28" t="n">
+        <v>0.7098284368692533</v>
+      </c>
+      <c r="BA187" s="15" t="n">
+        <v>18.12</v>
+      </c>
       <c r="BB187" s="5" t="n"/>
       <c r="BC187" s="5" t="n"/>
       <c r="BD187" s="5" t="n"/>
@@ -24041,23 +24078,60 @@
       <c r="AI188" s="15" t="n">
         <v>588.26</v>
       </c>
-      <c r="AJ188" s="15" t="n"/>
-      <c r="AK188" s="15" t="n"/>
-      <c r="AL188" s="15" t="n"/>
-      <c r="AM188" s="15" t="n"/>
-      <c r="AN188" s="15" t="n"/>
-      <c r="AO188" s="15" t="n"/>
-      <c r="AP188" s="15" t="n"/>
-      <c r="AQ188" s="15" t="n"/>
-      <c r="AR188" s="15" t="n"/>
-      <c r="AS188" s="15" t="n"/>
-      <c r="AT188" s="15" t="n"/>
-      <c r="AU188" s="15" t="n"/>
-      <c r="AV188" s="15" t="n"/>
-      <c r="AX188" s="16" t="n"/>
-      <c r="AY188" s="16" t="n"/>
-      <c r="AZ188" s="28" t="n"/>
-      <c r="BA188" s="15" t="n"/>
+      <c r="AJ188" s="15" t="n">
+        <v>-51.39</v>
+      </c>
+      <c r="AK188" s="15" t="n">
+        <v>-196.59</v>
+      </c>
+      <c r="AL188" s="15" t="n">
+        <v>10103.53</v>
+      </c>
+      <c r="AM188" s="15" t="n">
+        <v>-688.08</v>
+      </c>
+      <c r="AN188" s="15" t="n">
+        <v>-648.76</v>
+      </c>
+      <c r="AO188" s="15" t="n">
+        <v>-5180.15</v>
+      </c>
+      <c r="AP188" s="15" t="n">
+        <v>-733.37</v>
+      </c>
+      <c r="AQ188" s="15" t="n">
+        <v>570.12</v>
+      </c>
+      <c r="AR188" s="15" t="n">
+        <v>-1945.17</v>
+      </c>
+      <c r="AS188" s="15" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AT188" s="15" t="n">
+        <v>1478.14</v>
+      </c>
+      <c r="AU188" s="15" t="n">
+        <v>523.52</v>
+      </c>
+      <c r="AV188" s="15" t="n">
+        <v>169.6</v>
+      </c>
+      <c r="AW188" s="0" t="n">
+        <v>88789.06</v>
+      </c>
+      <c r="AX188" s="16" t="n">
+        <v>90267.2</v>
+      </c>
+      <c r="AY188" s="16" t="n">
+        <v>98892.60000000001</v>
+      </c>
+      <c r="AZ188" s="28" t="n">
+        <v>0.8626909401657231</v>
+      </c>
+      <c r="BA188" s="15" t="n">
+        <v>574.92</v>
+      </c>
       <c r="BB188" s="5" t="n"/>
       <c r="BC188" s="5" t="n"/>
       <c r="BD188" s="5" t="n"/>
@@ -24169,23 +24243,60 @@
       <c r="AI189" s="15" t="n">
         <v>511.37</v>
       </c>
-      <c r="AJ189" s="15" t="n"/>
-      <c r="AK189" s="15" t="n"/>
-      <c r="AL189" s="15" t="n"/>
-      <c r="AM189" s="15" t="n"/>
-      <c r="AN189" s="15" t="n"/>
-      <c r="AO189" s="15" t="n"/>
-      <c r="AP189" s="15" t="n"/>
-      <c r="AQ189" s="15" t="n"/>
-      <c r="AR189" s="15" t="n"/>
-      <c r="AS189" s="15" t="n"/>
-      <c r="AT189" s="15" t="n"/>
-      <c r="AU189" s="15" t="n"/>
-      <c r="AV189" s="15" t="n"/>
-      <c r="AX189" s="16" t="n"/>
-      <c r="AY189" s="16" t="n"/>
-      <c r="AZ189" s="28" t="n"/>
-      <c r="BA189" s="15" t="n"/>
+      <c r="AJ189" s="15" t="n">
+        <v>-65.63</v>
+      </c>
+      <c r="AK189" s="15" t="n">
+        <v>-193.6</v>
+      </c>
+      <c r="AL189" s="15" t="n">
+        <v>12705.84</v>
+      </c>
+      <c r="AM189" s="15" t="n">
+        <v>-677.59</v>
+      </c>
+      <c r="AN189" s="15" t="n">
+        <v>-638.87</v>
+      </c>
+      <c r="AO189" s="15" t="n">
+        <v>-5432.11</v>
+      </c>
+      <c r="AP189" s="15" t="n">
+        <v>-769.04</v>
+      </c>
+      <c r="AQ189" s="15" t="n">
+        <v>561.4299999999999</v>
+      </c>
+      <c r="AR189" s="15" t="n">
+        <v>-1548.06</v>
+      </c>
+      <c r="AS189" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT189" s="15" t="n">
+        <v>4201.59</v>
+      </c>
+      <c r="AU189" s="15" t="n">
+        <v>435.39</v>
+      </c>
+      <c r="AV189" s="15" t="n">
+        <v>165.29</v>
+      </c>
+      <c r="AW189" s="0" t="n">
+        <v>71961.19</v>
+      </c>
+      <c r="AX189" s="16" t="n">
+        <v>76162.78</v>
+      </c>
+      <c r="AY189" s="16" t="n">
+        <v>84667.03999999999</v>
+      </c>
+      <c r="AZ189" s="28" t="n">
+        <v>0.8537846465356046</v>
+      </c>
+      <c r="BA189" s="15" t="n">
+        <v>501.02</v>
+      </c>
       <c r="BB189" s="5" t="n"/>
       <c r="BC189" s="5" t="n"/>
       <c r="BD189" s="5" t="n"/>
@@ -24246,23 +24357,57 @@
       <c r="R190" s="9" t="n">
         <v>394.74</v>
       </c>
-      <c r="S190" s="14" t="n"/>
-      <c r="T190" s="14" t="n"/>
-      <c r="U190" s="14" t="n"/>
-      <c r="V190" s="14" t="n"/>
-      <c r="W190" s="14" t="n"/>
-      <c r="X190" s="14" t="n"/>
-      <c r="Y190" s="14" t="n"/>
-      <c r="Z190" s="14" t="n"/>
-      <c r="AA190" s="14" t="n"/>
-      <c r="AB190" s="31" t="n"/>
-      <c r="AC190" s="14" t="n"/>
-      <c r="AD190" s="14" t="n"/>
-      <c r="AE190" s="14" t="n"/>
-      <c r="AF190" s="16" t="n"/>
-      <c r="AG190" s="16" t="n"/>
-      <c r="AH190" s="28" t="n"/>
-      <c r="AI190" s="15" t="n"/>
+      <c r="S190" s="14" t="n">
+        <v>376.47</v>
+      </c>
+      <c r="T190" s="14" t="n">
+        <v>-278.74</v>
+      </c>
+      <c r="U190" s="14" t="n">
+        <v>-104936.12</v>
+      </c>
+      <c r="V190" s="14" t="n">
+        <v>-975.58</v>
+      </c>
+      <c r="W190" s="14" t="n">
+        <v>-919.83</v>
+      </c>
+      <c r="X190" s="14" t="n">
+        <v>-2418.9</v>
+      </c>
+      <c r="Y190" s="14" t="n">
+        <v>-342.45</v>
+      </c>
+      <c r="Z190" s="14" t="n">
+        <v>808.34</v>
+      </c>
+      <c r="AA190" s="14" t="n">
+        <v>-13464.62</v>
+      </c>
+      <c r="AB190" s="31" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AC190" s="14" t="n">
+        <v>-122249.16</v>
+      </c>
+      <c r="AD190" s="14" t="n">
+        <v>428.04</v>
+      </c>
+      <c r="AE190" s="14" t="n">
+        <v>266.13</v>
+      </c>
+      <c r="AF190" s="16" t="n">
+        <v>113916.51</v>
+      </c>
+      <c r="AG190" s="16" t="n">
+        <v>-8332.65</v>
+      </c>
+      <c r="AH190" s="28" t="n">
+        <v>0.9547782411767343</v>
+      </c>
+      <c r="AI190" s="15" t="n">
+        <v>51.58</v>
+      </c>
       <c r="AJ190" s="15" t="n"/>
       <c r="AK190" s="15" t="n"/>
       <c r="AL190" s="15" t="n"/>
@@ -24289,39 +24434,108 @@
       <c r="A191" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="B191" s="10" t="n"/>
-      <c r="C191" s="10" t="n"/>
-      <c r="D191" s="10" t="n"/>
-      <c r="E191" s="10" t="n"/>
-      <c r="F191" s="10" t="n"/>
-      <c r="G191" s="10" t="n"/>
-      <c r="H191" s="10" t="n"/>
-      <c r="I191" s="10" t="n"/>
-      <c r="J191" s="10" t="n"/>
-      <c r="K191" s="10" t="n"/>
-      <c r="L191" s="10" t="n"/>
-      <c r="M191" s="10" t="n"/>
-      <c r="N191" s="10" t="n"/>
-      <c r="P191" s="11" t="n"/>
-      <c r="Q191" s="26" t="n"/>
-      <c r="R191" s="9" t="n"/>
-      <c r="S191" s="14" t="n"/>
-      <c r="T191" s="14" t="n"/>
-      <c r="U191" s="14" t="n"/>
-      <c r="V191" s="14" t="n"/>
-      <c r="W191" s="14" t="n"/>
-      <c r="X191" s="14" t="n"/>
-      <c r="Y191" s="14" t="n"/>
-      <c r="Z191" s="14" t="n"/>
-      <c r="AA191" s="14" t="n"/>
-      <c r="AB191" s="31" t="n"/>
-      <c r="AC191" s="14" t="n"/>
-      <c r="AD191" s="14" t="n"/>
-      <c r="AE191" s="14" t="n"/>
-      <c r="AF191" s="16" t="n"/>
-      <c r="AG191" s="16" t="n"/>
-      <c r="AH191" s="28" t="n"/>
-      <c r="AI191" s="15" t="n"/>
+      <c r="B191" s="10" t="n">
+        <v>388</v>
+      </c>
+      <c r="C191" s="10" t="n">
+        <v>-11.04</v>
+      </c>
+      <c r="D191" s="10" t="n">
+        <v>-4282.55</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>-38.63</v>
+      </c>
+      <c r="F191" s="10" t="n">
+        <v>-36.42</v>
+      </c>
+      <c r="G191" s="10" t="n">
+        <v>-1101.51</v>
+      </c>
+      <c r="H191" s="10" t="n">
+        <v>-155.94</v>
+      </c>
+      <c r="I191" s="10" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="J191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" s="10" t="n">
+        <v>-5583.05</v>
+      </c>
+      <c r="M191" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="N191" s="10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O191" s="0" t="n">
+        <v>7946.25</v>
+      </c>
+      <c r="P191" s="11" t="n">
+        <v>2363.2</v>
+      </c>
+      <c r="Q191" s="26" t="n">
+        <v>0.4799546998867498</v>
+      </c>
+      <c r="R191" s="9" t="n">
+        <v>1112</v>
+      </c>
+      <c r="S191" s="14" t="n">
+        <v>330</v>
+      </c>
+      <c r="T191" s="14" t="n">
+        <v>-11.04</v>
+      </c>
+      <c r="U191" s="14" t="n">
+        <v>-3642.38</v>
+      </c>
+      <c r="V191" s="14" t="n">
+        <v>-38.63</v>
+      </c>
+      <c r="W191" s="14" t="n">
+        <v>-36.42</v>
+      </c>
+      <c r="X191" s="14" t="n">
+        <v>-1237.76</v>
+      </c>
+      <c r="Y191" s="14" t="n">
+        <v>-175.23</v>
+      </c>
+      <c r="Z191" s="14" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="AA191" s="14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB191" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC191" s="14" t="n">
+        <v>-5098.41</v>
+      </c>
+      <c r="AD191" s="14" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="AE191" s="14" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="AF191" s="16" t="n">
+        <v>1755.15</v>
+      </c>
+      <c r="AG191" s="16" t="n">
+        <v>-3343.26</v>
+      </c>
+      <c r="AH191" s="28" t="n">
+        <v>0.4156285390713477</v>
+      </c>
+      <c r="AI191" s="15" t="n">
+        <v>52.59</v>
+      </c>
       <c r="AJ191" s="15" t="n"/>
       <c r="AK191" s="15" t="n"/>
       <c r="AL191" s="15" t="n"/>
@@ -24348,39 +24562,108 @@
       <c r="A192" s="3" t="n">
         <v>46169</v>
       </c>
-      <c r="B192" s="10" t="n"/>
-      <c r="C192" s="10" t="n"/>
-      <c r="D192" s="10" t="n"/>
-      <c r="E192" s="10" t="n"/>
-      <c r="F192" s="10" t="n"/>
-      <c r="G192" s="10" t="n"/>
-      <c r="H192" s="10" t="n"/>
-      <c r="I192" s="10" t="n"/>
-      <c r="J192" s="10" t="n"/>
-      <c r="K192" s="10" t="n"/>
-      <c r="L192" s="10" t="n"/>
-      <c r="M192" s="10" t="n"/>
-      <c r="N192" s="10" t="n"/>
-      <c r="P192" s="11" t="n"/>
-      <c r="Q192" s="26" t="n"/>
-      <c r="R192" s="9" t="n"/>
-      <c r="S192" s="14" t="n"/>
-      <c r="T192" s="14" t="n"/>
-      <c r="U192" s="14" t="n"/>
-      <c r="V192" s="14" t="n"/>
-      <c r="W192" s="14" t="n"/>
-      <c r="X192" s="14" t="n"/>
-      <c r="Y192" s="14" t="n"/>
-      <c r="Z192" s="14" t="n"/>
-      <c r="AA192" s="14" t="n"/>
-      <c r="AB192" s="31" t="n"/>
-      <c r="AC192" s="14" t="n"/>
-      <c r="AD192" s="14" t="n"/>
-      <c r="AE192" s="14" t="n"/>
-      <c r="AF192" s="16" t="n"/>
-      <c r="AG192" s="16" t="n"/>
-      <c r="AH192" s="28" t="n"/>
-      <c r="AI192" s="15" t="n"/>
+      <c r="B192" s="10" t="n">
+        <v>382</v>
+      </c>
+      <c r="C192" s="10" t="n">
+        <v>-10</v>
+      </c>
+      <c r="D192" s="10" t="n">
+        <v>-3820</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>-35</v>
+      </c>
+      <c r="F192" s="10" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G192" s="10" t="n">
+        <v>-76.76000000000001</v>
+      </c>
+      <c r="H192" s="10" t="n">
+        <v>-10.87</v>
+      </c>
+      <c r="I192" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="J192" s="10" t="n">
+        <v>-705</v>
+      </c>
+      <c r="K192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L192" s="10" t="n">
+        <v>-4651.63</v>
+      </c>
+      <c r="M192" s="10" t="n">
+        <v>1215.22</v>
+      </c>
+      <c r="N192" s="10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="O192" s="0" t="n">
+        <v>11666.11</v>
+      </c>
+      <c r="P192" s="11" t="n">
+        <v>7014.48</v>
+      </c>
+      <c r="Q192" s="26" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="R192" s="9" t="n">
+        <v>833.22</v>
+      </c>
+      <c r="S192" s="14" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="T192" s="14" t="n">
+        <v>-10</v>
+      </c>
+      <c r="U192" s="14" t="n">
+        <v>-3679.01</v>
+      </c>
+      <c r="V192" s="14" t="n">
+        <v>-35</v>
+      </c>
+      <c r="W192" s="14" t="n">
+        <v>-33</v>
+      </c>
+      <c r="X192" s="14" t="n">
+        <v>3211.93</v>
+      </c>
+      <c r="Y192" s="14" t="n">
+        <v>454.72</v>
+      </c>
+      <c r="Z192" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA192" s="14" t="n">
+        <v>-705</v>
+      </c>
+      <c r="AB192" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC192" s="14" t="n">
+        <v>-756.36</v>
+      </c>
+      <c r="AD192" s="14" t="n">
+        <v>448.27</v>
+      </c>
+      <c r="AE192" s="14" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="AF192" s="16" t="n">
+        <v>11985.67</v>
+      </c>
+      <c r="AG192" s="16" t="n">
+        <v>11229.31</v>
+      </c>
+      <c r="AH192" s="28" t="n">
+        <v>2.67375</v>
+      </c>
+      <c r="AI192" s="15" t="n">
+        <v>80.37</v>
+      </c>
       <c r="AJ192" s="15" t="n"/>
       <c r="AK192" s="15" t="n"/>
       <c r="AL192" s="15" t="n"/>
@@ -24407,39 +24690,108 @@
       <c r="A193" s="3" t="n">
         <v>46170</v>
       </c>
-      <c r="B193" s="10" t="n"/>
-      <c r="C193" s="10" t="n"/>
-      <c r="D193" s="10" t="n"/>
-      <c r="E193" s="10" t="n"/>
-      <c r="F193" s="10" t="n"/>
-      <c r="G193" s="10" t="n"/>
-      <c r="H193" s="10" t="n"/>
-      <c r="I193" s="10" t="n"/>
-      <c r="J193" s="10" t="n"/>
-      <c r="K193" s="10" t="n"/>
-      <c r="L193" s="10" t="n"/>
-      <c r="M193" s="10" t="n"/>
-      <c r="N193" s="10" t="n"/>
-      <c r="P193" s="11" t="n"/>
-      <c r="Q193" s="26" t="n"/>
-      <c r="R193" s="9" t="n"/>
-      <c r="S193" s="14" t="n"/>
-      <c r="T193" s="14" t="n"/>
-      <c r="U193" s="14" t="n"/>
-      <c r="V193" s="14" t="n"/>
-      <c r="W193" s="14" t="n"/>
-      <c r="X193" s="14" t="n"/>
-      <c r="Y193" s="14" t="n"/>
-      <c r="Z193" s="14" t="n"/>
-      <c r="AA193" s="14" t="n"/>
-      <c r="AB193" s="31" t="n"/>
-      <c r="AC193" s="14" t="n"/>
-      <c r="AD193" s="14" t="n"/>
-      <c r="AE193" s="14" t="n"/>
-      <c r="AF193" s="16" t="n"/>
-      <c r="AG193" s="16" t="n"/>
-      <c r="AH193" s="28" t="n"/>
-      <c r="AI193" s="15" t="n"/>
+      <c r="B193" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C193" s="10" t="n">
+        <v>-178</v>
+      </c>
+      <c r="D193" s="10" t="n">
+        <v>14240</v>
+      </c>
+      <c r="E193" s="10" t="n">
+        <v>-623</v>
+      </c>
+      <c r="F193" s="10" t="n">
+        <v>-587.4</v>
+      </c>
+      <c r="G193" s="10" t="n">
+        <v>987.33</v>
+      </c>
+      <c r="H193" s="10" t="n">
+        <v>139.78</v>
+      </c>
+      <c r="I193" s="10" t="n">
+        <v>516.2</v>
+      </c>
+      <c r="J193" s="10" t="n">
+        <v>-1254.9</v>
+      </c>
+      <c r="K193" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L193" s="10" t="n">
+        <v>13418</v>
+      </c>
+      <c r="M193" s="10" t="n">
+        <v>1438.28</v>
+      </c>
+      <c r="N193" s="10" t="n">
+        <v>183.14</v>
+      </c>
+      <c r="O193" s="0" t="n">
+        <v>263414.57</v>
+      </c>
+      <c r="P193" s="11" t="n">
+        <v>276832.57</v>
+      </c>
+      <c r="Q193" s="26" t="n">
+        <v>1.028904494382022</v>
+      </c>
+      <c r="R193" s="9" t="n">
+        <v>1518.28</v>
+      </c>
+      <c r="S193" s="14" t="n">
+        <v>-80</v>
+      </c>
+      <c r="T193" s="14" t="n">
+        <v>-181.4</v>
+      </c>
+      <c r="U193" s="14" t="n">
+        <v>14512</v>
+      </c>
+      <c r="V193" s="14" t="n">
+        <v>-634.9</v>
+      </c>
+      <c r="W193" s="14" t="n">
+        <v>-598.62</v>
+      </c>
+      <c r="X193" s="14" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="Y193" s="14" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="Z193" s="14" t="n">
+        <v>526.0599999999999</v>
+      </c>
+      <c r="AA193" s="14" t="n">
+        <v>-1361.71</v>
+      </c>
+      <c r="AB193" s="31" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AC193" s="14" t="n">
+        <v>12825.65</v>
+      </c>
+      <c r="AD193" s="14" t="n">
+        <v>677.55</v>
+      </c>
+      <c r="AE193" s="14" t="n">
+        <v>183.15</v>
+      </c>
+      <c r="AF193" s="16" t="n">
+        <v>124092.21</v>
+      </c>
+      <c r="AG193" s="16" t="n">
+        <v>136917.86</v>
+      </c>
+      <c r="AH193" s="28" t="n">
+        <v>1.009633406835722</v>
+      </c>
+      <c r="AI193" s="15" t="n">
+        <v>757.55</v>
+      </c>
       <c r="AJ193" s="15" t="n"/>
       <c r="AK193" s="15" t="n"/>
       <c r="AL193" s="15" t="n"/>
@@ -24466,39 +24818,108 @@
       <c r="A194" s="3" t="n">
         <v>46171</v>
       </c>
-      <c r="B194" s="10" t="n"/>
-      <c r="C194" s="10" t="n"/>
-      <c r="D194" s="10" t="n"/>
-      <c r="E194" s="10" t="n"/>
-      <c r="F194" s="10" t="n"/>
-      <c r="G194" s="10" t="n"/>
-      <c r="H194" s="10" t="n"/>
-      <c r="I194" s="10" t="n"/>
-      <c r="J194" s="10" t="n"/>
-      <c r="K194" s="10" t="n"/>
-      <c r="L194" s="10" t="n"/>
-      <c r="M194" s="10" t="n"/>
-      <c r="N194" s="10" t="n"/>
-      <c r="P194" s="11" t="n"/>
-      <c r="Q194" s="26" t="n"/>
-      <c r="R194" s="9" t="n"/>
-      <c r="S194" s="14" t="n"/>
-      <c r="T194" s="14" t="n"/>
-      <c r="U194" s="14" t="n"/>
-      <c r="V194" s="14" t="n"/>
-      <c r="W194" s="14" t="n"/>
-      <c r="X194" s="14" t="n"/>
-      <c r="Y194" s="14" t="n"/>
-      <c r="Z194" s="14" t="n"/>
-      <c r="AA194" s="14" t="n"/>
-      <c r="AB194" s="31" t="n"/>
-      <c r="AC194" s="14" t="n"/>
-      <c r="AD194" s="14" t="n"/>
-      <c r="AE194" s="14" t="n"/>
-      <c r="AF194" s="16" t="n"/>
-      <c r="AG194" s="16" t="n"/>
-      <c r="AH194" s="28" t="n"/>
-      <c r="AI194" s="15" t="n"/>
+      <c r="B194" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C194" s="10" t="n">
+        <v>-178</v>
+      </c>
+      <c r="D194" s="10" t="n">
+        <v>14240</v>
+      </c>
+      <c r="E194" s="10" t="n">
+        <v>-623</v>
+      </c>
+      <c r="F194" s="10" t="n">
+        <v>-587.4</v>
+      </c>
+      <c r="G194" s="10" t="n">
+        <v>-1131.25</v>
+      </c>
+      <c r="H194" s="10" t="n">
+        <v>-160.16</v>
+      </c>
+      <c r="I194" s="10" t="n">
+        <v>516.2</v>
+      </c>
+      <c r="J194" s="10" t="n">
+        <v>-1254.9</v>
+      </c>
+      <c r="K194" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L194" s="10" t="n">
+        <v>10999.49</v>
+      </c>
+      <c r="M194" s="10" t="n">
+        <v>544.5</v>
+      </c>
+      <c r="N194" s="10" t="n">
+        <v>172.11</v>
+      </c>
+      <c r="O194" s="0" t="n">
+        <v>93711.96000000001</v>
+      </c>
+      <c r="P194" s="11" t="n">
+        <v>104711.45</v>
+      </c>
+      <c r="Q194" s="26" t="n">
+        <v>0.9668820224719106</v>
+      </c>
+      <c r="R194" s="9" t="n">
+        <v>624.5</v>
+      </c>
+      <c r="S194" s="14" t="n">
+        <v>-80</v>
+      </c>
+      <c r="T194" s="14" t="n">
+        <v>-178.12</v>
+      </c>
+      <c r="U194" s="14" t="n">
+        <v>14249.6</v>
+      </c>
+      <c r="V194" s="14" t="n">
+        <v>-623.42</v>
+      </c>
+      <c r="W194" s="14" t="n">
+        <v>-587.8</v>
+      </c>
+      <c r="X194" s="14" t="n">
+        <v>-1151.88</v>
+      </c>
+      <c r="Y194" s="14" t="n">
+        <v>-163.08</v>
+      </c>
+      <c r="Z194" s="14" t="n">
+        <v>516.55</v>
+      </c>
+      <c r="AA194" s="14" t="n">
+        <v>-1493.33</v>
+      </c>
+      <c r="AB194" s="31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC194" s="14" t="n">
+        <v>10746.65</v>
+      </c>
+      <c r="AD194" s="14" t="n">
+        <v>516.11</v>
+      </c>
+      <c r="AE194" s="14" t="n">
+        <v>172.12</v>
+      </c>
+      <c r="AF194" s="16" t="n">
+        <v>88831.34</v>
+      </c>
+      <c r="AG194" s="16" t="n">
+        <v>99577.98</v>
+      </c>
+      <c r="AH194" s="28" t="n">
+        <v>0.9663008084437457</v>
+      </c>
+      <c r="AI194" s="15" t="n">
+        <v>596.11</v>
+      </c>
       <c r="AJ194" s="15" t="n"/>
       <c r="AK194" s="15" t="n"/>
       <c r="AL194" s="15" t="n"/>
@@ -24525,39 +24946,108 @@
       <c r="A195" s="3" t="n">
         <v>46172</v>
       </c>
-      <c r="B195" s="10" t="n"/>
-      <c r="C195" s="10" t="n"/>
-      <c r="D195" s="10" t="n"/>
-      <c r="E195" s="10" t="n"/>
-      <c r="F195" s="10" t="n"/>
-      <c r="G195" s="10" t="n"/>
-      <c r="H195" s="10" t="n"/>
-      <c r="I195" s="10" t="n"/>
-      <c r="J195" s="10" t="n"/>
-      <c r="K195" s="10" t="n"/>
-      <c r="L195" s="10" t="n"/>
-      <c r="M195" s="10" t="n"/>
-      <c r="N195" s="10" t="n"/>
-      <c r="P195" s="11" t="n"/>
-      <c r="Q195" s="26" t="n"/>
-      <c r="R195" s="9" t="n"/>
-      <c r="S195" s="14" t="n"/>
-      <c r="T195" s="14" t="n"/>
-      <c r="U195" s="14" t="n"/>
-      <c r="V195" s="14" t="n"/>
-      <c r="W195" s="14" t="n"/>
-      <c r="X195" s="14" t="n"/>
-      <c r="Y195" s="14" t="n"/>
-      <c r="Z195" s="14" t="n"/>
-      <c r="AA195" s="14" t="n"/>
-      <c r="AB195" s="31" t="n"/>
-      <c r="AC195" s="14" t="n"/>
-      <c r="AD195" s="14" t="n"/>
-      <c r="AE195" s="14" t="n"/>
-      <c r="AF195" s="16" t="n"/>
-      <c r="AG195" s="16" t="n"/>
-      <c r="AH195" s="28" t="n"/>
-      <c r="AI195" s="15" t="n"/>
+      <c r="B195" s="10" t="n">
+        <v>-76.11</v>
+      </c>
+      <c r="C195" s="10" t="n">
+        <v>-179.15</v>
+      </c>
+      <c r="D195" s="10" t="n">
+        <v>13634.16</v>
+      </c>
+      <c r="E195" s="10" t="n">
+        <v>-627.01</v>
+      </c>
+      <c r="F195" s="10" t="n">
+        <v>-591.1799999999999</v>
+      </c>
+      <c r="G195" s="10" t="n">
+        <v>-1442.61</v>
+      </c>
+      <c r="H195" s="10" t="n">
+        <v>-204.24</v>
+      </c>
+      <c r="I195" s="10" t="n">
+        <v>519.52</v>
+      </c>
+      <c r="J195" s="10" t="n">
+        <v>-7365.08</v>
+      </c>
+      <c r="K195" s="10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L195" s="10" t="n">
+        <v>3923.58</v>
+      </c>
+      <c r="M195" s="10" t="n">
+        <v>489.4</v>
+      </c>
+      <c r="N195" s="10" t="n">
+        <v>171.63</v>
+      </c>
+      <c r="O195" s="0" t="n">
+        <v>83994.53</v>
+      </c>
+      <c r="P195" s="11" t="n">
+        <v>87918.11</v>
+      </c>
+      <c r="Q195" s="26" t="n">
+        <v>0.9580367858438695</v>
+      </c>
+      <c r="R195" s="9" t="n">
+        <v>565.51</v>
+      </c>
+      <c r="S195" s="14" t="n">
+        <v>-76.68000000000001</v>
+      </c>
+      <c r="T195" s="14" t="n">
+        <v>-179.15</v>
+      </c>
+      <c r="U195" s="14" t="n">
+        <v>13736.09</v>
+      </c>
+      <c r="V195" s="14" t="n">
+        <v>-627.01</v>
+      </c>
+      <c r="W195" s="14" t="n">
+        <v>-591.1799999999999</v>
+      </c>
+      <c r="X195" s="14" t="n">
+        <v>-1447.41</v>
+      </c>
+      <c r="Y195" s="14" t="n">
+        <v>-204.91</v>
+      </c>
+      <c r="Z195" s="14" t="n">
+        <v>519.52</v>
+      </c>
+      <c r="AA195" s="14" t="n">
+        <v>-7365.08</v>
+      </c>
+      <c r="AB195" s="31" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC195" s="14" t="n">
+        <v>4020.03</v>
+      </c>
+      <c r="AD195" s="14" t="n">
+        <v>402.46</v>
+      </c>
+      <c r="AE195" s="14" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="AF195" s="16" t="n">
+        <v>69062.92</v>
+      </c>
+      <c r="AG195" s="16" t="n">
+        <v>73082.94</v>
+      </c>
+      <c r="AH195" s="28" t="n">
+        <v>0.9578972340841219</v>
+      </c>
+      <c r="AI195" s="15" t="n">
+        <v>479.13</v>
+      </c>
       <c r="AJ195" s="15" t="n"/>
       <c r="AK195" s="15" t="n"/>
       <c r="AL195" s="15" t="n"/>
@@ -24584,39 +25074,108 @@
       <c r="A196" s="3" t="n">
         <v>46173</v>
       </c>
-      <c r="B196" s="10" t="n"/>
-      <c r="C196" s="10" t="n"/>
-      <c r="D196" s="10" t="n"/>
-      <c r="E196" s="10" t="n"/>
-      <c r="F196" s="10" t="n"/>
-      <c r="G196" s="10" t="n"/>
-      <c r="H196" s="10" t="n"/>
-      <c r="I196" s="10" t="n"/>
-      <c r="J196" s="10" t="n"/>
-      <c r="K196" s="10" t="n"/>
-      <c r="L196" s="10" t="n"/>
-      <c r="M196" s="10" t="n"/>
-      <c r="N196" s="10" t="n"/>
-      <c r="P196" s="11" t="n"/>
-      <c r="Q196" s="26" t="n"/>
-      <c r="R196" s="9" t="n"/>
-      <c r="S196" s="14" t="n"/>
-      <c r="T196" s="14" t="n"/>
-      <c r="U196" s="14" t="n"/>
-      <c r="V196" s="14" t="n"/>
-      <c r="W196" s="14" t="n"/>
-      <c r="X196" s="14" t="n"/>
-      <c r="Y196" s="14" t="n"/>
-      <c r="Z196" s="14" t="n"/>
-      <c r="AA196" s="14" t="n"/>
-      <c r="AB196" s="31" t="n"/>
-      <c r="AC196" s="14" t="n"/>
-      <c r="AD196" s="14" t="n"/>
-      <c r="AE196" s="14" t="n"/>
-      <c r="AF196" s="16" t="n"/>
-      <c r="AG196" s="16" t="n"/>
-      <c r="AH196" s="28" t="n"/>
-      <c r="AI196" s="15" t="n"/>
+      <c r="B196" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C196" s="10" t="n">
+        <v>-178</v>
+      </c>
+      <c r="D196" s="10" t="n">
+        <v>14240</v>
+      </c>
+      <c r="E196" s="10" t="n">
+        <v>-623</v>
+      </c>
+      <c r="F196" s="10" t="n">
+        <v>-587.4</v>
+      </c>
+      <c r="G196" s="10" t="n">
+        <v>-1120.22</v>
+      </c>
+      <c r="H196" s="10" t="n">
+        <v>-158.59</v>
+      </c>
+      <c r="I196" s="10" t="n">
+        <v>516.2</v>
+      </c>
+      <c r="J196" s="10" t="n">
+        <v>-1254.9</v>
+      </c>
+      <c r="K196" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L196" s="10" t="n">
+        <v>11012.09</v>
+      </c>
+      <c r="M196" s="10" t="n">
+        <v>405.7</v>
+      </c>
+      <c r="N196" s="10" t="n">
+        <v>172.16</v>
+      </c>
+      <c r="O196" s="0" t="n">
+        <v>69845.97</v>
+      </c>
+      <c r="P196" s="11" t="n">
+        <v>80858.07000000001</v>
+      </c>
+      <c r="Q196" s="26" t="n">
+        <v>0.9672050561797756</v>
+      </c>
+      <c r="R196" s="9" t="n">
+        <v>485.7</v>
+      </c>
+      <c r="S196" s="14" t="n">
+        <v>-80</v>
+      </c>
+      <c r="T196" s="14" t="n">
+        <v>-178.86</v>
+      </c>
+      <c r="U196" s="14" t="n">
+        <v>14308.8</v>
+      </c>
+      <c r="V196" s="14" t="n">
+        <v>-626.01</v>
+      </c>
+      <c r="W196" s="14" t="n">
+        <v>-590.24</v>
+      </c>
+      <c r="X196" s="14" t="n">
+        <v>-1280.93</v>
+      </c>
+      <c r="Y196" s="14" t="n">
+        <v>-181.35</v>
+      </c>
+      <c r="Z196" s="14" t="n">
+        <v>518.6900000000001</v>
+      </c>
+      <c r="AA196" s="14" t="n">
+        <v>-1338.3</v>
+      </c>
+      <c r="AB196" s="31" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AC196" s="14" t="n">
+        <v>10810.67</v>
+      </c>
+      <c r="AD196" s="14" t="n">
+        <v>380.05</v>
+      </c>
+      <c r="AE196" s="14" t="n">
+        <v>172.19</v>
+      </c>
+      <c r="AF196" s="16" t="n">
+        <v>65439.63</v>
+      </c>
+      <c r="AG196" s="16" t="n">
+        <v>76250.3</v>
+      </c>
+      <c r="AH196" s="28" t="n">
+        <v>0.9626803086212684</v>
+      </c>
+      <c r="AI196" s="15" t="n">
+        <v>460.05</v>
+      </c>
       <c r="AJ196" s="15" t="n"/>
       <c r="AK196" s="15" t="n"/>
       <c r="AL196" s="15" t="n"/>
@@ -24643,22 +25202,57 @@
       <c r="A197" s="3" t="n">
         <v>46174</v>
       </c>
-      <c r="B197" s="10" t="n"/>
-      <c r="C197" s="10" t="n"/>
-      <c r="D197" s="10" t="n"/>
-      <c r="E197" s="10" t="n"/>
-      <c r="F197" s="10" t="n"/>
-      <c r="G197" s="10" t="n"/>
-      <c r="H197" s="10" t="n"/>
-      <c r="I197" s="10" t="n"/>
-      <c r="J197" s="10" t="n"/>
-      <c r="K197" s="10" t="n"/>
-      <c r="L197" s="10" t="n"/>
-      <c r="M197" s="10" t="n"/>
-      <c r="N197" s="10" t="n"/>
-      <c r="P197" s="11" t="n"/>
-      <c r="Q197" s="26" t="n"/>
-      <c r="R197" s="9" t="n"/>
+      <c r="B197" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C197" s="10" t="n">
+        <v>-178</v>
+      </c>
+      <c r="D197" s="10" t="n">
+        <v>14240</v>
+      </c>
+      <c r="E197" s="10" t="n">
+        <v>-623</v>
+      </c>
+      <c r="F197" s="10" t="n">
+        <v>-587.4</v>
+      </c>
+      <c r="G197" s="10" t="n">
+        <v>-1245.91</v>
+      </c>
+      <c r="H197" s="10" t="n">
+        <v>-176.39</v>
+      </c>
+      <c r="I197" s="10" t="n">
+        <v>516.2</v>
+      </c>
+      <c r="J197" s="10" t="n">
+        <v>-1663.8</v>
+      </c>
+      <c r="K197" s="10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L197" s="10" t="n">
+        <v>10459.7</v>
+      </c>
+      <c r="M197" s="10" t="n">
+        <v>611.95</v>
+      </c>
+      <c r="N197" s="10" t="n">
+        <v>171.51</v>
+      </c>
+      <c r="O197" t="n">
+        <v>104954.49</v>
+      </c>
+      <c r="P197" s="11" t="n">
+        <v>115414.19</v>
+      </c>
+      <c r="Q197" s="26" t="n">
+        <v>0.9635252808988766</v>
+      </c>
+      <c r="R197" s="9" t="n">
+        <v>691.95</v>
+      </c>
       <c r="S197" s="14" t="n"/>
       <c r="T197" s="14" t="n"/>
       <c r="U197" s="14" t="n"/>
@@ -33408,18 +34002,18 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="S2:AC2"/>
     <mergeCell ref="AU2:AW2"/>
     <mergeCell ref="B2:L2"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="AJ1:AZ1"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>
   </mergeCells>
@@ -35500,18 +36094,18 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="S2:AC2"/>
     <mergeCell ref="AU2:AW2"/>
     <mergeCell ref="B2:L2"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="AJ1:AZ1"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>
   </mergeCells>

--- a/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
+++ b/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
@@ -23389,7 +23389,7 @@
         <v>0</v>
       </c>
       <c r="Z184" s="14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA184" s="14" t="n">
         <v>0</v>
@@ -23443,7 +23443,7 @@
         <v>22.73</v>
       </c>
       <c r="AR184" s="15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS184" s="15" t="n">
         <v>0</v>
@@ -23557,7 +23557,7 @@
         <v>0.04</v>
       </c>
       <c r="AA185" s="14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB185" s="31" t="n">
         <v>0</v>
@@ -23887,7 +23887,7 @@
         <v>55.16</v>
       </c>
       <c r="AA187" s="14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB187" s="31" t="n">
         <v>0</v>
@@ -24510,7 +24510,7 @@
         <v>32.01</v>
       </c>
       <c r="AA191" s="14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB191" s="31" t="n">
         <v>0</v>
@@ -25241,7 +25241,7 @@
       <c r="N197" s="10" t="n">
         <v>171.51</v>
       </c>
-      <c r="O197" t="n">
+      <c r="O197" s="0" t="n">
         <v>104954.49</v>
       </c>
       <c r="P197" s="11" t="n">
@@ -25430,23 +25430,57 @@
       <c r="P200" s="11" t="n"/>
       <c r="Q200" s="26" t="n"/>
       <c r="R200" s="9" t="n"/>
-      <c r="S200" s="14" t="n"/>
-      <c r="T200" s="14" t="n"/>
-      <c r="U200" s="14" t="n"/>
-      <c r="V200" s="14" t="n"/>
-      <c r="W200" s="14" t="n"/>
-      <c r="X200" s="14" t="n"/>
-      <c r="Y200" s="14" t="n"/>
-      <c r="Z200" s="14" t="n"/>
-      <c r="AA200" s="14" t="n"/>
-      <c r="AB200" s="31" t="n"/>
-      <c r="AC200" s="14" t="n"/>
-      <c r="AD200" s="14" t="n"/>
-      <c r="AE200" s="14" t="n"/>
-      <c r="AF200" s="16" t="n"/>
-      <c r="AG200" s="16" t="n"/>
-      <c r="AH200" s="28" t="n"/>
-      <c r="AI200" s="15" t="n"/>
+      <c r="S200" s="14" t="n">
+        <v>-80</v>
+      </c>
+      <c r="T200" s="14" t="n">
+        <v>-178</v>
+      </c>
+      <c r="U200" s="14" t="n">
+        <v>14239.8</v>
+      </c>
+      <c r="V200" s="14" t="n">
+        <v>-622.99</v>
+      </c>
+      <c r="W200" s="14" t="n">
+        <v>-587.39</v>
+      </c>
+      <c r="X200" s="14" t="n">
+        <v>-589.13</v>
+      </c>
+      <c r="Y200" s="14" t="n">
+        <v>-83.41</v>
+      </c>
+      <c r="Z200" s="14" t="n">
+        <v>516.1900000000001</v>
+      </c>
+      <c r="AA200" s="14" t="n">
+        <v>-1456.97</v>
+      </c>
+      <c r="AB200" s="31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC200" s="14" t="n">
+        <v>11416.1</v>
+      </c>
+      <c r="AD200" s="14" t="n">
+        <v>622.64</v>
+      </c>
+      <c r="AE200" s="14" t="n">
+        <v>174.93</v>
+      </c>
+      <c r="AF200" s="16" t="n">
+        <v>108916.03</v>
+      </c>
+      <c r="AG200" s="16" t="n">
+        <v>120332.13</v>
+      </c>
+      <c r="AH200" s="28" t="n">
+        <v>0.9827525667495332</v>
+      </c>
+      <c r="AI200" s="15" t="n">
+        <v>702.64</v>
+      </c>
       <c r="AJ200" s="15" t="n"/>
       <c r="AK200" s="15" t="n"/>
       <c r="AL200" s="15" t="n"/>
@@ -25489,23 +25523,57 @@
       <c r="P201" s="11" t="n"/>
       <c r="Q201" s="26" t="n"/>
       <c r="R201" s="9" t="n"/>
-      <c r="S201" s="14" t="n"/>
-      <c r="T201" s="14" t="n"/>
-      <c r="U201" s="14" t="n"/>
-      <c r="V201" s="14" t="n"/>
-      <c r="W201" s="14" t="n"/>
-      <c r="X201" s="14" t="n"/>
-      <c r="Y201" s="14" t="n"/>
-      <c r="Z201" s="14" t="n"/>
-      <c r="AA201" s="14" t="n"/>
-      <c r="AB201" s="31" t="n"/>
-      <c r="AC201" s="14" t="n"/>
-      <c r="AD201" s="14" t="n"/>
-      <c r="AE201" s="14" t="n"/>
-      <c r="AF201" s="16" t="n"/>
-      <c r="AG201" s="16" t="n"/>
-      <c r="AH201" s="28" t="n"/>
-      <c r="AI201" s="15" t="n"/>
+      <c r="S201" s="14" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="T201" s="14" t="n">
+        <v>-174.46</v>
+      </c>
+      <c r="U201" s="14" t="n">
+        <v>-9097.35</v>
+      </c>
+      <c r="V201" s="14" t="n">
+        <v>-610.61</v>
+      </c>
+      <c r="W201" s="14" t="n">
+        <v>-575.72</v>
+      </c>
+      <c r="X201" s="14" t="n">
+        <v>-174.63</v>
+      </c>
+      <c r="Y201" s="14" t="n">
+        <v>-24.72</v>
+      </c>
+      <c r="Z201" s="14" t="n">
+        <v>505.93</v>
+      </c>
+      <c r="AA201" s="14" t="n">
+        <v>-2151.8</v>
+      </c>
+      <c r="AB201" s="31" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AC201" s="14" t="n">
+        <v>-12128.9</v>
+      </c>
+      <c r="AD201" s="14" t="n">
+        <v>565.8</v>
+      </c>
+      <c r="AE201" s="14" t="n">
+        <v>173.55</v>
+      </c>
+      <c r="AF201" s="16" t="n">
+        <v>98193.87</v>
+      </c>
+      <c r="AG201" s="16" t="n">
+        <v>86064.97</v>
+      </c>
+      <c r="AH201" s="28" t="n">
+        <v>0.9947839046199703</v>
+      </c>
+      <c r="AI201" s="15" t="n">
+        <v>513.65</v>
+      </c>
       <c r="AJ201" s="15" t="n"/>
       <c r="AK201" s="15" t="n"/>
       <c r="AL201" s="15" t="n"/>
@@ -25548,23 +25616,57 @@
       <c r="P202" s="11" t="n"/>
       <c r="Q202" s="26" t="n"/>
       <c r="R202" s="9" t="n"/>
-      <c r="S202" s="14" t="n"/>
-      <c r="T202" s="14" t="n"/>
-      <c r="U202" s="14" t="n"/>
-      <c r="V202" s="14" t="n"/>
-      <c r="W202" s="14" t="n"/>
-      <c r="X202" s="14" t="n"/>
-      <c r="Y202" s="14" t="n"/>
-      <c r="Z202" s="14" t="n"/>
-      <c r="AA202" s="14" t="n"/>
-      <c r="AB202" s="31" t="n"/>
-      <c r="AC202" s="14" t="n"/>
-      <c r="AD202" s="14" t="n"/>
-      <c r="AE202" s="14" t="n"/>
-      <c r="AF202" s="16" t="n"/>
-      <c r="AG202" s="16" t="n"/>
-      <c r="AH202" s="28" t="n"/>
-      <c r="AI202" s="15" t="n"/>
+      <c r="S202" s="14" t="n">
+        <v>336.38</v>
+      </c>
+      <c r="T202" s="14" t="n">
+        <v>-25</v>
+      </c>
+      <c r="U202" s="14" t="n">
+        <v>-8409.43</v>
+      </c>
+      <c r="V202" s="14" t="n">
+        <v>-87.5</v>
+      </c>
+      <c r="W202" s="14" t="n">
+        <v>-82.5</v>
+      </c>
+      <c r="X202" s="14" t="n">
+        <v>639.99</v>
+      </c>
+      <c r="Y202" s="14" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="Z202" s="14" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AA202" s="14" t="n">
+        <v>-1762.5</v>
+      </c>
+      <c r="AB202" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC202" s="14" t="n">
+        <v>-9538.83</v>
+      </c>
+      <c r="AD202" s="14" t="n">
+        <v>533.8</v>
+      </c>
+      <c r="AE202" s="14" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="AF202" s="16" t="n">
+        <v>15125.29</v>
+      </c>
+      <c r="AG202" s="16" t="n">
+        <v>5586.46</v>
+      </c>
+      <c r="AH202" s="28" t="n">
+        <v>1.1334</v>
+      </c>
+      <c r="AI202" s="15" t="n">
+        <v>197.43</v>
+      </c>
       <c r="AJ202" s="15" t="n"/>
       <c r="AK202" s="15" t="n"/>
       <c r="AL202" s="15" t="n"/>
@@ -25607,23 +25709,57 @@
       <c r="P203" s="11" t="n"/>
       <c r="Q203" s="26" t="n"/>
       <c r="R203" s="9" t="n"/>
-      <c r="S203" s="14" t="n"/>
-      <c r="T203" s="14" t="n"/>
-      <c r="U203" s="14" t="n"/>
-      <c r="V203" s="14" t="n"/>
-      <c r="W203" s="14" t="n"/>
-      <c r="X203" s="14" t="n"/>
-      <c r="Y203" s="14" t="n"/>
-      <c r="Z203" s="14" t="n"/>
-      <c r="AA203" s="14" t="n"/>
-      <c r="AB203" s="31" t="n"/>
-      <c r="AC203" s="14" t="n"/>
-      <c r="AD203" s="14" t="n"/>
-      <c r="AE203" s="14" t="n"/>
-      <c r="AF203" s="16" t="n"/>
-      <c r="AG203" s="16" t="n"/>
-      <c r="AH203" s="28" t="n"/>
-      <c r="AI203" s="15" t="n"/>
+      <c r="S203" s="14" t="n">
+        <v>-84.97</v>
+      </c>
+      <c r="T203" s="14" t="n">
+        <v>-180.37</v>
+      </c>
+      <c r="U203" s="14" t="n">
+        <v>15326.05</v>
+      </c>
+      <c r="V203" s="14" t="n">
+        <v>-631.29</v>
+      </c>
+      <c r="W203" s="14" t="n">
+        <v>-595.21</v>
+      </c>
+      <c r="X203" s="14" t="n">
+        <v>-1822.57</v>
+      </c>
+      <c r="Y203" s="14" t="n">
+        <v>-258.03</v>
+      </c>
+      <c r="Z203" s="14" t="n">
+        <v>523.0700000000001</v>
+      </c>
+      <c r="AA203" s="14" t="n">
+        <v>-4753.54</v>
+      </c>
+      <c r="AB203" s="31" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC203" s="14" t="n">
+        <v>7788.47</v>
+      </c>
+      <c r="AD203" s="14" t="n">
+        <v>610</v>
+      </c>
+      <c r="AE203" s="14" t="n">
+        <v>170.87</v>
+      </c>
+      <c r="AF203" s="16" t="n">
+        <v>104230.76</v>
+      </c>
+      <c r="AG203" s="16" t="n">
+        <v>112019.24</v>
+      </c>
+      <c r="AH203" s="28" t="n">
+        <v>0.9473436178912498</v>
+      </c>
+      <c r="AI203" s="15" t="n">
+        <v>694.97</v>
+      </c>
       <c r="AJ203" s="15" t="n"/>
       <c r="AK203" s="15" t="n"/>
       <c r="AL203" s="15" t="n"/>
@@ -34002,18 +34138,18 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="S2:AC2"/>
     <mergeCell ref="AU2:AW2"/>
     <mergeCell ref="B2:L2"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
-    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="AJ1:AZ1"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>
   </mergeCells>
@@ -36094,18 +36230,18 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="S2:AC2"/>
     <mergeCell ref="AU2:AW2"/>
     <mergeCell ref="B2:L2"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
-    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="AJ1:AZ1"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>
   </mergeCells>

--- a/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
+++ b/05 Review_Dashboard_and _weeklyreport/output/山东夏津储能收益统计表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="等线"/>
       <family val="2"/>
@@ -113,8 +113,23 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -156,8 +171,20 @@
         <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="45">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -669,6 +696,82 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -689,6 +792,17 @@
     <border>
       <left/>
       <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color rgb="FF1F2329"/>
       </right>
       <top style="thin">
@@ -698,10 +812,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="23" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -796,6 +913,64 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -812,6 +987,14 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -822,9 +1005,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -904,93 +1100,93 @@
     <author>None</author>
   </authors>
   <commentList>
-    <comment ref="AX127" authorId="0" shapeId="0">
+    <comment ref="AZ127" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    70763.66    </t>
       </text>
     </comment>
-    <comment ref="AX128" authorId="0" shapeId="0">
+    <comment ref="AZ128" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    89354.34    </t>
       </text>
     </comment>
-    <comment ref="AX129" authorId="0" shapeId="0">
+    <comment ref="AZ129" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    72212.28    </t>
       </text>
     </comment>
-    <comment ref="AX130" authorId="0" shapeId="0">
+    <comment ref="AZ130" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    90064.55    </t>
       </text>
     </comment>
-    <comment ref="AX131" authorId="0" shapeId="0">
+    <comment ref="AZ131" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    103494.66    </t>
       </text>
     </comment>
-    <comment ref="AX132" authorId="0" shapeId="0">
+    <comment ref="AZ132" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    51068.14    </t>
       </text>
     </comment>
-    <comment ref="AX133" authorId="0" shapeId="0">
+    <comment ref="AZ133" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    84900.86    </t>
       </text>
     </comment>
-    <comment ref="AX134" authorId="0" shapeId="0">
+    <comment ref="AZ134" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    -6910.85    
 报了调频但未中</t>
       </text>
     </comment>
-    <comment ref="BE134" authorId="0" shapeId="0">
+    <comment ref="BG134" authorId="0" shapeId="0">
       <text>
         <t>中标未调用</t>
       </text>
     </comment>
-    <comment ref="AX135" authorId="0" shapeId="0">
+    <comment ref="AY135" authorId="0" shapeId="0">
+      <text>
+        <t>日前价差200，应该报调频。火电竞价空间报价策略改变。</t>
+      </text>
+    </comment>
+    <comment ref="AZ135" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    13578.53    </t>
       </text>
     </comment>
-    <comment ref="BA135" authorId="0" shapeId="0">
-      <text>
-        <t>日前价差200，应该报调频。火电竞价空间报价策略改变。</t>
-      </text>
-    </comment>
-    <comment ref="AX136" authorId="0" shapeId="0">
+    <comment ref="AZ136" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    96513.48    </t>
       </text>
     </comment>
-    <comment ref="AX137" authorId="0" shapeId="0">
+    <comment ref="AZ137" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    90250.15    </t>
       </text>
     </comment>
-    <comment ref="AX138" authorId="0" shapeId="0">
+    <comment ref="AZ138" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    118988.14    </t>
       </text>
     </comment>
-    <comment ref="AX139" authorId="0" shapeId="0">
+    <comment ref="AZ139" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    67602.79    </t>
       </text>
     </comment>
-    <comment ref="AX140" authorId="0" shapeId="0">
+    <comment ref="AZ140" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    68470.58    </t>
       </text>
     </comment>
-    <comment ref="AX141" authorId="0" shapeId="0">
+    <comment ref="AZ141" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    70389.53    </t>
       </text>
     </comment>
-    <comment ref="AX142" authorId="0" shapeId="0">
+    <comment ref="AZ142" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    64748.29    </t>
       </text>
@@ -1000,173 +1196,173 @@
         <t>充电时段来了一片云</t>
       </text>
     </comment>
-    <comment ref="AX143" authorId="0" shapeId="0">
+    <comment ref="AZ143" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    -499.23    
 充电时段变阴天，价格升高。</t>
       </text>
     </comment>
-    <comment ref="AX144" authorId="0" shapeId="0">
+    <comment ref="AZ144" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    -19970.42    
 日前不想出清，被调度强制调用</t>
       </text>
     </comment>
-    <comment ref="AX145" authorId="0" shapeId="0">
+    <comment ref="AZ145" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    86853.74    </t>
       </text>
     </comment>
-    <comment ref="AX146" authorId="0" shapeId="0">
+    <comment ref="AZ146" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    89297.08    </t>
       </text>
     </comment>
-    <comment ref="AX147" authorId="0" shapeId="0">
+    <comment ref="AZ147" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    111455.25    </t>
       </text>
     </comment>
-    <comment ref="AX148" authorId="0" shapeId="0">
+    <comment ref="AZ148" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    56983.34    
 13号和16号是一对多云天气随机性的反例。多云天气光伏比预估的高4000左右，压低了中午电价。电价在多云天气很敏感。</t>
       </text>
     </comment>
-    <comment ref="AX149" authorId="0" shapeId="0">
+    <comment ref="AZ149" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    84241.89    </t>
       </text>
     </comment>
-    <comment ref="AX150" authorId="0" shapeId="0">
+    <comment ref="AZ150" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    92309.77    </t>
       </text>
     </comment>
-    <comment ref="AX151" authorId="0" shapeId="0">
+    <comment ref="AZ151" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    5995.48    </t>
       </text>
     </comment>
-    <comment ref="AX152" authorId="0" shapeId="0">
+    <comment ref="AZ152" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    84447.29    </t>
       </text>
     </comment>
-    <comment ref="AX153" authorId="0" shapeId="0">
+    <comment ref="AZ153" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    95255.76    </t>
       </text>
     </comment>
-    <comment ref="AX154" authorId="0" shapeId="0">
+    <comment ref="AZ154" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    82725.27    </t>
       </text>
     </comment>
-    <comment ref="AX155" authorId="0" shapeId="0">
+    <comment ref="AZ155" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    96141.42    </t>
       </text>
     </comment>
-    <comment ref="AX156" authorId="0" shapeId="0">
+    <comment ref="AZ156" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    26349.01    
 日前预测准。日前价差不大，不想中电能量市场。因此电能量高价差申报，未出清。报调频4元，中标11.2元。收入2.7万。</t>
       </text>
     </comment>
-    <comment ref="AX157" authorId="0" shapeId="0">
+    <comment ref="AZ157" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    75027.73    </t>
       </text>
     </comment>
-    <comment ref="AX158" authorId="0" shapeId="0">
+    <comment ref="AZ158" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    79229.64    </t>
       </text>
     </comment>
-    <comment ref="AX159" authorId="0" shapeId="0">
+    <comment ref="AZ159" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    64726.22    </t>
       </text>
     </comment>
-    <comment ref="AX160" authorId="0" shapeId="0">
+    <comment ref="AZ160" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    67867.40    </t>
       </text>
     </comment>
-    <comment ref="AX161" authorId="0" shapeId="0">
+    <comment ref="AZ161" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    11984.59    
 运气不好。日前预测价格形态对，有地板价。按日前电价，是个大晴天，会有7.8万收益。光伏出力不及预期，11:15预计光伏出力19000，达到最大。实际上光伏出力16000。在储能和抽蓄开始充电的时点上，价格上去了。润津储能完全在高价充电。前一个地板时段充电的场站，可以保持7万多的收益。</t>
       </text>
     </comment>
-    <comment ref="AX162" authorId="0" shapeId="0">
+    <comment ref="AZ162" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    90443.09    </t>
       </text>
     </comment>
-    <comment ref="AX163" authorId="0" shapeId="0">
+    <comment ref="AZ163" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    88465.18    </t>
       </text>
     </comment>
-    <comment ref="AX164" authorId="0" shapeId="0">
+    <comment ref="AZ164" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    103356.33    </t>
       </text>
     </comment>
-    <comment ref="AX165" authorId="0" shapeId="0">
+    <comment ref="AZ165" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    76166.25    </t>
       </text>
     </comment>
-    <comment ref="AX166" authorId="0" shapeId="0">
+    <comment ref="AZ166" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    96403.85    </t>
       </text>
     </comment>
-    <comment ref="AX167" authorId="0" shapeId="0">
+    <comment ref="AZ167" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    -1504.64    
 新能源出力很低，预测日前电价有高价差。但根据历史经验，调度过度估算供需，预计实时电价不会那么高的价差，会是直线为主，即使偶尔有高价差，日前也不一定可以出清到合适的时点。因此报高价差不中电能量，按之前的经验，有担心会有偶尔高价差影响调频造成大损失，所以也未申报调频。其实申报调频收益可能会更好。其他场站出清了大量电量，充电在高价时段，会有更高的过网费和容量分摊，估算在2.7万左右损失。</t>
       </text>
     </comment>
-    <comment ref="AX168" authorId="0" shapeId="0">
+    <comment ref="AZ168" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    109044.21    </t>
       </text>
     </comment>
-    <comment ref="AX169" authorId="0" shapeId="0">
+    <comment ref="AZ169" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    77830.46    </t>
       </text>
     </comment>
-    <comment ref="AX170" authorId="0" shapeId="0">
+    <comment ref="AZ170" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    85087.21    </t>
       </text>
     </comment>
-    <comment ref="AX171" authorId="0" shapeId="0">
+    <comment ref="AZ171" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    85697.62    </t>
       </text>
     </comment>
-    <comment ref="AX172" authorId="0" shapeId="0">
+    <comment ref="AZ172" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    117795.73    </t>
       </text>
     </comment>
-    <comment ref="AX173" authorId="0" shapeId="0">
+    <comment ref="AZ173" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    101194.61    </t>
       </text>
     </comment>
-    <comment ref="AX174" authorId="0" shapeId="0">
+    <comment ref="AZ174" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    79790.00    </t>
       </text>
     </comment>
-    <comment ref="AX175" authorId="0" shapeId="0">
+    <comment ref="AZ175" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">    120976.52    </t>
       </text>
@@ -1698,7 +1894,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE270"/>
+  <dimension ref="A1:BG270"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14" defaultRowHeight="13.2"/>
   <cols>
     <col width="17" customWidth="1" style="30" min="1" max="1"/>
@@ -1712,203 +1908,203 @@
     <col hidden="1" width="15" customWidth="1" style="30" min="32" max="32"/>
     <col width="15" customWidth="1" style="30" min="33" max="37"/>
     <col hidden="1" width="15" customWidth="1" style="30" min="38" max="46"/>
-    <col width="15" customWidth="1" style="30" min="47" max="48"/>
-    <col hidden="1" width="15" customWidth="1" style="30" min="49" max="49"/>
-    <col width="15" customWidth="1" style="30" min="50" max="57"/>
+    <col width="15" customWidth="1" style="30" min="47" max="52"/>
+    <col width="15" customWidth="1" style="37" min="53" max="54"/>
+    <col width="15" customWidth="1" style="30" min="55" max="59"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="30">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="40" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t>日前机组组合收益复盘</t>
         </is>
       </c>
-      <c r="C1" s="41" t="n"/>
-      <c r="D1" s="41" t="n"/>
-      <c r="E1" s="41" t="n"/>
-      <c r="F1" s="41" t="n"/>
-      <c r="G1" s="41" t="n"/>
-      <c r="H1" s="41" t="n"/>
-      <c r="I1" s="41" t="n"/>
-      <c r="J1" s="41" t="n"/>
-      <c r="K1" s="41" t="n"/>
-      <c r="L1" s="41" t="n"/>
-      <c r="M1" s="41" t="n"/>
-      <c r="N1" s="41" t="n"/>
-      <c r="O1" s="41" t="n"/>
-      <c r="P1" s="41" t="n"/>
-      <c r="Q1" s="41" t="n"/>
-      <c r="R1" s="42" t="n"/>
-      <c r="S1" s="40" t="inlineStr">
+      <c r="C1" s="65" t="n"/>
+      <c r="D1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="65" t="n"/>
+      <c r="H1" s="65" t="n"/>
+      <c r="I1" s="65" t="n"/>
+      <c r="J1" s="65" t="n"/>
+      <c r="K1" s="65" t="n"/>
+      <c r="L1" s="65" t="n"/>
+      <c r="M1" s="65" t="n"/>
+      <c r="N1" s="65" t="n"/>
+      <c r="O1" s="65" t="n"/>
+      <c r="P1" s="65" t="n"/>
+      <c r="Q1" s="65" t="n"/>
+      <c r="R1" s="66" t="n"/>
+      <c r="S1" s="64" t="inlineStr">
         <is>
           <t>实时机组组合收益复盘</t>
         </is>
       </c>
-      <c r="T1" s="41" t="n"/>
-      <c r="U1" s="41" t="n"/>
-      <c r="V1" s="41" t="n"/>
-      <c r="W1" s="41" t="n"/>
-      <c r="X1" s="41" t="n"/>
-      <c r="Y1" s="41" t="n"/>
-      <c r="Z1" s="41" t="n"/>
-      <c r="AA1" s="41" t="n"/>
-      <c r="AB1" s="41" t="n"/>
-      <c r="AC1" s="41" t="n"/>
-      <c r="AD1" s="41" t="n"/>
-      <c r="AE1" s="41" t="n"/>
-      <c r="AF1" s="41" t="n"/>
-      <c r="AG1" s="41" t="n"/>
-      <c r="AH1" s="41" t="n"/>
-      <c r="AI1" s="42" t="n"/>
-      <c r="AJ1" s="40" t="inlineStr">
+      <c r="T1" s="65" t="n"/>
+      <c r="U1" s="65" t="n"/>
+      <c r="V1" s="65" t="n"/>
+      <c r="W1" s="65" t="n"/>
+      <c r="X1" s="65" t="n"/>
+      <c r="Y1" s="65" t="n"/>
+      <c r="Z1" s="65" t="n"/>
+      <c r="AA1" s="65" t="n"/>
+      <c r="AB1" s="65" t="n"/>
+      <c r="AC1" s="65" t="n"/>
+      <c r="AD1" s="65" t="n"/>
+      <c r="AE1" s="65" t="n"/>
+      <c r="AF1" s="65" t="n"/>
+      <c r="AG1" s="65" t="n"/>
+      <c r="AH1" s="65" t="n"/>
+      <c r="AI1" s="66" t="n"/>
+      <c r="AJ1" s="64" t="inlineStr">
         <is>
           <t>日结算收益复盘</t>
         </is>
       </c>
-      <c r="AK1" s="41" t="n"/>
-      <c r="AL1" s="41" t="n"/>
-      <c r="AM1" s="41" t="n"/>
-      <c r="AN1" s="41" t="n"/>
-      <c r="AO1" s="41" t="n"/>
-      <c r="AP1" s="41" t="n"/>
-      <c r="AQ1" s="41" t="n"/>
-      <c r="AR1" s="41" t="n"/>
-      <c r="AS1" s="41" t="n"/>
-      <c r="AT1" s="41" t="n"/>
-      <c r="AU1" s="41" t="n"/>
-      <c r="AV1" s="41" t="n"/>
-      <c r="AW1" s="41" t="n"/>
-      <c r="AX1" s="41" t="n"/>
-      <c r="AY1" s="41" t="n"/>
-      <c r="AZ1" s="41" t="n"/>
-      <c r="BA1" s="42" t="n"/>
-      <c r="BB1" s="35" t="inlineStr">
+      <c r="AK1" s="65" t="n"/>
+      <c r="AL1" s="65" t="n"/>
+      <c r="AM1" s="65" t="n"/>
+      <c r="AN1" s="65" t="n"/>
+      <c r="AO1" s="65" t="n"/>
+      <c r="AP1" s="65" t="n"/>
+      <c r="AQ1" s="65" t="n"/>
+      <c r="AR1" s="65" t="n"/>
+      <c r="AS1" s="65" t="n"/>
+      <c r="AT1" s="65" t="n"/>
+      <c r="AU1" s="65" t="n"/>
+      <c r="AV1" s="65" t="n"/>
+      <c r="AW1" s="65" t="n"/>
+      <c r="AX1" s="65" t="n"/>
+      <c r="AY1" s="65" t="n"/>
+      <c r="AZ1" s="65" t="n"/>
+      <c r="BA1" s="65" t="n"/>
+      <c r="BB1" s="65" t="n"/>
+      <c r="BC1" s="66" t="n"/>
+      <c r="BD1" s="55" t="inlineStr">
         <is>
           <t>调频收益</t>
         </is>
       </c>
-      <c r="BC1" s="38" t="n"/>
-      <c r="BD1" s="38" t="n"/>
-      <c r="BE1" s="36" t="n"/>
+      <c r="BE1" s="58" t="n"/>
+      <c r="BF1" s="58" t="n"/>
+      <c r="BG1" s="56" t="n"/>
     </row>
     <row r="2" ht="25.95" customHeight="1" s="30">
-      <c r="A2" s="33" t="n"/>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="C2" s="38" t="n"/>
-      <c r="D2" s="38" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="36" t="n"/>
-      <c r="M2" s="37" t="inlineStr">
+      <c r="C2" s="58" t="n"/>
+      <c r="D2" s="58" t="n"/>
+      <c r="E2" s="58" t="n"/>
+      <c r="F2" s="58" t="n"/>
+      <c r="G2" s="58" t="n"/>
+      <c r="H2" s="58" t="n"/>
+      <c r="I2" s="58" t="n"/>
+      <c r="J2" s="58" t="n"/>
+      <c r="K2" s="58" t="n"/>
+      <c r="L2" s="56" t="n"/>
+      <c r="M2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="36" t="n"/>
+      <c r="N2" s="58" t="n"/>
+      <c r="O2" s="56" t="n"/>
       <c r="P2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="Q2" s="35" t="inlineStr">
+      <c r="Q2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="R2" s="36" t="n"/>
-      <c r="S2" s="39" t="inlineStr">
+      <c r="R2" s="56" t="n"/>
+      <c r="S2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="T2" s="38" t="n"/>
-      <c r="U2" s="38" t="n"/>
-      <c r="V2" s="38" t="n"/>
-      <c r="W2" s="38" t="n"/>
-      <c r="X2" s="38" t="n"/>
-      <c r="Y2" s="38" t="n"/>
-      <c r="Z2" s="38" t="n"/>
-      <c r="AA2" s="38" t="n"/>
-      <c r="AB2" s="38" t="n"/>
-      <c r="AC2" s="36" t="n"/>
-      <c r="AD2" s="37" t="inlineStr">
+      <c r="T2" s="58" t="n"/>
+      <c r="U2" s="58" t="n"/>
+      <c r="V2" s="58" t="n"/>
+      <c r="W2" s="58" t="n"/>
+      <c r="X2" s="58" t="n"/>
+      <c r="Y2" s="58" t="n"/>
+      <c r="Z2" s="58" t="n"/>
+      <c r="AA2" s="58" t="n"/>
+      <c r="AB2" s="58" t="n"/>
+      <c r="AC2" s="56" t="n"/>
+      <c r="AD2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="AE2" s="38" t="n"/>
-      <c r="AF2" s="36" t="n"/>
+      <c r="AE2" s="58" t="n"/>
+      <c r="AF2" s="56" t="n"/>
       <c r="AG2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="AH2" s="35" t="inlineStr">
+      <c r="AH2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="AI2" s="36" t="n"/>
-      <c r="AJ2" s="39" t="inlineStr">
+      <c r="AI2" s="56" t="n"/>
+      <c r="AJ2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="AK2" s="38" t="n"/>
-      <c r="AL2" s="38" t="n"/>
-      <c r="AM2" s="38" t="n"/>
-      <c r="AN2" s="38" t="n"/>
-      <c r="AO2" s="38" t="n"/>
-      <c r="AP2" s="38" t="n"/>
-      <c r="AQ2" s="38" t="n"/>
-      <c r="AR2" s="38" t="n"/>
-      <c r="AS2" s="38" t="n"/>
-      <c r="AT2" s="36" t="n"/>
-      <c r="AU2" s="37" t="inlineStr">
+      <c r="AK2" s="58" t="n"/>
+      <c r="AL2" s="58" t="n"/>
+      <c r="AM2" s="58" t="n"/>
+      <c r="AN2" s="58" t="n"/>
+      <c r="AO2" s="58" t="n"/>
+      <c r="AP2" s="58" t="n"/>
+      <c r="AQ2" s="58" t="n"/>
+      <c r="AR2" s="58" t="n"/>
+      <c r="AS2" s="58" t="n"/>
+      <c r="AT2" s="56" t="n"/>
+      <c r="AU2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="AV2" s="38" t="n"/>
-      <c r="AW2" s="36" t="n"/>
-      <c r="AX2" s="21" t="inlineStr">
-        <is>
-          <t>现货收益</t>
-        </is>
-      </c>
-      <c r="AY2" s="19" t="inlineStr">
-        <is>
-          <t>现货收益（含过网费等）</t>
-        </is>
-      </c>
-      <c r="AZ2" s="35" t="inlineStr">
+      <c r="AV2" s="58" t="n"/>
+      <c r="AW2" s="56" t="n"/>
+      <c r="AX2" s="60" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="BA2" s="36" t="n"/>
-      <c r="BB2" s="35" t="n"/>
-      <c r="BC2" s="38" t="n"/>
-      <c r="BD2" s="38" t="n"/>
-      <c r="BE2" s="36" t="n"/>
+      <c r="AY2" s="56" t="n"/>
+      <c r="AZ2" s="61" t="inlineStr">
+        <is>
+          <t>收益</t>
+        </is>
+      </c>
+      <c r="BA2" s="62" t="n"/>
+      <c r="BB2" s="62" t="n"/>
+      <c r="BC2" s="63" t="n"/>
+      <c r="BD2" s="55" t="n"/>
+      <c r="BE2" s="58" t="n"/>
+      <c r="BF2" s="58" t="n"/>
+      <c r="BG2" s="56" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1" s="30">
-      <c r="A3" s="34" t="n"/>
+      <c r="A3" s="54" t="n"/>
       <c r="B3" s="20" t="inlineStr">
         <is>
           <t>充电均价
@@ -2169,39 +2365,54 @@
  (元)</t>
         </is>
       </c>
-      <c r="AX3" s="21" t="inlineStr">
-        <is>
-          <t>（元）</t>
-        </is>
-      </c>
-      <c r="AY3" s="1" t="n"/>
-      <c r="AZ3" s="1" t="inlineStr">
+      <c r="AX3" s="41" t="inlineStr">
         <is>
           <t>综合效率</t>
         </is>
       </c>
-      <c r="BA3" s="19" t="inlineStr">
+      <c r="AY3" s="42" t="inlineStr">
         <is>
           <t>充放价差
  (元/MWh)</t>
         </is>
       </c>
-      <c r="BB3" s="19" t="inlineStr">
+      <c r="AZ3" s="46" t="inlineStr">
+        <is>
+          <t>现货价差
+收入</t>
+        </is>
+      </c>
+      <c r="BA3" s="47" t="inlineStr">
+        <is>
+          <t>调频收入</t>
+        </is>
+      </c>
+      <c r="BB3" s="46" t="inlineStr">
+        <is>
+          <t>其他费用（过网费、容量分摊等）</t>
+        </is>
+      </c>
+      <c r="BC3" s="47" t="inlineStr">
+        <is>
+          <t>总收入</t>
+        </is>
+      </c>
+      <c r="BD3" s="19" t="inlineStr">
         <is>
           <t>时点个数</t>
         </is>
       </c>
-      <c r="BC3" s="19" t="inlineStr">
+      <c r="BE3" s="19" t="inlineStr">
         <is>
           <t>均价</t>
         </is>
       </c>
-      <c r="BD3" s="19" t="inlineStr">
+      <c r="BF3" s="19" t="inlineStr">
         <is>
           <t>性能</t>
         </is>
       </c>
-      <c r="BE3" s="19" t="inlineStr">
+      <c r="BG3" s="19" t="inlineStr">
         <is>
           <t>收益</t>
         </is>
@@ -4495,20 +4706,22 @@
       <c r="AW46" s="6" t="n">
         <v>-8987.860000000001</v>
       </c>
-      <c r="AX46" s="7" t="n">
+      <c r="AX46" s="24" t="n">
+        <v>0.7315</v>
+      </c>
+      <c r="AY46" s="5" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AZ46" s="7" t="n">
         <v>-14543.5</v>
       </c>
-      <c r="AY46" s="24" t="n"/>
-      <c r="AZ46" s="24" t="n">
-        <v>0.7315</v>
-      </c>
-      <c r="BA46" s="5" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="BB46" s="5" t="n"/>
-      <c r="BC46" s="5" t="n"/>
+      <c r="BA46" s="43" t="n"/>
+      <c r="BB46" s="43" t="n"/>
+      <c r="BC46" s="24" t="n"/>
       <c r="BD46" s="5" t="n"/>
       <c r="BE46" s="5" t="n"/>
+      <c r="BF46" s="5" t="n"/>
+      <c r="BG46" s="5" t="n"/>
     </row>
     <row r="47" ht="21" customHeight="1" s="30">
       <c r="A47" s="3" t="n">
@@ -4659,20 +4872,22 @@
       <c r="AW47" s="6" t="n">
         <v>70943.14999999999</v>
       </c>
-      <c r="AX47" s="7" t="n">
+      <c r="AX47" s="24" t="n">
+        <v>0.8427</v>
+      </c>
+      <c r="AY47" s="5" t="n">
+        <v>431.6</v>
+      </c>
+      <c r="AZ47" s="7" t="n">
         <v>53318.53</v>
       </c>
-      <c r="AY47" s="24" t="n"/>
-      <c r="AZ47" s="24" t="n">
-        <v>0.8427</v>
-      </c>
-      <c r="BA47" s="5" t="n">
-        <v>431.6</v>
-      </c>
-      <c r="BB47" s="5" t="n"/>
-      <c r="BC47" s="5" t="n"/>
+      <c r="BA47" s="43" t="n"/>
+      <c r="BB47" s="43" t="n"/>
+      <c r="BC47" s="24" t="n"/>
       <c r="BD47" s="5" t="n"/>
       <c r="BE47" s="5" t="n"/>
+      <c r="BF47" s="5" t="n"/>
+      <c r="BG47" s="5" t="n"/>
     </row>
     <row r="48" ht="21" customHeight="1" s="30">
       <c r="A48" s="3" t="n">
@@ -4823,20 +5038,22 @@
       <c r="AW48" s="6" t="n">
         <v>80198.37</v>
       </c>
-      <c r="AX48" s="7" t="n">
+      <c r="AX48" s="24" t="n">
+        <v>0.9609</v>
+      </c>
+      <c r="AY48" s="5" t="n">
+        <v>525.46</v>
+      </c>
+      <c r="AZ48" s="7" t="n">
         <v>73167.53999999999</v>
       </c>
-      <c r="AY48" s="24" t="n"/>
-      <c r="AZ48" s="24" t="n">
-        <v>0.9609</v>
-      </c>
-      <c r="BA48" s="5" t="n">
-        <v>525.46</v>
-      </c>
-      <c r="BB48" s="5" t="n"/>
-      <c r="BC48" s="5" t="n"/>
+      <c r="BA48" s="43" t="n"/>
+      <c r="BB48" s="43" t="n"/>
+      <c r="BC48" s="24" t="n"/>
       <c r="BD48" s="5" t="n"/>
       <c r="BE48" s="5" t="n"/>
+      <c r="BF48" s="5" t="n"/>
+      <c r="BG48" s="5" t="n"/>
     </row>
     <row r="49" ht="21" customHeight="1" s="30">
       <c r="A49" s="3" t="n">
@@ -4987,20 +5204,22 @@
       <c r="AW49" s="6" t="n">
         <v>52564.62</v>
       </c>
-      <c r="AX49" s="7" t="n">
+      <c r="AX49" s="24" t="n">
+        <v>0.8149</v>
+      </c>
+      <c r="AY49" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="AZ49" s="7" t="n">
         <v>-25822.67</v>
       </c>
-      <c r="AY49" s="24" t="n"/>
-      <c r="AZ49" s="24" t="n">
-        <v>0.8149</v>
-      </c>
-      <c r="BA49" s="5" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="BB49" s="5" t="n"/>
-      <c r="BC49" s="5" t="n"/>
+      <c r="BA49" s="43" t="n"/>
+      <c r="BB49" s="43" t="n"/>
+      <c r="BC49" s="24" t="n"/>
       <c r="BD49" s="5" t="n"/>
       <c r="BE49" s="5" t="n"/>
+      <c r="BF49" s="5" t="n"/>
+      <c r="BG49" s="5" t="n"/>
     </row>
     <row r="50" ht="21" customHeight="1" s="30">
       <c r="A50" s="3" t="n">
@@ -5151,20 +5370,22 @@
       <c r="AW50" s="6" t="n">
         <v>56749.85</v>
       </c>
-      <c r="AX50" s="7" t="n">
+      <c r="AX50" s="24" t="n">
+        <v>0.8355</v>
+      </c>
+      <c r="AY50" s="5" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="AZ50" s="7" t="n">
         <v>36334.93</v>
       </c>
-      <c r="AY50" s="24" t="n"/>
-      <c r="AZ50" s="24" t="n">
-        <v>0.8355</v>
-      </c>
-      <c r="BA50" s="5" t="n">
-        <v>360.34</v>
-      </c>
-      <c r="BB50" s="5" t="n"/>
-      <c r="BC50" s="5" t="n"/>
+      <c r="BA50" s="43" t="n"/>
+      <c r="BB50" s="43" t="n"/>
+      <c r="BC50" s="24" t="n"/>
       <c r="BD50" s="5" t="n"/>
       <c r="BE50" s="5" t="n"/>
+      <c r="BF50" s="5" t="n"/>
+      <c r="BG50" s="5" t="n"/>
     </row>
     <row r="51" ht="21" customHeight="1" s="30">
       <c r="A51" s="3" t="n">
@@ -5315,20 +5536,22 @@
       <c r="AW51" s="6" t="n">
         <v>58175.72</v>
       </c>
-      <c r="AX51" s="7" t="n">
+      <c r="AX51" s="24" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="AY51" s="5" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="AZ51" s="7" t="n">
         <v>-17530.69</v>
       </c>
-      <c r="AY51" s="24" t="n"/>
-      <c r="AZ51" s="24" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="BA51" s="5" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="BB51" s="5" t="n"/>
-      <c r="BC51" s="5" t="n"/>
+      <c r="BA51" s="43" t="n"/>
+      <c r="BB51" s="43" t="n"/>
+      <c r="BC51" s="24" t="n"/>
       <c r="BD51" s="5" t="n"/>
       <c r="BE51" s="5" t="n"/>
+      <c r="BF51" s="5" t="n"/>
+      <c r="BG51" s="5" t="n"/>
     </row>
     <row r="52" ht="21" customHeight="1" s="30">
       <c r="A52" s="3" t="n">
@@ -5479,20 +5702,22 @@
       <c r="AW52" s="6" t="n">
         <v>110766.63</v>
       </c>
-      <c r="AX52" s="7" t="n">
+      <c r="AX52" s="24" t="n">
+        <v>0.9253</v>
+      </c>
+      <c r="AY52" s="5" t="n">
+        <v>465.59</v>
+      </c>
+      <c r="AZ52" s="7" t="n">
         <v>97007.2</v>
       </c>
-      <c r="AY52" s="24" t="n"/>
-      <c r="AZ52" s="24" t="n">
-        <v>0.9253</v>
-      </c>
-      <c r="BA52" s="5" t="n">
-        <v>465.59</v>
-      </c>
-      <c r="BB52" s="5" t="n"/>
-      <c r="BC52" s="5" t="n"/>
+      <c r="BA52" s="43" t="n"/>
+      <c r="BB52" s="43" t="n"/>
+      <c r="BC52" s="24" t="n"/>
       <c r="BD52" s="5" t="n"/>
       <c r="BE52" s="5" t="n"/>
+      <c r="BF52" s="5" t="n"/>
+      <c r="BG52" s="5" t="n"/>
     </row>
     <row r="53" ht="21" customHeight="1" s="30">
       <c r="A53" s="3" t="n">
@@ -5643,20 +5868,22 @@
       <c r="AW53" s="6" t="n">
         <v>31451.87</v>
       </c>
-      <c r="AX53" s="7" t="n">
+      <c r="AX53" s="24" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="AY53" s="5" t="n">
+        <v>255.96</v>
+      </c>
+      <c r="AZ53" s="7" t="n">
         <v>31151.54</v>
       </c>
-      <c r="AY53" s="24" t="n"/>
-      <c r="AZ53" s="24" t="n">
-        <v>0.8629</v>
-      </c>
-      <c r="BA53" s="5" t="n">
-        <v>255.96</v>
-      </c>
-      <c r="BB53" s="5" t="n"/>
-      <c r="BC53" s="5" t="n"/>
+      <c r="BA53" s="43" t="n"/>
+      <c r="BB53" s="43" t="n"/>
+      <c r="BC53" s="24" t="n"/>
       <c r="BD53" s="5" t="n"/>
       <c r="BE53" s="5" t="n"/>
+      <c r="BF53" s="5" t="n"/>
+      <c r="BG53" s="5" t="n"/>
     </row>
     <row r="54" ht="21" customHeight="1" s="30">
       <c r="A54" s="3" t="n">
@@ -5807,20 +6034,22 @@
       <c r="AW54" s="6" t="n">
         <v>82064.69</v>
       </c>
-      <c r="AX54" s="7" t="n">
+      <c r="AX54" s="24" t="n">
+        <v>0.9137</v>
+      </c>
+      <c r="AY54" s="5" t="n">
+        <v>270.65</v>
+      </c>
+      <c r="AZ54" s="7" t="n">
         <v>69953.13</v>
       </c>
-      <c r="AY54" s="24" t="n"/>
-      <c r="AZ54" s="24" t="n">
-        <v>0.9137</v>
-      </c>
-      <c r="BA54" s="5" t="n">
-        <v>270.65</v>
-      </c>
-      <c r="BB54" s="5" t="n"/>
-      <c r="BC54" s="5" t="n"/>
+      <c r="BA54" s="43" t="n"/>
+      <c r="BB54" s="43" t="n"/>
+      <c r="BC54" s="24" t="n"/>
       <c r="BD54" s="5" t="n"/>
       <c r="BE54" s="5" t="n"/>
+      <c r="BF54" s="5" t="n"/>
+      <c r="BG54" s="5" t="n"/>
     </row>
     <row r="55" ht="21" customHeight="1" s="30">
       <c r="A55" s="3" t="n">
@@ -5971,20 +6200,22 @@
       <c r="AW55" s="6" t="n">
         <v>62762.37</v>
       </c>
-      <c r="AX55" s="7" t="n">
+      <c r="AX55" s="24" t="n">
+        <v>0.8095</v>
+      </c>
+      <c r="AY55" s="5" t="n">
+        <v>466.18</v>
+      </c>
+      <c r="AZ55" s="7" t="n">
         <v>62304.38</v>
       </c>
-      <c r="AY55" s="24" t="n"/>
-      <c r="AZ55" s="24" t="n">
-        <v>0.8095</v>
-      </c>
-      <c r="BA55" s="5" t="n">
-        <v>466.18</v>
-      </c>
-      <c r="BB55" s="5" t="n"/>
-      <c r="BC55" s="5" t="n"/>
+      <c r="BA55" s="43" t="n"/>
+      <c r="BB55" s="43" t="n"/>
+      <c r="BC55" s="24" t="n"/>
       <c r="BD55" s="5" t="n"/>
       <c r="BE55" s="5" t="n"/>
+      <c r="BF55" s="5" t="n"/>
+      <c r="BG55" s="5" t="n"/>
     </row>
     <row r="56" ht="21" customHeight="1" s="30">
       <c r="A56" s="3" t="n">
@@ -6135,20 +6366,22 @@
       <c r="AW56" s="6" t="n">
         <v>106499.22</v>
       </c>
-      <c r="AX56" s="7" t="n">
+      <c r="AX56" s="24" t="n">
+        <v>0.8851</v>
+      </c>
+      <c r="AY56" s="5" t="n">
+        <v>700.1799999999999</v>
+      </c>
+      <c r="AZ56" s="7" t="n">
         <v>108029.84</v>
       </c>
-      <c r="AY56" s="24" t="n"/>
-      <c r="AZ56" s="24" t="n">
-        <v>0.8851</v>
-      </c>
-      <c r="BA56" s="5" t="n">
-        <v>700.1799999999999</v>
-      </c>
-      <c r="BB56" s="5" t="n"/>
-      <c r="BC56" s="5" t="n"/>
+      <c r="BA56" s="43" t="n"/>
+      <c r="BB56" s="43" t="n"/>
+      <c r="BC56" s="24" t="n"/>
       <c r="BD56" s="5" t="n"/>
       <c r="BE56" s="5" t="n"/>
+      <c r="BF56" s="5" t="n"/>
+      <c r="BG56" s="5" t="n"/>
     </row>
     <row r="57" ht="21" customHeight="1" s="30">
       <c r="A57" s="3" t="n">
@@ -6299,20 +6532,22 @@
       <c r="AW57" s="6" t="n">
         <v>88261.28999999999</v>
       </c>
-      <c r="AX57" s="7" t="n">
+      <c r="AX57" s="24" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="AY57" s="5" t="n">
+        <v>409.89</v>
+      </c>
+      <c r="AZ57" s="7" t="n">
         <v>90002.25999999999</v>
       </c>
-      <c r="AY57" s="24" t="n"/>
-      <c r="AZ57" s="24" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="BA57" s="5" t="n">
-        <v>409.89</v>
-      </c>
-      <c r="BB57" s="5" t="n"/>
-      <c r="BC57" s="5" t="n"/>
+      <c r="BA57" s="43" t="n"/>
+      <c r="BB57" s="43" t="n"/>
+      <c r="BC57" s="24" t="n"/>
       <c r="BD57" s="5" t="n"/>
       <c r="BE57" s="5" t="n"/>
+      <c r="BF57" s="5" t="n"/>
+      <c r="BG57" s="5" t="n"/>
     </row>
     <row r="58" ht="21" customHeight="1" s="30">
       <c r="A58" s="3" t="n">
@@ -6462,20 +6697,22 @@
       <c r="AW58" s="6" t="n">
         <v>48333.81</v>
       </c>
-      <c r="AX58" s="7" t="n">
+      <c r="AX58" s="24" t="n">
+        <v>0.8326</v>
+      </c>
+      <c r="AY58" s="5" t="n">
+        <v>334.41</v>
+      </c>
+      <c r="AZ58" s="7" t="n">
         <v>41072.61</v>
       </c>
-      <c r="AY58" s="24" t="n"/>
-      <c r="AZ58" s="24" t="n">
-        <v>0.8326</v>
-      </c>
-      <c r="BA58" s="5" t="n">
-        <v>334.41</v>
-      </c>
-      <c r="BB58" s="5" t="n"/>
-      <c r="BC58" s="5" t="n"/>
+      <c r="BA58" s="43" t="n"/>
+      <c r="BB58" s="43" t="n"/>
+      <c r="BC58" s="24" t="n"/>
       <c r="BD58" s="5" t="n"/>
       <c r="BE58" s="5" t="n"/>
+      <c r="BF58" s="5" t="n"/>
+      <c r="BG58" s="5" t="n"/>
     </row>
     <row r="59" ht="21" customHeight="1" s="30">
       <c r="A59" s="3" t="n">
@@ -6575,20 +6812,22 @@
       <c r="AW59" s="6" t="n">
         <v>2212.33</v>
       </c>
-      <c r="AX59" s="7" t="n">
+      <c r="AX59" s="24" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="AY59" s="5" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="AZ59" s="7" t="n">
         <v>-1013.34</v>
       </c>
-      <c r="AY59" s="24" t="n"/>
-      <c r="AZ59" s="24" t="n">
-        <v>0.9193</v>
-      </c>
-      <c r="BA59" s="5" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="BB59" s="5" t="n"/>
-      <c r="BC59" s="5" t="n"/>
+      <c r="BA59" s="43" t="n"/>
+      <c r="BB59" s="43" t="n"/>
+      <c r="BC59" s="24" t="n"/>
       <c r="BD59" s="5" t="n"/>
       <c r="BE59" s="5" t="n"/>
+      <c r="BF59" s="5" t="n"/>
+      <c r="BG59" s="5" t="n"/>
     </row>
     <row r="60" ht="21" customHeight="1" s="30">
       <c r="A60" s="3" t="n">
@@ -6738,20 +6977,22 @@
       <c r="AW60" s="6" t="n">
         <v>977.21</v>
       </c>
-      <c r="AX60" s="7" t="n">
+      <c r="AX60" s="24" t="n">
+        <v>0.8126</v>
+      </c>
+      <c r="AY60" s="5" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="AZ60" s="7" t="n">
         <v>-1195.98</v>
       </c>
-      <c r="AY60" s="24" t="n"/>
-      <c r="AZ60" s="24" t="n">
-        <v>0.8126</v>
-      </c>
-      <c r="BA60" s="5" t="n">
-        <v>77.92</v>
-      </c>
-      <c r="BB60" s="5" t="n"/>
-      <c r="BC60" s="5" t="n"/>
+      <c r="BA60" s="43" t="n"/>
+      <c r="BB60" s="43" t="n"/>
+      <c r="BC60" s="24" t="n"/>
       <c r="BD60" s="5" t="n"/>
       <c r="BE60" s="5" t="n"/>
+      <c r="BF60" s="5" t="n"/>
+      <c r="BG60" s="5" t="n"/>
     </row>
     <row r="61" ht="21" customHeight="1" s="30">
       <c r="A61" s="3" t="n">
@@ -6851,20 +7092,22 @@
       <c r="AW61" s="6" t="n">
         <v>816.53</v>
       </c>
-      <c r="AX61" s="7" t="n">
+      <c r="AX61" s="24" t="n">
+        <v>1.7206</v>
+      </c>
+      <c r="AY61" s="5" t="n">
+        <v>-178.89</v>
+      </c>
+      <c r="AZ61" s="7" t="n">
         <v>-490.06</v>
       </c>
-      <c r="AY61" s="24" t="n"/>
-      <c r="AZ61" s="24" t="n">
-        <v>1.7206</v>
-      </c>
-      <c r="BA61" s="5" t="n">
-        <v>-178.89</v>
-      </c>
-      <c r="BB61" s="5" t="n"/>
-      <c r="BC61" s="5" t="n"/>
+      <c r="BA61" s="43" t="n"/>
+      <c r="BB61" s="43" t="n"/>
+      <c r="BC61" s="24" t="n"/>
       <c r="BD61" s="5" t="n"/>
       <c r="BE61" s="5" t="n"/>
+      <c r="BF61" s="5" t="n"/>
+      <c r="BG61" s="5" t="n"/>
     </row>
     <row r="62" ht="21" customHeight="1" s="30">
       <c r="A62" s="3" t="n">
@@ -7014,20 +7257,22 @@
       <c r="AW62" s="6" t="n">
         <v>-4162.6</v>
       </c>
-      <c r="AX62" s="7" t="n">
+      <c r="AX62" s="24" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="AY62" s="5" t="n">
+        <v>-108.42</v>
+      </c>
+      <c r="AZ62" s="7" t="n">
         <v>-41704.23</v>
       </c>
-      <c r="AY62" s="24" t="n"/>
-      <c r="AZ62" s="24" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="BA62" s="5" t="n">
-        <v>-108.42</v>
-      </c>
-      <c r="BB62" s="5" t="n"/>
-      <c r="BC62" s="5" t="n"/>
+      <c r="BA62" s="43" t="n"/>
+      <c r="BB62" s="43" t="n"/>
+      <c r="BC62" s="24" t="n"/>
       <c r="BD62" s="5" t="n"/>
       <c r="BE62" s="5" t="n"/>
+      <c r="BF62" s="5" t="n"/>
+      <c r="BG62" s="5" t="n"/>
     </row>
     <row r="63" ht="21" customHeight="1" s="30">
       <c r="A63" s="3" t="n">
@@ -7127,20 +7372,22 @@
       <c r="AW63" s="6" t="n">
         <v>5975.79</v>
       </c>
-      <c r="AX63" s="7" t="n">
+      <c r="AX63" s="24" t="n">
+        <v>1.0245</v>
+      </c>
+      <c r="AY63" s="5" t="n">
+        <v>386.36</v>
+      </c>
+      <c r="AZ63" s="7" t="n">
         <v>2073.77</v>
       </c>
-      <c r="AY63" s="24" t="n"/>
-      <c r="AZ63" s="24" t="n">
-        <v>1.0245</v>
-      </c>
-      <c r="BA63" s="5" t="n">
-        <v>386.36</v>
-      </c>
-      <c r="BB63" s="5" t="n"/>
-      <c r="BC63" s="5" t="n"/>
+      <c r="BA63" s="43" t="n"/>
+      <c r="BB63" s="43" t="n"/>
+      <c r="BC63" s="24" t="n"/>
       <c r="BD63" s="5" t="n"/>
       <c r="BE63" s="5" t="n"/>
+      <c r="BF63" s="5" t="n"/>
+      <c r="BG63" s="5" t="n"/>
     </row>
     <row r="64" ht="21" customHeight="1" s="30">
       <c r="A64" s="3" t="n">
@@ -7290,20 +7537,22 @@
       <c r="AW64" s="6" t="n">
         <v>83907.39999999999</v>
       </c>
-      <c r="AX64" s="7" t="n">
+      <c r="AX64" s="24" t="n">
+        <v>0.8188</v>
+      </c>
+      <c r="AY64" s="5" t="n">
+        <v>340.74</v>
+      </c>
+      <c r="AZ64" s="7" t="n">
         <v>19455.11</v>
       </c>
-      <c r="AY64" s="24" t="n"/>
-      <c r="AZ64" s="24" t="n">
-        <v>0.8188</v>
-      </c>
-      <c r="BA64" s="5" t="n">
-        <v>340.74</v>
-      </c>
-      <c r="BB64" s="5" t="n"/>
-      <c r="BC64" s="5" t="n"/>
+      <c r="BA64" s="43" t="n"/>
+      <c r="BB64" s="43" t="n"/>
+      <c r="BC64" s="24" t="n"/>
       <c r="BD64" s="5" t="n"/>
       <c r="BE64" s="5" t="n"/>
+      <c r="BF64" s="5" t="n"/>
+      <c r="BG64" s="5" t="n"/>
     </row>
     <row r="65" ht="21" customHeight="1" s="30">
       <c r="A65" s="3" t="n">
@@ -7453,20 +7702,22 @@
       <c r="AW65" s="6" t="n">
         <v>62245.69</v>
       </c>
-      <c r="AX65" s="7" t="n">
+      <c r="AX65" s="24" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="AY65" s="5" t="n">
+        <v>257.2</v>
+      </c>
+      <c r="AZ65" s="7" t="n">
         <v>18929.8</v>
       </c>
-      <c r="AY65" s="24" t="n"/>
-      <c r="AZ65" s="24" t="n">
-        <v>0.8146</v>
-      </c>
-      <c r="BA65" s="5" t="n">
-        <v>257.2</v>
-      </c>
-      <c r="BB65" s="5" t="n"/>
-      <c r="BC65" s="5" t="n"/>
+      <c r="BA65" s="43" t="n"/>
+      <c r="BB65" s="43" t="n"/>
+      <c r="BC65" s="24" t="n"/>
       <c r="BD65" s="5" t="n"/>
       <c r="BE65" s="5" t="n"/>
+      <c r="BF65" s="5" t="n"/>
+      <c r="BG65" s="5" t="n"/>
     </row>
     <row r="66" ht="21" customHeight="1" s="30">
       <c r="A66" s="3" t="n">
@@ -7616,20 +7867,22 @@
       <c r="AW66" s="6" t="n">
         <v>71342.46000000001</v>
       </c>
-      <c r="AX66" s="7" t="n">
+      <c r="AX66" s="24" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="AY66" s="5" t="n">
+        <v>501.44</v>
+      </c>
+      <c r="AZ66" s="7" t="n">
         <v>66901.99000000001</v>
       </c>
-      <c r="AY66" s="24" t="n"/>
-      <c r="AZ66" s="24" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="BA66" s="5" t="n">
-        <v>501.44</v>
-      </c>
-      <c r="BB66" s="5" t="n"/>
-      <c r="BC66" s="5" t="n"/>
+      <c r="BA66" s="43" t="n"/>
+      <c r="BB66" s="43" t="n"/>
+      <c r="BC66" s="24" t="n"/>
       <c r="BD66" s="5" t="n"/>
       <c r="BE66" s="5" t="n"/>
+      <c r="BF66" s="5" t="n"/>
+      <c r="BG66" s="5" t="n"/>
     </row>
     <row r="67" ht="21" customHeight="1" s="30">
       <c r="A67" s="3" t="n">
@@ -7779,20 +8032,22 @@
       <c r="AW67" s="6" t="n">
         <v>71839.64</v>
       </c>
-      <c r="AX67" s="7" t="n">
+      <c r="AX67" s="24" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="AY67" s="5" t="n">
+        <v>523.47</v>
+      </c>
+      <c r="AZ67" s="7" t="n">
         <v>70178.39999999999</v>
       </c>
-      <c r="AY67" s="24" t="n"/>
-      <c r="AZ67" s="24" t="n">
-        <v>0.8522</v>
-      </c>
-      <c r="BA67" s="5" t="n">
-        <v>523.47</v>
-      </c>
-      <c r="BB67" s="5" t="n"/>
-      <c r="BC67" s="5" t="n"/>
+      <c r="BA67" s="43" t="n"/>
+      <c r="BB67" s="43" t="n"/>
+      <c r="BC67" s="24" t="n"/>
       <c r="BD67" s="5" t="n"/>
       <c r="BE67" s="5" t="n"/>
+      <c r="BF67" s="5" t="n"/>
+      <c r="BG67" s="5" t="n"/>
     </row>
     <row r="68" ht="21" customHeight="1" s="30">
       <c r="A68" s="3" t="n">
@@ -7942,20 +8197,22 @@
       <c r="AW68" s="6" t="n">
         <v>73025.55</v>
       </c>
-      <c r="AX68" s="7" t="n">
+      <c r="AX68" s="24" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="AY68" s="5" t="n">
+        <v>440.7</v>
+      </c>
+      <c r="AZ68" s="7" t="n">
         <v>56351</v>
       </c>
-      <c r="AY68" s="24" t="n"/>
-      <c r="AZ68" s="24" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="BA68" s="5" t="n">
-        <v>440.7</v>
-      </c>
-      <c r="BB68" s="5" t="n"/>
-      <c r="BC68" s="5" t="n"/>
+      <c r="BA68" s="43" t="n"/>
+      <c r="BB68" s="43" t="n"/>
+      <c r="BC68" s="24" t="n"/>
       <c r="BD68" s="5" t="n"/>
       <c r="BE68" s="5" t="n"/>
+      <c r="BF68" s="5" t="n"/>
+      <c r="BG68" s="5" t="n"/>
     </row>
     <row r="69" ht="21" customHeight="1" s="30">
       <c r="A69" s="3" t="n">
@@ -8105,20 +8362,22 @@
       <c r="AW69" s="6" t="n">
         <v>59900.71</v>
       </c>
-      <c r="AX69" s="7" t="n">
+      <c r="AX69" s="24" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="AY69" s="5" t="n">
+        <v>435.37</v>
+      </c>
+      <c r="AZ69" s="7" t="n">
         <v>55411.33</v>
       </c>
-      <c r="AY69" s="24" t="n"/>
-      <c r="AZ69" s="24" t="n">
-        <v>0.8608</v>
-      </c>
-      <c r="BA69" s="5" t="n">
-        <v>435.37</v>
-      </c>
-      <c r="BB69" s="5" t="n"/>
-      <c r="BC69" s="5" t="n"/>
+      <c r="BA69" s="43" t="n"/>
+      <c r="BB69" s="43" t="n"/>
+      <c r="BC69" s="24" t="n"/>
       <c r="BD69" s="5" t="n"/>
       <c r="BE69" s="5" t="n"/>
+      <c r="BF69" s="5" t="n"/>
+      <c r="BG69" s="5" t="n"/>
     </row>
     <row r="70" ht="21" customHeight="1" s="30">
       <c r="A70" s="3" t="n">
@@ -8268,20 +8527,22 @@
       <c r="AW70" s="6" t="n">
         <v>58987.92</v>
       </c>
-      <c r="AX70" s="7" t="n">
+      <c r="AX70" s="24" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="AY70" s="5" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="AZ70" s="7" t="n">
         <v>51621.31</v>
       </c>
-      <c r="AY70" s="24" t="n"/>
-      <c r="AZ70" s="24" t="n">
-        <v>0.9045</v>
-      </c>
-      <c r="BA70" s="5" t="n">
-        <v>386.78</v>
-      </c>
-      <c r="BB70" s="5" t="n"/>
-      <c r="BC70" s="5" t="n"/>
+      <c r="BA70" s="43" t="n"/>
+      <c r="BB70" s="43" t="n"/>
+      <c r="BC70" s="24" t="n"/>
       <c r="BD70" s="5" t="n"/>
       <c r="BE70" s="5" t="n"/>
+      <c r="BF70" s="5" t="n"/>
+      <c r="BG70" s="5" t="n"/>
     </row>
     <row r="71" ht="21" customHeight="1" s="30">
       <c r="A71" s="3" t="n">
@@ -8431,20 +8692,22 @@
       <c r="AW71" s="6" t="n">
         <v>199110.26</v>
       </c>
-      <c r="AX71" s="7" t="n">
+      <c r="AX71" s="24" t="n">
+        <v>0.9305</v>
+      </c>
+      <c r="AY71" s="5" t="n">
+        <v>847.3099999999999</v>
+      </c>
+      <c r="AZ71" s="7" t="n">
         <v>125562.01</v>
       </c>
-      <c r="AY71" s="24" t="n"/>
-      <c r="AZ71" s="24" t="n">
-        <v>0.9305</v>
-      </c>
-      <c r="BA71" s="5" t="n">
-        <v>847.3099999999999</v>
-      </c>
-      <c r="BB71" s="5" t="n"/>
-      <c r="BC71" s="5" t="n"/>
+      <c r="BA71" s="43" t="n"/>
+      <c r="BB71" s="43" t="n"/>
+      <c r="BC71" s="24" t="n"/>
       <c r="BD71" s="5" t="n"/>
       <c r="BE71" s="5" t="n"/>
+      <c r="BF71" s="5" t="n"/>
+      <c r="BG71" s="5" t="n"/>
     </row>
     <row r="72" ht="21" customHeight="1" s="30">
       <c r="A72" s="3" t="n">
@@ -8594,20 +8857,22 @@
       <c r="AW72" s="6" t="n">
         <v>58522.05</v>
       </c>
-      <c r="AX72" s="7" t="n">
+      <c r="AX72" s="24" t="n">
+        <v>0.8637</v>
+      </c>
+      <c r="AY72" s="5" t="n">
+        <v>308.58</v>
+      </c>
+      <c r="AZ72" s="7" t="n">
         <v>34314.58</v>
       </c>
-      <c r="AY72" s="24" t="n"/>
-      <c r="AZ72" s="24" t="n">
-        <v>0.8637</v>
-      </c>
-      <c r="BA72" s="5" t="n">
-        <v>308.58</v>
-      </c>
-      <c r="BB72" s="5" t="n"/>
-      <c r="BC72" s="5" t="n"/>
+      <c r="BA72" s="43" t="n"/>
+      <c r="BB72" s="43" t="n"/>
+      <c r="BC72" s="24" t="n"/>
       <c r="BD72" s="5" t="n"/>
       <c r="BE72" s="5" t="n"/>
+      <c r="BF72" s="5" t="n"/>
+      <c r="BG72" s="5" t="n"/>
     </row>
     <row r="73" ht="21" customHeight="1" s="30">
       <c r="A73" s="3" t="n">
@@ -8757,20 +9022,22 @@
       <c r="AW73" s="6" t="n">
         <v>53406.07</v>
       </c>
-      <c r="AX73" s="7" t="n">
+      <c r="AX73" s="24" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="AY73" s="5" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="AZ73" s="7" t="n">
         <v>-8950.23</v>
       </c>
-      <c r="AY73" s="24" t="n"/>
-      <c r="AZ73" s="24" t="n">
-        <v>0.8575</v>
-      </c>
-      <c r="BA73" s="5" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="BB73" s="5" t="n"/>
-      <c r="BC73" s="5" t="n"/>
+      <c r="BA73" s="43" t="n"/>
+      <c r="BB73" s="43" t="n"/>
+      <c r="BC73" s="24" t="n"/>
       <c r="BD73" s="5" t="n"/>
       <c r="BE73" s="5" t="n"/>
+      <c r="BF73" s="5" t="n"/>
+      <c r="BG73" s="5" t="n"/>
     </row>
     <row r="74" ht="21" customHeight="1" s="30">
       <c r="A74" s="3" t="n">
@@ -8920,20 +9187,22 @@
       <c r="AW74" s="6" t="n">
         <v>52523.05</v>
       </c>
-      <c r="AX74" s="7" t="n">
+      <c r="AX74" s="24" t="n">
+        <v>0.8496</v>
+      </c>
+      <c r="AY74" s="5" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="AZ74" s="7" t="n">
         <v>-37620.96</v>
       </c>
-      <c r="AY74" s="24" t="n"/>
-      <c r="AZ74" s="24" t="n">
-        <v>0.8496</v>
-      </c>
-      <c r="BA74" s="5" t="n">
-        <v>-7.22</v>
-      </c>
-      <c r="BB74" s="5" t="n"/>
-      <c r="BC74" s="5" t="n"/>
+      <c r="BA74" s="43" t="n"/>
+      <c r="BB74" s="43" t="n"/>
+      <c r="BC74" s="24" t="n"/>
       <c r="BD74" s="5" t="n"/>
       <c r="BE74" s="5" t="n"/>
+      <c r="BF74" s="5" t="n"/>
+      <c r="BG74" s="5" t="n"/>
     </row>
     <row r="75" ht="21" customHeight="1" s="30">
       <c r="A75" s="3" t="n">
@@ -9083,20 +9352,22 @@
       <c r="AW75" s="6" t="n">
         <v>79928.42999999999</v>
       </c>
-      <c r="AX75" s="6" t="n">
+      <c r="AX75" s="24" t="n">
+        <v>0.8585</v>
+      </c>
+      <c r="AY75" s="5" t="n">
+        <v>-191.95</v>
+      </c>
+      <c r="AZ75" s="6" t="n">
         <v>-4378.91</v>
       </c>
-      <c r="AY75" s="24" t="n"/>
-      <c r="AZ75" s="24" t="n">
-        <v>0.8585</v>
-      </c>
-      <c r="BA75" s="5" t="n">
-        <v>-191.95</v>
-      </c>
-      <c r="BB75" s="5" t="n"/>
-      <c r="BC75" s="5" t="n"/>
+      <c r="BA75" s="38" t="n"/>
+      <c r="BB75" s="38" t="n"/>
+      <c r="BC75" s="24" t="n"/>
       <c r="BD75" s="5" t="n"/>
       <c r="BE75" s="5" t="n"/>
+      <c r="BF75" s="5" t="n"/>
+      <c r="BG75" s="5" t="n"/>
     </row>
     <row r="76" ht="21" customHeight="1" s="30">
       <c r="A76" s="3" t="n">
@@ -9196,20 +9467,22 @@
       <c r="AW76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AX76" s="6" t="n">
+      <c r="AX76" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY76" s="5" t="n">
+        <v>-340.01</v>
+      </c>
+      <c r="AZ76" s="6" t="n">
         <v>-4492.15</v>
       </c>
-      <c r="AY76" s="24" t="n"/>
-      <c r="AZ76" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA76" s="5" t="n">
-        <v>-340.01</v>
-      </c>
-      <c r="BB76" s="5" t="n"/>
-      <c r="BC76" s="5" t="n"/>
+      <c r="BA76" s="38" t="n"/>
+      <c r="BB76" s="38" t="n"/>
+      <c r="BC76" s="24" t="n"/>
       <c r="BD76" s="5" t="n"/>
       <c r="BE76" s="5" t="n"/>
+      <c r="BF76" s="5" t="n"/>
+      <c r="BG76" s="5" t="n"/>
     </row>
     <row r="77" ht="21" customHeight="1" s="30">
       <c r="A77" s="3" t="n">
@@ -9359,20 +9632,22 @@
       <c r="AW77" s="6" t="n">
         <v>73933.23</v>
       </c>
-      <c r="AX77" s="6" t="n">
+      <c r="AX77" s="24" t="n">
+        <v>0.8624000000000001</v>
+      </c>
+      <c r="AY77" s="5" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AZ77" s="6" t="n">
         <v>-23667.78</v>
       </c>
-      <c r="AY77" s="24" t="n"/>
-      <c r="AZ77" s="24" t="n">
-        <v>0.8624000000000001</v>
-      </c>
-      <c r="BA77" s="5" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="BB77" s="5" t="n"/>
-      <c r="BC77" s="5" t="n"/>
+      <c r="BA77" s="38" t="n"/>
+      <c r="BB77" s="38" t="n"/>
+      <c r="BC77" s="24" t="n"/>
       <c r="BD77" s="5" t="n"/>
       <c r="BE77" s="5" t="n"/>
+      <c r="BF77" s="5" t="n"/>
+      <c r="BG77" s="5" t="n"/>
     </row>
     <row r="78" ht="21" customHeight="1" s="30">
       <c r="A78" s="3" t="n">
@@ -9522,20 +9797,22 @@
       <c r="AW78" s="6" t="n">
         <v>68718.64999999999</v>
       </c>
-      <c r="AX78" s="6" t="n">
+      <c r="AX78" s="24" t="n">
+        <v>0.8694</v>
+      </c>
+      <c r="AY78" s="5" t="n">
+        <v>492.12</v>
+      </c>
+      <c r="AZ78" s="6" t="n">
         <v>68942.13</v>
       </c>
-      <c r="AY78" s="24" t="n"/>
-      <c r="AZ78" s="24" t="n">
-        <v>0.8694</v>
-      </c>
-      <c r="BA78" s="5" t="n">
-        <v>492.12</v>
-      </c>
-      <c r="BB78" s="5" t="n"/>
-      <c r="BC78" s="5" t="n"/>
+      <c r="BA78" s="38" t="n"/>
+      <c r="BB78" s="38" t="n"/>
+      <c r="BC78" s="24" t="n"/>
       <c r="BD78" s="5" t="n"/>
       <c r="BE78" s="5" t="n"/>
+      <c r="BF78" s="5" t="n"/>
+      <c r="BG78" s="5" t="n"/>
     </row>
     <row r="79" ht="21" customHeight="1" s="30">
       <c r="A79" s="3" t="n">
@@ -9685,20 +9962,22 @@
       <c r="AW79" s="6" t="n">
         <v>51879.21</v>
       </c>
-      <c r="AX79" s="6" t="n">
+      <c r="AX79" s="24" t="n">
+        <v>0.8502999999999999</v>
+      </c>
+      <c r="AY79" s="5" t="n">
+        <v>354.54</v>
+      </c>
+      <c r="AZ79" s="6" t="n">
         <v>42810.64</v>
       </c>
-      <c r="AY79" s="24" t="n"/>
-      <c r="AZ79" s="24" t="n">
-        <v>0.8502999999999999</v>
-      </c>
-      <c r="BA79" s="5" t="n">
-        <v>354.54</v>
-      </c>
-      <c r="BB79" s="5" t="n"/>
-      <c r="BC79" s="5" t="n"/>
+      <c r="BA79" s="38" t="n"/>
+      <c r="BB79" s="38" t="n"/>
+      <c r="BC79" s="24" t="n"/>
       <c r="BD79" s="5" t="n"/>
       <c r="BE79" s="5" t="n"/>
+      <c r="BF79" s="5" t="n"/>
+      <c r="BG79" s="5" t="n"/>
     </row>
     <row r="80" ht="21" customHeight="1" s="30">
       <c r="A80" s="3" t="n">
@@ -9848,20 +10127,22 @@
       <c r="AW80" s="6" t="n">
         <v>125673.6</v>
       </c>
-      <c r="AX80" s="6" t="n">
+      <c r="AX80" s="24" t="n">
+        <v>0.8643</v>
+      </c>
+      <c r="AY80" s="5" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="AZ80" s="6" t="n">
         <v>71318.84</v>
       </c>
-      <c r="AY80" s="24" t="n"/>
-      <c r="AZ80" s="24" t="n">
-        <v>0.8643</v>
-      </c>
-      <c r="BA80" s="5" t="n">
-        <v>377.78</v>
-      </c>
-      <c r="BB80" s="5" t="n"/>
-      <c r="BC80" s="5" t="n"/>
+      <c r="BA80" s="38" t="n"/>
+      <c r="BB80" s="38" t="n"/>
+      <c r="BC80" s="24" t="n"/>
       <c r="BD80" s="5" t="n"/>
       <c r="BE80" s="5" t="n"/>
+      <c r="BF80" s="5" t="n"/>
+      <c r="BG80" s="5" t="n"/>
     </row>
     <row r="81" ht="21" customHeight="1" s="30">
       <c r="A81" s="3" t="n">
@@ -10011,20 +10292,22 @@
       <c r="AW81" s="6" t="n">
         <v>38823.22</v>
       </c>
-      <c r="AX81" s="6" t="n">
+      <c r="AX81" s="24" t="n">
+        <v>0.6466</v>
+      </c>
+      <c r="AY81" s="5" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="AZ81" s="6" t="n">
         <v>26358.98</v>
       </c>
-      <c r="AY81" s="24" t="n"/>
-      <c r="AZ81" s="24" t="n">
-        <v>0.6466</v>
-      </c>
-      <c r="BA81" s="5" t="n">
-        <v>370.62</v>
-      </c>
-      <c r="BB81" s="5" t="n"/>
-      <c r="BC81" s="5" t="n"/>
+      <c r="BA81" s="38" t="n"/>
+      <c r="BB81" s="38" t="n"/>
+      <c r="BC81" s="24" t="n"/>
       <c r="BD81" s="5" t="n"/>
       <c r="BE81" s="5" t="n"/>
+      <c r="BF81" s="5" t="n"/>
+      <c r="BG81" s="5" t="n"/>
     </row>
     <row r="82" ht="21" customHeight="1" s="30">
       <c r="A82" s="3" t="n">
@@ -10595,20 +10878,22 @@
       <c r="AW105" s="6" t="n">
         <v>128330.83</v>
       </c>
-      <c r="AX105" s="6" t="n">
+      <c r="AX105" s="24" t="n">
+        <v>0.8702</v>
+      </c>
+      <c r="AY105" s="5" t="n">
+        <v>495.03</v>
+      </c>
+      <c r="AZ105" s="6" t="n">
         <v>62127.32</v>
       </c>
-      <c r="AY105" s="24" t="n"/>
-      <c r="AZ105" s="24" t="n">
-        <v>0.8702</v>
-      </c>
-      <c r="BA105" s="5" t="n">
-        <v>495.03</v>
-      </c>
-      <c r="BB105" s="5" t="n"/>
-      <c r="BC105" s="5" t="n"/>
+      <c r="BA105" s="38" t="n"/>
+      <c r="BB105" s="38" t="n"/>
+      <c r="BC105" s="24" t="n"/>
       <c r="BD105" s="5" t="n"/>
       <c r="BE105" s="5" t="n"/>
+      <c r="BF105" s="5" t="n"/>
+      <c r="BG105" s="5" t="n"/>
     </row>
     <row r="106" ht="21" customHeight="1" s="30">
       <c r="A106" s="3" t="n">
@@ -10758,20 +11043,22 @@
       <c r="AW106" s="6" t="n">
         <v>56638.62</v>
       </c>
-      <c r="AX106" s="6" t="n">
+      <c r="AX106" s="24" t="n">
+        <v>0.8639</v>
+      </c>
+      <c r="AY106" s="5" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="AZ106" s="6" t="n">
         <v>-10342.27</v>
       </c>
-      <c r="AY106" s="24" t="n"/>
-      <c r="AZ106" s="24" t="n">
-        <v>0.8639</v>
-      </c>
-      <c r="BA106" s="5" t="n">
-        <v>48.76</v>
-      </c>
-      <c r="BB106" s="5" t="n"/>
-      <c r="BC106" s="5" t="n"/>
+      <c r="BA106" s="38" t="n"/>
+      <c r="BB106" s="38" t="n"/>
+      <c r="BC106" s="24" t="n"/>
       <c r="BD106" s="5" t="n"/>
       <c r="BE106" s="5" t="n"/>
+      <c r="BF106" s="5" t="n"/>
+      <c r="BG106" s="5" t="n"/>
     </row>
     <row r="107" ht="21" customHeight="1" s="30">
       <c r="A107" s="3" t="n">
@@ -10921,26 +11208,28 @@
       <c r="AW107" s="6" t="n">
         <v>164460.38</v>
       </c>
-      <c r="AX107" s="6" t="n">
+      <c r="AX107" s="24" t="n">
+        <v>0.9058</v>
+      </c>
+      <c r="AY107" s="5" t="n">
+        <v>38.13</v>
+      </c>
+      <c r="AZ107" s="6" t="n">
         <v>-2182.01</v>
       </c>
-      <c r="AY107" s="24" t="n"/>
-      <c r="AZ107" s="24" t="n">
-        <v>0.9058</v>
-      </c>
-      <c r="BA107" s="5" t="n">
-        <v>38.13</v>
-      </c>
-      <c r="BB107" s="5" t="n">
+      <c r="BA107" s="38" t="n"/>
+      <c r="BB107" s="38" t="n"/>
+      <c r="BC107" s="24" t="n"/>
+      <c r="BD107" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="BC107" s="5" t="n">
+      <c r="BE107" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="BD107" s="5" t="n">
+      <c r="BF107" s="5" t="n">
         <v>1.865</v>
       </c>
-      <c r="BE107" s="5" t="n">
+      <c r="BG107" s="5" t="n">
         <v>27915</v>
       </c>
     </row>
@@ -10992,16 +11281,18 @@
       <c r="AW108" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AX108" s="6" t="n">
+      <c r="AX108" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" s="5" t="n">
+        <v>-435.44</v>
+      </c>
+      <c r="AZ108" s="6" t="n">
         <v>-5834.21</v>
       </c>
-      <c r="AY108" s="24" t="n"/>
-      <c r="AZ108" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA108" s="5" t="n">
-        <v>-435.44</v>
-      </c>
+      <c r="BA108" s="38" t="n"/>
+      <c r="BB108" s="38" t="n"/>
+      <c r="BC108" s="24" t="n"/>
     </row>
     <row r="109" ht="21" customHeight="1" s="30">
       <c r="A109" s="3" t="n">
@@ -11151,26 +11442,28 @@
       <c r="AW109" s="6" t="n">
         <v>109155.31</v>
       </c>
-      <c r="AX109" s="6" t="n">
+      <c r="AX109" s="24" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="AY109" s="5" t="n">
+        <v>431.25</v>
+      </c>
+      <c r="AZ109" s="6" t="n">
         <v>47098.14</v>
       </c>
-      <c r="AY109" s="24" t="n"/>
-      <c r="AZ109" s="24" t="n">
-        <v>0.8566</v>
-      </c>
-      <c r="BA109" s="5" t="n">
-        <v>431.25</v>
-      </c>
-      <c r="BB109" s="5" t="n">
+      <c r="BA109" s="38" t="n"/>
+      <c r="BB109" s="38" t="n"/>
+      <c r="BC109" s="24" t="n"/>
+      <c r="BD109" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="BC109" s="5" t="n">
+      <c r="BE109" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="BD109" s="5" t="n">
+      <c r="BF109" s="5" t="n">
         <v>1.8578</v>
       </c>
-      <c r="BE109" s="5" t="n">
+      <c r="BG109" s="5" t="n">
         <v>18054</v>
       </c>
     </row>
@@ -11322,26 +11615,28 @@
       <c r="AW110" s="6" t="n">
         <v>79473.05</v>
       </c>
-      <c r="AX110" s="6" t="n">
+      <c r="AX110" s="24" t="n">
+        <v>0.8663999999999999</v>
+      </c>
+      <c r="AY110" s="5" t="n">
+        <v>446.93</v>
+      </c>
+      <c r="AZ110" s="6" t="n">
         <v>80377.82000000001</v>
       </c>
-      <c r="AY110" s="24" t="n"/>
-      <c r="AZ110" s="24" t="n">
-        <v>0.8663999999999999</v>
-      </c>
-      <c r="BA110" s="5" t="n">
-        <v>446.93</v>
-      </c>
-      <c r="BB110" s="5" t="n">
+      <c r="BA110" s="38" t="n"/>
+      <c r="BB110" s="38" t="n"/>
+      <c r="BC110" s="24" t="n"/>
+      <c r="BD110" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="BC110" s="5" t="n">
+      <c r="BE110" s="5" t="n">
         <v>11.25</v>
       </c>
-      <c r="BD110" s="5" t="n">
+      <c r="BF110" s="5" t="n">
         <v>1.8483</v>
       </c>
-      <c r="BE110" s="5" t="n">
+      <c r="BG110" s="5" t="n">
         <v>20764</v>
       </c>
     </row>
@@ -11493,20 +11788,22 @@
       <c r="AW111" s="6" t="n">
         <v>71547.52</v>
       </c>
-      <c r="AX111" s="6" t="n">
+      <c r="AX111" s="24" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AY111" s="5" t="n">
+        <v>489.77</v>
+      </c>
+      <c r="AZ111" s="6" t="n">
         <v>65712.92</v>
       </c>
-      <c r="AY111" s="24" t="n"/>
-      <c r="AZ111" s="24" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="BA111" s="5" t="n">
-        <v>489.77</v>
-      </c>
-      <c r="BB111" s="5" t="n"/>
-      <c r="BC111" s="5" t="n"/>
+      <c r="BA111" s="38" t="n"/>
+      <c r="BB111" s="38" t="n"/>
+      <c r="BC111" s="24" t="n"/>
       <c r="BD111" s="5" t="n"/>
       <c r="BE111" s="5" t="n"/>
+      <c r="BF111" s="5" t="n"/>
+      <c r="BG111" s="5" t="n"/>
     </row>
     <row r="112" ht="21" customHeight="1" s="30">
       <c r="A112" s="3" t="n">
@@ -11656,20 +11953,22 @@
       <c r="AW112" s="6" t="n">
         <v>82857.17</v>
       </c>
-      <c r="AX112" s="6" t="n">
+      <c r="AX112" s="24" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="AY112" s="5" t="n">
+        <v>225.72</v>
+      </c>
+      <c r="AZ112" s="6" t="n">
         <v>19920.51</v>
       </c>
-      <c r="AY112" s="24" t="n"/>
-      <c r="AZ112" s="24" t="n">
-        <v>0.8899</v>
-      </c>
-      <c r="BA112" s="5" t="n">
-        <v>225.72</v>
-      </c>
-      <c r="BB112" s="5" t="n"/>
-      <c r="BC112" s="5" t="n"/>
+      <c r="BA112" s="38" t="n"/>
+      <c r="BB112" s="38" t="n"/>
+      <c r="BC112" s="24" t="n"/>
       <c r="BD112" s="5" t="n"/>
       <c r="BE112" s="5" t="n"/>
+      <c r="BF112" s="5" t="n"/>
+      <c r="BG112" s="5" t="n"/>
     </row>
     <row r="113" ht="21" customHeight="1" s="30">
       <c r="A113" s="3" t="n">
@@ -11819,20 +12118,22 @@
       <c r="AW113" s="6" t="n">
         <v>81330.8</v>
       </c>
-      <c r="AX113" s="6" t="n">
+      <c r="AX113" s="24" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AY113" s="5" t="n">
+        <v>577.15</v>
+      </c>
+      <c r="AZ113" s="6" t="n">
         <v>83637.85000000001</v>
       </c>
-      <c r="AY113" s="24" t="n"/>
-      <c r="AZ113" s="24" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BA113" s="5" t="n">
-        <v>577.15</v>
-      </c>
-      <c r="BB113" s="5" t="n"/>
-      <c r="BC113" s="5" t="n"/>
+      <c r="BA113" s="38" t="n"/>
+      <c r="BB113" s="38" t="n"/>
+      <c r="BC113" s="24" t="n"/>
       <c r="BD113" s="5" t="n"/>
       <c r="BE113" s="5" t="n"/>
+      <c r="BF113" s="5" t="n"/>
+      <c r="BG113" s="5" t="n"/>
     </row>
     <row r="114" ht="21" customHeight="1" s="30">
       <c r="A114" s="3" t="n">
@@ -11982,20 +12283,22 @@
       <c r="AW114" s="6" t="n">
         <v>54697.29</v>
       </c>
-      <c r="AX114" s="6" t="n">
+      <c r="AX114" s="24" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="AY114" s="5" t="n">
+        <v>404.31</v>
+      </c>
+      <c r="AZ114" s="6" t="n">
         <v>54382.48</v>
       </c>
-      <c r="AY114" s="24" t="n"/>
-      <c r="AZ114" s="24" t="n">
-        <v>0.854</v>
-      </c>
-      <c r="BA114" s="5" t="n">
-        <v>404.31</v>
-      </c>
-      <c r="BB114" s="5" t="n"/>
-      <c r="BC114" s="5" t="n"/>
+      <c r="BA114" s="38" t="n"/>
+      <c r="BB114" s="38" t="n"/>
+      <c r="BC114" s="24" t="n"/>
       <c r="BD114" s="5" t="n"/>
       <c r="BE114" s="5" t="n"/>
+      <c r="BF114" s="5" t="n"/>
+      <c r="BG114" s="5" t="n"/>
     </row>
     <row r="115" ht="21" customHeight="1" s="30">
       <c r="A115" s="3" t="n">
@@ -12145,26 +12448,28 @@
       <c r="AW115" s="6" t="n">
         <v>56638.72</v>
       </c>
-      <c r="AX115" s="6" t="n">
+      <c r="AX115" s="24" t="n">
+        <v>0.8764999999999999</v>
+      </c>
+      <c r="AY115" s="5" t="n">
+        <v>315.23</v>
+      </c>
+      <c r="AZ115" s="6" t="n">
         <v>44733.27</v>
       </c>
-      <c r="AY115" s="24" t="n"/>
-      <c r="AZ115" s="24" t="n">
-        <v>0.8764999999999999</v>
-      </c>
-      <c r="BA115" s="5" t="n">
-        <v>315.23</v>
-      </c>
-      <c r="BB115" s="5" t="n">
+      <c r="BA115" s="38" t="n"/>
+      <c r="BB115" s="38" t="n"/>
+      <c r="BC115" s="24" t="n"/>
+      <c r="BD115" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="BC115" s="5" t="n">
+      <c r="BE115" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="BD115" s="5" t="n">
+      <c r="BF115" s="5" t="n">
         <v>1.8697</v>
       </c>
-      <c r="BE115" s="5" t="n">
+      <c r="BG115" s="5" t="n">
         <v>19032</v>
       </c>
     </row>
@@ -12316,26 +12621,28 @@
       <c r="AW116" s="6" t="n">
         <v>53649.92</v>
       </c>
-      <c r="AX116" s="6" t="n">
+      <c r="AX116" s="24" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="AY116" s="5" t="n">
+        <v>255.15</v>
+      </c>
+      <c r="AZ116" s="6" t="n">
         <v>46144.11</v>
       </c>
-      <c r="AY116" s="24" t="n"/>
-      <c r="AZ116" s="24" t="n">
-        <v>0.8522</v>
-      </c>
-      <c r="BA116" s="5" t="n">
-        <v>255.15</v>
-      </c>
-      <c r="BB116" s="5" t="n">
+      <c r="BA116" s="38" t="n"/>
+      <c r="BB116" s="38" t="n"/>
+      <c r="BC116" s="24" t="n"/>
+      <c r="BD116" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="BC116" s="5" t="n">
+      <c r="BE116" s="5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BD116" s="5" t="n">
+      <c r="BF116" s="5" t="n">
         <v>1.8451</v>
       </c>
-      <c r="BE116" s="5" t="n">
+      <c r="BG116" s="5" t="n">
         <v>22277</v>
       </c>
     </row>
@@ -12487,20 +12794,22 @@
       <c r="AW117" s="6" t="n">
         <v>83318.7</v>
       </c>
-      <c r="AX117" s="6" t="n">
+      <c r="AX117" s="24" t="n">
+        <v>0.8583</v>
+      </c>
+      <c r="AY117" s="5" t="n">
+        <v>594.1900000000001</v>
+      </c>
+      <c r="AZ117" s="6" t="n">
         <v>85065.99000000001</v>
       </c>
-      <c r="AY117" s="24" t="n"/>
-      <c r="AZ117" s="24" t="n">
-        <v>0.8583</v>
-      </c>
-      <c r="BA117" s="5" t="n">
-        <v>594.1900000000001</v>
-      </c>
-      <c r="BB117" s="5" t="n"/>
-      <c r="BC117" s="5" t="n"/>
+      <c r="BA117" s="38" t="n"/>
+      <c r="BB117" s="38" t="n"/>
+      <c r="BC117" s="24" t="n"/>
       <c r="BD117" s="5" t="n"/>
       <c r="BE117" s="5" t="n"/>
+      <c r="BF117" s="5" t="n"/>
+      <c r="BG117" s="5" t="n"/>
     </row>
     <row r="118" ht="21" customHeight="1" s="30">
       <c r="A118" s="3" t="n">
@@ -12650,20 +12959,22 @@
       <c r="AW118" s="6" t="n">
         <v>56071.98</v>
       </c>
-      <c r="AX118" s="6" t="n">
+      <c r="AX118" s="24" t="n">
+        <v>0.8391999999999999</v>
+      </c>
+      <c r="AY118" s="5" t="n">
+        <v>-29.25</v>
+      </c>
+      <c r="AZ118" s="6" t="n">
         <v>-28111.24</v>
       </c>
-      <c r="AY118" s="24" t="n"/>
-      <c r="AZ118" s="24" t="n">
-        <v>0.8391999999999999</v>
-      </c>
-      <c r="BA118" s="5" t="n">
-        <v>-29.25</v>
-      </c>
-      <c r="BB118" s="5" t="n"/>
-      <c r="BC118" s="5" t="n"/>
+      <c r="BA118" s="38" t="n"/>
+      <c r="BB118" s="38" t="n"/>
+      <c r="BC118" s="24" t="n"/>
       <c r="BD118" s="5" t="n"/>
       <c r="BE118" s="5" t="n"/>
+      <c r="BF118" s="5" t="n"/>
+      <c r="BG118" s="5" t="n"/>
     </row>
     <row r="119" ht="21" customHeight="1" s="30">
       <c r="A119" s="3" t="n">
@@ -12813,20 +13124,22 @@
       <c r="AW119" s="6" t="n">
         <v>78042.81</v>
       </c>
-      <c r="AX119" s="6" t="n">
+      <c r="AX119" s="24" t="n">
+        <v>0.8213</v>
+      </c>
+      <c r="AY119" s="5" t="n">
+        <v>629.13</v>
+      </c>
+      <c r="AZ119" s="6" t="n">
         <v>80411.91</v>
       </c>
-      <c r="AY119" s="24" t="n"/>
-      <c r="AZ119" s="24" t="n">
-        <v>0.8213</v>
-      </c>
-      <c r="BA119" s="5" t="n">
-        <v>629.13</v>
-      </c>
-      <c r="BB119" s="5" t="n"/>
-      <c r="BC119" s="5" t="n"/>
+      <c r="BA119" s="38" t="n"/>
+      <c r="BB119" s="38" t="n"/>
+      <c r="BC119" s="24" t="n"/>
       <c r="BD119" s="5" t="n"/>
       <c r="BE119" s="5" t="n"/>
+      <c r="BF119" s="5" t="n"/>
+      <c r="BG119" s="5" t="n"/>
     </row>
     <row r="120" ht="21" customHeight="1" s="30">
       <c r="A120" s="3" t="n">
@@ -12976,20 +13289,22 @@
       <c r="AW120" s="6" t="n">
         <v>91280.07000000001</v>
       </c>
-      <c r="AX120" s="6" t="n">
+      <c r="AX120" s="24" t="n">
+        <v>0.8733</v>
+      </c>
+      <c r="AY120" s="5" t="n">
+        <v>514.4</v>
+      </c>
+      <c r="AZ120" s="6" t="n">
         <v>69914.77</v>
       </c>
-      <c r="AY120" s="24" t="n"/>
-      <c r="AZ120" s="24" t="n">
-        <v>0.8733</v>
-      </c>
-      <c r="BA120" s="5" t="n">
-        <v>514.4</v>
-      </c>
-      <c r="BB120" s="5" t="n"/>
-      <c r="BC120" s="5" t="n"/>
+      <c r="BA120" s="38" t="n"/>
+      <c r="BB120" s="38" t="n"/>
+      <c r="BC120" s="24" t="n"/>
       <c r="BD120" s="5" t="n"/>
       <c r="BE120" s="5" t="n"/>
+      <c r="BF120" s="5" t="n"/>
+      <c r="BG120" s="5" t="n"/>
     </row>
     <row r="121" ht="21" customHeight="1" s="30">
       <c r="A121" s="3" t="n">
@@ -13139,20 +13454,22 @@
       <c r="AW121" s="6" t="n">
         <v>87119.88</v>
       </c>
-      <c r="AX121" s="6" t="n">
+      <c r="AX121" s="24" t="n">
+        <v>0.8763</v>
+      </c>
+      <c r="AY121" s="5" t="n">
+        <v>635.14</v>
+      </c>
+      <c r="AZ121" s="6" t="n">
         <v>89078.42999999999</v>
       </c>
-      <c r="AY121" s="24" t="n"/>
-      <c r="AZ121" s="24" t="n">
-        <v>0.8763</v>
-      </c>
-      <c r="BA121" s="5" t="n">
-        <v>635.14</v>
-      </c>
-      <c r="BB121" s="5" t="n"/>
-      <c r="BC121" s="5" t="n"/>
+      <c r="BA121" s="38" t="n"/>
+      <c r="BB121" s="38" t="n"/>
+      <c r="BC121" s="24" t="n"/>
       <c r="BD121" s="5" t="n"/>
       <c r="BE121" s="5" t="n"/>
+      <c r="BF121" s="5" t="n"/>
+      <c r="BG121" s="5" t="n"/>
     </row>
     <row r="122" ht="21" customHeight="1" s="30">
       <c r="A122" s="3" t="n">
@@ -13302,26 +13619,28 @@
       <c r="AW122" s="6" t="n">
         <v>63419.57</v>
       </c>
-      <c r="AX122" s="6" t="n">
+      <c r="AX122" s="24" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="AY122" s="5" t="n">
+        <v>-115.47</v>
+      </c>
+      <c r="AZ122" s="6" t="n">
         <v>144.13</v>
       </c>
-      <c r="AY122" s="24" t="n"/>
-      <c r="AZ122" s="24" t="n">
-        <v>0.9713000000000001</v>
-      </c>
-      <c r="BA122" s="5" t="n">
-        <v>-115.47</v>
-      </c>
-      <c r="BB122" s="5" t="n">
+      <c r="BA122" s="38" t="n"/>
+      <c r="BB122" s="38" t="n"/>
+      <c r="BC122" s="24" t="n"/>
+      <c r="BD122" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="BC122" s="5" t="n">
+      <c r="BE122" s="5" t="n">
         <v>9.27</v>
       </c>
-      <c r="BD122" s="5" t="n">
+      <c r="BF122" s="5" t="n">
         <v>1.8435</v>
       </c>
-      <c r="BE122" s="5" t="n">
+      <c r="BG122" s="5" t="n">
         <v>28887</v>
       </c>
     </row>
@@ -13473,20 +13792,22 @@
       <c r="AW123" s="6" t="n">
         <v>69356.96000000001</v>
       </c>
-      <c r="AX123" s="6" t="n">
+      <c r="AX123" s="24" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="AY123" s="5" t="n">
+        <v>479.08</v>
+      </c>
+      <c r="AZ123" s="6" t="n">
         <v>66133.10000000001</v>
       </c>
-      <c r="AY123" s="24" t="n"/>
-      <c r="AZ123" s="24" t="n">
-        <v>0.7669</v>
-      </c>
-      <c r="BA123" s="5" t="n">
-        <v>479.08</v>
-      </c>
-      <c r="BB123" s="5" t="n"/>
-      <c r="BC123" s="5" t="n"/>
+      <c r="BA123" s="38" t="n"/>
+      <c r="BB123" s="38" t="n"/>
+      <c r="BC123" s="24" t="n"/>
       <c r="BD123" s="5" t="n"/>
       <c r="BE123" s="5" t="n"/>
+      <c r="BF123" s="5" t="n"/>
+      <c r="BG123" s="5" t="n"/>
     </row>
     <row r="124" ht="21" customHeight="1" s="30">
       <c r="A124" s="3" t="n">
@@ -13636,20 +13957,22 @@
       <c r="AW124" s="6" t="n">
         <v>57658.75</v>
       </c>
-      <c r="AX124" s="6" t="n">
+      <c r="AX124" s="24" t="n">
+        <v>0.8819</v>
+      </c>
+      <c r="AY124" s="5" t="n">
+        <v>440.05</v>
+      </c>
+      <c r="AZ124" s="6" t="n">
         <v>59595.65</v>
       </c>
-      <c r="AY124" s="24" t="n"/>
-      <c r="AZ124" s="24" t="n">
-        <v>0.8819</v>
-      </c>
-      <c r="BA124" s="5" t="n">
-        <v>440.05</v>
-      </c>
-      <c r="BB124" s="5" t="n"/>
-      <c r="BC124" s="5" t="n"/>
+      <c r="BA124" s="38" t="n"/>
+      <c r="BB124" s="38" t="n"/>
+      <c r="BC124" s="24" t="n"/>
       <c r="BD124" s="5" t="n"/>
       <c r="BE124" s="5" t="n"/>
+      <c r="BF124" s="5" t="n"/>
+      <c r="BG124" s="5" t="n"/>
     </row>
     <row r="125" ht="21" customHeight="1" s="30">
       <c r="A125" s="3" t="n">
@@ -13799,20 +14122,22 @@
       <c r="AW125" s="6" t="n">
         <v>55316.08</v>
       </c>
-      <c r="AX125" s="6" t="n">
+      <c r="AX125" s="24" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="AY125" s="5" t="n">
+        <v>409.7</v>
+      </c>
+      <c r="AZ125" s="6" t="n">
         <v>55739.26</v>
       </c>
-      <c r="AY125" s="24" t="n"/>
-      <c r="AZ125" s="24" t="n">
-        <v>0.8555</v>
-      </c>
-      <c r="BA125" s="5" t="n">
-        <v>409.7</v>
-      </c>
-      <c r="BB125" s="5" t="n"/>
-      <c r="BC125" s="5" t="n"/>
+      <c r="BA125" s="38" t="n"/>
+      <c r="BB125" s="38" t="n"/>
+      <c r="BC125" s="24" t="n"/>
       <c r="BD125" s="5" t="n"/>
       <c r="BE125" s="5" t="n"/>
+      <c r="BF125" s="5" t="n"/>
+      <c r="BG125" s="5" t="n"/>
     </row>
     <row r="126" ht="21" customHeight="1" s="30">
       <c r="A126" s="3" t="n">
@@ -13962,20 +14287,22 @@
       <c r="AW126" s="6" t="n">
         <v>97260.53999999999</v>
       </c>
-      <c r="AX126" s="6" t="n">
+      <c r="AX126" s="24" t="n">
+        <v>0.8797</v>
+      </c>
+      <c r="AY126" s="5" t="n">
+        <v>297.67</v>
+      </c>
+      <c r="AZ126" s="6" t="n">
         <v>32386.38</v>
       </c>
-      <c r="AY126" s="24" t="n"/>
-      <c r="AZ126" s="24" t="n">
-        <v>0.8797</v>
-      </c>
-      <c r="BA126" s="5" t="n">
-        <v>297.67</v>
-      </c>
-      <c r="BB126" s="5" t="n"/>
-      <c r="BC126" s="5" t="n"/>
+      <c r="BA126" s="38" t="n"/>
+      <c r="BB126" s="38" t="n"/>
+      <c r="BC126" s="24" t="n"/>
       <c r="BD126" s="5" t="n"/>
       <c r="BE126" s="5" t="n"/>
+      <c r="BF126" s="5" t="n"/>
+      <c r="BG126" s="5" t="n"/>
     </row>
     <row r="127" ht="21" customHeight="1" s="30">
       <c r="A127" s="3" t="n">
@@ -14125,20 +14452,22 @@
       <c r="AW127" s="6" t="n">
         <v>82263.61</v>
       </c>
-      <c r="AX127" s="6" t="n">
+      <c r="AX127" s="24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AY127" s="5" t="n">
+        <v>450.07</v>
+      </c>
+      <c r="AZ127" s="6" t="n">
         <v>59978.39</v>
       </c>
-      <c r="AY127" s="24" t="n"/>
-      <c r="AZ127" s="24" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BA127" s="5" t="n">
-        <v>450.07</v>
-      </c>
-      <c r="BB127" s="5" t="n"/>
-      <c r="BC127" s="5" t="n"/>
+      <c r="BA127" s="38" t="n"/>
+      <c r="BB127" s="38" t="n"/>
+      <c r="BC127" s="24" t="n"/>
       <c r="BD127" s="5" t="n"/>
       <c r="BE127" s="5" t="n"/>
+      <c r="BF127" s="5" t="n"/>
+      <c r="BG127" s="5" t="n"/>
     </row>
     <row r="128" ht="21" customHeight="1" s="30">
       <c r="A128" s="3" t="n">
@@ -14288,20 +14617,22 @@
       <c r="AW128" s="6" t="n">
         <v>80056.58</v>
       </c>
-      <c r="AX128" s="6" t="n">
+      <c r="AX128" s="24" t="n">
+        <v>0.8725000000000001</v>
+      </c>
+      <c r="AY128" s="5" t="n">
+        <v>535.12</v>
+      </c>
+      <c r="AZ128" s="6" t="n">
         <v>78980.7</v>
       </c>
-      <c r="AY128" s="24" t="n"/>
-      <c r="AZ128" s="24" t="n">
-        <v>0.8725000000000001</v>
-      </c>
-      <c r="BA128" s="5" t="n">
-        <v>535.12</v>
-      </c>
-      <c r="BB128" s="5" t="n"/>
-      <c r="BC128" s="5" t="n"/>
+      <c r="BA128" s="38" t="n"/>
+      <c r="BB128" s="38" t="n"/>
+      <c r="BC128" s="24" t="n"/>
       <c r="BD128" s="5" t="n"/>
       <c r="BE128" s="5" t="n"/>
+      <c r="BF128" s="5" t="n"/>
+      <c r="BG128" s="5" t="n"/>
     </row>
     <row r="129" ht="21" customHeight="1" s="30">
       <c r="A129" s="3" t="n">
@@ -14451,20 +14782,22 @@
       <c r="AW129" s="6" t="n">
         <v>59901.4</v>
       </c>
-      <c r="AX129" s="6" t="n">
+      <c r="AX129" s="24" t="n">
+        <v>0.8583</v>
+      </c>
+      <c r="AY129" s="5" t="n">
+        <v>429.75</v>
+      </c>
+      <c r="AZ129" s="6" t="n">
         <v>61123.3</v>
       </c>
-      <c r="AY129" s="24" t="n"/>
-      <c r="AZ129" s="24" t="n">
-        <v>0.8583</v>
-      </c>
-      <c r="BA129" s="5" t="n">
-        <v>429.75</v>
-      </c>
-      <c r="BB129" s="5" t="n"/>
-      <c r="BC129" s="5" t="n"/>
+      <c r="BA129" s="38" t="n"/>
+      <c r="BB129" s="38" t="n"/>
+      <c r="BC129" s="24" t="n"/>
       <c r="BD129" s="5" t="n"/>
       <c r="BE129" s="5" t="n"/>
+      <c r="BF129" s="5" t="n"/>
+      <c r="BG129" s="5" t="n"/>
     </row>
     <row r="130" ht="21" customHeight="1" s="30">
       <c r="A130" s="3" t="n">
@@ -14614,20 +14947,22 @@
       <c r="AW130" s="6" t="n">
         <v>77945.41</v>
       </c>
-      <c r="AX130" s="6" t="n">
+      <c r="AX130" s="24" t="n">
+        <v>0.8488</v>
+      </c>
+      <c r="AY130" s="5" t="n">
+        <v>541.87</v>
+      </c>
+      <c r="AZ130" s="6" t="n">
         <v>78530.28</v>
       </c>
-      <c r="AY130" s="24" t="n"/>
-      <c r="AZ130" s="24" t="n">
-        <v>0.8488</v>
-      </c>
-      <c r="BA130" s="5" t="n">
-        <v>541.87</v>
-      </c>
-      <c r="BB130" s="5" t="n"/>
-      <c r="BC130" s="5" t="n"/>
+      <c r="BA130" s="38" t="n"/>
+      <c r="BB130" s="38" t="n"/>
+      <c r="BC130" s="24" t="n"/>
       <c r="BD130" s="5" t="n"/>
       <c r="BE130" s="5" t="n"/>
+      <c r="BF130" s="5" t="n"/>
+      <c r="BG130" s="5" t="n"/>
     </row>
     <row r="131" ht="21" customHeight="1" s="30">
       <c r="A131" s="3" t="n">
@@ -14777,20 +15112,22 @@
       <c r="AW131" s="6" t="n">
         <v>90881.82000000001</v>
       </c>
-      <c r="AX131" s="6" t="n">
+      <c r="AX131" s="24" t="n">
+        <v>0.8826000000000001</v>
+      </c>
+      <c r="AY131" s="5" t="n">
+        <v>600.87</v>
+      </c>
+      <c r="AZ131" s="6" t="n">
         <v>93351.86</v>
       </c>
-      <c r="AY131" s="24" t="n"/>
-      <c r="AZ131" s="24" t="n">
-        <v>0.8826000000000001</v>
-      </c>
-      <c r="BA131" s="5" t="n">
-        <v>600.87</v>
-      </c>
-      <c r="BB131" s="5" t="n"/>
-      <c r="BC131" s="5" t="n"/>
+      <c r="BA131" s="38" t="n"/>
+      <c r="BB131" s="38" t="n"/>
+      <c r="BC131" s="24" t="n"/>
       <c r="BD131" s="5" t="n"/>
       <c r="BE131" s="5" t="n"/>
+      <c r="BF131" s="5" t="n"/>
+      <c r="BG131" s="5" t="n"/>
     </row>
     <row r="132" ht="21" customHeight="1" s="30">
       <c r="A132" s="3" t="n">
@@ -14940,20 +15277,22 @@
       <c r="AW132" s="6" t="n">
         <v>73007.74000000001</v>
       </c>
-      <c r="AX132" s="6" t="n">
+      <c r="AX132" s="24" t="n">
+        <v>0.8472</v>
+      </c>
+      <c r="AY132" s="5" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="AZ132" s="6" t="n">
         <v>39519.29</v>
       </c>
-      <c r="AY132" s="24" t="n"/>
-      <c r="AZ132" s="24" t="n">
-        <v>0.8472</v>
-      </c>
-      <c r="BA132" s="5" t="n">
-        <v>336.4</v>
-      </c>
-      <c r="BB132" s="5" t="n"/>
-      <c r="BC132" s="5" t="n"/>
+      <c r="BA132" s="38" t="n"/>
+      <c r="BB132" s="38" t="n"/>
+      <c r="BC132" s="24" t="n"/>
       <c r="BD132" s="5" t="n"/>
       <c r="BE132" s="5" t="n"/>
+      <c r="BF132" s="5" t="n"/>
+      <c r="BG132" s="5" t="n"/>
     </row>
     <row r="133" ht="21" customHeight="1" s="30">
       <c r="A133" s="3" t="n">
@@ -15103,20 +15442,22 @@
       <c r="AW133" s="6" t="n">
         <v>103031.85</v>
       </c>
-      <c r="AX133" s="6" t="n">
+      <c r="AX133" s="24" t="n">
+        <v>0.8658</v>
+      </c>
+      <c r="AY133" s="5" t="n">
+        <v>529.5</v>
+      </c>
+      <c r="AZ133" s="6" t="n">
         <v>74153.89</v>
       </c>
-      <c r="AY133" s="24" t="n"/>
-      <c r="AZ133" s="24" t="n">
-        <v>0.8658</v>
-      </c>
-      <c r="BA133" s="5" t="n">
-        <v>529.5</v>
-      </c>
-      <c r="BB133" s="5" t="n"/>
-      <c r="BC133" s="5" t="n"/>
+      <c r="BA133" s="38" t="n"/>
+      <c r="BB133" s="38" t="n"/>
+      <c r="BC133" s="24" t="n"/>
       <c r="BD133" s="5" t="n"/>
       <c r="BE133" s="5" t="n"/>
+      <c r="BF133" s="5" t="n"/>
+      <c r="BG133" s="5" t="n"/>
     </row>
     <row r="134" ht="21" customHeight="1" s="30">
       <c r="A134" s="3" t="n">
@@ -15266,20 +15607,22 @@
       <c r="AW134" s="6" t="n">
         <v>-525.85</v>
       </c>
-      <c r="AX134" s="6" t="n">
+      <c r="AX134" s="24" t="n">
+        <v>0.5508999999999999</v>
+      </c>
+      <c r="AY134" s="5" t="n">
+        <v>-393.06</v>
+      </c>
+      <c r="AZ134" s="6" t="n">
         <v>-9252.15</v>
       </c>
-      <c r="AY134" s="24" t="n"/>
-      <c r="AZ134" s="24" t="n">
-        <v>0.5508999999999999</v>
-      </c>
-      <c r="BA134" s="5" t="n">
-        <v>-393.06</v>
-      </c>
-      <c r="BB134" s="5" t="n"/>
-      <c r="BC134" s="5" t="n"/>
+      <c r="BA134" s="38" t="n"/>
+      <c r="BB134" s="38" t="n"/>
+      <c r="BC134" s="24" t="n"/>
       <c r="BD134" s="5" t="n"/>
-      <c r="BE134" s="5" t="n">
+      <c r="BE134" s="5" t="n"/>
+      <c r="BF134" s="5" t="n"/>
+      <c r="BG134" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15431,20 +15774,22 @@
       <c r="AW135" s="6" t="n">
         <v>51396.42</v>
       </c>
-      <c r="AX135" s="6" t="n">
+      <c r="AX135" s="24" t="n">
+        <v>0.8471</v>
+      </c>
+      <c r="AY135" s="5" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="AZ135" s="6" t="n">
         <v>1996.15</v>
       </c>
-      <c r="AY135" s="24" t="n"/>
-      <c r="AZ135" s="24" t="n">
-        <v>0.8471</v>
-      </c>
-      <c r="BA135" s="5" t="n">
-        <v>119.35</v>
-      </c>
-      <c r="BB135" s="5" t="n"/>
-      <c r="BC135" s="5" t="n"/>
+      <c r="BA135" s="38" t="n"/>
+      <c r="BB135" s="38" t="n"/>
+      <c r="BC135" s="24" t="n"/>
       <c r="BD135" s="5" t="n"/>
       <c r="BE135" s="5" t="n"/>
+      <c r="BF135" s="5" t="n"/>
+      <c r="BG135" s="5" t="n"/>
     </row>
     <row r="136" ht="21" customHeight="1" s="30">
       <c r="A136" s="3" t="n">
@@ -15594,20 +15939,22 @@
       <c r="AW136" s="6" t="n">
         <v>84086.27</v>
       </c>
-      <c r="AX136" s="6" t="n">
+      <c r="AX136" s="24" t="n">
+        <v>0.8595</v>
+      </c>
+      <c r="AY136" s="5" t="n">
+        <v>585.8</v>
+      </c>
+      <c r="AZ136" s="6" t="n">
         <v>85636.64999999999</v>
       </c>
-      <c r="AY136" s="24" t="n"/>
-      <c r="AZ136" s="24" t="n">
-        <v>0.8595</v>
-      </c>
-      <c r="BA136" s="5" t="n">
-        <v>585.8</v>
-      </c>
-      <c r="BB136" s="5" t="n"/>
-      <c r="BC136" s="5" t="n"/>
+      <c r="BA136" s="38" t="n"/>
+      <c r="BB136" s="38" t="n"/>
+      <c r="BC136" s="24" t="n"/>
       <c r="BD136" s="5" t="n"/>
       <c r="BE136" s="5" t="n"/>
+      <c r="BF136" s="5" t="n"/>
+      <c r="BG136" s="5" t="n"/>
     </row>
     <row r="137" ht="21" customHeight="1" s="30">
       <c r="A137" s="3" t="n">
@@ -15757,20 +16104,22 @@
       <c r="AW137" s="6" t="n">
         <v>79790.22</v>
       </c>
-      <c r="AX137" s="6" t="n">
+      <c r="AX137" s="24" t="n">
+        <v>0.8438</v>
+      </c>
+      <c r="AY137" s="5" t="n">
+        <v>545.7</v>
+      </c>
+      <c r="AZ137" s="6" t="n">
         <v>78467.88</v>
       </c>
-      <c r="AY137" s="24" t="n"/>
-      <c r="AZ137" s="24" t="n">
-        <v>0.8438</v>
-      </c>
-      <c r="BA137" s="5" t="n">
-        <v>545.7</v>
-      </c>
-      <c r="BB137" s="5" t="n"/>
-      <c r="BC137" s="5" t="n"/>
+      <c r="BA137" s="38" t="n"/>
+      <c r="BB137" s="38" t="n"/>
+      <c r="BC137" s="24" t="n"/>
       <c r="BD137" s="5" t="n"/>
       <c r="BE137" s="5" t="n"/>
+      <c r="BF137" s="5" t="n"/>
+      <c r="BG137" s="5" t="n"/>
     </row>
     <row r="138" ht="21" customHeight="1" s="30">
       <c r="A138" s="3" t="n">
@@ -15920,20 +16269,22 @@
       <c r="AW138" s="6" t="n">
         <v>108207.65</v>
       </c>
-      <c r="AX138" s="6" t="n">
+      <c r="AX138" s="24" t="n">
+        <v>0.8508</v>
+      </c>
+      <c r="AY138" s="5" t="n">
+        <v>720.49</v>
+      </c>
+      <c r="AZ138" s="6" t="n">
         <v>107559.77</v>
       </c>
-      <c r="AY138" s="24" t="n"/>
-      <c r="AZ138" s="24" t="n">
-        <v>0.8508</v>
-      </c>
-      <c r="BA138" s="5" t="n">
-        <v>720.49</v>
-      </c>
-      <c r="BB138" s="5" t="n"/>
-      <c r="BC138" s="5" t="n"/>
+      <c r="BA138" s="38" t="n"/>
+      <c r="BB138" s="38" t="n"/>
+      <c r="BC138" s="24" t="n"/>
       <c r="BD138" s="5" t="n"/>
       <c r="BE138" s="5" t="n"/>
+      <c r="BF138" s="5" t="n"/>
+      <c r="BG138" s="5" t="n"/>
     </row>
     <row r="139" ht="21" customHeight="1" s="30">
       <c r="A139" s="3" t="n">
@@ -16083,20 +16434,22 @@
       <c r="AW139" s="6" t="n">
         <v>56739.61</v>
       </c>
-      <c r="AX139" s="6" t="n">
+      <c r="AX139" s="24" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="AY139" s="5" t="n">
+        <v>406.78</v>
+      </c>
+      <c r="AZ139" s="6" t="n">
         <v>57604.81</v>
       </c>
-      <c r="AY139" s="24" t="n"/>
-      <c r="AZ139" s="24" t="n">
-        <v>0.8774</v>
-      </c>
-      <c r="BA139" s="5" t="n">
-        <v>406.78</v>
-      </c>
-      <c r="BB139" s="5" t="n"/>
-      <c r="BC139" s="5" t="n"/>
+      <c r="BA139" s="38" t="n"/>
+      <c r="BB139" s="38" t="n"/>
+      <c r="BC139" s="24" t="n"/>
       <c r="BD139" s="5" t="n"/>
       <c r="BE139" s="5" t="n"/>
+      <c r="BF139" s="5" t="n"/>
+      <c r="BG139" s="5" t="n"/>
     </row>
     <row r="140" ht="21" customHeight="1" s="30">
       <c r="A140" s="3" t="n">
@@ -16246,20 +16599,22 @@
       <c r="AW140" s="6" t="n">
         <v>58391.96</v>
       </c>
-      <c r="AX140" s="6" t="n">
+      <c r="AX140" s="24" t="n">
+        <v>0.8502</v>
+      </c>
+      <c r="AY140" s="5" t="n">
+        <v>415.72</v>
+      </c>
+      <c r="AZ140" s="6" t="n">
         <v>57136.34</v>
       </c>
-      <c r="AY140" s="24" t="n"/>
-      <c r="AZ140" s="24" t="n">
-        <v>0.8502</v>
-      </c>
-      <c r="BA140" s="5" t="n">
-        <v>415.72</v>
-      </c>
-      <c r="BB140" s="5" t="n"/>
-      <c r="BC140" s="5" t="n"/>
+      <c r="BA140" s="38" t="n"/>
+      <c r="BB140" s="38" t="n"/>
+      <c r="BC140" s="24" t="n"/>
       <c r="BD140" s="5" t="n"/>
       <c r="BE140" s="5" t="n"/>
+      <c r="BF140" s="5" t="n"/>
+      <c r="BG140" s="5" t="n"/>
     </row>
     <row r="141" ht="21" customHeight="1" s="30">
       <c r="A141" s="3" t="n">
@@ -16409,20 +16764,22 @@
       <c r="AW141" s="6" t="n">
         <v>59621.91</v>
       </c>
-      <c r="AX141" s="6" t="n">
+      <c r="AX141" s="24" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="AY141" s="5" t="n">
+        <v>431.24</v>
+      </c>
+      <c r="AZ141" s="6" t="n">
         <v>59719.85</v>
       </c>
-      <c r="AY141" s="24" t="n"/>
-      <c r="AZ141" s="24" t="n">
-        <v>0.8608</v>
-      </c>
-      <c r="BA141" s="5" t="n">
-        <v>431.24</v>
-      </c>
-      <c r="BB141" s="5" t="n"/>
-      <c r="BC141" s="5" t="n"/>
+      <c r="BA141" s="38" t="n"/>
+      <c r="BB141" s="38" t="n"/>
+      <c r="BC141" s="24" t="n"/>
       <c r="BD141" s="5" t="n"/>
       <c r="BE141" s="5" t="n"/>
+      <c r="BF141" s="5" t="n"/>
+      <c r="BG141" s="5" t="n"/>
     </row>
     <row r="142" ht="21" customHeight="1" s="30">
       <c r="A142" s="3" t="n">
@@ -16572,20 +16929,22 @@
       <c r="AW142" s="6" t="n">
         <v>55763.39</v>
       </c>
-      <c r="AX142" s="6" t="n">
+      <c r="AX142" s="24" t="n">
+        <v>0.8733</v>
+      </c>
+      <c r="AY142" s="5" t="n">
+        <v>396.43</v>
+      </c>
+      <c r="AZ142" s="6" t="n">
         <v>54687.85</v>
       </c>
-      <c r="AY142" s="24" t="n"/>
-      <c r="AZ142" s="24" t="n">
-        <v>0.8733</v>
-      </c>
-      <c r="BA142" s="5" t="n">
-        <v>396.43</v>
-      </c>
-      <c r="BB142" s="5" t="n"/>
-      <c r="BC142" s="5" t="n"/>
+      <c r="BA142" s="38" t="n"/>
+      <c r="BB142" s="38" t="n"/>
+      <c r="BC142" s="24" t="n"/>
       <c r="BD142" s="5" t="n"/>
       <c r="BE142" s="5" t="n"/>
+      <c r="BF142" s="5" t="n"/>
+      <c r="BG142" s="5" t="n"/>
     </row>
     <row r="143" ht="21" customHeight="1" s="30">
       <c r="A143" s="3" t="n">
@@ -16735,20 +17094,22 @@
       <c r="AW143" s="6" t="n">
         <v>57370.54</v>
       </c>
-      <c r="AX143" s="6" t="n">
+      <c r="AX143" s="24" t="n">
+        <v>0.8614000000000001</v>
+      </c>
+      <c r="AY143" s="5" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="AZ143" s="6" t="n">
         <v>-11079.71</v>
       </c>
-      <c r="AY143" s="24" t="n"/>
-      <c r="AZ143" s="24" t="n">
-        <v>0.8614000000000001</v>
-      </c>
-      <c r="BA143" s="5" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="BB143" s="5" t="n"/>
-      <c r="BC143" s="5" t="n"/>
+      <c r="BA143" s="38" t="n"/>
+      <c r="BB143" s="38" t="n"/>
+      <c r="BC143" s="24" t="n"/>
       <c r="BD143" s="5" t="n"/>
       <c r="BE143" s="5" t="n"/>
+      <c r="BF143" s="5" t="n"/>
+      <c r="BG143" s="5" t="n"/>
     </row>
     <row r="144" ht="21" customHeight="1" s="30">
       <c r="A144" s="3" t="n">
@@ -16898,20 +17259,22 @@
       <c r="AW144" s="6" t="n">
         <v>77624.09</v>
       </c>
-      <c r="AX144" s="6" t="n">
+      <c r="AX144" s="24" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="AY144" s="5" t="n">
+        <v>-63.66</v>
+      </c>
+      <c r="AZ144" s="6" t="n">
         <v>-31844.64</v>
       </c>
-      <c r="AY144" s="24" t="n"/>
-      <c r="AZ144" s="24" t="n">
-        <v>0.8512999999999999</v>
-      </c>
-      <c r="BA144" s="5" t="n">
-        <v>-63.66</v>
-      </c>
-      <c r="BB144" s="5" t="n"/>
-      <c r="BC144" s="5" t="n"/>
+      <c r="BA144" s="38" t="n"/>
+      <c r="BB144" s="38" t="n"/>
+      <c r="BC144" s="24" t="n"/>
       <c r="BD144" s="5" t="n"/>
       <c r="BE144" s="5" t="n"/>
+      <c r="BF144" s="5" t="n"/>
+      <c r="BG144" s="5" t="n"/>
     </row>
     <row r="145" ht="21" customHeight="1" s="30">
       <c r="A145" s="3" t="n">
@@ -17061,20 +17424,22 @@
       <c r="AW145" s="6" t="n">
         <v>74460.47</v>
       </c>
-      <c r="AX145" s="6" t="n">
+      <c r="AX145" s="24" t="n">
+        <v>0.8653</v>
+      </c>
+      <c r="AY145" s="5" t="n">
+        <v>533.23</v>
+      </c>
+      <c r="AZ145" s="6" t="n">
         <v>76422.50999999999</v>
       </c>
-      <c r="AY145" s="24" t="n"/>
-      <c r="AZ145" s="24" t="n">
-        <v>0.8653</v>
-      </c>
-      <c r="BA145" s="5" t="n">
-        <v>533.23</v>
-      </c>
-      <c r="BB145" s="5" t="n"/>
-      <c r="BC145" s="5" t="n"/>
+      <c r="BA145" s="38" t="n"/>
+      <c r="BB145" s="38" t="n"/>
+      <c r="BC145" s="24" t="n"/>
       <c r="BD145" s="5" t="n"/>
       <c r="BE145" s="5" t="n"/>
+      <c r="BF145" s="5" t="n"/>
+      <c r="BG145" s="5" t="n"/>
     </row>
     <row r="146" ht="21" customHeight="1" s="30">
       <c r="A146" s="3" t="n">
@@ -17224,20 +17589,22 @@
       <c r="AW146" s="6" t="n">
         <v>89258.07000000001</v>
       </c>
-      <c r="AX146" s="6" t="n">
+      <c r="AX146" s="24" t="n">
+        <v>0.8491</v>
+      </c>
+      <c r="AY146" s="5" t="n">
+        <v>569.59</v>
+      </c>
+      <c r="AZ146" s="6" t="n">
         <v>78211.05</v>
       </c>
-      <c r="AY146" s="24" t="n"/>
-      <c r="AZ146" s="24" t="n">
-        <v>0.8491</v>
-      </c>
-      <c r="BA146" s="5" t="n">
-        <v>569.59</v>
-      </c>
-      <c r="BB146" s="5" t="n"/>
-      <c r="BC146" s="5" t="n"/>
+      <c r="BA146" s="38" t="n"/>
+      <c r="BB146" s="38" t="n"/>
+      <c r="BC146" s="24" t="n"/>
       <c r="BD146" s="5" t="n"/>
       <c r="BE146" s="5" t="n"/>
+      <c r="BF146" s="5" t="n"/>
+      <c r="BG146" s="5" t="n"/>
     </row>
     <row r="147" ht="21" customHeight="1" s="30">
       <c r="A147" s="3" t="n">
@@ -17387,20 +17754,22 @@
       <c r="AW147" s="6" t="n">
         <v>98541.35000000001</v>
       </c>
-      <c r="AX147" s="6" t="n">
+      <c r="AX147" s="24" t="n">
+        <v>0.8522</v>
+      </c>
+      <c r="AY147" s="5" t="n">
+        <v>701.96</v>
+      </c>
+      <c r="AZ147" s="6" t="n">
         <v>100583.36</v>
       </c>
-      <c r="AY147" s="24" t="n"/>
-      <c r="AZ147" s="24" t="n">
-        <v>0.8522</v>
-      </c>
-      <c r="BA147" s="5" t="n">
-        <v>701.96</v>
-      </c>
-      <c r="BB147" s="5" t="n"/>
-      <c r="BC147" s="5" t="n"/>
+      <c r="BA147" s="38" t="n"/>
+      <c r="BB147" s="38" t="n"/>
+      <c r="BC147" s="24" t="n"/>
       <c r="BD147" s="5" t="n"/>
       <c r="BE147" s="5" t="n"/>
+      <c r="BF147" s="5" t="n"/>
+      <c r="BG147" s="5" t="n"/>
     </row>
     <row r="148" ht="21" customHeight="1" s="30">
       <c r="A148" s="3" t="n">
@@ -17550,26 +17919,28 @@
       <c r="AW148" s="6" t="n">
         <v>61722.51</v>
       </c>
-      <c r="AX148" s="6" t="n">
+      <c r="AX148" s="24" t="n">
+        <v>0.9785</v>
+      </c>
+      <c r="AY148" s="5" t="n">
+        <v>301.76</v>
+      </c>
+      <c r="AZ148" s="6" t="n">
         <v>51756.21</v>
       </c>
-      <c r="AY148" s="24" t="n"/>
-      <c r="AZ148" s="24" t="n">
-        <v>0.9785</v>
-      </c>
-      <c r="BA148" s="5" t="n">
-        <v>301.76</v>
-      </c>
-      <c r="BB148" s="5" t="n">
+      <c r="BA148" s="38" t="n"/>
+      <c r="BB148" s="38" t="n"/>
+      <c r="BC148" s="24" t="n"/>
+      <c r="BD148" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="BC148" s="5" t="n">
+      <c r="BE148" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="BD148" s="5" t="n">
+      <c r="BF148" s="5" t="n">
         <v>1.8392</v>
       </c>
-      <c r="BE148" s="5" t="n">
+      <c r="BG148" s="5" t="n">
         <v>8428</v>
       </c>
     </row>
@@ -17721,20 +18092,22 @@
       <c r="AW149" s="6" t="n">
         <v>79253.03999999999</v>
       </c>
-      <c r="AX149" s="6" t="n">
+      <c r="AX149" s="24" t="n">
+        <v>0.7409</v>
+      </c>
+      <c r="AY149" s="5" t="n">
+        <v>544.4</v>
+      </c>
+      <c r="AZ149" s="6" t="n">
         <v>67012.84</v>
       </c>
-      <c r="AY149" s="24" t="n"/>
-      <c r="AZ149" s="24" t="n">
-        <v>0.7409</v>
-      </c>
-      <c r="BA149" s="5" t="n">
-        <v>544.4</v>
-      </c>
-      <c r="BB149" s="5" t="n"/>
-      <c r="BC149" s="5" t="n"/>
+      <c r="BA149" s="38" t="n"/>
+      <c r="BB149" s="38" t="n"/>
+      <c r="BC149" s="24" t="n"/>
       <c r="BD149" s="5" t="n"/>
       <c r="BE149" s="5" t="n"/>
+      <c r="BF149" s="5" t="n"/>
+      <c r="BG149" s="5" t="n"/>
     </row>
     <row r="150" ht="21" customHeight="1" s="30">
       <c r="A150" s="3" t="n">
@@ -17884,20 +18257,22 @@
       <c r="AW150" s="6" t="n">
         <v>77874.86</v>
       </c>
-      <c r="AX150" s="6" t="n">
+      <c r="AX150" s="24" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="AY150" s="5" t="n">
+        <v>525.14</v>
+      </c>
+      <c r="AZ150" s="6" t="n">
         <v>83541.87</v>
       </c>
-      <c r="AY150" s="24" t="n"/>
-      <c r="AZ150" s="24" t="n">
-        <v>0.9126</v>
-      </c>
-      <c r="BA150" s="5" t="n">
-        <v>525.14</v>
-      </c>
-      <c r="BB150" s="5" t="n"/>
-      <c r="BC150" s="5" t="n"/>
+      <c r="BA150" s="38" t="n"/>
+      <c r="BB150" s="38" t="n"/>
+      <c r="BC150" s="24" t="n"/>
       <c r="BD150" s="5" t="n"/>
       <c r="BE150" s="5" t="n"/>
+      <c r="BF150" s="5" t="n"/>
+      <c r="BG150" s="5" t="n"/>
     </row>
     <row r="151" ht="21" customHeight="1" s="30">
       <c r="A151" s="3" t="n">
@@ -18047,26 +18422,28 @@
       <c r="AW151" s="6" t="n">
         <v>20517.31</v>
       </c>
-      <c r="AX151" s="6" t="n">
+      <c r="AX151" s="24" t="n">
+        <v>0.7841</v>
+      </c>
+      <c r="AY151" s="5" t="n">
+        <v>-54.3</v>
+      </c>
+      <c r="AZ151" s="6" t="n">
         <v>3554.54</v>
       </c>
-      <c r="AY151" s="24" t="n"/>
-      <c r="AZ151" s="24" t="n">
-        <v>0.7841</v>
-      </c>
-      <c r="BA151" s="5" t="n">
-        <v>-54.3</v>
-      </c>
-      <c r="BB151" s="5" t="n">
+      <c r="BA151" s="38" t="n"/>
+      <c r="BB151" s="38" t="n"/>
+      <c r="BC151" s="24" t="n"/>
+      <c r="BD151" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="BC151" s="5" t="n">
+      <c r="BE151" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="BD151" s="5" t="n">
+      <c r="BF151" s="5" t="n">
         <v>1.8662</v>
       </c>
-      <c r="BE151" s="5" t="n">
+      <c r="BG151" s="5" t="n">
         <v>10529.61</v>
       </c>
     </row>
@@ -18218,20 +18595,22 @@
       <c r="AW152" s="6" t="n">
         <v>89211.81</v>
       </c>
-      <c r="AX152" s="6" t="n">
+      <c r="AX152" s="24" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="AY152" s="5" t="n">
+        <v>496</v>
+      </c>
+      <c r="AZ152" s="6" t="n">
         <v>72823.27</v>
       </c>
-      <c r="AY152" s="24" t="n"/>
-      <c r="AZ152" s="24" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="BA152" s="5" t="n">
-        <v>496</v>
-      </c>
-      <c r="BB152" s="5" t="n"/>
-      <c r="BC152" s="5" t="n"/>
+      <c r="BA152" s="38" t="n"/>
+      <c r="BB152" s="38" t="n"/>
+      <c r="BC152" s="24" t="n"/>
       <c r="BD152" s="5" t="n"/>
       <c r="BE152" s="5" t="n"/>
+      <c r="BF152" s="5" t="n"/>
+      <c r="BG152" s="5" t="n"/>
     </row>
     <row r="153" ht="21" customHeight="1" s="30">
       <c r="A153" s="3" t="n">
@@ -18381,20 +18760,22 @@
       <c r="AW153" s="6" t="n">
         <v>88993.52</v>
       </c>
-      <c r="AX153" s="6" t="n">
+      <c r="AX153" s="24" t="n">
+        <v>0.8287</v>
+      </c>
+      <c r="AY153" s="5" t="n">
+        <v>547.9400000000001</v>
+      </c>
+      <c r="AZ153" s="6" t="n">
         <v>81868.91</v>
       </c>
-      <c r="AY153" s="24" t="n"/>
-      <c r="AZ153" s="24" t="n">
-        <v>0.8287</v>
-      </c>
-      <c r="BA153" s="5" t="n">
-        <v>547.9400000000001</v>
-      </c>
-      <c r="BB153" s="5" t="n"/>
-      <c r="BC153" s="5" t="n"/>
+      <c r="BA153" s="38" t="n"/>
+      <c r="BB153" s="38" t="n"/>
+      <c r="BC153" s="24" t="n"/>
       <c r="BD153" s="5" t="n"/>
       <c r="BE153" s="5" t="n"/>
+      <c r="BF153" s="5" t="n"/>
+      <c r="BG153" s="5" t="n"/>
     </row>
     <row r="154" ht="21" customHeight="1" s="30">
       <c r="A154" s="3" t="n">
@@ -18544,20 +18925,22 @@
       <c r="AW154" s="6" t="n">
         <v>69710.22</v>
       </c>
-      <c r="AX154" s="6" t="n">
+      <c r="AX154" s="24" t="n">
+        <v>0.8622</v>
+      </c>
+      <c r="AY154" s="5" t="n">
+        <v>492.25</v>
+      </c>
+      <c r="AZ154" s="6" t="n">
         <v>71819.53</v>
       </c>
-      <c r="AY154" s="24" t="n"/>
-      <c r="AZ154" s="24" t="n">
-        <v>0.8622</v>
-      </c>
-      <c r="BA154" s="5" t="n">
-        <v>492.25</v>
-      </c>
-      <c r="BB154" s="5" t="n"/>
-      <c r="BC154" s="5" t="n"/>
+      <c r="BA154" s="38" t="n"/>
+      <c r="BB154" s="38" t="n"/>
+      <c r="BC154" s="24" t="n"/>
       <c r="BD154" s="5" t="n"/>
       <c r="BE154" s="5" t="n"/>
+      <c r="BF154" s="5" t="n"/>
+      <c r="BG154" s="5" t="n"/>
     </row>
     <row r="155" ht="21" customHeight="1" s="30">
       <c r="A155" s="3" t="n">
@@ -18707,20 +19090,22 @@
       <c r="AW155" s="6" t="n">
         <v>83590.59</v>
       </c>
-      <c r="AX155" s="27" t="n">
+      <c r="AX155" s="24" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="AY155" s="5" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="AZ155" s="27" t="n">
         <v>85710</v>
       </c>
-      <c r="AY155" s="24" t="n"/>
-      <c r="AZ155" s="24" t="n">
-        <v>0.8663</v>
-      </c>
-      <c r="BA155" s="5" t="n">
-        <v>588.4</v>
-      </c>
-      <c r="BB155" s="5" t="n"/>
-      <c r="BC155" s="5" t="n"/>
+      <c r="BA155" s="44" t="n"/>
+      <c r="BB155" s="44" t="n"/>
+      <c r="BC155" s="24" t="n"/>
       <c r="BD155" s="5" t="n"/>
       <c r="BE155" s="5" t="n"/>
+      <c r="BF155" s="5" t="n"/>
+      <c r="BG155" s="5" t="n"/>
     </row>
     <row r="156" ht="21" customHeight="1" s="30">
       <c r="A156" s="3" t="n">
@@ -18870,26 +19255,28 @@
       <c r="AW156" s="6" t="n">
         <v>37565.03</v>
       </c>
-      <c r="AX156" s="12" t="n">
+      <c r="AX156" s="24" t="n">
+        <v>0.9263</v>
+      </c>
+      <c r="AY156" s="5" t="n">
+        <v>-10.65</v>
+      </c>
+      <c r="AZ156" s="12" t="n">
         <v>25030.22</v>
       </c>
-      <c r="AY156" s="24" t="n"/>
-      <c r="AZ156" s="24" t="n">
-        <v>0.9263</v>
-      </c>
-      <c r="BA156" s="5" t="n">
-        <v>-10.65</v>
-      </c>
-      <c r="BB156" s="5" t="n">
+      <c r="BA156" s="45" t="n"/>
+      <c r="BB156" s="45" t="n"/>
+      <c r="BC156" s="24" t="n"/>
+      <c r="BD156" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="BC156" s="5" t="n">
+      <c r="BE156" s="5" t="n">
         <v>11.2</v>
       </c>
-      <c r="BD156" s="5" t="n">
+      <c r="BF156" s="5" t="n">
         <v>1.8674</v>
       </c>
-      <c r="BE156" s="5" t="n">
+      <c r="BG156" s="5" t="n">
         <v>27477.43</v>
       </c>
     </row>
@@ -19041,20 +19428,22 @@
       <c r="AW157" s="6" t="n">
         <v>63898.38</v>
       </c>
-      <c r="AX157" s="6" t="n">
+      <c r="AX157" s="24" t="n">
+        <v>0.8208</v>
+      </c>
+      <c r="AY157" s="5" t="n">
+        <v>449.98</v>
+      </c>
+      <c r="AZ157" s="6" t="n">
         <v>61925.71</v>
       </c>
-      <c r="AY157" s="24" t="n"/>
-      <c r="AZ157" s="24" t="n">
-        <v>0.8208</v>
-      </c>
-      <c r="BA157" s="5" t="n">
-        <v>449.98</v>
-      </c>
-      <c r="BB157" s="5" t="n"/>
-      <c r="BC157" s="5" t="n"/>
+      <c r="BA157" s="38" t="n"/>
+      <c r="BB157" s="38" t="n"/>
+      <c r="BC157" s="24" t="n"/>
       <c r="BD157" s="5" t="n"/>
       <c r="BE157" s="5" t="n"/>
+      <c r="BF157" s="5" t="n"/>
+      <c r="BG157" s="5" t="n"/>
     </row>
     <row r="158" ht="21" customHeight="1" s="30">
       <c r="A158" s="3" t="n">
@@ -19204,20 +19593,22 @@
       <c r="AW158" s="6" t="n">
         <v>65154.26</v>
       </c>
-      <c r="AX158" s="6" t="n">
+      <c r="AX158" s="24" t="n">
+        <v>0.8662</v>
+      </c>
+      <c r="AY158" s="5" t="n">
+        <v>457.71</v>
+      </c>
+      <c r="AZ158" s="6" t="n">
         <v>68241.78999999999</v>
       </c>
-      <c r="AY158" s="24" t="n"/>
-      <c r="AZ158" s="24" t="n">
-        <v>0.8662</v>
-      </c>
-      <c r="BA158" s="5" t="n">
-        <v>457.71</v>
-      </c>
-      <c r="BB158" s="5" t="n"/>
-      <c r="BC158" s="5" t="n"/>
+      <c r="BA158" s="38" t="n"/>
+      <c r="BB158" s="38" t="n"/>
+      <c r="BC158" s="24" t="n"/>
       <c r="BD158" s="5" t="n"/>
       <c r="BE158" s="5" t="n"/>
+      <c r="BF158" s="5" t="n"/>
+      <c r="BG158" s="5" t="n"/>
     </row>
     <row r="159" ht="21" customHeight="1" s="30">
       <c r="A159" s="3" t="n">
@@ -19367,20 +19758,22 @@
       <c r="AW159" s="6" t="n">
         <v>52726.08</v>
       </c>
-      <c r="AX159" s="6" t="n">
+      <c r="AX159" s="24" t="n">
+        <v>0.8306</v>
+      </c>
+      <c r="AY159" s="5" t="n">
+        <v>392.01</v>
+      </c>
+      <c r="AZ159" s="6" t="n">
         <v>52382.96</v>
       </c>
-      <c r="AY159" s="24" t="n"/>
-      <c r="AZ159" s="24" t="n">
-        <v>0.8306</v>
-      </c>
-      <c r="BA159" s="5" t="n">
-        <v>392.01</v>
-      </c>
-      <c r="BB159" s="5" t="n"/>
-      <c r="BC159" s="5" t="n"/>
+      <c r="BA159" s="38" t="n"/>
+      <c r="BB159" s="38" t="n"/>
+      <c r="BC159" s="24" t="n"/>
       <c r="BD159" s="5" t="n"/>
       <c r="BE159" s="5" t="n"/>
+      <c r="BF159" s="5" t="n"/>
+      <c r="BG159" s="5" t="n"/>
     </row>
     <row r="160" ht="21" customHeight="1" s="30">
       <c r="A160" s="3" t="n">
@@ -19530,20 +19923,22 @@
       <c r="AW160" s="6" t="n">
         <v>56216.35</v>
       </c>
-      <c r="AX160" s="6" t="n">
+      <c r="AX160" s="24" t="n">
+        <v>0.8687</v>
+      </c>
+      <c r="AY160" s="5" t="n">
+        <v>409.17</v>
+      </c>
+      <c r="AZ160" s="6" t="n">
         <v>57457.7</v>
       </c>
-      <c r="AY160" s="24" t="n"/>
-      <c r="AZ160" s="24" t="n">
-        <v>0.8687</v>
-      </c>
-      <c r="BA160" s="5" t="n">
-        <v>409.17</v>
-      </c>
-      <c r="BB160" s="5" t="n"/>
-      <c r="BC160" s="5" t="n"/>
+      <c r="BA160" s="38" t="n"/>
+      <c r="BB160" s="38" t="n"/>
+      <c r="BC160" s="24" t="n"/>
       <c r="BD160" s="5" t="n"/>
       <c r="BE160" s="5" t="n"/>
+      <c r="BF160" s="5" t="n"/>
+      <c r="BG160" s="5" t="n"/>
     </row>
     <row r="161" ht="21" customHeight="1" s="30">
       <c r="A161" s="3" t="n">
@@ -19693,20 +20088,22 @@
       <c r="AW161" s="6" t="n">
         <v>72446.35000000001</v>
       </c>
-      <c r="AX161" s="12" t="n">
+      <c r="AX161" s="24" t="n">
+        <v>0.8497</v>
+      </c>
+      <c r="AY161" s="5" t="n">
+        <v>133.46</v>
+      </c>
+      <c r="AZ161" s="12" t="n">
         <v>845.5599999999999</v>
       </c>
-      <c r="AY161" s="24" t="n"/>
-      <c r="AZ161" s="24" t="n">
-        <v>0.8497</v>
-      </c>
-      <c r="BA161" s="5" t="n">
-        <v>133.46</v>
-      </c>
-      <c r="BB161" s="5" t="n"/>
-      <c r="BC161" s="5" t="n"/>
+      <c r="BA161" s="45" t="n"/>
+      <c r="BB161" s="45" t="n"/>
+      <c r="BC161" s="24" t="n"/>
       <c r="BD161" s="5" t="n"/>
       <c r="BE161" s="5" t="n"/>
+      <c r="BF161" s="5" t="n"/>
+      <c r="BG161" s="5" t="n"/>
     </row>
     <row r="162" ht="21" customHeight="1" s="30">
       <c r="A162" s="3" t="n">
@@ -19856,20 +20253,22 @@
       <c r="AW162" s="11" t="n">
         <v>78236.10000000001</v>
       </c>
-      <c r="AX162" s="11" t="n">
+      <c r="AX162" s="26" t="n">
+        <v>0.7637</v>
+      </c>
+      <c r="AY162" s="9" t="n">
+        <v>595.98</v>
+      </c>
+      <c r="AZ162" s="11" t="n">
         <v>75292.62</v>
       </c>
-      <c r="AY162" s="26" t="n"/>
-      <c r="AZ162" s="26" t="n">
-        <v>0.7637</v>
-      </c>
-      <c r="BA162" s="9" t="n">
-        <v>595.98</v>
-      </c>
-      <c r="BB162" s="5" t="n"/>
-      <c r="BC162" s="5" t="n"/>
+      <c r="BA162" s="39" t="n"/>
+      <c r="BB162" s="39" t="n"/>
+      <c r="BC162" s="26" t="n"/>
       <c r="BD162" s="5" t="n"/>
       <c r="BE162" s="5" t="n"/>
+      <c r="BF162" s="5" t="n"/>
+      <c r="BG162" s="5" t="n"/>
     </row>
     <row r="163" ht="21" customHeight="1" s="30">
       <c r="A163" s="3" t="n">
@@ -20019,20 +20418,22 @@
       <c r="AW163" s="11" t="n">
         <v>89168.5</v>
       </c>
-      <c r="AX163" s="11" t="n">
+      <c r="AX163" s="26" t="n">
+        <v>0.9484</v>
+      </c>
+      <c r="AY163" s="9" t="n">
+        <v>440.72</v>
+      </c>
+      <c r="AZ163" s="11" t="n">
         <v>80353.3</v>
       </c>
-      <c r="AY163" s="26" t="n"/>
-      <c r="AZ163" s="26" t="n">
-        <v>0.9484</v>
-      </c>
-      <c r="BA163" s="9" t="n">
-        <v>440.72</v>
-      </c>
-      <c r="BB163" s="5" t="n"/>
-      <c r="BC163" s="5" t="n"/>
+      <c r="BA163" s="39" t="n"/>
+      <c r="BB163" s="39" t="n"/>
+      <c r="BC163" s="26" t="n"/>
       <c r="BD163" s="5" t="n"/>
       <c r="BE163" s="5" t="n"/>
+      <c r="BF163" s="5" t="n"/>
+      <c r="BG163" s="5" t="n"/>
     </row>
     <row r="164" ht="21" customHeight="1" s="30">
       <c r="A164" s="3" t="n">
@@ -20182,20 +20583,22 @@
       <c r="AW164" s="11" t="n">
         <v>91237.19</v>
       </c>
-      <c r="AX164" s="11" t="n">
+      <c r="AX164" s="26" t="n">
+        <v>0.8525</v>
+      </c>
+      <c r="AY164" s="9" t="n">
+        <v>621.09</v>
+      </c>
+      <c r="AZ164" s="11" t="n">
         <v>91976.28999999999</v>
       </c>
-      <c r="AY164" s="26" t="n"/>
-      <c r="AZ164" s="26" t="n">
-        <v>0.8525</v>
-      </c>
-      <c r="BA164" s="9" t="n">
-        <v>621.09</v>
-      </c>
-      <c r="BB164" s="5" t="n"/>
-      <c r="BC164" s="5" t="n"/>
+      <c r="BA164" s="39" t="n"/>
+      <c r="BB164" s="39" t="n"/>
+      <c r="BC164" s="26" t="n"/>
       <c r="BD164" s="5" t="n"/>
       <c r="BE164" s="5" t="n"/>
+      <c r="BF164" s="5" t="n"/>
+      <c r="BG164" s="5" t="n"/>
     </row>
     <row r="165" ht="21" customHeight="1" s="30">
       <c r="A165" s="3" t="n">
@@ -20345,20 +20748,22 @@
       <c r="AW165" s="11" t="n">
         <v>61082.42</v>
       </c>
-      <c r="AX165" s="11" t="n">
+      <c r="AX165" s="26" t="n">
+        <v>0.8546</v>
+      </c>
+      <c r="AY165" s="9" t="n">
+        <v>450.17</v>
+      </c>
+      <c r="AZ165" s="11" t="n">
         <v>64850.97</v>
       </c>
-      <c r="AY165" s="26" t="n"/>
-      <c r="AZ165" s="26" t="n">
-        <v>0.8546</v>
-      </c>
-      <c r="BA165" s="9" t="n">
-        <v>450.17</v>
-      </c>
-      <c r="BB165" s="5" t="n"/>
-      <c r="BC165" s="5" t="n"/>
+      <c r="BA165" s="39" t="n"/>
+      <c r="BB165" s="39" t="n"/>
+      <c r="BC165" s="26" t="n"/>
       <c r="BD165" s="5" t="n"/>
       <c r="BE165" s="5" t="n"/>
+      <c r="BF165" s="5" t="n"/>
+      <c r="BG165" s="5" t="n"/>
     </row>
     <row r="166" ht="21" customHeight="1" s="30">
       <c r="A166" s="3" t="n">
@@ -20508,20 +20913,22 @@
       <c r="AW166" s="11" t="n">
         <v>83805.00999999999</v>
       </c>
-      <c r="AX166" s="11" t="n">
+      <c r="AX166" s="26" t="n">
+        <v>0.8388</v>
+      </c>
+      <c r="AY166" s="9" t="n">
+        <v>601.67</v>
+      </c>
+      <c r="AZ166" s="11" t="n">
         <v>84751.95</v>
       </c>
-      <c r="AY166" s="26" t="n"/>
-      <c r="AZ166" s="26" t="n">
-        <v>0.8388</v>
-      </c>
-      <c r="BA166" s="9" t="n">
-        <v>601.67</v>
-      </c>
-      <c r="BB166" s="5" t="n"/>
-      <c r="BC166" s="5" t="n"/>
+      <c r="BA166" s="39" t="n"/>
+      <c r="BB166" s="39" t="n"/>
+      <c r="BC166" s="26" t="n"/>
       <c r="BD166" s="5" t="n"/>
       <c r="BE166" s="5" t="n"/>
+      <c r="BF166" s="5" t="n"/>
+      <c r="BG166" s="5" t="n"/>
     </row>
     <row r="167" ht="21" customHeight="1" s="30">
       <c r="A167" s="3" t="n">
@@ -20671,20 +21078,22 @@
       <c r="AW167" s="11" t="n">
         <v>1340.66</v>
       </c>
-      <c r="AX167" s="12" t="n">
+      <c r="AX167" s="26" t="n">
+        <v>0.4991</v>
+      </c>
+      <c r="AY167" s="9" t="n">
+        <v>-23.19</v>
+      </c>
+      <c r="AZ167" s="12" t="n">
         <v>-2443.95</v>
       </c>
-      <c r="AY167" s="26" t="n"/>
-      <c r="AZ167" s="26" t="n">
-        <v>0.4991</v>
-      </c>
-      <c r="BA167" s="9" t="n">
-        <v>-23.19</v>
-      </c>
-      <c r="BB167" s="5" t="n"/>
-      <c r="BC167" s="5" t="n"/>
+      <c r="BA167" s="45" t="n"/>
+      <c r="BB167" s="45" t="n"/>
+      <c r="BC167" s="26" t="n"/>
       <c r="BD167" s="5" t="n"/>
       <c r="BE167" s="5" t="n"/>
+      <c r="BF167" s="5" t="n"/>
+      <c r="BG167" s="5" t="n"/>
     </row>
     <row r="168" ht="21" customHeight="1" s="30">
       <c r="A168" s="3" t="n">
@@ -20834,20 +21243,22 @@
       <c r="AW168" s="11" t="n">
         <v>96339.89999999999</v>
       </c>
-      <c r="AX168" s="11" t="n">
+      <c r="AX168" s="26" t="n">
+        <v>0.8431999999999999</v>
+      </c>
+      <c r="AY168" s="9" t="n">
+        <v>650.77</v>
+      </c>
+      <c r="AZ168" s="11" t="n">
         <v>96798.98</v>
       </c>
-      <c r="AY168" s="26" t="n"/>
-      <c r="AZ168" s="26" t="n">
-        <v>0.8431999999999999</v>
-      </c>
-      <c r="BA168" s="9" t="n">
-        <v>650.77</v>
-      </c>
-      <c r="BB168" s="5" t="n"/>
-      <c r="BC168" s="5" t="n"/>
+      <c r="BA168" s="39" t="n"/>
+      <c r="BB168" s="39" t="n"/>
+      <c r="BC168" s="26" t="n"/>
       <c r="BD168" s="5" t="n"/>
       <c r="BE168" s="5" t="n"/>
+      <c r="BF168" s="5" t="n"/>
+      <c r="BG168" s="5" t="n"/>
     </row>
     <row r="169" ht="21" customHeight="1" s="30">
       <c r="A169" s="3" t="n">
@@ -20997,22 +21408,24 @@
       <c r="AW169" s="16" t="n">
         <v>64854.54</v>
       </c>
-      <c r="AX169" s="16" t="n">
+      <c r="AX169" s="28" t="n">
+        <v>0.8538280514590524</v>
+      </c>
+      <c r="AY169" s="15" t="n">
+        <v>465.08</v>
+      </c>
+      <c r="AZ169" s="16" t="n">
         <v>69352.25999999999</v>
       </c>
-      <c r="AY169" s="28" t="n">
+      <c r="BA169" s="40" t="n"/>
+      <c r="BB169" s="40" t="n"/>
+      <c r="BC169" s="28" t="n">
         <v>77830.46000000001</v>
       </c>
-      <c r="AZ169" s="28" t="n">
-        <v>0.8538280514590524</v>
-      </c>
-      <c r="BA169" s="15" t="n">
-        <v>465.08</v>
-      </c>
-      <c r="BB169" s="5" t="n"/>
-      <c r="BC169" s="5" t="n"/>
       <c r="BD169" s="5" t="n"/>
       <c r="BE169" s="5" t="n"/>
+      <c r="BF169" s="5" t="n"/>
+      <c r="BG169" s="5" t="n"/>
     </row>
     <row r="170" ht="21" customHeight="1" s="30">
       <c r="A170" s="3" t="n">
@@ -21162,20 +21575,22 @@
       <c r="AW170" s="16" t="n">
         <v>71182.71000000001</v>
       </c>
-      <c r="AX170" s="16" t="n">
+      <c r="AX170" s="28" t="n">
+        <v>0.8331</v>
+      </c>
+      <c r="AY170" s="15" t="n">
+        <v>506.93</v>
+      </c>
+      <c r="AZ170" s="16" t="n">
         <v>72630.61</v>
       </c>
-      <c r="AY170" s="28" t="n"/>
-      <c r="AZ170" s="28" t="n">
-        <v>0.8331</v>
-      </c>
-      <c r="BA170" s="15" t="n">
-        <v>506.93</v>
-      </c>
-      <c r="BB170" s="5" t="n"/>
-      <c r="BC170" s="5" t="n"/>
+      <c r="BA170" s="40" t="n"/>
+      <c r="BB170" s="40" t="n"/>
+      <c r="BC170" s="28" t="n"/>
       <c r="BD170" s="5" t="n"/>
       <c r="BE170" s="5" t="n"/>
+      <c r="BF170" s="5" t="n"/>
+      <c r="BG170" s="5" t="n"/>
     </row>
     <row r="171" ht="21" customHeight="1" s="30">
       <c r="A171" s="3" t="n">
@@ -21325,20 +21740,22 @@
       <c r="AW171" s="16" t="n">
         <v>75464.64</v>
       </c>
-      <c r="AX171" s="16" t="n">
+      <c r="AX171" s="28" t="n">
+        <v>0.8474</v>
+      </c>
+      <c r="AY171" s="15" t="n">
+        <v>530.5700000000001</v>
+      </c>
+      <c r="AZ171" s="16" t="n">
         <v>74387.53999999999</v>
       </c>
-      <c r="AY171" s="28" t="n"/>
-      <c r="AZ171" s="28" t="n">
-        <v>0.8474</v>
-      </c>
-      <c r="BA171" s="15" t="n">
-        <v>530.5700000000001</v>
-      </c>
-      <c r="BB171" s="5" t="n"/>
-      <c r="BC171" s="5" t="n"/>
+      <c r="BA171" s="40" t="n"/>
+      <c r="BB171" s="40" t="n"/>
+      <c r="BC171" s="28" t="n"/>
       <c r="BD171" s="5" t="n"/>
       <c r="BE171" s="5" t="n"/>
+      <c r="BF171" s="5" t="n"/>
+      <c r="BG171" s="5" t="n"/>
     </row>
     <row r="172" ht="21" customHeight="1" s="30">
       <c r="A172" s="3" t="n">
@@ -21488,20 +21905,22 @@
       <c r="AW172" s="16" t="n">
         <v>109048.97</v>
       </c>
-      <c r="AX172" s="16" t="n">
+      <c r="AX172" s="28" t="n">
+        <v>0.8578</v>
+      </c>
+      <c r="AY172" s="15" t="n">
+        <v>695.66</v>
+      </c>
+      <c r="AZ172" s="16" t="n">
         <v>106434.45</v>
       </c>
-      <c r="AY172" s="28" t="n"/>
-      <c r="AZ172" s="28" t="n">
-        <v>0.8578</v>
-      </c>
-      <c r="BA172" s="15" t="n">
-        <v>695.66</v>
-      </c>
-      <c r="BB172" s="5" t="n"/>
-      <c r="BC172" s="5" t="n"/>
+      <c r="BA172" s="40" t="n"/>
+      <c r="BB172" s="40" t="n"/>
+      <c r="BC172" s="28" t="n"/>
       <c r="BD172" s="5" t="n"/>
       <c r="BE172" s="5" t="n"/>
+      <c r="BF172" s="5" t="n"/>
+      <c r="BG172" s="5" t="n"/>
     </row>
     <row r="173" ht="21" customHeight="1" s="30">
       <c r="A173" s="3" t="n">
@@ -21651,20 +22070,22 @@
       <c r="AW173" s="16" t="n">
         <v>88348.77</v>
       </c>
-      <c r="AX173" s="16" t="n">
+      <c r="AX173" s="28" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AY173" s="15" t="n">
+        <v>597.14</v>
+      </c>
+      <c r="AZ173" s="16" t="n">
         <v>90507.92</v>
       </c>
-      <c r="AY173" s="28" t="n"/>
-      <c r="AZ173" s="28" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="BA173" s="15" t="n">
-        <v>597.14</v>
-      </c>
-      <c r="BB173" s="5" t="n"/>
-      <c r="BC173" s="5" t="n"/>
+      <c r="BA173" s="40" t="n"/>
+      <c r="BB173" s="40" t="n"/>
+      <c r="BC173" s="28" t="n"/>
       <c r="BD173" s="5" t="n"/>
       <c r="BE173" s="5" t="n"/>
+      <c r="BF173" s="5" t="n"/>
+      <c r="BG173" s="5" t="n"/>
     </row>
     <row r="174" ht="21" customHeight="1" s="30">
       <c r="A174" s="3" t="n">
@@ -21814,20 +22235,22 @@
       <c r="AW174" s="16" t="n">
         <v>68558.92999999999</v>
       </c>
-      <c r="AX174" s="16" t="n">
+      <c r="AX174" s="28" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="AY174" s="15" t="n">
+        <v>484.99</v>
+      </c>
+      <c r="AZ174" s="16" t="n">
         <v>67261.42</v>
       </c>
-      <c r="AY174" s="28" t="n"/>
-      <c r="AZ174" s="28" t="n">
-        <v>0.8332000000000001</v>
-      </c>
-      <c r="BA174" s="15" t="n">
-        <v>484.99</v>
-      </c>
-      <c r="BB174" s="5" t="n"/>
-      <c r="BC174" s="5" t="n"/>
+      <c r="BA174" s="40" t="n"/>
+      <c r="BB174" s="40" t="n"/>
+      <c r="BC174" s="28" t="n"/>
       <c r="BD174" s="5" t="n"/>
       <c r="BE174" s="5" t="n"/>
+      <c r="BF174" s="5" t="n"/>
+      <c r="BG174" s="5" t="n"/>
     </row>
     <row r="175" ht="21" customHeight="1" s="30">
       <c r="A175" s="3" t="n">
@@ -21977,20 +22400,22 @@
       <c r="AW175" s="16" t="n">
         <v>108668.59</v>
       </c>
-      <c r="AX175" s="16" t="n">
+      <c r="AX175" s="28" t="n">
+        <v>0.8619</v>
+      </c>
+      <c r="AY175" s="15" t="n">
+        <v>737.28</v>
+      </c>
+      <c r="AZ175" s="16" t="n">
         <v>109928.19</v>
       </c>
-      <c r="AY175" s="28" t="n"/>
-      <c r="AZ175" s="28" t="n">
-        <v>0.8619</v>
-      </c>
-      <c r="BA175" s="15" t="n">
-        <v>737.28</v>
-      </c>
-      <c r="BB175" s="5" t="n"/>
-      <c r="BC175" s="5" t="n"/>
+      <c r="BA175" s="40" t="n"/>
+      <c r="BB175" s="40" t="n"/>
+      <c r="BC175" s="28" t="n"/>
       <c r="BD175" s="5" t="n"/>
       <c r="BE175" s="5" t="n"/>
+      <c r="BF175" s="5" t="n"/>
+      <c r="BG175" s="5" t="n"/>
     </row>
     <row r="176" ht="21" customHeight="1" s="30">
       <c r="A176" s="3" t="n">
@@ -22140,22 +22565,24 @@
       <c r="AW176" s="15" t="n">
         <v>174651.22</v>
       </c>
-      <c r="AX176" s="16" t="n">
+      <c r="AX176" s="28" t="n">
+        <v>0.853553989203736</v>
+      </c>
+      <c r="AY176" s="15" t="n">
+        <v>78.54000000000001</v>
+      </c>
+      <c r="AZ176" s="16" t="n">
         <v>-28789.16</v>
       </c>
-      <c r="AY176" s="16" t="n">
+      <c r="BA176" s="40" t="n"/>
+      <c r="BB176" s="40" t="n"/>
+      <c r="BC176" s="16" t="n">
         <v>-95.37</v>
       </c>
-      <c r="AZ176" s="28" t="n">
-        <v>0.853553989203736</v>
-      </c>
-      <c r="BA176" s="15" t="n">
-        <v>78.54000000000001</v>
-      </c>
-      <c r="BB176" s="5" t="n"/>
-      <c r="BC176" s="5" t="n"/>
       <c r="BD176" s="5" t="n"/>
       <c r="BE176" s="5" t="n"/>
+      <c r="BF176" s="5" t="n"/>
+      <c r="BG176" s="5" t="n"/>
     </row>
     <row r="177" ht="21" customHeight="1" s="30">
       <c r="A177" s="3" t="n">
@@ -22305,22 +22732,24 @@
       <c r="AW177" s="15" t="n">
         <v>86404</v>
       </c>
-      <c r="AX177" s="16" t="n">
+      <c r="AX177" s="28" t="n">
+        <v>0.8491343218377654</v>
+      </c>
+      <c r="AY177" s="15" t="n">
+        <v>596.17</v>
+      </c>
+      <c r="AZ177" s="16" t="n">
         <v>90509.3</v>
       </c>
-      <c r="AY177" s="16" t="n">
+      <c r="BA177" s="40" t="n"/>
+      <c r="BB177" s="40" t="n"/>
+      <c r="BC177" s="16" t="n">
         <v>99278.17999999999</v>
       </c>
-      <c r="AZ177" s="28" t="n">
-        <v>0.8491343218377654</v>
-      </c>
-      <c r="BA177" s="15" t="n">
-        <v>596.17</v>
-      </c>
-      <c r="BB177" s="5" t="n"/>
-      <c r="BC177" s="5" t="n"/>
       <c r="BD177" s="5" t="n"/>
       <c r="BE177" s="5" t="n"/>
+      <c r="BF177" s="5" t="n"/>
+      <c r="BG177" s="5" t="n"/>
     </row>
     <row r="178" ht="21" customHeight="1" s="30">
       <c r="A178" s="3" t="n">
@@ -22470,22 +22899,24 @@
       <c r="AW178" s="15" t="n">
         <v>95219.31</v>
       </c>
-      <c r="AX178" s="16" t="n">
+      <c r="AX178" s="28" t="n">
+        <v>0.848870228926598</v>
+      </c>
+      <c r="AY178" s="15" t="n">
+        <v>659.17</v>
+      </c>
+      <c r="AZ178" s="16" t="n">
         <v>98899.27</v>
       </c>
-      <c r="AY178" s="16" t="n">
+      <c r="BA178" s="40" t="n"/>
+      <c r="BB178" s="40" t="n"/>
+      <c r="BC178" s="16" t="n">
         <v>107236.3</v>
       </c>
-      <c r="AZ178" s="28" t="n">
-        <v>0.848870228926598</v>
-      </c>
-      <c r="BA178" s="15" t="n">
-        <v>659.17</v>
-      </c>
-      <c r="BB178" s="5" t="n"/>
-      <c r="BC178" s="5" t="n"/>
       <c r="BD178" s="5" t="n"/>
       <c r="BE178" s="5" t="n"/>
+      <c r="BF178" s="5" t="n"/>
+      <c r="BG178" s="5" t="n"/>
     </row>
     <row r="179" ht="21" customHeight="1" s="30">
       <c r="A179" s="3" t="n">
@@ -22635,22 +23066,24 @@
       <c r="AW179" s="15" t="n">
         <v>170558.93</v>
       </c>
-      <c r="AX179" s="16" t="n">
+      <c r="AX179" s="28" t="n">
+        <v>1.663373386737873</v>
+      </c>
+      <c r="AY179" s="15" t="n">
+        <v>520.59</v>
+      </c>
+      <c r="AZ179" s="16" t="n">
         <v>199666.68</v>
       </c>
-      <c r="AY179" s="16" t="n">
+      <c r="BA179" s="40" t="n"/>
+      <c r="BB179" s="40" t="n"/>
+      <c r="BC179" s="16" t="n">
         <v>173295.38</v>
       </c>
-      <c r="AZ179" s="28" t="n">
-        <v>1.663373386737873</v>
-      </c>
-      <c r="BA179" s="15" t="n">
-        <v>520.59</v>
-      </c>
-      <c r="BB179" s="5" t="n"/>
-      <c r="BC179" s="5" t="n"/>
       <c r="BD179" s="5" t="n"/>
       <c r="BE179" s="5" t="n"/>
+      <c r="BF179" s="5" t="n"/>
+      <c r="BG179" s="5" t="n"/>
     </row>
     <row r="180" ht="21" customHeight="1" s="30">
       <c r="A180" s="3" t="n">
@@ -22800,22 +23233,24 @@
       <c r="AW180" s="15" t="n">
         <v>95076.78999999999</v>
       </c>
-      <c r="AX180" s="16" t="n">
+      <c r="AX180" s="28" t="n">
+        <v>0.8540295794948924</v>
+      </c>
+      <c r="AY180" s="15" t="n">
+        <v>657.29</v>
+      </c>
+      <c r="AZ180" s="16" t="n">
         <v>101054.99</v>
       </c>
-      <c r="AY180" s="16" t="n">
+      <c r="BA180" s="40" t="n"/>
+      <c r="BB180" s="40" t="n"/>
+      <c r="BC180" s="16" t="n">
         <v>109604.49</v>
       </c>
-      <c r="AZ180" s="28" t="n">
-        <v>0.8540295794948924</v>
-      </c>
-      <c r="BA180" s="15" t="n">
-        <v>657.29</v>
-      </c>
-      <c r="BB180" s="5" t="n"/>
-      <c r="BC180" s="5" t="n"/>
       <c r="BD180" s="5" t="n"/>
       <c r="BE180" s="5" t="n"/>
+      <c r="BF180" s="5" t="n"/>
+      <c r="BG180" s="5" t="n"/>
     </row>
     <row r="181" ht="21" customHeight="1" s="30">
       <c r="A181" s="3" t="n">
@@ -22965,22 +23400,24 @@
       <c r="AW181" s="15" t="n">
         <v>92882.34</v>
       </c>
-      <c r="AX181" s="16" t="n">
+      <c r="AX181" s="28" t="n">
+        <v>0.8457553120246692</v>
+      </c>
+      <c r="AY181" s="15" t="n">
+        <v>567.1</v>
+      </c>
+      <c r="AZ181" s="16" t="n">
         <v>83427.52</v>
       </c>
-      <c r="AY181" s="16" t="n">
+      <c r="BA181" s="40" t="n"/>
+      <c r="BB181" s="40" t="n"/>
+      <c r="BC181" s="16" t="n">
         <v>92299.74000000001</v>
       </c>
-      <c r="AZ181" s="28" t="n">
-        <v>0.8457553120246692</v>
-      </c>
-      <c r="BA181" s="15" t="n">
-        <v>567.1</v>
-      </c>
-      <c r="BB181" s="5" t="n"/>
-      <c r="BC181" s="5" t="n"/>
       <c r="BD181" s="5" t="n"/>
       <c r="BE181" s="5" t="n"/>
+      <c r="BF181" s="5" t="n"/>
+      <c r="BG181" s="5" t="n"/>
     </row>
     <row r="182" ht="21" customHeight="1" s="30">
       <c r="A182" s="3" t="n">
@@ -23130,22 +23567,24 @@
       <c r="AW182" s="15" t="n">
         <v>66936.75</v>
       </c>
-      <c r="AX182" s="16" t="n">
+      <c r="AX182" s="28" t="n">
+        <v>0.8356181365509974</v>
+      </c>
+      <c r="AY182" s="15" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="AZ182" s="16" t="n">
         <v>52587.28</v>
       </c>
-      <c r="AY182" s="16" t="n">
+      <c r="BA182" s="40" t="n"/>
+      <c r="BB182" s="40" t="n"/>
+      <c r="BC182" s="16" t="n">
         <v>62107.01</v>
       </c>
-      <c r="AZ182" s="28" t="n">
-        <v>0.8356181365509974</v>
-      </c>
-      <c r="BA182" s="15" t="n">
-        <v>388.94</v>
-      </c>
-      <c r="BB182" s="5" t="n"/>
-      <c r="BC182" s="5" t="n"/>
       <c r="BD182" s="5" t="n"/>
       <c r="BE182" s="5" t="n"/>
+      <c r="BF182" s="5" t="n"/>
+      <c r="BG182" s="5" t="n"/>
     </row>
     <row r="183" ht="21" customHeight="1" s="30">
       <c r="A183" s="3" t="n">
@@ -23286,31 +23725,33 @@
       <c r="AT183" s="15" t="n">
         <v>-89194.33</v>
       </c>
-      <c r="AU183" s="15" t="n">
+      <c r="AU183" s="33" t="n">
         <v>416.74</v>
       </c>
-      <c r="AV183" s="15" t="n">
+      <c r="AV183" s="33" t="n">
         <v>165.64</v>
       </c>
-      <c r="AW183" s="15" t="n">
+      <c r="AW183" s="33" t="n">
         <v>69029.28</v>
       </c>
-      <c r="AX183" s="16" t="n">
+      <c r="AX183" s="28" t="n">
+        <v>0.8845804673815525</v>
+      </c>
+      <c r="AY183" s="15" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AZ183" s="34" t="n">
         <v>-20165.05</v>
       </c>
-      <c r="AY183" s="16" t="n">
+      <c r="BA183" s="15" t="n"/>
+      <c r="BB183" s="15" t="n"/>
+      <c r="BC183" s="16" t="n">
         <v>-1498.49</v>
       </c>
-      <c r="AZ183" s="28" t="n">
-        <v>0.8845804673815525</v>
-      </c>
-      <c r="BA183" s="15" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="BB183" s="5" t="n"/>
-      <c r="BC183" s="5" t="n"/>
       <c r="BD183" s="5" t="n"/>
       <c r="BE183" s="5" t="n"/>
+      <c r="BF183" s="5" t="n"/>
+      <c r="BG183" s="5" t="n"/>
     </row>
     <row r="184" ht="21" customHeight="1" s="30">
       <c r="A184" s="3" t="n">
@@ -23448,34 +23889,36 @@
       <c r="AS184" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AT184" s="15" t="n">
+      <c r="AT184" s="32" t="n">
         <v>-4116.31</v>
       </c>
-      <c r="AU184" s="15" t="n">
+      <c r="AU184" s="35" t="n">
         <v>426.02</v>
       </c>
-      <c r="AV184" s="15" t="n">
+      <c r="AV184" s="35" t="n">
         <v>1.5</v>
       </c>
-      <c r="AW184" s="15" t="n">
+      <c r="AW184" s="35" t="n">
         <v>636.91</v>
       </c>
-      <c r="AX184" s="16" t="n">
+      <c r="AX184" s="28" t="n">
+        <v>0.1907131011608623</v>
+      </c>
+      <c r="AY184" s="15" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="AZ184" s="36" t="n">
         <v>-3479.41</v>
       </c>
-      <c r="AY184" s="16" t="n">
+      <c r="BA184" s="15" t="n"/>
+      <c r="BB184" s="15" t="n"/>
+      <c r="BC184" s="16" t="n">
         <v>-2059.07</v>
       </c>
-      <c r="AZ184" s="28" t="n">
-        <v>0.1907131011608623</v>
-      </c>
-      <c r="BA184" s="15" t="n">
-        <v>82.11</v>
-      </c>
-      <c r="BB184" s="5" t="n"/>
-      <c r="BC184" s="5" t="n"/>
       <c r="BD184" s="5" t="n"/>
       <c r="BE184" s="5" t="n"/>
+      <c r="BF184" s="5" t="n"/>
+      <c r="BG184" s="5" t="n"/>
     </row>
     <row r="185" ht="21" customHeight="1" s="30">
       <c r="A185" s="3" t="n">
@@ -23613,34 +24056,36 @@
       <c r="AS185" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AT185" s="15" t="n">
+      <c r="AT185" s="32" t="n">
         <v>-5411.21</v>
       </c>
-      <c r="AU185" s="15" t="n">
+      <c r="AU185" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="AV185" s="15" t="n">
+      <c r="AV185" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="AW185" s="0" t="n">
+      <c r="AW185" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="AX185" s="16" t="n">
+      <c r="AX185" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY185" s="15" t="n">
+        <v>-381.67</v>
+      </c>
+      <c r="AZ185" s="36" t="n">
         <v>-5411.21</v>
       </c>
-      <c r="AY185" s="16" t="n">
+      <c r="BA185" s="15" t="n"/>
+      <c r="BB185" s="15" t="n"/>
+      <c r="BC185" s="16" t="n">
         <v>-3059.06</v>
       </c>
-      <c r="AZ185" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA185" s="15" t="n">
-        <v>-381.67</v>
-      </c>
-      <c r="BB185" s="5" t="n"/>
-      <c r="BC185" s="5" t="n"/>
       <c r="BD185" s="5" t="n"/>
       <c r="BE185" s="5" t="n"/>
+      <c r="BF185" s="5" t="n"/>
+      <c r="BG185" s="5" t="n"/>
     </row>
     <row r="186" ht="21" customHeight="1" s="30">
       <c r="A186" s="3" t="n">
@@ -23778,34 +24223,36 @@
       <c r="AS186" s="15" t="n">
         <v>0.12</v>
       </c>
-      <c r="AT186" s="15" t="n">
+      <c r="AT186" s="32" t="n">
         <v>4400.96</v>
       </c>
-      <c r="AU186" s="15" t="n">
+      <c r="AU186" s="35" t="n">
         <v>615.34</v>
       </c>
-      <c r="AV186" s="15" t="n">
+      <c r="AV186" s="35" t="n">
         <v>161.95</v>
       </c>
-      <c r="AW186" s="0" t="n">
+      <c r="AW186" s="35" t="n">
         <v>99652.85000000001</v>
       </c>
-      <c r="AX186" s="16" t="n">
+      <c r="AX186" s="28" t="n">
+        <v>0.8369076533512479</v>
+      </c>
+      <c r="AY186" s="15" t="n">
+        <v>685.91</v>
+      </c>
+      <c r="AZ186" s="36" t="n">
         <v>104053.81</v>
       </c>
-      <c r="AY186" s="16" t="n">
+      <c r="BA186" s="15" t="n"/>
+      <c r="BB186" s="15" t="n"/>
+      <c r="BC186" s="16" t="n">
         <v>113308.19</v>
       </c>
-      <c r="AZ186" s="28" t="n">
-        <v>0.8369076533512479</v>
-      </c>
-      <c r="BA186" s="15" t="n">
-        <v>685.91</v>
-      </c>
-      <c r="BB186" s="5" t="n"/>
-      <c r="BC186" s="5" t="n"/>
       <c r="BD186" s="5" t="n"/>
       <c r="BE186" s="5" t="n"/>
+      <c r="BF186" s="5" t="n"/>
+      <c r="BG186" s="5" t="n"/>
     </row>
     <row r="187" ht="21" customHeight="1" s="30">
       <c r="A187" s="3" t="n">
@@ -23943,34 +24390,36 @@
       <c r="AS187" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AT187" s="15" t="n">
+      <c r="AT187" s="32" t="n">
         <v>-18712.97</v>
       </c>
-      <c r="AU187" s="15" t="n">
+      <c r="AU187" s="35" t="n">
         <v>404.74</v>
       </c>
-      <c r="AV187" s="15" t="n">
+      <c r="AV187" s="35" t="n">
         <v>25.32</v>
       </c>
-      <c r="AW187" s="0" t="n">
+      <c r="AW187" s="35" t="n">
         <v>10228.61</v>
       </c>
-      <c r="AX187" s="16" t="n">
+      <c r="AX187" s="28" t="n">
+        <v>0.7098284368692533</v>
+      </c>
+      <c r="AY187" s="15" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="AZ187" s="36" t="n">
         <v>-8484.35</v>
       </c>
-      <c r="AY187" s="16" t="n">
+      <c r="BA187" s="15" t="n"/>
+      <c r="BB187" s="15" t="n"/>
+      <c r="BC187" s="16" t="n">
         <v>-3562.78</v>
       </c>
-      <c r="AZ187" s="28" t="n">
-        <v>0.7098284368692533</v>
-      </c>
-      <c r="BA187" s="15" t="n">
-        <v>18.12</v>
-      </c>
-      <c r="BB187" s="5" t="n"/>
-      <c r="BC187" s="5" t="n"/>
       <c r="BD187" s="5" t="n"/>
       <c r="BE187" s="5" t="n"/>
+      <c r="BF187" s="5" t="n"/>
+      <c r="BG187" s="5" t="n"/>
     </row>
     <row r="188" ht="21" customHeight="1" s="30">
       <c r="A188" s="3" t="n">
@@ -24108,34 +24557,36 @@
       <c r="AS188" s="15" t="n">
         <v>0.14</v>
       </c>
-      <c r="AT188" s="15" t="n">
+      <c r="AT188" s="32" t="n">
         <v>1478.14</v>
       </c>
-      <c r="AU188" s="15" t="n">
+      <c r="AU188" s="35" t="n">
         <v>523.52</v>
       </c>
-      <c r="AV188" s="15" t="n">
+      <c r="AV188" s="35" t="n">
         <v>169.6</v>
       </c>
-      <c r="AW188" s="0" t="n">
+      <c r="AW188" s="35" t="n">
         <v>88789.06</v>
       </c>
-      <c r="AX188" s="16" t="n">
+      <c r="AX188" s="28" t="n">
+        <v>0.8626909401657231</v>
+      </c>
+      <c r="AY188" s="15" t="n">
+        <v>574.92</v>
+      </c>
+      <c r="AZ188" s="36" t="n">
         <v>90267.2</v>
       </c>
-      <c r="AY188" s="16" t="n">
+      <c r="BA188" s="15" t="n"/>
+      <c r="BB188" s="15" t="n"/>
+      <c r="BC188" s="16" t="n">
         <v>98892.60000000001</v>
       </c>
-      <c r="AZ188" s="28" t="n">
-        <v>0.8626909401657231</v>
-      </c>
-      <c r="BA188" s="15" t="n">
-        <v>574.92</v>
-      </c>
-      <c r="BB188" s="5" t="n"/>
-      <c r="BC188" s="5" t="n"/>
       <c r="BD188" s="5" t="n"/>
       <c r="BE188" s="5" t="n"/>
+      <c r="BF188" s="5" t="n"/>
+      <c r="BG188" s="5" t="n"/>
     </row>
     <row r="189" ht="21" customHeight="1" s="30">
       <c r="A189" s="3" t="n">
@@ -24273,34 +24724,36 @@
       <c r="AS189" s="15" t="n">
         <v>0.11</v>
       </c>
-      <c r="AT189" s="15" t="n">
+      <c r="AT189" s="32" t="n">
         <v>4201.59</v>
       </c>
-      <c r="AU189" s="15" t="n">
+      <c r="AU189" s="35" t="n">
         <v>435.39</v>
       </c>
-      <c r="AV189" s="15" t="n">
+      <c r="AV189" s="35" t="n">
         <v>165.29</v>
       </c>
-      <c r="AW189" s="0" t="n">
+      <c r="AW189" s="35" t="n">
         <v>71961.19</v>
       </c>
-      <c r="AX189" s="16" t="n">
+      <c r="AX189" s="28" t="n">
+        <v>0.8537846465356046</v>
+      </c>
+      <c r="AY189" s="15" t="n">
+        <v>501.02</v>
+      </c>
+      <c r="AZ189" s="36" t="n">
         <v>76162.78</v>
       </c>
-      <c r="AY189" s="16" t="n">
+      <c r="BA189" s="15" t="n"/>
+      <c r="BB189" s="15" t="n"/>
+      <c r="BC189" s="16" t="n">
         <v>84667.03999999999</v>
       </c>
-      <c r="AZ189" s="28" t="n">
-        <v>0.8537846465356046</v>
-      </c>
-      <c r="BA189" s="15" t="n">
-        <v>501.02</v>
-      </c>
-      <c r="BB189" s="5" t="n"/>
-      <c r="BC189" s="5" t="n"/>
       <c r="BD189" s="5" t="n"/>
       <c r="BE189" s="5" t="n"/>
+      <c r="BF189" s="5" t="n"/>
+      <c r="BG189" s="5" t="n"/>
     </row>
     <row r="190" ht="21" customHeight="1" s="30">
       <c r="A190" s="3" t="n">
@@ -24408,27 +24861,70 @@
       <c r="AI190" s="15" t="n">
         <v>51.58</v>
       </c>
-      <c r="AJ190" s="15" t="n"/>
-      <c r="AK190" s="15" t="n"/>
-      <c r="AL190" s="15" t="n"/>
-      <c r="AM190" s="15" t="n"/>
-      <c r="AN190" s="15" t="n"/>
-      <c r="AO190" s="15" t="n"/>
-      <c r="AP190" s="15" t="n"/>
-      <c r="AQ190" s="15" t="n"/>
-      <c r="AR190" s="15" t="n"/>
-      <c r="AS190" s="15" t="n"/>
-      <c r="AT190" s="15" t="n"/>
-      <c r="AU190" s="15" t="n"/>
-      <c r="AV190" s="15" t="n"/>
-      <c r="AX190" s="16" t="n"/>
-      <c r="AY190" s="16" t="n"/>
-      <c r="AZ190" s="28" t="n"/>
-      <c r="BA190" s="15" t="n"/>
-      <c r="BB190" s="5" t="n"/>
-      <c r="BC190" s="5" t="n"/>
+      <c r="AJ190" s="48" t="n">
+        <v>363.7111423014542</v>
+      </c>
+      <c r="AK190" s="48" t="n">
+        <v>-215.177</v>
+      </c>
+      <c r="AL190" s="48" t="n">
+        <v>-78262.272467</v>
+      </c>
+      <c r="AM190" s="48" t="n">
+        <v>-753.1195</v>
+      </c>
+      <c r="AN190" s="48" t="n">
+        <v>-710.0840999999999</v>
+      </c>
+      <c r="AO190" s="48" t="n">
+        <v>-4899.590799999999</v>
+      </c>
+      <c r="AP190" s="48" t="n">
+        <v>-693.6533759999998</v>
+      </c>
+      <c r="AQ190" s="48" t="n">
+        <v>624.0133</v>
+      </c>
+      <c r="AR190" s="48" t="n">
+        <v>-10263.32484199245</v>
+      </c>
+      <c r="AS190" s="48" t="n">
+        <v>0.6765550025</v>
+      </c>
+      <c r="AT190" s="49" t="n">
+        <v>-94958.03178499245</v>
+      </c>
+      <c r="AU190" s="50" t="n">
+        <v>416.6165402726146</v>
+      </c>
+      <c r="AV190" s="50" t="n">
+        <v>189.645</v>
+      </c>
+      <c r="AW190" s="73" t="n">
+        <v>79009.24378</v>
+      </c>
+      <c r="AX190" s="51" t="n">
+        <v>0.8813441957086492</v>
+      </c>
+      <c r="AY190" s="48" t="n">
+        <v>52.90539797116043</v>
+      </c>
+      <c r="AZ190" s="72" t="n">
+        <v>746.9713130000018</v>
+      </c>
+      <c r="BA190" s="70" t="n">
+        <v>20981.27</v>
+      </c>
+      <c r="BB190" s="70" t="n">
+        <v>-16695.75931799244</v>
+      </c>
+      <c r="BC190" s="71" t="n">
+        <v>5032.481995007558</v>
+      </c>
       <c r="BD190" s="5" t="n"/>
       <c r="BE190" s="5" t="n"/>
+      <c r="BF190" s="5" t="n"/>
+      <c r="BG190" s="5" t="n"/>
     </row>
     <row r="191" ht="21" customHeight="1" s="30">
       <c r="A191" s="3" t="n">
@@ -24536,27 +25032,70 @@
       <c r="AI191" s="15" t="n">
         <v>52.59</v>
       </c>
-      <c r="AJ191" s="15" t="n"/>
-      <c r="AK191" s="15" t="n"/>
-      <c r="AL191" s="15" t="n"/>
-      <c r="AM191" s="15" t="n"/>
-      <c r="AN191" s="15" t="n"/>
-      <c r="AO191" s="15" t="n"/>
-      <c r="AP191" s="15" t="n"/>
-      <c r="AQ191" s="15" t="n"/>
-      <c r="AR191" s="15" t="n"/>
-      <c r="AS191" s="15" t="n"/>
-      <c r="AT191" s="15" t="n"/>
-      <c r="AU191" s="15" t="n"/>
-      <c r="AV191" s="15" t="n"/>
-      <c r="AX191" s="16" t="n"/>
-      <c r="AY191" s="16" t="n"/>
-      <c r="AZ191" s="28" t="n"/>
-      <c r="BA191" s="15" t="n"/>
-      <c r="BB191" s="5" t="n"/>
-      <c r="BC191" s="5" t="n"/>
+      <c r="AJ191" s="48" t="n">
+        <v>327.8694297937692</v>
+      </c>
+      <c r="AK191" s="48" t="n">
+        <v>-18.232</v>
+      </c>
+      <c r="AL191" s="48" t="n">
+        <v>-5977.715444</v>
+      </c>
+      <c r="AM191" s="48" t="n">
+        <v>-63.812</v>
+      </c>
+      <c r="AN191" s="48" t="n">
+        <v>-60.1656</v>
+      </c>
+      <c r="AO191" s="48" t="n">
+        <v>-3009.3758</v>
+      </c>
+      <c r="AP191" s="48" t="n">
+        <v>-426.048576</v>
+      </c>
+      <c r="AQ191" s="48" t="n">
+        <v>52.8728</v>
+      </c>
+      <c r="AR191" s="48" t="n">
+        <v>-1285.356</v>
+      </c>
+      <c r="AS191" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT191" s="49" t="n">
+        <v>-10769.60062</v>
+      </c>
+      <c r="AU191" s="50" t="n">
+        <v>381.3540741176471</v>
+      </c>
+      <c r="AV191" s="50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW191" s="73" t="n">
+        <v>972.452889</v>
+      </c>
+      <c r="AX191" s="28" t="n">
+        <v>0.1398639754278192</v>
+      </c>
+      <c r="AY191" s="48" t="n">
+        <v>53.48464432387789</v>
+      </c>
+      <c r="AZ191" s="72" t="n">
+        <v>-5005.262555</v>
+      </c>
+      <c r="BA191" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB191" s="70" t="n">
+        <v>-4791.885176</v>
+      </c>
+      <c r="BC191" s="71" t="n">
+        <v>-9797.147731000001</v>
+      </c>
       <c r="BD191" s="5" t="n"/>
       <c r="BE191" s="5" t="n"/>
+      <c r="BF191" s="5" t="n"/>
+      <c r="BG191" s="5" t="n"/>
     </row>
     <row r="192" ht="21" customHeight="1" s="30">
       <c r="A192" s="3" t="n">
@@ -24664,27 +25203,70 @@
       <c r="AI192" s="15" t="n">
         <v>80.37</v>
       </c>
-      <c r="AJ192" s="15" t="n"/>
-      <c r="AK192" s="15" t="n"/>
-      <c r="AL192" s="15" t="n"/>
-      <c r="AM192" s="15" t="n"/>
-      <c r="AN192" s="15" t="n"/>
-      <c r="AO192" s="15" t="n"/>
-      <c r="AP192" s="15" t="n"/>
-      <c r="AQ192" s="15" t="n"/>
-      <c r="AR192" s="15" t="n"/>
-      <c r="AS192" s="15" t="n"/>
-      <c r="AT192" s="15" t="n"/>
-      <c r="AU192" s="15" t="n"/>
-      <c r="AV192" s="15" t="n"/>
-      <c r="AX192" s="16" t="n"/>
-      <c r="AY192" s="16" t="n"/>
-      <c r="AZ192" s="28" t="n"/>
-      <c r="BA192" s="15" t="n"/>
-      <c r="BB192" s="5" t="n"/>
-      <c r="BC192" s="5" t="n"/>
+      <c r="AJ192" s="48" t="n">
+        <v>379.2823258162514</v>
+      </c>
+      <c r="AK192" s="48" t="n">
+        <v>-96.447</v>
+      </c>
+      <c r="AL192" s="48" t="n">
+        <v>-36580.642478</v>
+      </c>
+      <c r="AM192" s="48" t="n">
+        <v>-337.5645</v>
+      </c>
+      <c r="AN192" s="48" t="n">
+        <v>-318.2751</v>
+      </c>
+      <c r="AO192" s="48" t="n">
+        <v>-3087.095300000001</v>
+      </c>
+      <c r="AP192" s="48" t="n">
+        <v>-437.0516160000002</v>
+      </c>
+      <c r="AQ192" s="48" t="n">
+        <v>279.6963</v>
+      </c>
+      <c r="AR192" s="48" t="n">
+        <v>-6799.5135</v>
+      </c>
+      <c r="AS192" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT192" s="49" t="n">
+        <v>-47280.446194</v>
+      </c>
+      <c r="AU192" s="50" t="n">
+        <v>426.442130985565</v>
+      </c>
+      <c r="AV192" s="50" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="AW192" s="73" t="n">
+        <v>34268.889646</v>
+      </c>
+      <c r="AX192" s="28" t="n">
+        <v>0.8332037284726326</v>
+      </c>
+      <c r="AY192" s="48" t="n">
+        <v>47.15980516931364</v>
+      </c>
+      <c r="AZ192" s="72" t="n">
+        <v>-2311.752831999998</v>
+      </c>
+      <c r="BA192" s="70" t="n">
+        <v>12184.2</v>
+      </c>
+      <c r="BB192" s="70" t="n">
+        <v>-10699.803716</v>
+      </c>
+      <c r="BC192" s="71" t="n">
+        <v>-827.3565479999979</v>
+      </c>
       <c r="BD192" s="5" t="n"/>
       <c r="BE192" s="5" t="n"/>
+      <c r="BF192" s="5" t="n"/>
+      <c r="BG192" s="5" t="n"/>
     </row>
     <row r="193" ht="21" customHeight="1" s="30">
       <c r="A193" s="3" t="n">
@@ -24792,27 +25374,70 @@
       <c r="AI193" s="15" t="n">
         <v>757.55</v>
       </c>
-      <c r="AJ193" s="15" t="n"/>
-      <c r="AK193" s="15" t="n"/>
-      <c r="AL193" s="15" t="n"/>
-      <c r="AM193" s="15" t="n"/>
-      <c r="AN193" s="15" t="n"/>
-      <c r="AO193" s="15" t="n"/>
-      <c r="AP193" s="15" t="n"/>
-      <c r="AQ193" s="15" t="n"/>
-      <c r="AR193" s="15" t="n"/>
-      <c r="AS193" s="15" t="n"/>
-      <c r="AT193" s="15" t="n"/>
-      <c r="AU193" s="15" t="n"/>
-      <c r="AV193" s="15" t="n"/>
-      <c r="AX193" s="16" t="n"/>
-      <c r="AY193" s="16" t="n"/>
-      <c r="AZ193" s="28" t="n"/>
-      <c r="BA193" s="15" t="n"/>
-      <c r="BB193" s="5" t="n"/>
-      <c r="BC193" s="5" t="n"/>
+      <c r="AJ193" s="48" t="n">
+        <v>-68.84533855156675</v>
+      </c>
+      <c r="AK193" s="48" t="n">
+        <v>-194.127</v>
+      </c>
+      <c r="AL193" s="48" t="n">
+        <v>13364.739037</v>
+      </c>
+      <c r="AM193" s="48" t="n">
+        <v>-679.4445000000001</v>
+      </c>
+      <c r="AN193" s="48" t="n">
+        <v>-640.6191</v>
+      </c>
+      <c r="AO193" s="48" t="n">
+        <v>-6157.8791</v>
+      </c>
+      <c r="AP193" s="48" t="n">
+        <v>-871.793952</v>
+      </c>
+      <c r="AQ193" s="48" t="n">
+        <v>562.9683</v>
+      </c>
+      <c r="AR193" s="48" t="n">
+        <v>-1599.460937766084</v>
+      </c>
+      <c r="AS193" s="48" t="n">
+        <v>0.1168687982</v>
+      </c>
+      <c r="AT193" s="49" t="n">
+        <v>3978.509747233917</v>
+      </c>
+      <c r="AU193" s="50" t="n">
+        <v>693.6515735815055</v>
+      </c>
+      <c r="AV193" s="50" t="n">
+        <v>162.038</v>
+      </c>
+      <c r="AW193" s="73" t="n">
+        <v>112397.91368</v>
+      </c>
+      <c r="AX193" s="28" t="n">
+        <v>0.8347009947096489</v>
+      </c>
+      <c r="AY193" s="48" t="n">
+        <v>762.4969121330723</v>
+      </c>
+      <c r="AZ193" s="72" t="n">
+        <v>125762.652717</v>
+      </c>
+      <c r="BA193" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB193" s="70" t="n">
+        <v>-9386.229289766083</v>
+      </c>
+      <c r="BC193" s="71" t="n">
+        <v>116376.4234272339</v>
+      </c>
       <c r="BD193" s="5" t="n"/>
       <c r="BE193" s="5" t="n"/>
+      <c r="BF193" s="5" t="n"/>
+      <c r="BG193" s="5" t="n"/>
     </row>
     <row r="194" ht="21" customHeight="1" s="30">
       <c r="A194" s="3" t="n">
@@ -24920,27 +25545,70 @@
       <c r="AI194" s="15" t="n">
         <v>596.11</v>
       </c>
-      <c r="AJ194" s="15" t="n"/>
-      <c r="AK194" s="15" t="n"/>
-      <c r="AL194" s="15" t="n"/>
-      <c r="AM194" s="15" t="n"/>
-      <c r="AN194" s="15" t="n"/>
-      <c r="AO194" s="15" t="n"/>
-      <c r="AP194" s="15" t="n"/>
-      <c r="AQ194" s="15" t="n"/>
-      <c r="AR194" s="15" t="n"/>
-      <c r="AS194" s="15" t="n"/>
-      <c r="AT194" s="15" t="n"/>
-      <c r="AU194" s="15" t="n"/>
-      <c r="AV194" s="15" t="n"/>
-      <c r="AX194" s="16" t="n"/>
-      <c r="AY194" s="16" t="n"/>
-      <c r="AZ194" s="28" t="n"/>
-      <c r="BA194" s="15" t="n"/>
-      <c r="BB194" s="5" t="n"/>
-      <c r="BC194" s="5" t="n"/>
+      <c r="AJ194" s="48" t="n">
+        <v>-62.45206039695229</v>
+      </c>
+      <c r="AK194" s="48" t="n">
+        <v>-192.013</v>
+      </c>
+      <c r="AL194" s="48" t="n">
+        <v>11991.607473</v>
+      </c>
+      <c r="AM194" s="48" t="n">
+        <v>-672.0455000000001</v>
+      </c>
+      <c r="AN194" s="48" t="n">
+        <v>-633.6428999999999</v>
+      </c>
+      <c r="AO194" s="48" t="n">
+        <v>-5414.842300000001</v>
+      </c>
+      <c r="AP194" s="48" t="n">
+        <v>-766.5994560000001</v>
+      </c>
+      <c r="AQ194" s="48" t="n">
+        <v>556.8377</v>
+      </c>
+      <c r="AR194" s="48" t="n">
+        <v>-1433.946443950444</v>
+      </c>
+      <c r="AS194" s="48" t="n">
+        <v>0.1059285875</v>
+      </c>
+      <c r="AT194" s="49" t="n">
+        <v>3627.368573049554</v>
+      </c>
+      <c r="AU194" s="50" t="n">
+        <v>516.9518730432977</v>
+      </c>
+      <c r="AV194" s="50" t="n">
+        <v>163.796</v>
+      </c>
+      <c r="AW194" s="73" t="n">
+        <v>84674.648997</v>
+      </c>
+      <c r="AX194" s="28" t="n">
+        <v>0.8530464083161036</v>
+      </c>
+      <c r="AY194" s="48" t="n">
+        <v>579.4039334402501</v>
+      </c>
+      <c r="AZ194" s="72" t="n">
+        <v>96666.25646999999</v>
+      </c>
+      <c r="BA194" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB194" s="70" t="n">
+        <v>-8364.238899950446</v>
+      </c>
+      <c r="BC194" s="71" t="n">
+        <v>88302.01757004955</v>
+      </c>
       <c r="BD194" s="5" t="n"/>
       <c r="BE194" s="5" t="n"/>
+      <c r="BF194" s="5" t="n"/>
+      <c r="BG194" s="5" t="n"/>
     </row>
     <row r="195" ht="21" customHeight="1" s="30">
       <c r="A195" s="3" t="n">
@@ -25048,27 +25716,70 @@
       <c r="AI195" s="15" t="n">
         <v>479.13</v>
       </c>
-      <c r="AJ195" s="15" t="n"/>
-      <c r="AK195" s="15" t="n"/>
-      <c r="AL195" s="15" t="n"/>
-      <c r="AM195" s="15" t="n"/>
-      <c r="AN195" s="15" t="n"/>
-      <c r="AO195" s="15" t="n"/>
-      <c r="AP195" s="15" t="n"/>
-      <c r="AQ195" s="15" t="n"/>
-      <c r="AR195" s="15" t="n"/>
-      <c r="AS195" s="15" t="n"/>
-      <c r="AT195" s="15" t="n"/>
-      <c r="AU195" s="15" t="n"/>
-      <c r="AV195" s="15" t="n"/>
-      <c r="AX195" s="16" t="n"/>
-      <c r="AY195" s="16" t="n"/>
-      <c r="AZ195" s="28" t="n"/>
-      <c r="BA195" s="15" t="n"/>
-      <c r="BB195" s="5" t="n"/>
-      <c r="BC195" s="5" t="n"/>
+      <c r="AJ195" s="48" t="n">
+        <v>-57.97323468532337</v>
+      </c>
+      <c r="AK195" s="48" t="n">
+        <v>-193.246</v>
+      </c>
+      <c r="AL195" s="48" t="n">
+        <v>11203.09571</v>
+      </c>
+      <c r="AM195" s="48" t="n">
+        <v>-676.361</v>
+      </c>
+      <c r="AN195" s="48" t="n">
+        <v>-637.7118</v>
+      </c>
+      <c r="AO195" s="48" t="n">
+        <v>-6022.589600000001</v>
+      </c>
+      <c r="AP195" s="48" t="n">
+        <v>-852.6405120000002</v>
+      </c>
+      <c r="AQ195" s="48" t="n">
+        <v>560.4134</v>
+      </c>
+      <c r="AR195" s="48" t="n">
+        <v>-2550.463718067332</v>
+      </c>
+      <c r="AS195" s="48" t="n">
+        <v>0.1872058947</v>
+      </c>
+      <c r="AT195" s="49" t="n">
+        <v>1023.742479932666</v>
+      </c>
+      <c r="AU195" s="50" t="n">
+        <v>394.088985691515</v>
+      </c>
+      <c r="AV195" s="50" t="n">
+        <v>161.862</v>
+      </c>
+      <c r="AW195" s="73" t="n">
+        <v>63788.031402</v>
+      </c>
+      <c r="AX195" s="28" t="n">
+        <v>0.8375956035312503</v>
+      </c>
+      <c r="AY195" s="48" t="n">
+        <v>452.0622203768384</v>
+      </c>
+      <c r="AZ195" s="72" t="n">
+        <v>74991.127112</v>
+      </c>
+      <c r="BA195" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB195" s="70" t="n">
+        <v>-10179.35323006733</v>
+      </c>
+      <c r="BC195" s="71" t="n">
+        <v>64811.77388193267</v>
+      </c>
       <c r="BD195" s="5" t="n"/>
       <c r="BE195" s="5" t="n"/>
+      <c r="BF195" s="5" t="n"/>
+      <c r="BG195" s="5" t="n"/>
     </row>
     <row r="196" ht="21" customHeight="1" s="30">
       <c r="A196" s="3" t="n">
@@ -25176,27 +25887,70 @@
       <c r="AI196" s="15" t="n">
         <v>460.05</v>
       </c>
-      <c r="AJ196" s="15" t="n"/>
-      <c r="AK196" s="15" t="n"/>
-      <c r="AL196" s="15" t="n"/>
-      <c r="AM196" s="15" t="n"/>
-      <c r="AN196" s="15" t="n"/>
-      <c r="AO196" s="15" t="n"/>
-      <c r="AP196" s="15" t="n"/>
-      <c r="AQ196" s="15" t="n"/>
-      <c r="AR196" s="15" t="n"/>
-      <c r="AS196" s="15" t="n"/>
-      <c r="AT196" s="15" t="n"/>
-      <c r="AU196" s="15" t="n"/>
-      <c r="AV196" s="15" t="n"/>
-      <c r="AX196" s="16" t="n"/>
-      <c r="AY196" s="16" t="n"/>
-      <c r="AZ196" s="28" t="n"/>
-      <c r="BA196" s="15" t="n"/>
-      <c r="BB196" s="5" t="n"/>
-      <c r="BC196" s="5" t="n"/>
+      <c r="AJ196" s="48" t="n">
+        <v>-62.03064258434284</v>
+      </c>
+      <c r="AK196" s="48" t="n">
+        <v>-191.925</v>
+      </c>
+      <c r="AL196" s="48" t="n">
+        <v>11905.231078</v>
+      </c>
+      <c r="AM196" s="48" t="n">
+        <v>-671.7375000000001</v>
+      </c>
+      <c r="AN196" s="48" t="n">
+        <v>-633.3525</v>
+      </c>
+      <c r="AO196" s="48" t="n">
+        <v>-6157.111500000002</v>
+      </c>
+      <c r="AP196" s="48" t="n">
+        <v>-871.6852800000001</v>
+      </c>
+      <c r="AQ196" s="48" t="n">
+        <v>556.5825</v>
+      </c>
+      <c r="AR196" s="48" t="n">
+        <v>-1421.30731508541</v>
+      </c>
+      <c r="AS196" s="48" t="n">
+        <v>0.1050430504</v>
+      </c>
+      <c r="AT196" s="49" t="n">
+        <v>2706.619482914588</v>
+      </c>
+      <c r="AU196" s="50" t="n">
+        <v>374.8328886261261</v>
+      </c>
+      <c r="AV196" s="50" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AW196" s="73" t="n">
+        <v>59913.288918</v>
+      </c>
+      <c r="AX196" s="28" t="n">
+        <v>0.8328253223915592</v>
+      </c>
+      <c r="AY196" s="48" t="n">
+        <v>436.863531210469</v>
+      </c>
+      <c r="AZ196" s="72" t="n">
+        <v>71818.519996</v>
+      </c>
+      <c r="BA196" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB196" s="70" t="n">
+        <v>-9198.611595085413</v>
+      </c>
+      <c r="BC196" s="71" t="n">
+        <v>62619.90840091459</v>
+      </c>
       <c r="BD196" s="5" t="n"/>
       <c r="BE196" s="5" t="n"/>
+      <c r="BF196" s="5" t="n"/>
+      <c r="BG196" s="5" t="n"/>
     </row>
     <row r="197" ht="21" customHeight="1" s="30">
       <c r="A197" s="3" t="n">
@@ -25253,183 +26007,519 @@
       <c r="R197" s="9" t="n">
         <v>691.95</v>
       </c>
-      <c r="S197" s="14" t="n"/>
-      <c r="T197" s="14" t="n"/>
-      <c r="U197" s="14" t="n"/>
-      <c r="V197" s="14" t="n"/>
-      <c r="W197" s="14" t="n"/>
-      <c r="X197" s="14" t="n"/>
-      <c r="Y197" s="14" t="n"/>
-      <c r="Z197" s="14" t="n"/>
-      <c r="AA197" s="14" t="n"/>
-      <c r="AB197" s="31" t="n"/>
-      <c r="AC197" s="14" t="n"/>
-      <c r="AD197" s="14" t="n"/>
-      <c r="AE197" s="14" t="n"/>
-      <c r="AF197" s="16" t="n"/>
-      <c r="AG197" s="16" t="n"/>
-      <c r="AH197" s="28" t="n"/>
-      <c r="AI197" s="15" t="n"/>
-      <c r="AJ197" s="15" t="n"/>
-      <c r="AK197" s="15" t="n"/>
-      <c r="AL197" s="15" t="n"/>
-      <c r="AM197" s="15" t="n"/>
-      <c r="AN197" s="15" t="n"/>
-      <c r="AO197" s="15" t="n"/>
-      <c r="AP197" s="15" t="n"/>
-      <c r="AQ197" s="15" t="n"/>
-      <c r="AR197" s="15" t="n"/>
-      <c r="AS197" s="15" t="n"/>
-      <c r="AT197" s="15" t="n"/>
-      <c r="AU197" s="15" t="n"/>
-      <c r="AV197" s="15" t="n"/>
-      <c r="AX197" s="16" t="n"/>
-      <c r="AY197" s="16" t="n"/>
-      <c r="AZ197" s="28" t="n"/>
-      <c r="BA197" s="15" t="n"/>
-      <c r="BB197" s="5" t="n"/>
-      <c r="BC197" s="5" t="n"/>
+      <c r="S197" s="14" t="n">
+        <v>-88.56</v>
+      </c>
+      <c r="T197" s="14" t="n">
+        <v>-175.16</v>
+      </c>
+      <c r="U197" s="14" t="n">
+        <v>15513</v>
+      </c>
+      <c r="V197" s="14" t="n">
+        <v>-613.0700000000001</v>
+      </c>
+      <c r="W197" s="14" t="n">
+        <v>-578.04</v>
+      </c>
+      <c r="X197" s="14" t="n">
+        <v>-702.83</v>
+      </c>
+      <c r="Y197" s="14" t="n">
+        <v>-99.5</v>
+      </c>
+      <c r="Z197" s="14" t="n">
+        <v>507.97</v>
+      </c>
+      <c r="AA197" s="14" t="n">
+        <v>-1612.42</v>
+      </c>
+      <c r="AB197" s="31" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AC197" s="14" t="n">
+        <v>12415.11</v>
+      </c>
+      <c r="AD197" s="14" t="n">
+        <v>577.3</v>
+      </c>
+      <c r="AE197" s="14" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="AF197" s="16" t="n">
+        <v>99007.72</v>
+      </c>
+      <c r="AG197" s="16" t="n">
+        <v>111422.82</v>
+      </c>
+      <c r="AH197" s="28" t="n">
+        <v>0.9790908442160851</v>
+      </c>
+      <c r="AI197" s="15" t="n">
+        <v>665.87</v>
+      </c>
+      <c r="AJ197" s="48" t="n">
+        <v>-74.30022011481105</v>
+      </c>
+      <c r="AK197" s="48" t="n">
+        <v>-187.961</v>
+      </c>
+      <c r="AL197" s="48" t="n">
+        <v>13965.543673</v>
+      </c>
+      <c r="AM197" s="48" t="n">
+        <v>-657.8635</v>
+      </c>
+      <c r="AN197" s="48" t="n">
+        <v>-620.2713</v>
+      </c>
+      <c r="AO197" s="48" t="n">
+        <v>-5025.285300000004</v>
+      </c>
+      <c r="AP197" s="48" t="n">
+        <v>-711.4484160000005</v>
+      </c>
+      <c r="AQ197" s="48" t="n">
+        <v>545.0869</v>
+      </c>
+      <c r="AR197" s="48" t="n">
+        <v>-1325.12505</v>
+      </c>
+      <c r="AS197" s="48" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT197" s="49" t="n">
+        <v>6170.637006999996</v>
+      </c>
+      <c r="AU197" s="50" t="n">
+        <v>580.9814891391695</v>
+      </c>
+      <c r="AV197" s="50" t="n">
+        <v>161.774</v>
+      </c>
+      <c r="AW197" s="73" t="n">
+        <v>93987.69942400001</v>
+      </c>
+      <c r="AX197" s="28" t="n">
+        <v>0.8606785450173173</v>
+      </c>
+      <c r="AY197" s="48" t="n">
+        <v>655.2817092539806</v>
+      </c>
+      <c r="AZ197" s="72" t="n">
+        <v>107953.243097</v>
+      </c>
+      <c r="BA197" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB197" s="70" t="n">
+        <v>-7794.906666000004</v>
+      </c>
+      <c r="BC197" s="71" t="n">
+        <v>100158.336431</v>
+      </c>
       <c r="BD197" s="5" t="n"/>
       <c r="BE197" s="5" t="n"/>
+      <c r="BF197" s="5" t="n"/>
+      <c r="BG197" s="5" t="n"/>
     </row>
     <row r="198" ht="21" customHeight="1" s="30">
       <c r="A198" s="3" t="n">
         <v>46175</v>
       </c>
-      <c r="B198" s="10" t="n"/>
-      <c r="C198" s="10" t="n"/>
-      <c r="D198" s="10" t="n"/>
-      <c r="E198" s="10" t="n"/>
-      <c r="F198" s="10" t="n"/>
-      <c r="G198" s="10" t="n"/>
-      <c r="H198" s="10" t="n"/>
-      <c r="I198" s="10" t="n"/>
-      <c r="J198" s="10" t="n"/>
-      <c r="K198" s="10" t="n"/>
-      <c r="L198" s="10" t="n"/>
-      <c r="M198" s="10" t="n"/>
-      <c r="N198" s="10" t="n"/>
-      <c r="P198" s="11" t="n"/>
-      <c r="Q198" s="26" t="n"/>
-      <c r="R198" s="9" t="n"/>
-      <c r="S198" s="14" t="n"/>
-      <c r="T198" s="14" t="n"/>
-      <c r="U198" s="14" t="n"/>
-      <c r="V198" s="14" t="n"/>
-      <c r="W198" s="14" t="n"/>
-      <c r="X198" s="14" t="n"/>
-      <c r="Y198" s="14" t="n"/>
-      <c r="Z198" s="14" t="n"/>
-      <c r="AA198" s="14" t="n"/>
-      <c r="AB198" s="31" t="n"/>
-      <c r="AC198" s="14" t="n"/>
-      <c r="AD198" s="14" t="n"/>
-      <c r="AE198" s="14" t="n"/>
-      <c r="AF198" s="16" t="n"/>
-      <c r="AG198" s="16" t="n"/>
-      <c r="AH198" s="28" t="n"/>
-      <c r="AI198" s="15" t="n"/>
-      <c r="AJ198" s="15" t="n"/>
-      <c r="AK198" s="15" t="n"/>
-      <c r="AL198" s="15" t="n"/>
-      <c r="AM198" s="15" t="n"/>
-      <c r="AN198" s="15" t="n"/>
-      <c r="AO198" s="15" t="n"/>
-      <c r="AP198" s="15" t="n"/>
-      <c r="AQ198" s="15" t="n"/>
-      <c r="AR198" s="15" t="n"/>
-      <c r="AS198" s="15" t="n"/>
-      <c r="AT198" s="15" t="n"/>
-      <c r="AU198" s="15" t="n"/>
-      <c r="AV198" s="15" t="n"/>
-      <c r="AX198" s="16" t="n"/>
-      <c r="AY198" s="16" t="n"/>
-      <c r="AZ198" s="28" t="n"/>
-      <c r="BA198" s="15" t="n"/>
-      <c r="BB198" s="5" t="n"/>
-      <c r="BC198" s="5" t="n"/>
+      <c r="B198" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C198" s="10" t="n">
+        <v>-178</v>
+      </c>
+      <c r="D198" s="10" t="n">
+        <v>14239.8</v>
+      </c>
+      <c r="E198" s="10" t="n">
+        <v>-622.99</v>
+      </c>
+      <c r="F198" s="10" t="n">
+        <v>-587.39</v>
+      </c>
+      <c r="G198" s="10" t="n">
+        <v>-882.26</v>
+      </c>
+      <c r="H198" s="10" t="n">
+        <v>-124.9</v>
+      </c>
+      <c r="I198" s="10" t="n">
+        <v>516.1900000000001</v>
+      </c>
+      <c r="J198" s="10" t="n">
+        <v>-1466.38</v>
+      </c>
+      <c r="K198" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L198" s="10" t="n">
+        <v>11072.06</v>
+      </c>
+      <c r="M198" s="10" t="n">
+        <v>618.3099999999999</v>
+      </c>
+      <c r="N198" s="10" t="n">
+        <v>173.4</v>
+      </c>
+      <c r="O198" s="0" t="n">
+        <v>107214.21</v>
+      </c>
+      <c r="P198" s="11" t="n">
+        <v>118286.27</v>
+      </c>
+      <c r="Q198" s="26" t="n">
+        <v>0.9741709855475497</v>
+      </c>
+      <c r="R198" s="9" t="n">
+        <v>698.3099999999999</v>
+      </c>
+      <c r="S198" s="14" t="n">
+        <v>-98.2</v>
+      </c>
+      <c r="T198" s="14" t="n">
+        <v>-178.08</v>
+      </c>
+      <c r="U198" s="14" t="n">
+        <v>17487.2</v>
+      </c>
+      <c r="V198" s="14" t="n">
+        <v>-623.28</v>
+      </c>
+      <c r="W198" s="14" t="n">
+        <v>-587.66</v>
+      </c>
+      <c r="X198" s="14" t="n">
+        <v>-913.4400000000001</v>
+      </c>
+      <c r="Y198" s="14" t="n">
+        <v>-129.32</v>
+      </c>
+      <c r="Z198" s="14" t="n">
+        <v>516.4299999999999</v>
+      </c>
+      <c r="AA198" s="14" t="n">
+        <v>-1678.46</v>
+      </c>
+      <c r="AB198" s="31" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AC198" s="14" t="n">
+        <v>14071.46</v>
+      </c>
+      <c r="AD198" s="14" t="n">
+        <v>518.1799999999999</v>
+      </c>
+      <c r="AE198" s="14" t="n">
+        <v>173.32</v>
+      </c>
+      <c r="AF198" s="16" t="n">
+        <v>89810.22</v>
+      </c>
+      <c r="AG198" s="16" t="n">
+        <v>103881.68</v>
+      </c>
+      <c r="AH198" s="28" t="n">
+        <v>0.9732704402515724</v>
+      </c>
+      <c r="AI198" s="15" t="n">
+        <v>616.37</v>
+      </c>
+      <c r="AJ198" s="48" t="n">
+        <v>-80.11985657150882</v>
+      </c>
+      <c r="AK198" s="48" t="n">
+        <v>-192.277</v>
+      </c>
+      <c r="AL198" s="48" t="n">
+        <v>15405.205662</v>
+      </c>
+      <c r="AM198" s="48" t="n">
+        <v>-672.9694999999999</v>
+      </c>
+      <c r="AN198" s="48" t="n">
+        <v>-634.5140999999999</v>
+      </c>
+      <c r="AO198" s="48" t="n">
+        <v>-5397.955099999997</v>
+      </c>
+      <c r="AP198" s="48" t="n">
+        <v>-764.2086719999996</v>
+      </c>
+      <c r="AQ198" s="48" t="n">
+        <v>557.6033</v>
+      </c>
+      <c r="AR198" s="48" t="n">
+        <v>-1399.093742985376</v>
+      </c>
+      <c r="AS198" s="48" t="n">
+        <v>0.1032120395</v>
+      </c>
+      <c r="AT198" s="49" t="n">
+        <v>7094.067847014628</v>
+      </c>
+      <c r="AU198" s="50" t="n">
+        <v>517.1247554341204</v>
+      </c>
+      <c r="AV198" s="50" t="n">
+        <v>164.148</v>
+      </c>
+      <c r="AW198" s="73" t="n">
+        <v>84884.994355</v>
+      </c>
+      <c r="AX198" s="28" t="n">
+        <v>0.8537058514538921</v>
+      </c>
+      <c r="AY198" s="48" t="n">
+        <v>597.2446120056293</v>
+      </c>
+      <c r="AZ198" s="72" t="n">
+        <v>100290.200017</v>
+      </c>
+      <c r="BA198" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB198" s="70" t="n">
+        <v>-8311.137814985374</v>
+      </c>
+      <c r="BC198" s="71" t="n">
+        <v>91979.06220201463</v>
+      </c>
       <c r="BD198" s="5" t="n"/>
       <c r="BE198" s="5" t="n"/>
+      <c r="BF198" s="5" t="n"/>
+      <c r="BG198" s="5" t="n"/>
     </row>
     <row r="199" ht="21" customHeight="1" s="30">
       <c r="A199" s="3" t="n">
         <v>46176</v>
       </c>
-      <c r="B199" s="10" t="n"/>
-      <c r="C199" s="10" t="n"/>
-      <c r="D199" s="10" t="n"/>
-      <c r="E199" s="10" t="n"/>
-      <c r="F199" s="10" t="n"/>
-      <c r="G199" s="10" t="n"/>
-      <c r="H199" s="10" t="n"/>
-      <c r="I199" s="10" t="n"/>
-      <c r="J199" s="10" t="n"/>
-      <c r="K199" s="10" t="n"/>
-      <c r="L199" s="10" t="n"/>
-      <c r="M199" s="10" t="n"/>
-      <c r="N199" s="10" t="n"/>
-      <c r="P199" s="11" t="n"/>
-      <c r="Q199" s="26" t="n"/>
-      <c r="R199" s="9" t="n"/>
-      <c r="S199" s="14" t="n"/>
-      <c r="T199" s="14" t="n"/>
-      <c r="U199" s="14" t="n"/>
-      <c r="V199" s="14" t="n"/>
-      <c r="W199" s="14" t="n"/>
-      <c r="X199" s="14" t="n"/>
-      <c r="Y199" s="14" t="n"/>
-      <c r="Z199" s="14" t="n"/>
-      <c r="AA199" s="14" t="n"/>
-      <c r="AB199" s="31" t="n"/>
-      <c r="AC199" s="14" t="n"/>
-      <c r="AD199" s="14" t="n"/>
-      <c r="AE199" s="14" t="n"/>
-      <c r="AF199" s="16" t="n"/>
-      <c r="AG199" s="16" t="n"/>
-      <c r="AH199" s="28" t="n"/>
-      <c r="AI199" s="15" t="n"/>
-      <c r="AJ199" s="15" t="n"/>
-      <c r="AK199" s="15" t="n"/>
-      <c r="AL199" s="15" t="n"/>
-      <c r="AM199" s="15" t="n"/>
-      <c r="AN199" s="15" t="n"/>
-      <c r="AO199" s="15" t="n"/>
-      <c r="AP199" s="15" t="n"/>
-      <c r="AQ199" s="15" t="n"/>
-      <c r="AR199" s="15" t="n"/>
-      <c r="AS199" s="15" t="n"/>
-      <c r="AT199" s="15" t="n"/>
-      <c r="AU199" s="15" t="n"/>
-      <c r="AV199" s="15" t="n"/>
-      <c r="AX199" s="16" t="n"/>
-      <c r="AY199" s="16" t="n"/>
-      <c r="AZ199" s="28" t="n"/>
-      <c r="BA199" s="15" t="n"/>
-      <c r="BB199" s="5" t="n"/>
-      <c r="BC199" s="5" t="n"/>
+      <c r="B199" s="10" t="n">
+        <v>-81.27</v>
+      </c>
+      <c r="C199" s="10" t="n">
+        <v>-178</v>
+      </c>
+      <c r="D199" s="10" t="n">
+        <v>14465.56</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>-623</v>
+      </c>
+      <c r="F199" s="10" t="n">
+        <v>-587.4</v>
+      </c>
+      <c r="G199" s="10" t="n">
+        <v>-1125.01</v>
+      </c>
+      <c r="H199" s="10" t="n">
+        <v>-159.27</v>
+      </c>
+      <c r="I199" s="10" t="n">
+        <v>516.2</v>
+      </c>
+      <c r="J199" s="10" t="n">
+        <v>-1466.4</v>
+      </c>
+      <c r="K199" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L199" s="10" t="n">
+        <v>11020.67</v>
+      </c>
+      <c r="M199" s="10" t="n">
+        <v>573.97</v>
+      </c>
+      <c r="N199" s="10" t="n">
+        <v>172.14</v>
+      </c>
+      <c r="O199" s="0" t="n">
+        <v>98801.96000000001</v>
+      </c>
+      <c r="P199" s="11" t="n">
+        <v>109822.64</v>
+      </c>
+      <c r="Q199" s="26" t="n">
+        <v>0.9670646067415731</v>
+      </c>
+      <c r="R199" s="9" t="n">
+        <v>655.24</v>
+      </c>
+      <c r="S199" s="14" t="n">
+        <v>262.8</v>
+      </c>
+      <c r="T199" s="14" t="n">
+        <v>-178.86</v>
+      </c>
+      <c r="U199" s="14" t="n">
+        <v>-47004.65</v>
+      </c>
+      <c r="V199" s="14" t="n">
+        <v>-626.01</v>
+      </c>
+      <c r="W199" s="14" t="n">
+        <v>-590.24</v>
+      </c>
+      <c r="X199" s="14" t="n">
+        <v>-1248.31</v>
+      </c>
+      <c r="Y199" s="14" t="n">
+        <v>-176.73</v>
+      </c>
+      <c r="Z199" s="14" t="n">
+        <v>518.6900000000001</v>
+      </c>
+      <c r="AA199" s="14" t="n">
+        <v>-1472.46</v>
+      </c>
+      <c r="AB199" s="31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AC199" s="14" t="n">
+        <v>-50599.71</v>
+      </c>
+      <c r="AD199" s="14" t="n">
+        <v>504.68</v>
+      </c>
+      <c r="AE199" s="14" t="n">
+        <v>172.35</v>
+      </c>
+      <c r="AF199" s="16" t="n">
+        <v>86984.66</v>
+      </c>
+      <c r="AG199" s="16" t="n">
+        <v>36384.95</v>
+      </c>
+      <c r="AH199" s="28" t="n">
+        <v>0.963630772671363</v>
+      </c>
+      <c r="AI199" s="15" t="n">
+        <v>241.88</v>
+      </c>
+      <c r="AJ199" s="48" t="n">
+        <v>272.4197593211877</v>
+      </c>
+      <c r="AK199" s="48" t="n">
+        <v>-192.277</v>
+      </c>
+      <c r="AL199" s="48" t="n">
+        <v>-52380.054063</v>
+      </c>
+      <c r="AM199" s="48" t="n">
+        <v>-672.9694999999999</v>
+      </c>
+      <c r="AN199" s="48" t="n">
+        <v>-634.5140999999999</v>
+      </c>
+      <c r="AO199" s="48" t="n">
+        <v>-5887.300099999996</v>
+      </c>
+      <c r="AP199" s="48" t="n">
+        <v>-833.4870719999993</v>
+      </c>
+      <c r="AQ199" s="48" t="n">
+        <v>557.6033</v>
+      </c>
+      <c r="AR199" s="48" t="n">
+        <v>-1580.796228879918</v>
+      </c>
+      <c r="AS199" s="48" t="n">
+        <v>0.116616348</v>
+      </c>
+      <c r="AT199" s="49" t="n">
+        <v>-61431.51776387991</v>
+      </c>
+      <c r="AU199" s="50" t="n">
+        <v>508.823354793995</v>
+      </c>
+      <c r="AV199" s="50" t="n">
+        <v>161.598</v>
+      </c>
+      <c r="AW199" s="73" t="n">
+        <v>82224.836488</v>
+      </c>
+      <c r="AX199" s="28" t="n">
+        <v>0.8404437348200774</v>
+      </c>
+      <c r="AY199" s="48" t="n">
+        <v>236.4035954728072</v>
+      </c>
+      <c r="AZ199" s="72" t="n">
+        <v>29844.782425</v>
+      </c>
+      <c r="BA199" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB199" s="70" t="n">
+        <v>-9051.463700879913</v>
+      </c>
+      <c r="BC199" s="71" t="n">
+        <v>20793.31872412009</v>
+      </c>
       <c r="BD199" s="5" t="n"/>
       <c r="BE199" s="5" t="n"/>
+      <c r="BF199" s="5" t="n"/>
+      <c r="BG199" s="5" t="n"/>
     </row>
     <row r="200" ht="21" customHeight="1" s="30">
       <c r="A200" s="3" t="n">
         <v>46177</v>
       </c>
-      <c r="B200" s="10" t="n"/>
-      <c r="C200" s="10" t="n"/>
-      <c r="D200" s="10" t="n"/>
-      <c r="E200" s="10" t="n"/>
-      <c r="F200" s="10" t="n"/>
-      <c r="G200" s="10" t="n"/>
-      <c r="H200" s="10" t="n"/>
-      <c r="I200" s="10" t="n"/>
-      <c r="J200" s="10" t="n"/>
-      <c r="K200" s="10" t="n"/>
-      <c r="L200" s="10" t="n"/>
-      <c r="M200" s="10" t="n"/>
-      <c r="N200" s="10" t="n"/>
-      <c r="P200" s="11" t="n"/>
-      <c r="Q200" s="26" t="n"/>
-      <c r="R200" s="9" t="n"/>
+      <c r="B200" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="C200" s="10" t="n">
+        <v>-178</v>
+      </c>
+      <c r="D200" s="10" t="n">
+        <v>14239.8</v>
+      </c>
+      <c r="E200" s="10" t="n">
+        <v>-622.99</v>
+      </c>
+      <c r="F200" s="10" t="n">
+        <v>-587.39</v>
+      </c>
+      <c r="G200" s="10" t="n">
+        <v>-895.21</v>
+      </c>
+      <c r="H200" s="10" t="n">
+        <v>-126.74</v>
+      </c>
+      <c r="I200" s="10" t="n">
+        <v>516.1900000000001</v>
+      </c>
+      <c r="J200" s="10" t="n">
+        <v>-1677.88</v>
+      </c>
+      <c r="K200" s="10" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L200" s="10" t="n">
+        <v>10845.78</v>
+      </c>
+      <c r="M200" s="10" t="n">
+        <v>641.63</v>
+      </c>
+      <c r="N200" s="10" t="n">
+        <v>173.33</v>
+      </c>
+      <c r="O200" s="0" t="n">
+        <v>111215.7</v>
+      </c>
+      <c r="P200" s="11" t="n">
+        <v>122061.48</v>
+      </c>
+      <c r="Q200" s="26" t="n">
+        <v>0.9737917667382968</v>
+      </c>
+      <c r="R200" s="9" t="n">
+        <v>721.63</v>
+      </c>
       <c r="S200" s="14" t="n">
         <v>-80</v>
       </c>
@@ -25481,27 +26571,70 @@
       <c r="AI200" s="15" t="n">
         <v>702.64</v>
       </c>
-      <c r="AJ200" s="15" t="n"/>
-      <c r="AK200" s="15" t="n"/>
-      <c r="AL200" s="15" t="n"/>
-      <c r="AM200" s="15" t="n"/>
-      <c r="AN200" s="15" t="n"/>
-      <c r="AO200" s="15" t="n"/>
-      <c r="AP200" s="15" t="n"/>
-      <c r="AQ200" s="15" t="n"/>
-      <c r="AR200" s="15" t="n"/>
-      <c r="AS200" s="15" t="n"/>
-      <c r="AT200" s="15" t="n"/>
-      <c r="AU200" s="15" t="n"/>
-      <c r="AV200" s="15" t="n"/>
-      <c r="AX200" s="16" t="n"/>
-      <c r="AY200" s="16" t="n"/>
-      <c r="AZ200" s="28" t="n"/>
-      <c r="BA200" s="15" t="n"/>
-      <c r="BB200" s="5" t="n"/>
-      <c r="BC200" s="5" t="n"/>
+      <c r="AJ200" s="48" t="n">
+        <v>-64.7794563303959</v>
+      </c>
+      <c r="AK200" s="48" t="n">
+        <v>-190.075</v>
+      </c>
+      <c r="AL200" s="48" t="n">
+        <v>12312.955162</v>
+      </c>
+      <c r="AM200" s="48" t="n">
+        <v>-665.2624999999999</v>
+      </c>
+      <c r="AN200" s="48" t="n">
+        <v>-627.2474999999999</v>
+      </c>
+      <c r="AO200" s="48" t="n">
+        <v>-5515.205999999996</v>
+      </c>
+      <c r="AP200" s="48" t="n">
+        <v>-780.8083199999994</v>
+      </c>
+      <c r="AQ200" s="48" t="n">
+        <v>551.2175</v>
+      </c>
+      <c r="AR200" s="48" t="n">
+        <v>-1565.879464193674</v>
+      </c>
+      <c r="AS200" s="48" t="n">
+        <v>0.1168541693</v>
+      </c>
+      <c r="AT200" s="49" t="n">
+        <v>3709.76887780633</v>
+      </c>
+      <c r="AU200" s="50" t="n">
+        <v>611.2283410357331</v>
+      </c>
+      <c r="AV200" s="50" t="n">
+        <v>161.335</v>
+      </c>
+      <c r="AW200" s="73" t="n">
+        <v>98612.524401</v>
+      </c>
+      <c r="AX200" s="28" t="n">
+        <v>0.8487965276864397</v>
+      </c>
+      <c r="AY200" s="48" t="n">
+        <v>676.007797366129</v>
+      </c>
+      <c r="AZ200" s="72" t="n">
+        <v>110925.479563</v>
+      </c>
+      <c r="BA200" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB200" s="70" t="n">
+        <v>-8603.186284193671</v>
+      </c>
+      <c r="BC200" s="71" t="n">
+        <v>102322.2932788063</v>
+      </c>
       <c r="BD200" s="5" t="n"/>
       <c r="BE200" s="5" t="n"/>
+      <c r="BF200" s="5" t="n"/>
+      <c r="BG200" s="5" t="n"/>
     </row>
     <row r="201" ht="19.95" customHeight="1" s="30">
       <c r="A201" s="3" t="n">
@@ -25574,27 +26707,70 @@
       <c r="AI201" s="15" t="n">
         <v>513.65</v>
       </c>
-      <c r="AJ201" s="15" t="n"/>
-      <c r="AK201" s="15" t="n"/>
-      <c r="AL201" s="15" t="n"/>
-      <c r="AM201" s="15" t="n"/>
-      <c r="AN201" s="15" t="n"/>
-      <c r="AO201" s="15" t="n"/>
-      <c r="AP201" s="15" t="n"/>
-      <c r="AQ201" s="15" t="n"/>
-      <c r="AR201" s="15" t="n"/>
-      <c r="AS201" s="15" t="n"/>
-      <c r="AT201" s="15" t="n"/>
-      <c r="AU201" s="15" t="n"/>
-      <c r="AV201" s="15" t="n"/>
-      <c r="AX201" s="16" t="n"/>
-      <c r="AY201" s="16" t="n"/>
-      <c r="AZ201" s="28" t="n"/>
-      <c r="BA201" s="15" t="n"/>
-      <c r="BB201" s="5" t="n"/>
-      <c r="BC201" s="5" t="n"/>
+      <c r="AJ201" s="48" t="n">
+        <v>60.80350311389805</v>
+      </c>
+      <c r="AK201" s="48" t="n">
+        <v>-186.904</v>
+      </c>
+      <c r="AL201" s="48" t="n">
+        <v>-11364.417946</v>
+      </c>
+      <c r="AM201" s="48" t="n">
+        <v>-654.164</v>
+      </c>
+      <c r="AN201" s="48" t="n">
+        <v>-616.7832</v>
+      </c>
+      <c r="AO201" s="48" t="n">
+        <v>-4299.327599999999</v>
+      </c>
+      <c r="AP201" s="48" t="n">
+        <v>-608.6718719999998</v>
+      </c>
+      <c r="AQ201" s="48" t="n">
+        <v>542.0215999999999</v>
+      </c>
+      <c r="AR201" s="48" t="n">
+        <v>-1986.17746944291</v>
+      </c>
+      <c r="AS201" s="48" t="n">
+        <v>0.1507336925</v>
+      </c>
+      <c r="AT201" s="49" t="n">
+        <v>-18987.52048744291</v>
+      </c>
+      <c r="AU201" s="50" t="n">
+        <v>567.374609094225</v>
+      </c>
+      <c r="AV201" s="50" t="n">
+        <v>164.5</v>
+      </c>
+      <c r="AW201" s="73" t="n">
+        <v>93333.123196</v>
+      </c>
+      <c r="AX201" s="28" t="n">
+        <v>0.8801309763300946</v>
+      </c>
+      <c r="AY201" s="48" t="n">
+        <v>506.5711059803269</v>
+      </c>
+      <c r="AZ201" s="72" t="n">
+        <v>81968.70525</v>
+      </c>
+      <c r="BA201" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB201" s="70" t="n">
+        <v>-7623.102541442909</v>
+      </c>
+      <c r="BC201" s="71" t="n">
+        <v>74345.6027085571</v>
+      </c>
       <c r="BD201" s="5" t="n"/>
       <c r="BE201" s="5" t="n"/>
+      <c r="BF201" s="5" t="n"/>
+      <c r="BG201" s="5" t="n"/>
     </row>
     <row r="202" ht="19.95" customHeight="1" s="30">
       <c r="A202" s="3" t="n">
@@ -25667,27 +26843,70 @@
       <c r="AI202" s="15" t="n">
         <v>197.43</v>
       </c>
-      <c r="AJ202" s="15" t="n"/>
-      <c r="AK202" s="15" t="n"/>
-      <c r="AL202" s="15" t="n"/>
-      <c r="AM202" s="15" t="n"/>
-      <c r="AN202" s="15" t="n"/>
-      <c r="AO202" s="15" t="n"/>
-      <c r="AP202" s="15" t="n"/>
-      <c r="AQ202" s="15" t="n"/>
-      <c r="AR202" s="15" t="n"/>
-      <c r="AS202" s="15" t="n"/>
-      <c r="AT202" s="15" t="n"/>
-      <c r="AU202" s="15" t="n"/>
-      <c r="AV202" s="15" t="n"/>
-      <c r="AX202" s="16" t="n"/>
-      <c r="AY202" s="16" t="n"/>
-      <c r="AZ202" s="28" t="n"/>
-      <c r="BA202" s="15" t="n"/>
-      <c r="BB202" s="5" t="n"/>
-      <c r="BC202" s="5" t="n"/>
+      <c r="AJ202" s="48" t="n">
+        <v>435.1722542536315</v>
+      </c>
+      <c r="AK202" s="48" t="n">
+        <v>-32.149</v>
+      </c>
+      <c r="AL202" s="48" t="n">
+        <v>-13990.352802</v>
+      </c>
+      <c r="AM202" s="48" t="n">
+        <v>-112.5215</v>
+      </c>
+      <c r="AN202" s="48" t="n">
+        <v>-106.0917</v>
+      </c>
+      <c r="AO202" s="48" t="n">
+        <v>-1344.067600000001</v>
+      </c>
+      <c r="AP202" s="48" t="n">
+        <v>-190.2846720000001</v>
+      </c>
+      <c r="AQ202" s="48" t="n">
+        <v>93.2321</v>
+      </c>
+      <c r="AR202" s="48" t="n">
+        <v>-2266.5045</v>
+      </c>
+      <c r="AS202" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT202" s="49" t="n">
+        <v>-17916.590674</v>
+      </c>
+      <c r="AU202" s="50" t="n">
+        <v>520.9568149532711</v>
+      </c>
+      <c r="AV202" s="50" t="n">
+        <v>25.145</v>
+      </c>
+      <c r="AW202" s="73" t="n">
+        <v>13099.459112</v>
+      </c>
+      <c r="AX202" s="28" t="n">
+        <v>0.7821394133565585</v>
+      </c>
+      <c r="AY202" s="48" t="n">
+        <v>85.7845606996396</v>
+      </c>
+      <c r="AZ202" s="72" t="n">
+        <v>-890.893689999999</v>
+      </c>
+      <c r="BA202" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB202" s="70" t="n">
+        <v>-3926.237872000001</v>
+      </c>
+      <c r="BC202" s="71" t="n">
+        <v>-4817.131562</v>
+      </c>
       <c r="BD202" s="5" t="n"/>
       <c r="BE202" s="5" t="n"/>
+      <c r="BF202" s="5" t="n"/>
+      <c r="BG202" s="5" t="n"/>
     </row>
     <row r="203" ht="19.95" customHeight="1" s="30">
       <c r="A203" s="3" t="n">
@@ -25760,27 +26979,70 @@
       <c r="AI203" s="15" t="n">
         <v>694.97</v>
       </c>
-      <c r="AJ203" s="15" t="n"/>
-      <c r="AK203" s="15" t="n"/>
-      <c r="AL203" s="15" t="n"/>
-      <c r="AM203" s="15" t="n"/>
-      <c r="AN203" s="15" t="n"/>
-      <c r="AO203" s="15" t="n"/>
-      <c r="AP203" s="15" t="n"/>
-      <c r="AQ203" s="15" t="n"/>
-      <c r="AR203" s="15" t="n"/>
-      <c r="AS203" s="15" t="n"/>
-      <c r="AT203" s="15" t="n"/>
-      <c r="AU203" s="15" t="n"/>
-      <c r="AV203" s="15" t="n"/>
-      <c r="AX203" s="16" t="n"/>
-      <c r="AY203" s="16" t="n"/>
-      <c r="AZ203" s="28" t="n"/>
-      <c r="BA203" s="15" t="n"/>
-      <c r="BB203" s="5" t="n"/>
-      <c r="BC203" s="5" t="n"/>
+      <c r="AJ203" s="48" t="n">
+        <v>-66.05637125639153</v>
+      </c>
+      <c r="AK203" s="48" t="n">
+        <v>-191.66</v>
+      </c>
+      <c r="AL203" s="48" t="n">
+        <v>12660.364115</v>
+      </c>
+      <c r="AM203" s="48" t="n">
+        <v>-670.8099999999999</v>
+      </c>
+      <c r="AN203" s="48" t="n">
+        <v>-632.478</v>
+      </c>
+      <c r="AO203" s="48" t="n">
+        <v>-5633.800200000002</v>
+      </c>
+      <c r="AP203" s="48" t="n">
+        <v>-797.5981440000003</v>
+      </c>
+      <c r="AQ203" s="48" t="n">
+        <v>555.814</v>
+      </c>
+      <c r="AR203" s="48" t="n">
+        <v>-11385.20610025415</v>
+      </c>
+      <c r="AS203" s="48" t="n">
+        <v>0.8425977518</v>
+      </c>
+      <c r="AT203" s="49" t="n">
+        <v>-5903.714329254155</v>
+      </c>
+      <c r="AU203" s="50" t="n">
+        <v>610.6503944375301</v>
+      </c>
+      <c r="AV203" s="50" t="n">
+        <v>162.302</v>
+      </c>
+      <c r="AW203" s="73" t="n">
+        <v>99109.780318</v>
+      </c>
+      <c r="AX203" s="28" t="n">
+        <v>0.8468224981738495</v>
+      </c>
+      <c r="AY203" s="48" t="n">
+        <v>676.7067656939216</v>
+      </c>
+      <c r="AZ203" s="72" t="n">
+        <v>111770.144433</v>
+      </c>
+      <c r="BA203" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB203" s="70" t="n">
+        <v>-18564.07844425416</v>
+      </c>
+      <c r="BC203" s="71" t="n">
+        <v>93206.06598874586</v>
+      </c>
       <c r="BD203" s="5" t="n"/>
       <c r="BE203" s="5" t="n"/>
+      <c r="BF203" s="5" t="n"/>
+      <c r="BG203" s="5" t="n"/>
     </row>
     <row r="204" ht="19.95" customHeight="1" s="30">
       <c r="A204" s="3" t="n">
@@ -25829,17 +27091,20 @@
       <c r="AQ204" s="15" t="n"/>
       <c r="AR204" s="15" t="n"/>
       <c r="AS204" s="15" t="n"/>
-      <c r="AT204" s="15" t="n"/>
-      <c r="AU204" s="15" t="n"/>
-      <c r="AV204" s="15" t="n"/>
-      <c r="AX204" s="16" t="n"/>
-      <c r="AY204" s="16" t="n"/>
-      <c r="AZ204" s="28" t="n"/>
+      <c r="AT204" s="32" t="n"/>
+      <c r="AU204" s="35" t="n"/>
+      <c r="AV204" s="35" t="n"/>
+      <c r="AW204" s="35" t="n"/>
+      <c r="AX204" s="28" t="n"/>
+      <c r="AY204" s="15" t="n"/>
+      <c r="AZ204" s="36" t="n"/>
       <c r="BA204" s="15" t="n"/>
-      <c r="BB204" s="5" t="n"/>
-      <c r="BC204" s="5" t="n"/>
+      <c r="BB204" s="15" t="n"/>
+      <c r="BC204" s="16" t="n"/>
       <c r="BD204" s="5" t="n"/>
       <c r="BE204" s="5" t="n"/>
+      <c r="BF204" s="5" t="n"/>
+      <c r="BG204" s="5" t="n"/>
     </row>
     <row r="205" ht="19.95" customHeight="1" s="30">
       <c r="A205" s="3" t="n">
@@ -25888,17 +27153,20 @@
       <c r="AQ205" s="15" t="n"/>
       <c r="AR205" s="15" t="n"/>
       <c r="AS205" s="15" t="n"/>
-      <c r="AT205" s="15" t="n"/>
-      <c r="AU205" s="15" t="n"/>
-      <c r="AV205" s="15" t="n"/>
-      <c r="AX205" s="16" t="n"/>
-      <c r="AY205" s="16" t="n"/>
-      <c r="AZ205" s="28" t="n"/>
+      <c r="AT205" s="32" t="n"/>
+      <c r="AU205" s="35" t="n"/>
+      <c r="AV205" s="35" t="n"/>
+      <c r="AW205" s="35" t="n"/>
+      <c r="AX205" s="28" t="n"/>
+      <c r="AY205" s="15" t="n"/>
+      <c r="AZ205" s="36" t="n"/>
       <c r="BA205" s="15" t="n"/>
-      <c r="BB205" s="5" t="n"/>
-      <c r="BC205" s="5" t="n"/>
+      <c r="BB205" s="15" t="n"/>
+      <c r="BC205" s="16" t="n"/>
       <c r="BD205" s="5" t="n"/>
       <c r="BE205" s="5" t="n"/>
+      <c r="BF205" s="5" t="n"/>
+      <c r="BG205" s="5" t="n"/>
     </row>
     <row r="206" ht="19.95" customHeight="1" s="30">
       <c r="A206" s="3" t="n">
@@ -25947,17 +27215,20 @@
       <c r="AQ206" s="15" t="n"/>
       <c r="AR206" s="15" t="n"/>
       <c r="AS206" s="15" t="n"/>
-      <c r="AT206" s="15" t="n"/>
-      <c r="AU206" s="15" t="n"/>
-      <c r="AV206" s="15" t="n"/>
-      <c r="AX206" s="16" t="n"/>
-      <c r="AY206" s="16" t="n"/>
-      <c r="AZ206" s="28" t="n"/>
+      <c r="AT206" s="32" t="n"/>
+      <c r="AU206" s="35" t="n"/>
+      <c r="AV206" s="35" t="n"/>
+      <c r="AW206" s="35" t="n"/>
+      <c r="AX206" s="28" t="n"/>
+      <c r="AY206" s="15" t="n"/>
+      <c r="AZ206" s="36" t="n"/>
       <c r="BA206" s="15" t="n"/>
-      <c r="BB206" s="5" t="n"/>
-      <c r="BC206" s="5" t="n"/>
+      <c r="BB206" s="15" t="n"/>
+      <c r="BC206" s="16" t="n"/>
       <c r="BD206" s="5" t="n"/>
       <c r="BE206" s="5" t="n"/>
+      <c r="BF206" s="5" t="n"/>
+      <c r="BG206" s="5" t="n"/>
     </row>
     <row r="207" ht="19.95" customHeight="1" s="30">
       <c r="A207" s="3" t="n">
@@ -26006,17 +27277,20 @@
       <c r="AQ207" s="15" t="n"/>
       <c r="AR207" s="15" t="n"/>
       <c r="AS207" s="15" t="n"/>
-      <c r="AT207" s="15" t="n"/>
-      <c r="AU207" s="15" t="n"/>
-      <c r="AV207" s="15" t="n"/>
-      <c r="AX207" s="16" t="n"/>
-      <c r="AY207" s="16" t="n"/>
-      <c r="AZ207" s="28" t="n"/>
+      <c r="AT207" s="32" t="n"/>
+      <c r="AU207" s="35" t="n"/>
+      <c r="AV207" s="35" t="n"/>
+      <c r="AW207" s="35" t="n"/>
+      <c r="AX207" s="28" t="n"/>
+      <c r="AY207" s="15" t="n"/>
+      <c r="AZ207" s="36" t="n"/>
       <c r="BA207" s="15" t="n"/>
-      <c r="BB207" s="5" t="n"/>
-      <c r="BC207" s="5" t="n"/>
+      <c r="BB207" s="15" t="n"/>
+      <c r="BC207" s="16" t="n"/>
       <c r="BD207" s="5" t="n"/>
       <c r="BE207" s="5" t="n"/>
+      <c r="BF207" s="5" t="n"/>
+      <c r="BG207" s="5" t="n"/>
     </row>
     <row r="208" ht="19.95" customHeight="1" s="30">
       <c r="A208" s="3" t="n">
@@ -26065,17 +27339,20 @@
       <c r="AQ208" s="15" t="n"/>
       <c r="AR208" s="15" t="n"/>
       <c r="AS208" s="15" t="n"/>
-      <c r="AT208" s="15" t="n"/>
-      <c r="AU208" s="15" t="n"/>
-      <c r="AV208" s="15" t="n"/>
-      <c r="AX208" s="16" t="n"/>
-      <c r="AY208" s="16" t="n"/>
-      <c r="AZ208" s="28" t="n"/>
+      <c r="AT208" s="32" t="n"/>
+      <c r="AU208" s="35" t="n"/>
+      <c r="AV208" s="35" t="n"/>
+      <c r="AW208" s="35" t="n"/>
+      <c r="AX208" s="28" t="n"/>
+      <c r="AY208" s="15" t="n"/>
+      <c r="AZ208" s="36" t="n"/>
       <c r="BA208" s="15" t="n"/>
-      <c r="BB208" s="5" t="n"/>
-      <c r="BC208" s="5" t="n"/>
+      <c r="BB208" s="15" t="n"/>
+      <c r="BC208" s="16" t="n"/>
       <c r="BD208" s="5" t="n"/>
       <c r="BE208" s="5" t="n"/>
+      <c r="BF208" s="5" t="n"/>
+      <c r="BG208" s="5" t="n"/>
     </row>
     <row r="209" ht="19.95" customHeight="1" s="30">
       <c r="A209" s="3" t="n">
@@ -26124,17 +27401,20 @@
       <c r="AQ209" s="15" t="n"/>
       <c r="AR209" s="15" t="n"/>
       <c r="AS209" s="15" t="n"/>
-      <c r="AT209" s="15" t="n"/>
-      <c r="AU209" s="15" t="n"/>
-      <c r="AV209" s="15" t="n"/>
-      <c r="AX209" s="16" t="n"/>
-      <c r="AY209" s="16" t="n"/>
-      <c r="AZ209" s="28" t="n"/>
+      <c r="AT209" s="32" t="n"/>
+      <c r="AU209" s="35" t="n"/>
+      <c r="AV209" s="35" t="n"/>
+      <c r="AW209" s="35" t="n"/>
+      <c r="AX209" s="28" t="n"/>
+      <c r="AY209" s="15" t="n"/>
+      <c r="AZ209" s="36" t="n"/>
       <c r="BA209" s="15" t="n"/>
-      <c r="BB209" s="5" t="n"/>
-      <c r="BC209" s="5" t="n"/>
+      <c r="BB209" s="15" t="n"/>
+      <c r="BC209" s="16" t="n"/>
       <c r="BD209" s="5" t="n"/>
       <c r="BE209" s="5" t="n"/>
+      <c r="BF209" s="5" t="n"/>
+      <c r="BG209" s="5" t="n"/>
     </row>
     <row r="210" ht="19.95" customHeight="1" s="30">
       <c r="A210" s="3" t="n">
@@ -26183,17 +27463,20 @@
       <c r="AQ210" s="15" t="n"/>
       <c r="AR210" s="15" t="n"/>
       <c r="AS210" s="15" t="n"/>
-      <c r="AT210" s="15" t="n"/>
-      <c r="AU210" s="15" t="n"/>
-      <c r="AV210" s="15" t="n"/>
-      <c r="AX210" s="16" t="n"/>
-      <c r="AY210" s="16" t="n"/>
-      <c r="AZ210" s="28" t="n"/>
+      <c r="AT210" s="32" t="n"/>
+      <c r="AU210" s="35" t="n"/>
+      <c r="AV210" s="35" t="n"/>
+      <c r="AW210" s="35" t="n"/>
+      <c r="AX210" s="28" t="n"/>
+      <c r="AY210" s="15" t="n"/>
+      <c r="AZ210" s="36" t="n"/>
       <c r="BA210" s="15" t="n"/>
-      <c r="BB210" s="5" t="n"/>
-      <c r="BC210" s="5" t="n"/>
+      <c r="BB210" s="15" t="n"/>
+      <c r="BC210" s="16" t="n"/>
       <c r="BD210" s="5" t="n"/>
       <c r="BE210" s="5" t="n"/>
+      <c r="BF210" s="5" t="n"/>
+      <c r="BG210" s="5" t="n"/>
     </row>
     <row r="211" ht="19.95" customHeight="1" s="30">
       <c r="A211" s="3" t="n">
@@ -26242,17 +27525,20 @@
       <c r="AQ211" s="15" t="n"/>
       <c r="AR211" s="15" t="n"/>
       <c r="AS211" s="15" t="n"/>
-      <c r="AT211" s="15" t="n"/>
-      <c r="AU211" s="15" t="n"/>
-      <c r="AV211" s="15" t="n"/>
-      <c r="AX211" s="16" t="n"/>
-      <c r="AY211" s="16" t="n"/>
-      <c r="AZ211" s="28" t="n"/>
+      <c r="AT211" s="32" t="n"/>
+      <c r="AU211" s="35" t="n"/>
+      <c r="AV211" s="35" t="n"/>
+      <c r="AW211" s="35" t="n"/>
+      <c r="AX211" s="28" t="n"/>
+      <c r="AY211" s="15" t="n"/>
+      <c r="AZ211" s="36" t="n"/>
       <c r="BA211" s="15" t="n"/>
-      <c r="BB211" s="5" t="n"/>
-      <c r="BC211" s="5" t="n"/>
+      <c r="BB211" s="15" t="n"/>
+      <c r="BC211" s="16" t="n"/>
       <c r="BD211" s="5" t="n"/>
       <c r="BE211" s="5" t="n"/>
+      <c r="BF211" s="5" t="n"/>
+      <c r="BG211" s="5" t="n"/>
     </row>
     <row r="212" ht="19.95" customHeight="1" s="30">
       <c r="A212" s="3" t="n">
@@ -26301,17 +27587,20 @@
       <c r="AQ212" s="15" t="n"/>
       <c r="AR212" s="15" t="n"/>
       <c r="AS212" s="15" t="n"/>
-      <c r="AT212" s="15" t="n"/>
-      <c r="AU212" s="15" t="n"/>
-      <c r="AV212" s="15" t="n"/>
-      <c r="AX212" s="16" t="n"/>
-      <c r="AY212" s="16" t="n"/>
-      <c r="AZ212" s="28" t="n"/>
+      <c r="AT212" s="32" t="n"/>
+      <c r="AU212" s="35" t="n"/>
+      <c r="AV212" s="35" t="n"/>
+      <c r="AW212" s="35" t="n"/>
+      <c r="AX212" s="28" t="n"/>
+      <c r="AY212" s="15" t="n"/>
+      <c r="AZ212" s="36" t="n"/>
       <c r="BA212" s="15" t="n"/>
-      <c r="BB212" s="5" t="n"/>
-      <c r="BC212" s="5" t="n"/>
+      <c r="BB212" s="15" t="n"/>
+      <c r="BC212" s="16" t="n"/>
       <c r="BD212" s="5" t="n"/>
       <c r="BE212" s="5" t="n"/>
+      <c r="BF212" s="5" t="n"/>
+      <c r="BG212" s="5" t="n"/>
     </row>
     <row r="213" ht="19.95" customHeight="1" s="30">
       <c r="A213" s="3" t="n">
@@ -26360,17 +27649,20 @@
       <c r="AQ213" s="15" t="n"/>
       <c r="AR213" s="15" t="n"/>
       <c r="AS213" s="15" t="n"/>
-      <c r="AT213" s="15" t="n"/>
-      <c r="AU213" s="15" t="n"/>
-      <c r="AV213" s="15" t="n"/>
-      <c r="AX213" s="16" t="n"/>
-      <c r="AY213" s="16" t="n"/>
-      <c r="AZ213" s="28" t="n"/>
+      <c r="AT213" s="32" t="n"/>
+      <c r="AU213" s="35" t="n"/>
+      <c r="AV213" s="35" t="n"/>
+      <c r="AW213" s="35" t="n"/>
+      <c r="AX213" s="28" t="n"/>
+      <c r="AY213" s="15" t="n"/>
+      <c r="AZ213" s="36" t="n"/>
       <c r="BA213" s="15" t="n"/>
-      <c r="BB213" s="5" t="n"/>
-      <c r="BC213" s="5" t="n"/>
+      <c r="BB213" s="15" t="n"/>
+      <c r="BC213" s="16" t="n"/>
       <c r="BD213" s="5" t="n"/>
       <c r="BE213" s="5" t="n"/>
+      <c r="BF213" s="5" t="n"/>
+      <c r="BG213" s="5" t="n"/>
     </row>
     <row r="214" ht="19.95" customHeight="1" s="30">
       <c r="A214" s="3" t="n">
@@ -26419,17 +27711,20 @@
       <c r="AQ214" s="15" t="n"/>
       <c r="AR214" s="15" t="n"/>
       <c r="AS214" s="15" t="n"/>
-      <c r="AT214" s="15" t="n"/>
-      <c r="AU214" s="15" t="n"/>
-      <c r="AV214" s="15" t="n"/>
-      <c r="AX214" s="16" t="n"/>
-      <c r="AY214" s="16" t="n"/>
-      <c r="AZ214" s="28" t="n"/>
+      <c r="AT214" s="32" t="n"/>
+      <c r="AU214" s="35" t="n"/>
+      <c r="AV214" s="35" t="n"/>
+      <c r="AW214" s="35" t="n"/>
+      <c r="AX214" s="28" t="n"/>
+      <c r="AY214" s="15" t="n"/>
+      <c r="AZ214" s="36" t="n"/>
       <c r="BA214" s="15" t="n"/>
-      <c r="BB214" s="5" t="n"/>
-      <c r="BC214" s="5" t="n"/>
+      <c r="BB214" s="15" t="n"/>
+      <c r="BC214" s="16" t="n"/>
       <c r="BD214" s="5" t="n"/>
       <c r="BE214" s="5" t="n"/>
+      <c r="BF214" s="5" t="n"/>
+      <c r="BG214" s="5" t="n"/>
     </row>
     <row r="215" ht="19.95" customHeight="1" s="30">
       <c r="A215" s="3" t="n">
@@ -26478,17 +27773,20 @@
       <c r="AQ215" s="15" t="n"/>
       <c r="AR215" s="15" t="n"/>
       <c r="AS215" s="15" t="n"/>
-      <c r="AT215" s="15" t="n"/>
-      <c r="AU215" s="15" t="n"/>
-      <c r="AV215" s="15" t="n"/>
-      <c r="AX215" s="16" t="n"/>
-      <c r="AY215" s="16" t="n"/>
-      <c r="AZ215" s="28" t="n"/>
+      <c r="AT215" s="32" t="n"/>
+      <c r="AU215" s="35" t="n"/>
+      <c r="AV215" s="35" t="n"/>
+      <c r="AW215" s="35" t="n"/>
+      <c r="AX215" s="28" t="n"/>
+      <c r="AY215" s="15" t="n"/>
+      <c r="AZ215" s="36" t="n"/>
       <c r="BA215" s="15" t="n"/>
-      <c r="BB215" s="5" t="n"/>
-      <c r="BC215" s="5" t="n"/>
+      <c r="BB215" s="15" t="n"/>
+      <c r="BC215" s="16" t="n"/>
       <c r="BD215" s="5" t="n"/>
       <c r="BE215" s="5" t="n"/>
+      <c r="BF215" s="5" t="n"/>
+      <c r="BG215" s="5" t="n"/>
     </row>
     <row r="216" ht="19.95" customHeight="1" s="30">
       <c r="A216" s="3" t="n">
@@ -26537,17 +27835,20 @@
       <c r="AQ216" s="15" t="n"/>
       <c r="AR216" s="15" t="n"/>
       <c r="AS216" s="15" t="n"/>
-      <c r="AT216" s="15" t="n"/>
-      <c r="AU216" s="15" t="n"/>
-      <c r="AV216" s="15" t="n"/>
-      <c r="AX216" s="16" t="n"/>
-      <c r="AY216" s="16" t="n"/>
-      <c r="AZ216" s="28" t="n"/>
+      <c r="AT216" s="32" t="n"/>
+      <c r="AU216" s="35" t="n"/>
+      <c r="AV216" s="35" t="n"/>
+      <c r="AW216" s="35" t="n"/>
+      <c r="AX216" s="28" t="n"/>
+      <c r="AY216" s="15" t="n"/>
+      <c r="AZ216" s="36" t="n"/>
       <c r="BA216" s="15" t="n"/>
-      <c r="BB216" s="5" t="n"/>
-      <c r="BC216" s="5" t="n"/>
+      <c r="BB216" s="15" t="n"/>
+      <c r="BC216" s="16" t="n"/>
       <c r="BD216" s="5" t="n"/>
       <c r="BE216" s="5" t="n"/>
+      <c r="BF216" s="5" t="n"/>
+      <c r="BG216" s="5" t="n"/>
     </row>
     <row r="217" ht="19.95" customHeight="1" s="30">
       <c r="A217" s="3" t="n">
@@ -26596,17 +27897,20 @@
       <c r="AQ217" s="15" t="n"/>
       <c r="AR217" s="15" t="n"/>
       <c r="AS217" s="15" t="n"/>
-      <c r="AT217" s="15" t="n"/>
-      <c r="AU217" s="15" t="n"/>
-      <c r="AV217" s="15" t="n"/>
-      <c r="AX217" s="16" t="n"/>
-      <c r="AY217" s="16" t="n"/>
-      <c r="AZ217" s="28" t="n"/>
+      <c r="AT217" s="32" t="n"/>
+      <c r="AU217" s="35" t="n"/>
+      <c r="AV217" s="35" t="n"/>
+      <c r="AW217" s="35" t="n"/>
+      <c r="AX217" s="28" t="n"/>
+      <c r="AY217" s="15" t="n"/>
+      <c r="AZ217" s="36" t="n"/>
       <c r="BA217" s="15" t="n"/>
-      <c r="BB217" s="5" t="n"/>
-      <c r="BC217" s="5" t="n"/>
+      <c r="BB217" s="15" t="n"/>
+      <c r="BC217" s="16" t="n"/>
       <c r="BD217" s="5" t="n"/>
       <c r="BE217" s="5" t="n"/>
+      <c r="BF217" s="5" t="n"/>
+      <c r="BG217" s="5" t="n"/>
     </row>
     <row r="218" ht="19.95" customHeight="1" s="30">
       <c r="A218" s="3" t="n">
@@ -26655,17 +27959,20 @@
       <c r="AQ218" s="15" t="n"/>
       <c r="AR218" s="15" t="n"/>
       <c r="AS218" s="15" t="n"/>
-      <c r="AT218" s="15" t="n"/>
-      <c r="AU218" s="15" t="n"/>
-      <c r="AV218" s="15" t="n"/>
-      <c r="AX218" s="16" t="n"/>
-      <c r="AY218" s="16" t="n"/>
-      <c r="AZ218" s="28" t="n"/>
+      <c r="AT218" s="32" t="n"/>
+      <c r="AU218" s="35" t="n"/>
+      <c r="AV218" s="35" t="n"/>
+      <c r="AW218" s="35" t="n"/>
+      <c r="AX218" s="28" t="n"/>
+      <c r="AY218" s="15" t="n"/>
+      <c r="AZ218" s="36" t="n"/>
       <c r="BA218" s="15" t="n"/>
-      <c r="BB218" s="5" t="n"/>
-      <c r="BC218" s="5" t="n"/>
+      <c r="BB218" s="15" t="n"/>
+      <c r="BC218" s="16" t="n"/>
       <c r="BD218" s="5" t="n"/>
       <c r="BE218" s="5" t="n"/>
+      <c r="BF218" s="5" t="n"/>
+      <c r="BG218" s="5" t="n"/>
     </row>
     <row r="219" ht="19.95" customHeight="1" s="30">
       <c r="A219" s="3" t="n">
@@ -26714,17 +28021,20 @@
       <c r="AQ219" s="15" t="n"/>
       <c r="AR219" s="15" t="n"/>
       <c r="AS219" s="15" t="n"/>
-      <c r="AT219" s="15" t="n"/>
-      <c r="AU219" s="15" t="n"/>
-      <c r="AV219" s="15" t="n"/>
-      <c r="AX219" s="16" t="n"/>
-      <c r="AY219" s="16" t="n"/>
-      <c r="AZ219" s="28" t="n"/>
+      <c r="AT219" s="32" t="n"/>
+      <c r="AU219" s="35" t="n"/>
+      <c r="AV219" s="35" t="n"/>
+      <c r="AW219" s="35" t="n"/>
+      <c r="AX219" s="28" t="n"/>
+      <c r="AY219" s="15" t="n"/>
+      <c r="AZ219" s="36" t="n"/>
       <c r="BA219" s="15" t="n"/>
-      <c r="BB219" s="5" t="n"/>
-      <c r="BC219" s="5" t="n"/>
+      <c r="BB219" s="15" t="n"/>
+      <c r="BC219" s="16" t="n"/>
       <c r="BD219" s="5" t="n"/>
       <c r="BE219" s="5" t="n"/>
+      <c r="BF219" s="5" t="n"/>
+      <c r="BG219" s="5" t="n"/>
     </row>
     <row r="220" ht="19.95" customHeight="1" s="30">
       <c r="A220" s="3" t="n">
@@ -26773,17 +28083,20 @@
       <c r="AQ220" s="15" t="n"/>
       <c r="AR220" s="15" t="n"/>
       <c r="AS220" s="15" t="n"/>
-      <c r="AT220" s="15" t="n"/>
-      <c r="AU220" s="15" t="n"/>
-      <c r="AV220" s="15" t="n"/>
-      <c r="AX220" s="16" t="n"/>
-      <c r="AY220" s="16" t="n"/>
-      <c r="AZ220" s="28" t="n"/>
+      <c r="AT220" s="32" t="n"/>
+      <c r="AU220" s="35" t="n"/>
+      <c r="AV220" s="35" t="n"/>
+      <c r="AW220" s="35" t="n"/>
+      <c r="AX220" s="28" t="n"/>
+      <c r="AY220" s="15" t="n"/>
+      <c r="AZ220" s="36" t="n"/>
       <c r="BA220" s="15" t="n"/>
-      <c r="BB220" s="5" t="n"/>
-      <c r="BC220" s="5" t="n"/>
+      <c r="BB220" s="15" t="n"/>
+      <c r="BC220" s="16" t="n"/>
       <c r="BD220" s="5" t="n"/>
       <c r="BE220" s="5" t="n"/>
+      <c r="BF220" s="5" t="n"/>
+      <c r="BG220" s="5" t="n"/>
     </row>
     <row r="221" ht="19.95" customHeight="1" s="30">
       <c r="A221" s="3" t="n">
@@ -26832,17 +28145,20 @@
       <c r="AQ221" s="15" t="n"/>
       <c r="AR221" s="15" t="n"/>
       <c r="AS221" s="15" t="n"/>
-      <c r="AT221" s="15" t="n"/>
-      <c r="AU221" s="15" t="n"/>
-      <c r="AV221" s="15" t="n"/>
-      <c r="AX221" s="16" t="n"/>
-      <c r="AY221" s="16" t="n"/>
-      <c r="AZ221" s="28" t="n"/>
+      <c r="AT221" s="32" t="n"/>
+      <c r="AU221" s="35" t="n"/>
+      <c r="AV221" s="35" t="n"/>
+      <c r="AW221" s="35" t="n"/>
+      <c r="AX221" s="28" t="n"/>
+      <c r="AY221" s="15" t="n"/>
+      <c r="AZ221" s="36" t="n"/>
       <c r="BA221" s="15" t="n"/>
-      <c r="BB221" s="5" t="n"/>
-      <c r="BC221" s="5" t="n"/>
+      <c r="BB221" s="15" t="n"/>
+      <c r="BC221" s="16" t="n"/>
       <c r="BD221" s="5" t="n"/>
       <c r="BE221" s="5" t="n"/>
+      <c r="BF221" s="5" t="n"/>
+      <c r="BG221" s="5" t="n"/>
     </row>
     <row r="222" ht="19.95" customHeight="1" s="30">
       <c r="A222" s="3" t="n">
@@ -26891,17 +28207,20 @@
       <c r="AQ222" s="15" t="n"/>
       <c r="AR222" s="15" t="n"/>
       <c r="AS222" s="15" t="n"/>
-      <c r="AT222" s="15" t="n"/>
-      <c r="AU222" s="15" t="n"/>
-      <c r="AV222" s="15" t="n"/>
-      <c r="AX222" s="16" t="n"/>
-      <c r="AY222" s="16" t="n"/>
-      <c r="AZ222" s="28" t="n"/>
+      <c r="AT222" s="32" t="n"/>
+      <c r="AU222" s="35" t="n"/>
+      <c r="AV222" s="35" t="n"/>
+      <c r="AW222" s="35" t="n"/>
+      <c r="AX222" s="28" t="n"/>
+      <c r="AY222" s="15" t="n"/>
+      <c r="AZ222" s="36" t="n"/>
       <c r="BA222" s="15" t="n"/>
-      <c r="BB222" s="5" t="n"/>
-      <c r="BC222" s="5" t="n"/>
+      <c r="BB222" s="15" t="n"/>
+      <c r="BC222" s="16" t="n"/>
       <c r="BD222" s="5" t="n"/>
       <c r="BE222" s="5" t="n"/>
+      <c r="BF222" s="5" t="n"/>
+      <c r="BG222" s="5" t="n"/>
     </row>
     <row r="223" ht="19.95" customHeight="1" s="30">
       <c r="A223" s="3" t="n">
@@ -26950,17 +28269,20 @@
       <c r="AQ223" s="15" t="n"/>
       <c r="AR223" s="15" t="n"/>
       <c r="AS223" s="15" t="n"/>
-      <c r="AT223" s="15" t="n"/>
-      <c r="AU223" s="15" t="n"/>
-      <c r="AV223" s="15" t="n"/>
-      <c r="AX223" s="16" t="n"/>
-      <c r="AY223" s="16" t="n"/>
-      <c r="AZ223" s="28" t="n"/>
+      <c r="AT223" s="32" t="n"/>
+      <c r="AU223" s="35" t="n"/>
+      <c r="AV223" s="35" t="n"/>
+      <c r="AW223" s="35" t="n"/>
+      <c r="AX223" s="28" t="n"/>
+      <c r="AY223" s="15" t="n"/>
+      <c r="AZ223" s="36" t="n"/>
       <c r="BA223" s="15" t="n"/>
-      <c r="BB223" s="5" t="n"/>
-      <c r="BC223" s="5" t="n"/>
+      <c r="BB223" s="15" t="n"/>
+      <c r="BC223" s="16" t="n"/>
       <c r="BD223" s="5" t="n"/>
       <c r="BE223" s="5" t="n"/>
+      <c r="BF223" s="5" t="n"/>
+      <c r="BG223" s="5" t="n"/>
     </row>
     <row r="224" ht="19.95" customHeight="1" s="30">
       <c r="A224" s="3" t="n">
@@ -27009,17 +28331,20 @@
       <c r="AQ224" s="15" t="n"/>
       <c r="AR224" s="15" t="n"/>
       <c r="AS224" s="15" t="n"/>
-      <c r="AT224" s="15" t="n"/>
-      <c r="AU224" s="15" t="n"/>
-      <c r="AV224" s="15" t="n"/>
-      <c r="AX224" s="16" t="n"/>
-      <c r="AY224" s="16" t="n"/>
-      <c r="AZ224" s="28" t="n"/>
+      <c r="AT224" s="32" t="n"/>
+      <c r="AU224" s="35" t="n"/>
+      <c r="AV224" s="35" t="n"/>
+      <c r="AW224" s="35" t="n"/>
+      <c r="AX224" s="28" t="n"/>
+      <c r="AY224" s="15" t="n"/>
+      <c r="AZ224" s="36" t="n"/>
       <c r="BA224" s="15" t="n"/>
-      <c r="BB224" s="5" t="n"/>
-      <c r="BC224" s="5" t="n"/>
+      <c r="BB224" s="15" t="n"/>
+      <c r="BC224" s="16" t="n"/>
       <c r="BD224" s="5" t="n"/>
       <c r="BE224" s="5" t="n"/>
+      <c r="BF224" s="5" t="n"/>
+      <c r="BG224" s="5" t="n"/>
     </row>
     <row r="225" ht="19.95" customHeight="1" s="30">
       <c r="A225" s="3" t="n">
@@ -27068,17 +28393,20 @@
       <c r="AQ225" s="15" t="n"/>
       <c r="AR225" s="15" t="n"/>
       <c r="AS225" s="15" t="n"/>
-      <c r="AT225" s="15" t="n"/>
-      <c r="AU225" s="15" t="n"/>
-      <c r="AV225" s="15" t="n"/>
-      <c r="AX225" s="16" t="n"/>
-      <c r="AY225" s="16" t="n"/>
-      <c r="AZ225" s="28" t="n"/>
+      <c r="AT225" s="32" t="n"/>
+      <c r="AU225" s="35" t="n"/>
+      <c r="AV225" s="35" t="n"/>
+      <c r="AW225" s="35" t="n"/>
+      <c r="AX225" s="28" t="n"/>
+      <c r="AY225" s="15" t="n"/>
+      <c r="AZ225" s="36" t="n"/>
       <c r="BA225" s="15" t="n"/>
-      <c r="BB225" s="5" t="n"/>
-      <c r="BC225" s="5" t="n"/>
+      <c r="BB225" s="15" t="n"/>
+      <c r="BC225" s="16" t="n"/>
       <c r="BD225" s="5" t="n"/>
       <c r="BE225" s="5" t="n"/>
+      <c r="BF225" s="5" t="n"/>
+      <c r="BG225" s="5" t="n"/>
     </row>
     <row r="226" ht="19.95" customHeight="1" s="30">
       <c r="A226" s="3" t="n">
@@ -27127,17 +28455,20 @@
       <c r="AQ226" s="15" t="n"/>
       <c r="AR226" s="15" t="n"/>
       <c r="AS226" s="15" t="n"/>
-      <c r="AT226" s="15" t="n"/>
-      <c r="AU226" s="15" t="n"/>
-      <c r="AV226" s="15" t="n"/>
-      <c r="AX226" s="16" t="n"/>
-      <c r="AY226" s="16" t="n"/>
-      <c r="AZ226" s="28" t="n"/>
+      <c r="AT226" s="32" t="n"/>
+      <c r="AU226" s="35" t="n"/>
+      <c r="AV226" s="35" t="n"/>
+      <c r="AW226" s="35" t="n"/>
+      <c r="AX226" s="28" t="n"/>
+      <c r="AY226" s="15" t="n"/>
+      <c r="AZ226" s="36" t="n"/>
       <c r="BA226" s="15" t="n"/>
-      <c r="BB226" s="5" t="n"/>
-      <c r="BC226" s="5" t="n"/>
+      <c r="BB226" s="15" t="n"/>
+      <c r="BC226" s="16" t="n"/>
       <c r="BD226" s="5" t="n"/>
       <c r="BE226" s="5" t="n"/>
+      <c r="BF226" s="5" t="n"/>
+      <c r="BG226" s="5" t="n"/>
     </row>
     <row r="227" ht="19.95" customHeight="1" s="30">
       <c r="A227" s="3" t="n">
@@ -27186,17 +28517,20 @@
       <c r="AQ227" s="15" t="n"/>
       <c r="AR227" s="15" t="n"/>
       <c r="AS227" s="15" t="n"/>
-      <c r="AT227" s="15" t="n"/>
-      <c r="AU227" s="15" t="n"/>
-      <c r="AV227" s="15" t="n"/>
-      <c r="AX227" s="16" t="n"/>
-      <c r="AY227" s="16" t="n"/>
-      <c r="AZ227" s="28" t="n"/>
+      <c r="AT227" s="32" t="n"/>
+      <c r="AU227" s="35" t="n"/>
+      <c r="AV227" s="35" t="n"/>
+      <c r="AW227" s="35" t="n"/>
+      <c r="AX227" s="28" t="n"/>
+      <c r="AY227" s="15" t="n"/>
+      <c r="AZ227" s="36" t="n"/>
       <c r="BA227" s="15" t="n"/>
-      <c r="BB227" s="5" t="n"/>
-      <c r="BC227" s="5" t="n"/>
+      <c r="BB227" s="15" t="n"/>
+      <c r="BC227" s="16" t="n"/>
       <c r="BD227" s="5" t="n"/>
       <c r="BE227" s="5" t="n"/>
+      <c r="BF227" s="5" t="n"/>
+      <c r="BG227" s="5" t="n"/>
     </row>
     <row r="228" ht="19.95" customHeight="1" s="30">
       <c r="A228" s="3" t="n">
@@ -27245,17 +28579,20 @@
       <c r="AQ228" s="15" t="n"/>
       <c r="AR228" s="15" t="n"/>
       <c r="AS228" s="15" t="n"/>
-      <c r="AT228" s="15" t="n"/>
-      <c r="AU228" s="15" t="n"/>
-      <c r="AV228" s="15" t="n"/>
-      <c r="AX228" s="16" t="n"/>
-      <c r="AY228" s="16" t="n"/>
-      <c r="AZ228" s="28" t="n"/>
+      <c r="AT228" s="32" t="n"/>
+      <c r="AU228" s="35" t="n"/>
+      <c r="AV228" s="35" t="n"/>
+      <c r="AW228" s="35" t="n"/>
+      <c r="AX228" s="28" t="n"/>
+      <c r="AY228" s="15" t="n"/>
+      <c r="AZ228" s="36" t="n"/>
       <c r="BA228" s="15" t="n"/>
-      <c r="BB228" s="5" t="n"/>
-      <c r="BC228" s="5" t="n"/>
+      <c r="BB228" s="15" t="n"/>
+      <c r="BC228" s="16" t="n"/>
       <c r="BD228" s="5" t="n"/>
       <c r="BE228" s="5" t="n"/>
+      <c r="BF228" s="5" t="n"/>
+      <c r="BG228" s="5" t="n"/>
     </row>
     <row r="229" ht="19.95" customHeight="1" s="30">
       <c r="A229" s="3" t="n">
@@ -27304,17 +28641,20 @@
       <c r="AQ229" s="15" t="n"/>
       <c r="AR229" s="15" t="n"/>
       <c r="AS229" s="15" t="n"/>
-      <c r="AT229" s="15" t="n"/>
-      <c r="AU229" s="15" t="n"/>
-      <c r="AV229" s="15" t="n"/>
-      <c r="AX229" s="16" t="n"/>
-      <c r="AY229" s="16" t="n"/>
-      <c r="AZ229" s="28" t="n"/>
+      <c r="AT229" s="32" t="n"/>
+      <c r="AU229" s="35" t="n"/>
+      <c r="AV229" s="35" t="n"/>
+      <c r="AW229" s="35" t="n"/>
+      <c r="AX229" s="28" t="n"/>
+      <c r="AY229" s="15" t="n"/>
+      <c r="AZ229" s="36" t="n"/>
       <c r="BA229" s="15" t="n"/>
-      <c r="BB229" s="5" t="n"/>
-      <c r="BC229" s="5" t="n"/>
+      <c r="BB229" s="15" t="n"/>
+      <c r="BC229" s="16" t="n"/>
       <c r="BD229" s="5" t="n"/>
       <c r="BE229" s="5" t="n"/>
+      <c r="BF229" s="5" t="n"/>
+      <c r="BG229" s="5" t="n"/>
     </row>
     <row r="230" ht="19.95" customHeight="1" s="30">
       <c r="A230" s="3" t="n">
@@ -27363,17 +28703,20 @@
       <c r="AQ230" s="15" t="n"/>
       <c r="AR230" s="15" t="n"/>
       <c r="AS230" s="15" t="n"/>
-      <c r="AT230" s="15" t="n"/>
-      <c r="AU230" s="15" t="n"/>
-      <c r="AV230" s="15" t="n"/>
-      <c r="AX230" s="16" t="n"/>
-      <c r="AY230" s="16" t="n"/>
-      <c r="AZ230" s="28" t="n"/>
+      <c r="AT230" s="32" t="n"/>
+      <c r="AU230" s="35" t="n"/>
+      <c r="AV230" s="35" t="n"/>
+      <c r="AW230" s="35" t="n"/>
+      <c r="AX230" s="28" t="n"/>
+      <c r="AY230" s="15" t="n"/>
+      <c r="AZ230" s="36" t="n"/>
       <c r="BA230" s="15" t="n"/>
-      <c r="BB230" s="5" t="n"/>
-      <c r="BC230" s="5" t="n"/>
+      <c r="BB230" s="15" t="n"/>
+      <c r="BC230" s="16" t="n"/>
       <c r="BD230" s="5" t="n"/>
       <c r="BE230" s="5" t="n"/>
+      <c r="BF230" s="5" t="n"/>
+      <c r="BG230" s="5" t="n"/>
     </row>
     <row r="231" ht="19.95" customHeight="1" s="30">
       <c r="A231" s="3" t="n">
@@ -27422,17 +28765,20 @@
       <c r="AQ231" s="15" t="n"/>
       <c r="AR231" s="15" t="n"/>
       <c r="AS231" s="15" t="n"/>
-      <c r="AT231" s="15" t="n"/>
-      <c r="AU231" s="15" t="n"/>
-      <c r="AV231" s="15" t="n"/>
-      <c r="AX231" s="16" t="n"/>
-      <c r="AY231" s="16" t="n"/>
-      <c r="AZ231" s="28" t="n"/>
+      <c r="AT231" s="32" t="n"/>
+      <c r="AU231" s="35" t="n"/>
+      <c r="AV231" s="35" t="n"/>
+      <c r="AW231" s="35" t="n"/>
+      <c r="AX231" s="28" t="n"/>
+      <c r="AY231" s="15" t="n"/>
+      <c r="AZ231" s="36" t="n"/>
       <c r="BA231" s="15" t="n"/>
-      <c r="BB231" s="5" t="n"/>
-      <c r="BC231" s="5" t="n"/>
+      <c r="BB231" s="15" t="n"/>
+      <c r="BC231" s="16" t="n"/>
       <c r="BD231" s="5" t="n"/>
       <c r="BE231" s="5" t="n"/>
+      <c r="BF231" s="5" t="n"/>
+      <c r="BG231" s="5" t="n"/>
     </row>
     <row r="232" ht="19.95" customHeight="1" s="30">
       <c r="A232" s="3" t="n">
@@ -27481,17 +28827,20 @@
       <c r="AQ232" s="15" t="n"/>
       <c r="AR232" s="15" t="n"/>
       <c r="AS232" s="15" t="n"/>
-      <c r="AT232" s="15" t="n"/>
-      <c r="AU232" s="15" t="n"/>
-      <c r="AV232" s="15" t="n"/>
-      <c r="AX232" s="16" t="n"/>
-      <c r="AY232" s="16" t="n"/>
-      <c r="AZ232" s="28" t="n"/>
+      <c r="AT232" s="32" t="n"/>
+      <c r="AU232" s="35" t="n"/>
+      <c r="AV232" s="35" t="n"/>
+      <c r="AW232" s="35" t="n"/>
+      <c r="AX232" s="28" t="n"/>
+      <c r="AY232" s="15" t="n"/>
+      <c r="AZ232" s="36" t="n"/>
       <c r="BA232" s="15" t="n"/>
-      <c r="BB232" s="5" t="n"/>
-      <c r="BC232" s="5" t="n"/>
+      <c r="BB232" s="15" t="n"/>
+      <c r="BC232" s="16" t="n"/>
       <c r="BD232" s="5" t="n"/>
       <c r="BE232" s="5" t="n"/>
+      <c r="BF232" s="5" t="n"/>
+      <c r="BG232" s="5" t="n"/>
     </row>
     <row r="233" ht="19.95" customHeight="1" s="30">
       <c r="A233" s="3" t="n">
@@ -27540,17 +28889,20 @@
       <c r="AQ233" s="15" t="n"/>
       <c r="AR233" s="15" t="n"/>
       <c r="AS233" s="15" t="n"/>
-      <c r="AT233" s="15" t="n"/>
-      <c r="AU233" s="15" t="n"/>
-      <c r="AV233" s="15" t="n"/>
-      <c r="AX233" s="16" t="n"/>
-      <c r="AY233" s="16" t="n"/>
-      <c r="AZ233" s="28" t="n"/>
+      <c r="AT233" s="32" t="n"/>
+      <c r="AU233" s="35" t="n"/>
+      <c r="AV233" s="35" t="n"/>
+      <c r="AW233" s="35" t="n"/>
+      <c r="AX233" s="28" t="n"/>
+      <c r="AY233" s="15" t="n"/>
+      <c r="AZ233" s="36" t="n"/>
       <c r="BA233" s="15" t="n"/>
-      <c r="BB233" s="5" t="n"/>
-      <c r="BC233" s="5" t="n"/>
+      <c r="BB233" s="15" t="n"/>
+      <c r="BC233" s="16" t="n"/>
       <c r="BD233" s="5" t="n"/>
       <c r="BE233" s="5" t="n"/>
+      <c r="BF233" s="5" t="n"/>
+      <c r="BG233" s="5" t="n"/>
     </row>
     <row r="234" ht="19.95" customHeight="1" s="30">
       <c r="A234" s="3" t="n">
@@ -27599,17 +28951,20 @@
       <c r="AQ234" s="15" t="n"/>
       <c r="AR234" s="15" t="n"/>
       <c r="AS234" s="15" t="n"/>
-      <c r="AT234" s="15" t="n"/>
-      <c r="AU234" s="15" t="n"/>
-      <c r="AV234" s="15" t="n"/>
-      <c r="AX234" s="16" t="n"/>
-      <c r="AY234" s="16" t="n"/>
-      <c r="AZ234" s="28" t="n"/>
+      <c r="AT234" s="32" t="n"/>
+      <c r="AU234" s="35" t="n"/>
+      <c r="AV234" s="35" t="n"/>
+      <c r="AW234" s="35" t="n"/>
+      <c r="AX234" s="28" t="n"/>
+      <c r="AY234" s="15" t="n"/>
+      <c r="AZ234" s="36" t="n"/>
       <c r="BA234" s="15" t="n"/>
-      <c r="BB234" s="5" t="n"/>
-      <c r="BC234" s="5" t="n"/>
+      <c r="BB234" s="15" t="n"/>
+      <c r="BC234" s="16" t="n"/>
       <c r="BD234" s="5" t="n"/>
       <c r="BE234" s="5" t="n"/>
+      <c r="BF234" s="5" t="n"/>
+      <c r="BG234" s="5" t="n"/>
     </row>
     <row r="235" ht="19.95" customHeight="1" s="30">
       <c r="A235" s="3" t="n">
@@ -27658,17 +29013,20 @@
       <c r="AQ235" s="15" t="n"/>
       <c r="AR235" s="15" t="n"/>
       <c r="AS235" s="15" t="n"/>
-      <c r="AT235" s="15" t="n"/>
-      <c r="AU235" s="15" t="n"/>
-      <c r="AV235" s="15" t="n"/>
-      <c r="AX235" s="16" t="n"/>
-      <c r="AY235" s="16" t="n"/>
-      <c r="AZ235" s="28" t="n"/>
+      <c r="AT235" s="32" t="n"/>
+      <c r="AU235" s="35" t="n"/>
+      <c r="AV235" s="35" t="n"/>
+      <c r="AW235" s="35" t="n"/>
+      <c r="AX235" s="28" t="n"/>
+      <c r="AY235" s="15" t="n"/>
+      <c r="AZ235" s="36" t="n"/>
       <c r="BA235" s="15" t="n"/>
-      <c r="BB235" s="5" t="n"/>
-      <c r="BC235" s="5" t="n"/>
+      <c r="BB235" s="15" t="n"/>
+      <c r="BC235" s="16" t="n"/>
       <c r="BD235" s="5" t="n"/>
       <c r="BE235" s="5" t="n"/>
+      <c r="BF235" s="5" t="n"/>
+      <c r="BG235" s="5" t="n"/>
     </row>
     <row r="236" ht="19.95" customHeight="1" s="30">
       <c r="A236" s="3" t="n">
@@ -27717,17 +29075,20 @@
       <c r="AQ236" s="15" t="n"/>
       <c r="AR236" s="15" t="n"/>
       <c r="AS236" s="15" t="n"/>
-      <c r="AT236" s="15" t="n"/>
-      <c r="AU236" s="15" t="n"/>
-      <c r="AV236" s="15" t="n"/>
-      <c r="AX236" s="16" t="n"/>
-      <c r="AY236" s="16" t="n"/>
-      <c r="AZ236" s="28" t="n"/>
+      <c r="AT236" s="32" t="n"/>
+      <c r="AU236" s="35" t="n"/>
+      <c r="AV236" s="35" t="n"/>
+      <c r="AW236" s="35" t="n"/>
+      <c r="AX236" s="28" t="n"/>
+      <c r="AY236" s="15" t="n"/>
+      <c r="AZ236" s="36" t="n"/>
       <c r="BA236" s="15" t="n"/>
-      <c r="BB236" s="5" t="n"/>
-      <c r="BC236" s="5" t="n"/>
+      <c r="BB236" s="15" t="n"/>
+      <c r="BC236" s="16" t="n"/>
       <c r="BD236" s="5" t="n"/>
       <c r="BE236" s="5" t="n"/>
+      <c r="BF236" s="5" t="n"/>
+      <c r="BG236" s="5" t="n"/>
     </row>
     <row r="237" ht="19.95" customHeight="1" s="30">
       <c r="A237" s="3" t="n">
@@ -27776,17 +29137,20 @@
       <c r="AQ237" s="15" t="n"/>
       <c r="AR237" s="15" t="n"/>
       <c r="AS237" s="15" t="n"/>
-      <c r="AT237" s="15" t="n"/>
-      <c r="AU237" s="15" t="n"/>
-      <c r="AV237" s="15" t="n"/>
-      <c r="AX237" s="16" t="n"/>
-      <c r="AY237" s="16" t="n"/>
-      <c r="AZ237" s="28" t="n"/>
+      <c r="AT237" s="32" t="n"/>
+      <c r="AU237" s="35" t="n"/>
+      <c r="AV237" s="35" t="n"/>
+      <c r="AW237" s="35" t="n"/>
+      <c r="AX237" s="28" t="n"/>
+      <c r="AY237" s="15" t="n"/>
+      <c r="AZ237" s="36" t="n"/>
       <c r="BA237" s="15" t="n"/>
-      <c r="BB237" s="5" t="n"/>
-      <c r="BC237" s="5" t="n"/>
+      <c r="BB237" s="15" t="n"/>
+      <c r="BC237" s="16" t="n"/>
       <c r="BD237" s="5" t="n"/>
       <c r="BE237" s="5" t="n"/>
+      <c r="BF237" s="5" t="n"/>
+      <c r="BG237" s="5" t="n"/>
     </row>
     <row r="238" ht="19.95" customHeight="1" s="30">
       <c r="A238" s="3" t="n">
@@ -27835,17 +29199,20 @@
       <c r="AQ238" s="15" t="n"/>
       <c r="AR238" s="15" t="n"/>
       <c r="AS238" s="15" t="n"/>
-      <c r="AT238" s="15" t="n"/>
-      <c r="AU238" s="15" t="n"/>
-      <c r="AV238" s="15" t="n"/>
-      <c r="AX238" s="16" t="n"/>
-      <c r="AY238" s="16" t="n"/>
-      <c r="AZ238" s="28" t="n"/>
+      <c r="AT238" s="32" t="n"/>
+      <c r="AU238" s="35" t="n"/>
+      <c r="AV238" s="35" t="n"/>
+      <c r="AW238" s="35" t="n"/>
+      <c r="AX238" s="28" t="n"/>
+      <c r="AY238" s="15" t="n"/>
+      <c r="AZ238" s="36" t="n"/>
       <c r="BA238" s="15" t="n"/>
-      <c r="BB238" s="5" t="n"/>
-      <c r="BC238" s="5" t="n"/>
+      <c r="BB238" s="15" t="n"/>
+      <c r="BC238" s="16" t="n"/>
       <c r="BD238" s="5" t="n"/>
       <c r="BE238" s="5" t="n"/>
+      <c r="BF238" s="5" t="n"/>
+      <c r="BG238" s="5" t="n"/>
     </row>
     <row r="239" ht="19.95" customHeight="1" s="30">
       <c r="A239" s="3" t="n">
@@ -27894,17 +29261,20 @@
       <c r="AQ239" s="15" t="n"/>
       <c r="AR239" s="15" t="n"/>
       <c r="AS239" s="15" t="n"/>
-      <c r="AT239" s="15" t="n"/>
-      <c r="AU239" s="15" t="n"/>
-      <c r="AV239" s="15" t="n"/>
-      <c r="AX239" s="16" t="n"/>
-      <c r="AY239" s="16" t="n"/>
-      <c r="AZ239" s="28" t="n"/>
+      <c r="AT239" s="32" t="n"/>
+      <c r="AU239" s="35" t="n"/>
+      <c r="AV239" s="35" t="n"/>
+      <c r="AW239" s="35" t="n"/>
+      <c r="AX239" s="28" t="n"/>
+      <c r="AY239" s="15" t="n"/>
+      <c r="AZ239" s="36" t="n"/>
       <c r="BA239" s="15" t="n"/>
-      <c r="BB239" s="5" t="n"/>
-      <c r="BC239" s="5" t="n"/>
+      <c r="BB239" s="15" t="n"/>
+      <c r="BC239" s="16" t="n"/>
       <c r="BD239" s="5" t="n"/>
       <c r="BE239" s="5" t="n"/>
+      <c r="BF239" s="5" t="n"/>
+      <c r="BG239" s="5" t="n"/>
     </row>
     <row r="240" ht="19.95" customHeight="1" s="30">
       <c r="A240" s="3" t="n">
@@ -27953,17 +29323,20 @@
       <c r="AQ240" s="15" t="n"/>
       <c r="AR240" s="15" t="n"/>
       <c r="AS240" s="15" t="n"/>
-      <c r="AT240" s="15" t="n"/>
-      <c r="AU240" s="15" t="n"/>
-      <c r="AV240" s="15" t="n"/>
-      <c r="AX240" s="16" t="n"/>
-      <c r="AY240" s="16" t="n"/>
-      <c r="AZ240" s="28" t="n"/>
+      <c r="AT240" s="32" t="n"/>
+      <c r="AU240" s="35" t="n"/>
+      <c r="AV240" s="35" t="n"/>
+      <c r="AW240" s="35" t="n"/>
+      <c r="AX240" s="28" t="n"/>
+      <c r="AY240" s="15" t="n"/>
+      <c r="AZ240" s="36" t="n"/>
       <c r="BA240" s="15" t="n"/>
-      <c r="BB240" s="5" t="n"/>
-      <c r="BC240" s="5" t="n"/>
+      <c r="BB240" s="15" t="n"/>
+      <c r="BC240" s="16" t="n"/>
       <c r="BD240" s="5" t="n"/>
       <c r="BE240" s="5" t="n"/>
+      <c r="BF240" s="5" t="n"/>
+      <c r="BG240" s="5" t="n"/>
     </row>
     <row r="241" ht="19.95" customHeight="1" s="30">
       <c r="A241" s="3" t="n">
@@ -28012,17 +29385,20 @@
       <c r="AQ241" s="15" t="n"/>
       <c r="AR241" s="15" t="n"/>
       <c r="AS241" s="15" t="n"/>
-      <c r="AT241" s="15" t="n"/>
-      <c r="AU241" s="15" t="n"/>
-      <c r="AV241" s="15" t="n"/>
-      <c r="AX241" s="16" t="n"/>
-      <c r="AY241" s="16" t="n"/>
-      <c r="AZ241" s="28" t="n"/>
+      <c r="AT241" s="32" t="n"/>
+      <c r="AU241" s="35" t="n"/>
+      <c r="AV241" s="35" t="n"/>
+      <c r="AW241" s="35" t="n"/>
+      <c r="AX241" s="28" t="n"/>
+      <c r="AY241" s="15" t="n"/>
+      <c r="AZ241" s="36" t="n"/>
       <c r="BA241" s="15" t="n"/>
-      <c r="BB241" s="5" t="n"/>
-      <c r="BC241" s="5" t="n"/>
+      <c r="BB241" s="15" t="n"/>
+      <c r="BC241" s="16" t="n"/>
       <c r="BD241" s="5" t="n"/>
       <c r="BE241" s="5" t="n"/>
+      <c r="BF241" s="5" t="n"/>
+      <c r="BG241" s="5" t="n"/>
     </row>
     <row r="242" ht="19.95" customHeight="1" s="30">
       <c r="A242" s="3" t="n">
@@ -28071,17 +29447,20 @@
       <c r="AQ242" s="15" t="n"/>
       <c r="AR242" s="15" t="n"/>
       <c r="AS242" s="15" t="n"/>
-      <c r="AT242" s="15" t="n"/>
-      <c r="AU242" s="15" t="n"/>
-      <c r="AV242" s="15" t="n"/>
-      <c r="AX242" s="16" t="n"/>
-      <c r="AY242" s="16" t="n"/>
-      <c r="AZ242" s="28" t="n"/>
+      <c r="AT242" s="32" t="n"/>
+      <c r="AU242" s="35" t="n"/>
+      <c r="AV242" s="35" t="n"/>
+      <c r="AW242" s="35" t="n"/>
+      <c r="AX242" s="28" t="n"/>
+      <c r="AY242" s="15" t="n"/>
+      <c r="AZ242" s="36" t="n"/>
       <c r="BA242" s="15" t="n"/>
-      <c r="BB242" s="5" t="n"/>
-      <c r="BC242" s="5" t="n"/>
+      <c r="BB242" s="15" t="n"/>
+      <c r="BC242" s="16" t="n"/>
       <c r="BD242" s="5" t="n"/>
       <c r="BE242" s="5" t="n"/>
+      <c r="BF242" s="5" t="n"/>
+      <c r="BG242" s="5" t="n"/>
     </row>
     <row r="243" ht="19.95" customHeight="1" s="30">
       <c r="A243" s="3" t="n">
@@ -28130,17 +29509,20 @@
       <c r="AQ243" s="15" t="n"/>
       <c r="AR243" s="15" t="n"/>
       <c r="AS243" s="15" t="n"/>
-      <c r="AT243" s="15" t="n"/>
-      <c r="AU243" s="15" t="n"/>
-      <c r="AV243" s="15" t="n"/>
-      <c r="AX243" s="16" t="n"/>
-      <c r="AY243" s="16" t="n"/>
-      <c r="AZ243" s="28" t="n"/>
+      <c r="AT243" s="32" t="n"/>
+      <c r="AU243" s="35" t="n"/>
+      <c r="AV243" s="35" t="n"/>
+      <c r="AW243" s="35" t="n"/>
+      <c r="AX243" s="28" t="n"/>
+      <c r="AY243" s="15" t="n"/>
+      <c r="AZ243" s="36" t="n"/>
       <c r="BA243" s="15" t="n"/>
-      <c r="BB243" s="5" t="n"/>
-      <c r="BC243" s="5" t="n"/>
+      <c r="BB243" s="15" t="n"/>
+      <c r="BC243" s="16" t="n"/>
       <c r="BD243" s="5" t="n"/>
       <c r="BE243" s="5" t="n"/>
+      <c r="BF243" s="5" t="n"/>
+      <c r="BG243" s="5" t="n"/>
     </row>
     <row r="244" ht="19.95" customHeight="1" s="30">
       <c r="A244" s="3" t="n">
@@ -28189,17 +29571,20 @@
       <c r="AQ244" s="15" t="n"/>
       <c r="AR244" s="15" t="n"/>
       <c r="AS244" s="15" t="n"/>
-      <c r="AT244" s="15" t="n"/>
-      <c r="AU244" s="15" t="n"/>
-      <c r="AV244" s="15" t="n"/>
-      <c r="AX244" s="16" t="n"/>
-      <c r="AY244" s="16" t="n"/>
-      <c r="AZ244" s="28" t="n"/>
+      <c r="AT244" s="32" t="n"/>
+      <c r="AU244" s="35" t="n"/>
+      <c r="AV244" s="35" t="n"/>
+      <c r="AW244" s="35" t="n"/>
+      <c r="AX244" s="28" t="n"/>
+      <c r="AY244" s="15" t="n"/>
+      <c r="AZ244" s="36" t="n"/>
       <c r="BA244" s="15" t="n"/>
-      <c r="BB244" s="5" t="n"/>
-      <c r="BC244" s="5" t="n"/>
+      <c r="BB244" s="15" t="n"/>
+      <c r="BC244" s="16" t="n"/>
       <c r="BD244" s="5" t="n"/>
       <c r="BE244" s="5" t="n"/>
+      <c r="BF244" s="5" t="n"/>
+      <c r="BG244" s="5" t="n"/>
     </row>
     <row r="245" ht="19.95" customHeight="1" s="30">
       <c r="A245" s="3" t="n">
@@ -28248,17 +29633,20 @@
       <c r="AQ245" s="15" t="n"/>
       <c r="AR245" s="15" t="n"/>
       <c r="AS245" s="15" t="n"/>
-      <c r="AT245" s="15" t="n"/>
-      <c r="AU245" s="15" t="n"/>
-      <c r="AV245" s="15" t="n"/>
-      <c r="AX245" s="16" t="n"/>
-      <c r="AY245" s="16" t="n"/>
-      <c r="AZ245" s="28" t="n"/>
+      <c r="AT245" s="32" t="n"/>
+      <c r="AU245" s="35" t="n"/>
+      <c r="AV245" s="35" t="n"/>
+      <c r="AW245" s="35" t="n"/>
+      <c r="AX245" s="28" t="n"/>
+      <c r="AY245" s="15" t="n"/>
+      <c r="AZ245" s="36" t="n"/>
       <c r="BA245" s="15" t="n"/>
-      <c r="BB245" s="5" t="n"/>
-      <c r="BC245" s="5" t="n"/>
+      <c r="BB245" s="15" t="n"/>
+      <c r="BC245" s="16" t="n"/>
       <c r="BD245" s="5" t="n"/>
       <c r="BE245" s="5" t="n"/>
+      <c r="BF245" s="5" t="n"/>
+      <c r="BG245" s="5" t="n"/>
     </row>
     <row r="246" ht="19.95" customHeight="1" s="30">
       <c r="A246" s="3" t="n">
@@ -28307,17 +29695,20 @@
       <c r="AQ246" s="15" t="n"/>
       <c r="AR246" s="15" t="n"/>
       <c r="AS246" s="15" t="n"/>
-      <c r="AT246" s="15" t="n"/>
-      <c r="AU246" s="15" t="n"/>
-      <c r="AV246" s="15" t="n"/>
-      <c r="AX246" s="16" t="n"/>
-      <c r="AY246" s="16" t="n"/>
-      <c r="AZ246" s="28" t="n"/>
+      <c r="AT246" s="32" t="n"/>
+      <c r="AU246" s="35" t="n"/>
+      <c r="AV246" s="35" t="n"/>
+      <c r="AW246" s="35" t="n"/>
+      <c r="AX246" s="28" t="n"/>
+      <c r="AY246" s="15" t="n"/>
+      <c r="AZ246" s="36" t="n"/>
       <c r="BA246" s="15" t="n"/>
-      <c r="BB246" s="5" t="n"/>
-      <c r="BC246" s="5" t="n"/>
+      <c r="BB246" s="15" t="n"/>
+      <c r="BC246" s="16" t="n"/>
       <c r="BD246" s="5" t="n"/>
       <c r="BE246" s="5" t="n"/>
+      <c r="BF246" s="5" t="n"/>
+      <c r="BG246" s="5" t="n"/>
     </row>
     <row r="247" ht="19.95" customHeight="1" s="30">
       <c r="A247" s="3" t="n">
@@ -28366,17 +29757,20 @@
       <c r="AQ247" s="15" t="n"/>
       <c r="AR247" s="15" t="n"/>
       <c r="AS247" s="15" t="n"/>
-      <c r="AT247" s="15" t="n"/>
-      <c r="AU247" s="15" t="n"/>
-      <c r="AV247" s="15" t="n"/>
-      <c r="AX247" s="16" t="n"/>
-      <c r="AY247" s="16" t="n"/>
-      <c r="AZ247" s="28" t="n"/>
+      <c r="AT247" s="32" t="n"/>
+      <c r="AU247" s="35" t="n"/>
+      <c r="AV247" s="35" t="n"/>
+      <c r="AW247" s="35" t="n"/>
+      <c r="AX247" s="28" t="n"/>
+      <c r="AY247" s="15" t="n"/>
+      <c r="AZ247" s="36" t="n"/>
       <c r="BA247" s="15" t="n"/>
-      <c r="BB247" s="5" t="n"/>
-      <c r="BC247" s="5" t="n"/>
+      <c r="BB247" s="15" t="n"/>
+      <c r="BC247" s="16" t="n"/>
       <c r="BD247" s="5" t="n"/>
       <c r="BE247" s="5" t="n"/>
+      <c r="BF247" s="5" t="n"/>
+      <c r="BG247" s="5" t="n"/>
     </row>
     <row r="248" ht="19.95" customHeight="1" s="30">
       <c r="A248" s="3" t="n">
@@ -28425,17 +29819,20 @@
       <c r="AQ248" s="15" t="n"/>
       <c r="AR248" s="15" t="n"/>
       <c r="AS248" s="15" t="n"/>
-      <c r="AT248" s="15" t="n"/>
-      <c r="AU248" s="15" t="n"/>
-      <c r="AV248" s="15" t="n"/>
-      <c r="AX248" s="16" t="n"/>
-      <c r="AY248" s="16" t="n"/>
-      <c r="AZ248" s="28" t="n"/>
+      <c r="AT248" s="32" t="n"/>
+      <c r="AU248" s="35" t="n"/>
+      <c r="AV248" s="35" t="n"/>
+      <c r="AW248" s="35" t="n"/>
+      <c r="AX248" s="28" t="n"/>
+      <c r="AY248" s="15" t="n"/>
+      <c r="AZ248" s="36" t="n"/>
       <c r="BA248" s="15" t="n"/>
-      <c r="BB248" s="5" t="n"/>
-      <c r="BC248" s="5" t="n"/>
+      <c r="BB248" s="15" t="n"/>
+      <c r="BC248" s="16" t="n"/>
       <c r="BD248" s="5" t="n"/>
       <c r="BE248" s="5" t="n"/>
+      <c r="BF248" s="5" t="n"/>
+      <c r="BG248" s="5" t="n"/>
     </row>
     <row r="249" ht="19.95" customHeight="1" s="30">
       <c r="A249" s="3" t="n">
@@ -28484,17 +29881,20 @@
       <c r="AQ249" s="15" t="n"/>
       <c r="AR249" s="15" t="n"/>
       <c r="AS249" s="15" t="n"/>
-      <c r="AT249" s="15" t="n"/>
-      <c r="AU249" s="15" t="n"/>
-      <c r="AV249" s="15" t="n"/>
-      <c r="AX249" s="16" t="n"/>
-      <c r="AY249" s="16" t="n"/>
-      <c r="AZ249" s="28" t="n"/>
+      <c r="AT249" s="32" t="n"/>
+      <c r="AU249" s="35" t="n"/>
+      <c r="AV249" s="35" t="n"/>
+      <c r="AW249" s="35" t="n"/>
+      <c r="AX249" s="28" t="n"/>
+      <c r="AY249" s="15" t="n"/>
+      <c r="AZ249" s="36" t="n"/>
       <c r="BA249" s="15" t="n"/>
-      <c r="BB249" s="5" t="n"/>
-      <c r="BC249" s="5" t="n"/>
+      <c r="BB249" s="15" t="n"/>
+      <c r="BC249" s="16" t="n"/>
       <c r="BD249" s="5" t="n"/>
       <c r="BE249" s="5" t="n"/>
+      <c r="BF249" s="5" t="n"/>
+      <c r="BG249" s="5" t="n"/>
     </row>
     <row r="250" ht="19.95" customHeight="1" s="30">
       <c r="A250" s="3" t="n">
@@ -28543,17 +29943,20 @@
       <c r="AQ250" s="15" t="n"/>
       <c r="AR250" s="15" t="n"/>
       <c r="AS250" s="15" t="n"/>
-      <c r="AT250" s="15" t="n"/>
-      <c r="AU250" s="15" t="n"/>
-      <c r="AV250" s="15" t="n"/>
-      <c r="AX250" s="16" t="n"/>
-      <c r="AY250" s="16" t="n"/>
-      <c r="AZ250" s="28" t="n"/>
+      <c r="AT250" s="32" t="n"/>
+      <c r="AU250" s="35" t="n"/>
+      <c r="AV250" s="35" t="n"/>
+      <c r="AW250" s="35" t="n"/>
+      <c r="AX250" s="28" t="n"/>
+      <c r="AY250" s="15" t="n"/>
+      <c r="AZ250" s="36" t="n"/>
       <c r="BA250" s="15" t="n"/>
-      <c r="BB250" s="5" t="n"/>
-      <c r="BC250" s="5" t="n"/>
+      <c r="BB250" s="15" t="n"/>
+      <c r="BC250" s="16" t="n"/>
       <c r="BD250" s="5" t="n"/>
       <c r="BE250" s="5" t="n"/>
+      <c r="BF250" s="5" t="n"/>
+      <c r="BG250" s="5" t="n"/>
     </row>
     <row r="251" ht="19.95" customHeight="1" s="30">
       <c r="A251" s="3" t="n">
@@ -28602,17 +30005,20 @@
       <c r="AQ251" s="15" t="n"/>
       <c r="AR251" s="15" t="n"/>
       <c r="AS251" s="15" t="n"/>
-      <c r="AT251" s="15" t="n"/>
-      <c r="AU251" s="15" t="n"/>
-      <c r="AV251" s="15" t="n"/>
-      <c r="AX251" s="16" t="n"/>
-      <c r="AY251" s="16" t="n"/>
-      <c r="AZ251" s="28" t="n"/>
+      <c r="AT251" s="32" t="n"/>
+      <c r="AU251" s="35" t="n"/>
+      <c r="AV251" s="35" t="n"/>
+      <c r="AW251" s="35" t="n"/>
+      <c r="AX251" s="28" t="n"/>
+      <c r="AY251" s="15" t="n"/>
+      <c r="AZ251" s="36" t="n"/>
       <c r="BA251" s="15" t="n"/>
-      <c r="BB251" s="5" t="n"/>
-      <c r="BC251" s="5" t="n"/>
+      <c r="BB251" s="15" t="n"/>
+      <c r="BC251" s="16" t="n"/>
       <c r="BD251" s="5" t="n"/>
       <c r="BE251" s="5" t="n"/>
+      <c r="BF251" s="5" t="n"/>
+      <c r="BG251" s="5" t="n"/>
     </row>
     <row r="252" ht="19.95" customHeight="1" s="30">
       <c r="A252" s="3" t="n">
@@ -28661,17 +30067,20 @@
       <c r="AQ252" s="15" t="n"/>
       <c r="AR252" s="15" t="n"/>
       <c r="AS252" s="15" t="n"/>
-      <c r="AT252" s="15" t="n"/>
-      <c r="AU252" s="15" t="n"/>
-      <c r="AV252" s="15" t="n"/>
-      <c r="AX252" s="16" t="n"/>
-      <c r="AY252" s="16" t="n"/>
-      <c r="AZ252" s="28" t="n"/>
+      <c r="AT252" s="32" t="n"/>
+      <c r="AU252" s="35" t="n"/>
+      <c r="AV252" s="35" t="n"/>
+      <c r="AW252" s="35" t="n"/>
+      <c r="AX252" s="28" t="n"/>
+      <c r="AY252" s="15" t="n"/>
+      <c r="AZ252" s="36" t="n"/>
       <c r="BA252" s="15" t="n"/>
-      <c r="BB252" s="5" t="n"/>
-      <c r="BC252" s="5" t="n"/>
+      <c r="BB252" s="15" t="n"/>
+      <c r="BC252" s="16" t="n"/>
       <c r="BD252" s="5" t="n"/>
       <c r="BE252" s="5" t="n"/>
+      <c r="BF252" s="5" t="n"/>
+      <c r="BG252" s="5" t="n"/>
     </row>
     <row r="253" ht="19.95" customHeight="1" s="30">
       <c r="A253" s="3" t="n">
@@ -28720,17 +30129,20 @@
       <c r="AQ253" s="15" t="n"/>
       <c r="AR253" s="15" t="n"/>
       <c r="AS253" s="15" t="n"/>
-      <c r="AT253" s="15" t="n"/>
-      <c r="AU253" s="15" t="n"/>
-      <c r="AV253" s="15" t="n"/>
-      <c r="AX253" s="16" t="n"/>
-      <c r="AY253" s="16" t="n"/>
-      <c r="AZ253" s="28" t="n"/>
+      <c r="AT253" s="32" t="n"/>
+      <c r="AU253" s="35" t="n"/>
+      <c r="AV253" s="35" t="n"/>
+      <c r="AW253" s="35" t="n"/>
+      <c r="AX253" s="28" t="n"/>
+      <c r="AY253" s="15" t="n"/>
+      <c r="AZ253" s="36" t="n"/>
       <c r="BA253" s="15" t="n"/>
-      <c r="BB253" s="5" t="n"/>
-      <c r="BC253" s="5" t="n"/>
+      <c r="BB253" s="15" t="n"/>
+      <c r="BC253" s="16" t="n"/>
       <c r="BD253" s="5" t="n"/>
       <c r="BE253" s="5" t="n"/>
+      <c r="BF253" s="5" t="n"/>
+      <c r="BG253" s="5" t="n"/>
     </row>
     <row r="254" ht="19.95" customHeight="1" s="30">
       <c r="A254" s="3" t="n">
@@ -28779,17 +30191,20 @@
       <c r="AQ254" s="15" t="n"/>
       <c r="AR254" s="15" t="n"/>
       <c r="AS254" s="15" t="n"/>
-      <c r="AT254" s="15" t="n"/>
-      <c r="AU254" s="15" t="n"/>
-      <c r="AV254" s="15" t="n"/>
-      <c r="AX254" s="16" t="n"/>
-      <c r="AY254" s="16" t="n"/>
-      <c r="AZ254" s="28" t="n"/>
+      <c r="AT254" s="32" t="n"/>
+      <c r="AU254" s="35" t="n"/>
+      <c r="AV254" s="35" t="n"/>
+      <c r="AW254" s="35" t="n"/>
+      <c r="AX254" s="28" t="n"/>
+      <c r="AY254" s="15" t="n"/>
+      <c r="AZ254" s="36" t="n"/>
       <c r="BA254" s="15" t="n"/>
-      <c r="BB254" s="5" t="n"/>
-      <c r="BC254" s="5" t="n"/>
+      <c r="BB254" s="15" t="n"/>
+      <c r="BC254" s="16" t="n"/>
       <c r="BD254" s="5" t="n"/>
       <c r="BE254" s="5" t="n"/>
+      <c r="BF254" s="5" t="n"/>
+      <c r="BG254" s="5" t="n"/>
     </row>
     <row r="255" ht="19.95" customHeight="1" s="30">
       <c r="A255" s="3" t="n">
@@ -28838,17 +30253,20 @@
       <c r="AQ255" s="15" t="n"/>
       <c r="AR255" s="15" t="n"/>
       <c r="AS255" s="15" t="n"/>
-      <c r="AT255" s="15" t="n"/>
-      <c r="AU255" s="15" t="n"/>
-      <c r="AV255" s="15" t="n"/>
-      <c r="AX255" s="16" t="n"/>
-      <c r="AY255" s="16" t="n"/>
-      <c r="AZ255" s="28" t="n"/>
+      <c r="AT255" s="32" t="n"/>
+      <c r="AU255" s="35" t="n"/>
+      <c r="AV255" s="35" t="n"/>
+      <c r="AW255" s="35" t="n"/>
+      <c r="AX255" s="28" t="n"/>
+      <c r="AY255" s="15" t="n"/>
+      <c r="AZ255" s="36" t="n"/>
       <c r="BA255" s="15" t="n"/>
-      <c r="BB255" s="5" t="n"/>
-      <c r="BC255" s="5" t="n"/>
+      <c r="BB255" s="15" t="n"/>
+      <c r="BC255" s="16" t="n"/>
       <c r="BD255" s="5" t="n"/>
       <c r="BE255" s="5" t="n"/>
+      <c r="BF255" s="5" t="n"/>
+      <c r="BG255" s="5" t="n"/>
     </row>
     <row r="256" ht="19.95" customHeight="1" s="30">
       <c r="A256" s="3" t="n">
@@ -28897,17 +30315,20 @@
       <c r="AQ256" s="15" t="n"/>
       <c r="AR256" s="15" t="n"/>
       <c r="AS256" s="15" t="n"/>
-      <c r="AT256" s="15" t="n"/>
-      <c r="AU256" s="15" t="n"/>
-      <c r="AV256" s="15" t="n"/>
-      <c r="AX256" s="16" t="n"/>
-      <c r="AY256" s="16" t="n"/>
-      <c r="AZ256" s="28" t="n"/>
+      <c r="AT256" s="32" t="n"/>
+      <c r="AU256" s="35" t="n"/>
+      <c r="AV256" s="35" t="n"/>
+      <c r="AW256" s="35" t="n"/>
+      <c r="AX256" s="28" t="n"/>
+      <c r="AY256" s="15" t="n"/>
+      <c r="AZ256" s="36" t="n"/>
       <c r="BA256" s="15" t="n"/>
-      <c r="BB256" s="5" t="n"/>
-      <c r="BC256" s="5" t="n"/>
+      <c r="BB256" s="15" t="n"/>
+      <c r="BC256" s="16" t="n"/>
       <c r="BD256" s="5" t="n"/>
       <c r="BE256" s="5" t="n"/>
+      <c r="BF256" s="5" t="n"/>
+      <c r="BG256" s="5" t="n"/>
     </row>
     <row r="257" ht="19.95" customHeight="1" s="30">
       <c r="A257" s="3" t="n">
@@ -28956,17 +30377,20 @@
       <c r="AQ257" s="15" t="n"/>
       <c r="AR257" s="15" t="n"/>
       <c r="AS257" s="15" t="n"/>
-      <c r="AT257" s="15" t="n"/>
-      <c r="AU257" s="15" t="n"/>
-      <c r="AV257" s="15" t="n"/>
-      <c r="AX257" s="16" t="n"/>
-      <c r="AY257" s="16" t="n"/>
-      <c r="AZ257" s="28" t="n"/>
+      <c r="AT257" s="32" t="n"/>
+      <c r="AU257" s="35" t="n"/>
+      <c r="AV257" s="35" t="n"/>
+      <c r="AW257" s="35" t="n"/>
+      <c r="AX257" s="28" t="n"/>
+      <c r="AY257" s="15" t="n"/>
+      <c r="AZ257" s="36" t="n"/>
       <c r="BA257" s="15" t="n"/>
-      <c r="BB257" s="5" t="n"/>
-      <c r="BC257" s="5" t="n"/>
+      <c r="BB257" s="15" t="n"/>
+      <c r="BC257" s="16" t="n"/>
       <c r="BD257" s="5" t="n"/>
       <c r="BE257" s="5" t="n"/>
+      <c r="BF257" s="5" t="n"/>
+      <c r="BG257" s="5" t="n"/>
     </row>
     <row r="258" ht="19.95" customHeight="1" s="30">
       <c r="A258" s="3" t="n">
@@ -29015,17 +30439,20 @@
       <c r="AQ258" s="15" t="n"/>
       <c r="AR258" s="15" t="n"/>
       <c r="AS258" s="15" t="n"/>
-      <c r="AT258" s="15" t="n"/>
-      <c r="AU258" s="15" t="n"/>
-      <c r="AV258" s="15" t="n"/>
-      <c r="AX258" s="16" t="n"/>
-      <c r="AY258" s="16" t="n"/>
-      <c r="AZ258" s="28" t="n"/>
+      <c r="AT258" s="32" t="n"/>
+      <c r="AU258" s="35" t="n"/>
+      <c r="AV258" s="35" t="n"/>
+      <c r="AW258" s="35" t="n"/>
+      <c r="AX258" s="28" t="n"/>
+      <c r="AY258" s="15" t="n"/>
+      <c r="AZ258" s="36" t="n"/>
       <c r="BA258" s="15" t="n"/>
-      <c r="BB258" s="5" t="n"/>
-      <c r="BC258" s="5" t="n"/>
+      <c r="BB258" s="15" t="n"/>
+      <c r="BC258" s="16" t="n"/>
       <c r="BD258" s="5" t="n"/>
       <c r="BE258" s="5" t="n"/>
+      <c r="BF258" s="5" t="n"/>
+      <c r="BG258" s="5" t="n"/>
     </row>
     <row r="259" ht="19.95" customHeight="1" s="30">
       <c r="A259" s="3" t="n">
@@ -29074,17 +30501,20 @@
       <c r="AQ259" s="15" t="n"/>
       <c r="AR259" s="15" t="n"/>
       <c r="AS259" s="15" t="n"/>
-      <c r="AT259" s="15" t="n"/>
-      <c r="AU259" s="15" t="n"/>
-      <c r="AV259" s="15" t="n"/>
-      <c r="AX259" s="16" t="n"/>
-      <c r="AY259" s="16" t="n"/>
-      <c r="AZ259" s="28" t="n"/>
+      <c r="AT259" s="32" t="n"/>
+      <c r="AU259" s="35" t="n"/>
+      <c r="AV259" s="35" t="n"/>
+      <c r="AW259" s="35" t="n"/>
+      <c r="AX259" s="28" t="n"/>
+      <c r="AY259" s="15" t="n"/>
+      <c r="AZ259" s="36" t="n"/>
       <c r="BA259" s="15" t="n"/>
-      <c r="BB259" s="5" t="n"/>
-      <c r="BC259" s="5" t="n"/>
+      <c r="BB259" s="15" t="n"/>
+      <c r="BC259" s="16" t="n"/>
       <c r="BD259" s="5" t="n"/>
       <c r="BE259" s="5" t="n"/>
+      <c r="BF259" s="5" t="n"/>
+      <c r="BG259" s="5" t="n"/>
     </row>
     <row r="260" ht="19.95" customHeight="1" s="30">
       <c r="A260" s="3" t="n">
@@ -29133,17 +30563,20 @@
       <c r="AQ260" s="15" t="n"/>
       <c r="AR260" s="15" t="n"/>
       <c r="AS260" s="15" t="n"/>
-      <c r="AT260" s="15" t="n"/>
-      <c r="AU260" s="15" t="n"/>
-      <c r="AV260" s="15" t="n"/>
-      <c r="AX260" s="16" t="n"/>
-      <c r="AY260" s="16" t="n"/>
-      <c r="AZ260" s="28" t="n"/>
+      <c r="AT260" s="32" t="n"/>
+      <c r="AU260" s="35" t="n"/>
+      <c r="AV260" s="35" t="n"/>
+      <c r="AW260" s="35" t="n"/>
+      <c r="AX260" s="28" t="n"/>
+      <c r="AY260" s="15" t="n"/>
+      <c r="AZ260" s="36" t="n"/>
       <c r="BA260" s="15" t="n"/>
-      <c r="BB260" s="5" t="n"/>
-      <c r="BC260" s="5" t="n"/>
+      <c r="BB260" s="15" t="n"/>
+      <c r="BC260" s="16" t="n"/>
       <c r="BD260" s="5" t="n"/>
       <c r="BE260" s="5" t="n"/>
+      <c r="BF260" s="5" t="n"/>
+      <c r="BG260" s="5" t="n"/>
     </row>
     <row r="261" ht="19.95" customHeight="1" s="30">
       <c r="A261" s="3" t="n">
@@ -29192,17 +30625,20 @@
       <c r="AQ261" s="15" t="n"/>
       <c r="AR261" s="15" t="n"/>
       <c r="AS261" s="15" t="n"/>
-      <c r="AT261" s="15" t="n"/>
-      <c r="AU261" s="15" t="n"/>
-      <c r="AV261" s="15" t="n"/>
-      <c r="AX261" s="16" t="n"/>
-      <c r="AY261" s="16" t="n"/>
-      <c r="AZ261" s="28" t="n"/>
+      <c r="AT261" s="32" t="n"/>
+      <c r="AU261" s="35" t="n"/>
+      <c r="AV261" s="35" t="n"/>
+      <c r="AW261" s="35" t="n"/>
+      <c r="AX261" s="28" t="n"/>
+      <c r="AY261" s="15" t="n"/>
+      <c r="AZ261" s="36" t="n"/>
       <c r="BA261" s="15" t="n"/>
-      <c r="BB261" s="5" t="n"/>
-      <c r="BC261" s="5" t="n"/>
+      <c r="BB261" s="15" t="n"/>
+      <c r="BC261" s="16" t="n"/>
       <c r="BD261" s="5" t="n"/>
       <c r="BE261" s="5" t="n"/>
+      <c r="BF261" s="5" t="n"/>
+      <c r="BG261" s="5" t="n"/>
     </row>
     <row r="262" ht="19.95" customHeight="1" s="30">
       <c r="A262" s="3" t="n">
@@ -29251,17 +30687,20 @@
       <c r="AQ262" s="15" t="n"/>
       <c r="AR262" s="15" t="n"/>
       <c r="AS262" s="15" t="n"/>
-      <c r="AT262" s="15" t="n"/>
-      <c r="AU262" s="15" t="n"/>
-      <c r="AV262" s="15" t="n"/>
-      <c r="AX262" s="16" t="n"/>
-      <c r="AY262" s="16" t="n"/>
-      <c r="AZ262" s="28" t="n"/>
+      <c r="AT262" s="32" t="n"/>
+      <c r="AU262" s="35" t="n"/>
+      <c r="AV262" s="35" t="n"/>
+      <c r="AW262" s="35" t="n"/>
+      <c r="AX262" s="28" t="n"/>
+      <c r="AY262" s="15" t="n"/>
+      <c r="AZ262" s="36" t="n"/>
       <c r="BA262" s="15" t="n"/>
-      <c r="BB262" s="5" t="n"/>
-      <c r="BC262" s="5" t="n"/>
+      <c r="BB262" s="15" t="n"/>
+      <c r="BC262" s="16" t="n"/>
       <c r="BD262" s="5" t="n"/>
       <c r="BE262" s="5" t="n"/>
+      <c r="BF262" s="5" t="n"/>
+      <c r="BG262" s="5" t="n"/>
     </row>
     <row r="263" ht="19.95" customHeight="1" s="30">
       <c r="A263" s="3" t="n">
@@ -29310,17 +30749,20 @@
       <c r="AQ263" s="15" t="n"/>
       <c r="AR263" s="15" t="n"/>
       <c r="AS263" s="15" t="n"/>
-      <c r="AT263" s="15" t="n"/>
-      <c r="AU263" s="15" t="n"/>
-      <c r="AV263" s="15" t="n"/>
-      <c r="AX263" s="16" t="n"/>
-      <c r="AY263" s="16" t="n"/>
-      <c r="AZ263" s="28" t="n"/>
+      <c r="AT263" s="32" t="n"/>
+      <c r="AU263" s="35" t="n"/>
+      <c r="AV263" s="35" t="n"/>
+      <c r="AW263" s="35" t="n"/>
+      <c r="AX263" s="28" t="n"/>
+      <c r="AY263" s="15" t="n"/>
+      <c r="AZ263" s="36" t="n"/>
       <c r="BA263" s="15" t="n"/>
-      <c r="BB263" s="5" t="n"/>
-      <c r="BC263" s="5" t="n"/>
+      <c r="BB263" s="15" t="n"/>
+      <c r="BC263" s="16" t="n"/>
       <c r="BD263" s="5" t="n"/>
       <c r="BE263" s="5" t="n"/>
+      <c r="BF263" s="5" t="n"/>
+      <c r="BG263" s="5" t="n"/>
     </row>
     <row r="264" ht="19.95" customHeight="1" s="30">
       <c r="A264" s="3" t="n">
@@ -29369,17 +30811,20 @@
       <c r="AQ264" s="15" t="n"/>
       <c r="AR264" s="15" t="n"/>
       <c r="AS264" s="15" t="n"/>
-      <c r="AT264" s="15" t="n"/>
-      <c r="AU264" s="15" t="n"/>
-      <c r="AV264" s="15" t="n"/>
-      <c r="AX264" s="16" t="n"/>
-      <c r="AY264" s="16" t="n"/>
-      <c r="AZ264" s="28" t="n"/>
+      <c r="AT264" s="32" t="n"/>
+      <c r="AU264" s="35" t="n"/>
+      <c r="AV264" s="35" t="n"/>
+      <c r="AW264" s="35" t="n"/>
+      <c r="AX264" s="28" t="n"/>
+      <c r="AY264" s="15" t="n"/>
+      <c r="AZ264" s="36" t="n"/>
       <c r="BA264" s="15" t="n"/>
-      <c r="BB264" s="5" t="n"/>
-      <c r="BC264" s="5" t="n"/>
+      <c r="BB264" s="15" t="n"/>
+      <c r="BC264" s="16" t="n"/>
       <c r="BD264" s="5" t="n"/>
       <c r="BE264" s="5" t="n"/>
+      <c r="BF264" s="5" t="n"/>
+      <c r="BG264" s="5" t="n"/>
     </row>
     <row r="265" ht="19.95" customHeight="1" s="30">
       <c r="A265" s="3" t="n">
@@ -29428,17 +30873,20 @@
       <c r="AQ265" s="15" t="n"/>
       <c r="AR265" s="15" t="n"/>
       <c r="AS265" s="15" t="n"/>
-      <c r="AT265" s="15" t="n"/>
-      <c r="AU265" s="15" t="n"/>
-      <c r="AV265" s="15" t="n"/>
-      <c r="AX265" s="16" t="n"/>
-      <c r="AY265" s="16" t="n"/>
-      <c r="AZ265" s="28" t="n"/>
+      <c r="AT265" s="32" t="n"/>
+      <c r="AU265" s="35" t="n"/>
+      <c r="AV265" s="35" t="n"/>
+      <c r="AW265" s="35" t="n"/>
+      <c r="AX265" s="28" t="n"/>
+      <c r="AY265" s="15" t="n"/>
+      <c r="AZ265" s="36" t="n"/>
       <c r="BA265" s="15" t="n"/>
-      <c r="BB265" s="5" t="n"/>
-      <c r="BC265" s="5" t="n"/>
+      <c r="BB265" s="15" t="n"/>
+      <c r="BC265" s="16" t="n"/>
       <c r="BD265" s="5" t="n"/>
       <c r="BE265" s="5" t="n"/>
+      <c r="BF265" s="5" t="n"/>
+      <c r="BG265" s="5" t="n"/>
     </row>
     <row r="266" ht="19.95" customHeight="1" s="30">
       <c r="A266" s="3" t="n">
@@ -29487,17 +30935,20 @@
       <c r="AQ266" s="15" t="n"/>
       <c r="AR266" s="15" t="n"/>
       <c r="AS266" s="15" t="n"/>
-      <c r="AT266" s="15" t="n"/>
-      <c r="AU266" s="15" t="n"/>
-      <c r="AV266" s="15" t="n"/>
-      <c r="AX266" s="16" t="n"/>
-      <c r="AY266" s="16" t="n"/>
-      <c r="AZ266" s="28" t="n"/>
+      <c r="AT266" s="32" t="n"/>
+      <c r="AU266" s="35" t="n"/>
+      <c r="AV266" s="35" t="n"/>
+      <c r="AW266" s="35" t="n"/>
+      <c r="AX266" s="28" t="n"/>
+      <c r="AY266" s="15" t="n"/>
+      <c r="AZ266" s="36" t="n"/>
       <c r="BA266" s="15" t="n"/>
-      <c r="BB266" s="5" t="n"/>
-      <c r="BC266" s="5" t="n"/>
+      <c r="BB266" s="15" t="n"/>
+      <c r="BC266" s="16" t="n"/>
       <c r="BD266" s="5" t="n"/>
       <c r="BE266" s="5" t="n"/>
+      <c r="BF266" s="5" t="n"/>
+      <c r="BG266" s="5" t="n"/>
     </row>
     <row r="267" ht="19.95" customHeight="1" s="30">
       <c r="A267" s="3" t="n">
@@ -29546,17 +30997,20 @@
       <c r="AQ267" s="15" t="n"/>
       <c r="AR267" s="15" t="n"/>
       <c r="AS267" s="15" t="n"/>
-      <c r="AT267" s="15" t="n"/>
-      <c r="AU267" s="15" t="n"/>
-      <c r="AV267" s="15" t="n"/>
-      <c r="AX267" s="16" t="n"/>
-      <c r="AY267" s="16" t="n"/>
-      <c r="AZ267" s="28" t="n"/>
+      <c r="AT267" s="32" t="n"/>
+      <c r="AU267" s="35" t="n"/>
+      <c r="AV267" s="35" t="n"/>
+      <c r="AW267" s="35" t="n"/>
+      <c r="AX267" s="28" t="n"/>
+      <c r="AY267" s="15" t="n"/>
+      <c r="AZ267" s="36" t="n"/>
       <c r="BA267" s="15" t="n"/>
-      <c r="BB267" s="5" t="n"/>
-      <c r="BC267" s="5" t="n"/>
+      <c r="BB267" s="15" t="n"/>
+      <c r="BC267" s="16" t="n"/>
       <c r="BD267" s="5" t="n"/>
       <c r="BE267" s="5" t="n"/>
+      <c r="BF267" s="5" t="n"/>
+      <c r="BG267" s="5" t="n"/>
     </row>
     <row r="268" ht="19.95" customHeight="1" s="30">
       <c r="A268" s="3" t="n">
@@ -29605,17 +31059,20 @@
       <c r="AQ268" s="15" t="n"/>
       <c r="AR268" s="15" t="n"/>
       <c r="AS268" s="15" t="n"/>
-      <c r="AT268" s="15" t="n"/>
-      <c r="AU268" s="15" t="n"/>
-      <c r="AV268" s="15" t="n"/>
-      <c r="AX268" s="16" t="n"/>
-      <c r="AY268" s="16" t="n"/>
-      <c r="AZ268" s="28" t="n"/>
+      <c r="AT268" s="32" t="n"/>
+      <c r="AU268" s="35" t="n"/>
+      <c r="AV268" s="35" t="n"/>
+      <c r="AW268" s="35" t="n"/>
+      <c r="AX268" s="28" t="n"/>
+      <c r="AY268" s="15" t="n"/>
+      <c r="AZ268" s="36" t="n"/>
       <c r="BA268" s="15" t="n"/>
-      <c r="BB268" s="5" t="n"/>
-      <c r="BC268" s="5" t="n"/>
+      <c r="BB268" s="15" t="n"/>
+      <c r="BC268" s="16" t="n"/>
       <c r="BD268" s="5" t="n"/>
       <c r="BE268" s="5" t="n"/>
+      <c r="BF268" s="5" t="n"/>
+      <c r="BG268" s="5" t="n"/>
     </row>
     <row r="269" ht="19.95" customHeight="1" s="30">
       <c r="A269" s="3" t="n">
@@ -29664,17 +31121,20 @@
       <c r="AQ269" s="15" t="n"/>
       <c r="AR269" s="15" t="n"/>
       <c r="AS269" s="15" t="n"/>
-      <c r="AT269" s="15" t="n"/>
-      <c r="AU269" s="15" t="n"/>
-      <c r="AV269" s="15" t="n"/>
-      <c r="AX269" s="16" t="n"/>
-      <c r="AY269" s="16" t="n"/>
-      <c r="AZ269" s="28" t="n"/>
+      <c r="AT269" s="32" t="n"/>
+      <c r="AU269" s="35" t="n"/>
+      <c r="AV269" s="35" t="n"/>
+      <c r="AW269" s="35" t="n"/>
+      <c r="AX269" s="28" t="n"/>
+      <c r="AY269" s="15" t="n"/>
+      <c r="AZ269" s="36" t="n"/>
       <c r="BA269" s="15" t="n"/>
-      <c r="BB269" s="5" t="n"/>
-      <c r="BC269" s="5" t="n"/>
+      <c r="BB269" s="15" t="n"/>
+      <c r="BC269" s="16" t="n"/>
       <c r="BD269" s="5" t="n"/>
       <c r="BE269" s="5" t="n"/>
+      <c r="BF269" s="5" t="n"/>
+      <c r="BG269" s="5" t="n"/>
     </row>
     <row r="270" ht="19.95" customHeight="1" s="30">
       <c r="A270" s="3" t="n">
@@ -29723,34 +31183,38 @@
       <c r="AQ270" s="15" t="n"/>
       <c r="AR270" s="15" t="n"/>
       <c r="AS270" s="15" t="n"/>
-      <c r="AT270" s="15" t="n"/>
-      <c r="AU270" s="15" t="n"/>
-      <c r="AV270" s="15" t="n"/>
-      <c r="AX270" s="16" t="n"/>
-      <c r="AY270" s="16" t="n"/>
-      <c r="AZ270" s="28" t="n"/>
+      <c r="AT270" s="32" t="n"/>
+      <c r="AU270" s="35" t="n"/>
+      <c r="AV270" s="35" t="n"/>
+      <c r="AW270" s="35" t="n"/>
+      <c r="AX270" s="28" t="n"/>
+      <c r="AY270" s="15" t="n"/>
+      <c r="AZ270" s="36" t="n"/>
       <c r="BA270" s="15" t="n"/>
-      <c r="BB270" s="5" t="n"/>
-      <c r="BC270" s="5" t="n"/>
+      <c r="BB270" s="15" t="n"/>
+      <c r="BC270" s="16" t="n"/>
       <c r="BD270" s="5" t="n"/>
       <c r="BE270" s="5" t="n"/>
+      <c r="BF270" s="5" t="n"/>
+      <c r="BG270" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="BD2:BG2"/>
     <mergeCell ref="S2:AC2"/>
     <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AZ2:BA2"/>
     <mergeCell ref="B2:L2"/>
-    <mergeCell ref="AJ1:BA1"/>
+    <mergeCell ref="AX2:AY2"/>
+    <mergeCell ref="AZ2:BC2"/>
     <mergeCell ref="AJ2:AT2"/>
-    <mergeCell ref="BB1:BE1"/>
     <mergeCell ref="S1:AI1"/>
+    <mergeCell ref="BD1:BG1"/>
     <mergeCell ref="M2:O2"/>
-    <mergeCell ref="BB2:BE2"/>
+    <mergeCell ref="AJ1:BC1"/>
     <mergeCell ref="B1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29782,191 +31246,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="30">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="40" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t>日前可靠性机组组合充放收益</t>
         </is>
       </c>
-      <c r="C1" s="41" t="n"/>
-      <c r="D1" s="41" t="n"/>
-      <c r="E1" s="41" t="n"/>
-      <c r="F1" s="41" t="n"/>
-      <c r="G1" s="41" t="n"/>
-      <c r="H1" s="41" t="n"/>
-      <c r="I1" s="41" t="n"/>
-      <c r="J1" s="41" t="n"/>
-      <c r="K1" s="41" t="n"/>
-      <c r="L1" s="41" t="n"/>
-      <c r="M1" s="41" t="n"/>
-      <c r="N1" s="41" t="n"/>
-      <c r="O1" s="41" t="n"/>
-      <c r="P1" s="41" t="n"/>
-      <c r="Q1" s="41" t="n"/>
-      <c r="R1" s="42" t="n"/>
-      <c r="S1" s="40" t="inlineStr">
+      <c r="C1" s="65" t="n"/>
+      <c r="D1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="65" t="n"/>
+      <c r="H1" s="65" t="n"/>
+      <c r="I1" s="65" t="n"/>
+      <c r="J1" s="65" t="n"/>
+      <c r="K1" s="65" t="n"/>
+      <c r="L1" s="65" t="n"/>
+      <c r="M1" s="65" t="n"/>
+      <c r="N1" s="65" t="n"/>
+      <c r="O1" s="65" t="n"/>
+      <c r="P1" s="65" t="n"/>
+      <c r="Q1" s="65" t="n"/>
+      <c r="R1" s="66" t="n"/>
+      <c r="S1" s="64" t="inlineStr">
         <is>
           <t>实时可靠性机组组合充放收益</t>
         </is>
       </c>
-      <c r="T1" s="41" t="n"/>
-      <c r="U1" s="41" t="n"/>
-      <c r="V1" s="41" t="n"/>
-      <c r="W1" s="41" t="n"/>
-      <c r="X1" s="41" t="n"/>
-      <c r="Y1" s="41" t="n"/>
-      <c r="Z1" s="41" t="n"/>
-      <c r="AA1" s="41" t="n"/>
-      <c r="AB1" s="41" t="n"/>
-      <c r="AC1" s="41" t="n"/>
-      <c r="AD1" s="41" t="n"/>
-      <c r="AE1" s="41" t="n"/>
-      <c r="AF1" s="41" t="n"/>
-      <c r="AG1" s="41" t="n"/>
-      <c r="AH1" s="41" t="n"/>
-      <c r="AI1" s="42" t="n"/>
-      <c r="AJ1" s="40" t="inlineStr">
+      <c r="T1" s="65" t="n"/>
+      <c r="U1" s="65" t="n"/>
+      <c r="V1" s="65" t="n"/>
+      <c r="W1" s="65" t="n"/>
+      <c r="X1" s="65" t="n"/>
+      <c r="Y1" s="65" t="n"/>
+      <c r="Z1" s="65" t="n"/>
+      <c r="AA1" s="65" t="n"/>
+      <c r="AB1" s="65" t="n"/>
+      <c r="AC1" s="65" t="n"/>
+      <c r="AD1" s="65" t="n"/>
+      <c r="AE1" s="65" t="n"/>
+      <c r="AF1" s="65" t="n"/>
+      <c r="AG1" s="65" t="n"/>
+      <c r="AH1" s="65" t="n"/>
+      <c r="AI1" s="66" t="n"/>
+      <c r="AJ1" s="64" t="inlineStr">
         <is>
           <t>日清分单收益</t>
         </is>
       </c>
-      <c r="AK1" s="41" t="n"/>
-      <c r="AL1" s="41" t="n"/>
-      <c r="AM1" s="41" t="n"/>
-      <c r="AN1" s="41" t="n"/>
-      <c r="AO1" s="41" t="n"/>
-      <c r="AP1" s="41" t="n"/>
-      <c r="AQ1" s="41" t="n"/>
-      <c r="AR1" s="41" t="n"/>
-      <c r="AS1" s="41" t="n"/>
-      <c r="AT1" s="41" t="n"/>
-      <c r="AU1" s="41" t="n"/>
-      <c r="AV1" s="41" t="n"/>
-      <c r="AW1" s="41" t="n"/>
-      <c r="AX1" s="41" t="n"/>
-      <c r="AY1" s="41" t="n"/>
-      <c r="AZ1" s="42" t="n"/>
-      <c r="BA1" s="35" t="inlineStr">
+      <c r="AK1" s="65" t="n"/>
+      <c r="AL1" s="65" t="n"/>
+      <c r="AM1" s="65" t="n"/>
+      <c r="AN1" s="65" t="n"/>
+      <c r="AO1" s="65" t="n"/>
+      <c r="AP1" s="65" t="n"/>
+      <c r="AQ1" s="65" t="n"/>
+      <c r="AR1" s="65" t="n"/>
+      <c r="AS1" s="65" t="n"/>
+      <c r="AT1" s="65" t="n"/>
+      <c r="AU1" s="65" t="n"/>
+      <c r="AV1" s="65" t="n"/>
+      <c r="AW1" s="65" t="n"/>
+      <c r="AX1" s="65" t="n"/>
+      <c r="AY1" s="65" t="n"/>
+      <c r="AZ1" s="66" t="n"/>
+      <c r="BA1" s="55" t="inlineStr">
         <is>
           <t>调频收益</t>
         </is>
       </c>
-      <c r="BB1" s="38" t="n"/>
-      <c r="BC1" s="38" t="n"/>
-      <c r="BD1" s="36" t="n"/>
+      <c r="BB1" s="58" t="n"/>
+      <c r="BC1" s="58" t="n"/>
+      <c r="BD1" s="56" t="n"/>
     </row>
     <row r="2" ht="21" customHeight="1" s="30">
-      <c r="A2" s="44" t="n"/>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="A2" s="68" t="n"/>
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="C2" s="38" t="n"/>
-      <c r="D2" s="38" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="36" t="n"/>
-      <c r="M2" s="37" t="inlineStr">
+      <c r="C2" s="58" t="n"/>
+      <c r="D2" s="58" t="n"/>
+      <c r="E2" s="58" t="n"/>
+      <c r="F2" s="58" t="n"/>
+      <c r="G2" s="58" t="n"/>
+      <c r="H2" s="58" t="n"/>
+      <c r="I2" s="58" t="n"/>
+      <c r="J2" s="58" t="n"/>
+      <c r="K2" s="58" t="n"/>
+      <c r="L2" s="56" t="n"/>
+      <c r="M2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="36" t="n"/>
+      <c r="N2" s="58" t="n"/>
+      <c r="O2" s="56" t="n"/>
       <c r="P2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="Q2" s="35" t="inlineStr">
+      <c r="Q2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="R2" s="36" t="n"/>
-      <c r="S2" s="39" t="inlineStr">
+      <c r="R2" s="56" t="n"/>
+      <c r="S2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="T2" s="38" t="n"/>
-      <c r="U2" s="38" t="n"/>
-      <c r="V2" s="38" t="n"/>
-      <c r="W2" s="38" t="n"/>
-      <c r="X2" s="38" t="n"/>
-      <c r="Y2" s="38" t="n"/>
-      <c r="Z2" s="38" t="n"/>
-      <c r="AA2" s="38" t="n"/>
-      <c r="AB2" s="38" t="n"/>
-      <c r="AC2" s="36" t="n"/>
-      <c r="AD2" s="37" t="inlineStr">
+      <c r="T2" s="58" t="n"/>
+      <c r="U2" s="58" t="n"/>
+      <c r="V2" s="58" t="n"/>
+      <c r="W2" s="58" t="n"/>
+      <c r="X2" s="58" t="n"/>
+      <c r="Y2" s="58" t="n"/>
+      <c r="Z2" s="58" t="n"/>
+      <c r="AA2" s="58" t="n"/>
+      <c r="AB2" s="58" t="n"/>
+      <c r="AC2" s="56" t="n"/>
+      <c r="AD2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="AE2" s="38" t="n"/>
-      <c r="AF2" s="36" t="n"/>
+      <c r="AE2" s="58" t="n"/>
+      <c r="AF2" s="56" t="n"/>
       <c r="AG2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="AH2" s="35" t="inlineStr">
+      <c r="AH2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="AI2" s="36" t="n"/>
-      <c r="AJ2" s="39" t="inlineStr">
+      <c r="AI2" s="56" t="n"/>
+      <c r="AJ2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="AK2" s="38" t="n"/>
-      <c r="AL2" s="38" t="n"/>
-      <c r="AM2" s="38" t="n"/>
-      <c r="AN2" s="38" t="n"/>
-      <c r="AO2" s="38" t="n"/>
-      <c r="AP2" s="38" t="n"/>
-      <c r="AQ2" s="38" t="n"/>
-      <c r="AR2" s="38" t="n"/>
-      <c r="AS2" s="38" t="n"/>
-      <c r="AT2" s="36" t="n"/>
-      <c r="AU2" s="37" t="inlineStr">
+      <c r="AK2" s="58" t="n"/>
+      <c r="AL2" s="58" t="n"/>
+      <c r="AM2" s="58" t="n"/>
+      <c r="AN2" s="58" t="n"/>
+      <c r="AO2" s="58" t="n"/>
+      <c r="AP2" s="58" t="n"/>
+      <c r="AQ2" s="58" t="n"/>
+      <c r="AR2" s="58" t="n"/>
+      <c r="AS2" s="58" t="n"/>
+      <c r="AT2" s="56" t="n"/>
+      <c r="AU2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="AV2" s="38" t="n"/>
-      <c r="AW2" s="36" t="n"/>
+      <c r="AV2" s="58" t="n"/>
+      <c r="AW2" s="56" t="n"/>
       <c r="AX2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="AY2" s="35" t="inlineStr">
+      <c r="AY2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="AZ2" s="36" t="n"/>
-      <c r="BA2" s="35" t="n"/>
-      <c r="BB2" s="38" t="n"/>
-      <c r="BC2" s="38" t="n"/>
-      <c r="BD2" s="36" t="n"/>
+      <c r="AZ2" s="56" t="n"/>
+      <c r="BA2" s="55" t="n"/>
+      <c r="BB2" s="58" t="n"/>
+      <c r="BC2" s="58" t="n"/>
+      <c r="BD2" s="56" t="n"/>
     </row>
     <row r="3" ht="21" customHeight="1" s="30">
-      <c r="A3" s="45" t="n"/>
+      <c r="A3" s="69" t="n"/>
       <c r="B3" s="20" t="inlineStr">
         <is>
           <t>充电均价
@@ -34138,7 +35602,7 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="S1:AI1"/>
+    <mergeCell ref="AJ1:AZ1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
@@ -34148,7 +35612,7 @@
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
-    <mergeCell ref="AJ1:AZ1"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>
@@ -34200,191 +35664,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="13.8" customHeight="1" s="30">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="40" t="inlineStr">
+      <c r="B1" s="64" t="inlineStr">
         <is>
           <t>日前可靠性机组组合充放收益</t>
         </is>
       </c>
-      <c r="C1" s="41" t="n"/>
-      <c r="D1" s="41" t="n"/>
-      <c r="E1" s="41" t="n"/>
-      <c r="F1" s="41" t="n"/>
-      <c r="G1" s="41" t="n"/>
-      <c r="H1" s="41" t="n"/>
-      <c r="I1" s="41" t="n"/>
-      <c r="J1" s="41" t="n"/>
-      <c r="K1" s="41" t="n"/>
-      <c r="L1" s="41" t="n"/>
-      <c r="M1" s="41" t="n"/>
-      <c r="N1" s="41" t="n"/>
-      <c r="O1" s="41" t="n"/>
-      <c r="P1" s="41" t="n"/>
-      <c r="Q1" s="41" t="n"/>
-      <c r="R1" s="42" t="n"/>
-      <c r="S1" s="40" t="inlineStr">
+      <c r="C1" s="65" t="n"/>
+      <c r="D1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="65" t="n"/>
+      <c r="H1" s="65" t="n"/>
+      <c r="I1" s="65" t="n"/>
+      <c r="J1" s="65" t="n"/>
+      <c r="K1" s="65" t="n"/>
+      <c r="L1" s="65" t="n"/>
+      <c r="M1" s="65" t="n"/>
+      <c r="N1" s="65" t="n"/>
+      <c r="O1" s="65" t="n"/>
+      <c r="P1" s="65" t="n"/>
+      <c r="Q1" s="65" t="n"/>
+      <c r="R1" s="66" t="n"/>
+      <c r="S1" s="64" t="inlineStr">
         <is>
           <t>实时可靠性机组组合充放收益</t>
         </is>
       </c>
-      <c r="T1" s="41" t="n"/>
-      <c r="U1" s="41" t="n"/>
-      <c r="V1" s="41" t="n"/>
-      <c r="W1" s="41" t="n"/>
-      <c r="X1" s="41" t="n"/>
-      <c r="Y1" s="41" t="n"/>
-      <c r="Z1" s="41" t="n"/>
-      <c r="AA1" s="41" t="n"/>
-      <c r="AB1" s="41" t="n"/>
-      <c r="AC1" s="41" t="n"/>
-      <c r="AD1" s="41" t="n"/>
-      <c r="AE1" s="41" t="n"/>
-      <c r="AF1" s="41" t="n"/>
-      <c r="AG1" s="41" t="n"/>
-      <c r="AH1" s="41" t="n"/>
-      <c r="AI1" s="42" t="n"/>
-      <c r="AJ1" s="40" t="inlineStr">
+      <c r="T1" s="65" t="n"/>
+      <c r="U1" s="65" t="n"/>
+      <c r="V1" s="65" t="n"/>
+      <c r="W1" s="65" t="n"/>
+      <c r="X1" s="65" t="n"/>
+      <c r="Y1" s="65" t="n"/>
+      <c r="Z1" s="65" t="n"/>
+      <c r="AA1" s="65" t="n"/>
+      <c r="AB1" s="65" t="n"/>
+      <c r="AC1" s="65" t="n"/>
+      <c r="AD1" s="65" t="n"/>
+      <c r="AE1" s="65" t="n"/>
+      <c r="AF1" s="65" t="n"/>
+      <c r="AG1" s="65" t="n"/>
+      <c r="AH1" s="65" t="n"/>
+      <c r="AI1" s="66" t="n"/>
+      <c r="AJ1" s="64" t="inlineStr">
         <is>
           <t>日清分单收益</t>
         </is>
       </c>
-      <c r="AK1" s="41" t="n"/>
-      <c r="AL1" s="41" t="n"/>
-      <c r="AM1" s="41" t="n"/>
-      <c r="AN1" s="41" t="n"/>
-      <c r="AO1" s="41" t="n"/>
-      <c r="AP1" s="41" t="n"/>
-      <c r="AQ1" s="41" t="n"/>
-      <c r="AR1" s="41" t="n"/>
-      <c r="AS1" s="41" t="n"/>
-      <c r="AT1" s="41" t="n"/>
-      <c r="AU1" s="41" t="n"/>
-      <c r="AV1" s="41" t="n"/>
-      <c r="AW1" s="41" t="n"/>
-      <c r="AX1" s="41" t="n"/>
-      <c r="AY1" s="41" t="n"/>
-      <c r="AZ1" s="42" t="n"/>
-      <c r="BA1" s="35" t="inlineStr">
+      <c r="AK1" s="65" t="n"/>
+      <c r="AL1" s="65" t="n"/>
+      <c r="AM1" s="65" t="n"/>
+      <c r="AN1" s="65" t="n"/>
+      <c r="AO1" s="65" t="n"/>
+      <c r="AP1" s="65" t="n"/>
+      <c r="AQ1" s="65" t="n"/>
+      <c r="AR1" s="65" t="n"/>
+      <c r="AS1" s="65" t="n"/>
+      <c r="AT1" s="65" t="n"/>
+      <c r="AU1" s="65" t="n"/>
+      <c r="AV1" s="65" t="n"/>
+      <c r="AW1" s="65" t="n"/>
+      <c r="AX1" s="65" t="n"/>
+      <c r="AY1" s="65" t="n"/>
+      <c r="AZ1" s="66" t="n"/>
+      <c r="BA1" s="55" t="inlineStr">
         <is>
           <t>调频收益</t>
         </is>
       </c>
-      <c r="BB1" s="38" t="n"/>
-      <c r="BC1" s="38" t="n"/>
-      <c r="BD1" s="36" t="n"/>
+      <c r="BB1" s="58" t="n"/>
+      <c r="BC1" s="58" t="n"/>
+      <c r="BD1" s="56" t="n"/>
     </row>
     <row r="2" ht="13.8" customHeight="1" s="30">
-      <c r="A2" s="44" t="n"/>
-      <c r="B2" s="39" t="inlineStr">
+      <c r="A2" s="68" t="n"/>
+      <c r="B2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="C2" s="38" t="n"/>
-      <c r="D2" s="38" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="36" t="n"/>
-      <c r="M2" s="37" t="inlineStr">
+      <c r="C2" s="58" t="n"/>
+      <c r="D2" s="58" t="n"/>
+      <c r="E2" s="58" t="n"/>
+      <c r="F2" s="58" t="n"/>
+      <c r="G2" s="58" t="n"/>
+      <c r="H2" s="58" t="n"/>
+      <c r="I2" s="58" t="n"/>
+      <c r="J2" s="58" t="n"/>
+      <c r="K2" s="58" t="n"/>
+      <c r="L2" s="56" t="n"/>
+      <c r="M2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="36" t="n"/>
+      <c r="N2" s="58" t="n"/>
+      <c r="O2" s="56" t="n"/>
       <c r="P2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="Q2" s="35" t="inlineStr">
+      <c r="Q2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="R2" s="36" t="n"/>
-      <c r="S2" s="39" t="inlineStr">
+      <c r="R2" s="56" t="n"/>
+      <c r="S2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="T2" s="38" t="n"/>
-      <c r="U2" s="38" t="n"/>
-      <c r="V2" s="38" t="n"/>
-      <c r="W2" s="38" t="n"/>
-      <c r="X2" s="38" t="n"/>
-      <c r="Y2" s="38" t="n"/>
-      <c r="Z2" s="38" t="n"/>
-      <c r="AA2" s="38" t="n"/>
-      <c r="AB2" s="38" t="n"/>
-      <c r="AC2" s="36" t="n"/>
-      <c r="AD2" s="37" t="inlineStr">
+      <c r="T2" s="58" t="n"/>
+      <c r="U2" s="58" t="n"/>
+      <c r="V2" s="58" t="n"/>
+      <c r="W2" s="58" t="n"/>
+      <c r="X2" s="58" t="n"/>
+      <c r="Y2" s="58" t="n"/>
+      <c r="Z2" s="58" t="n"/>
+      <c r="AA2" s="58" t="n"/>
+      <c r="AB2" s="58" t="n"/>
+      <c r="AC2" s="56" t="n"/>
+      <c r="AD2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="AE2" s="38" t="n"/>
-      <c r="AF2" s="36" t="n"/>
+      <c r="AE2" s="58" t="n"/>
+      <c r="AF2" s="56" t="n"/>
       <c r="AG2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="AH2" s="35" t="inlineStr">
+      <c r="AH2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="AI2" s="36" t="n"/>
-      <c r="AJ2" s="39" t="inlineStr">
+      <c r="AI2" s="56" t="n"/>
+      <c r="AJ2" s="59" t="inlineStr">
         <is>
           <t>充电支出</t>
         </is>
       </c>
-      <c r="AK2" s="38" t="n"/>
-      <c r="AL2" s="38" t="n"/>
-      <c r="AM2" s="38" t="n"/>
-      <c r="AN2" s="38" t="n"/>
-      <c r="AO2" s="38" t="n"/>
-      <c r="AP2" s="38" t="n"/>
-      <c r="AQ2" s="38" t="n"/>
-      <c r="AR2" s="38" t="n"/>
-      <c r="AS2" s="38" t="n"/>
-      <c r="AT2" s="36" t="n"/>
-      <c r="AU2" s="37" t="inlineStr">
+      <c r="AK2" s="58" t="n"/>
+      <c r="AL2" s="58" t="n"/>
+      <c r="AM2" s="58" t="n"/>
+      <c r="AN2" s="58" t="n"/>
+      <c r="AO2" s="58" t="n"/>
+      <c r="AP2" s="58" t="n"/>
+      <c r="AQ2" s="58" t="n"/>
+      <c r="AR2" s="58" t="n"/>
+      <c r="AS2" s="58" t="n"/>
+      <c r="AT2" s="56" t="n"/>
+      <c r="AU2" s="57" t="inlineStr">
         <is>
           <t>放电收入</t>
         </is>
       </c>
-      <c r="AV2" s="38" t="n"/>
-      <c r="AW2" s="36" t="n"/>
+      <c r="AV2" s="58" t="n"/>
+      <c r="AW2" s="56" t="n"/>
       <c r="AX2" s="21" t="inlineStr">
         <is>
           <t>现货收益</t>
         </is>
       </c>
-      <c r="AY2" s="35" t="inlineStr">
+      <c r="AY2" s="55" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="AZ2" s="36" t="n"/>
-      <c r="BA2" s="35" t="n"/>
-      <c r="BB2" s="38" t="n"/>
-      <c r="BC2" s="38" t="n"/>
-      <c r="BD2" s="36" t="n"/>
+      <c r="AZ2" s="56" t="n"/>
+      <c r="BA2" s="55" t="n"/>
+      <c r="BB2" s="58" t="n"/>
+      <c r="BC2" s="58" t="n"/>
+      <c r="BD2" s="56" t="n"/>
     </row>
     <row r="3" ht="27.6" customHeight="1" s="30">
-      <c r="A3" s="45" t="n"/>
+      <c r="A3" s="69" t="n"/>
       <c r="B3" s="20" t="inlineStr">
         <is>
           <t>充电均价
@@ -36230,7 +37694,7 @@
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:A3"/>
-    <mergeCell ref="S1:AI1"/>
+    <mergeCell ref="AJ1:AZ1"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AD2:AF2"/>
@@ -36240,7 +37704,7 @@
     <mergeCell ref="AY2:AZ2"/>
     <mergeCell ref="AJ2:AT2"/>
     <mergeCell ref="BA1:BD1"/>
-    <mergeCell ref="AJ1:AZ1"/>
+    <mergeCell ref="S1:AI1"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="BA2:BD2"/>
     <mergeCell ref="B1:R1"/>
